--- a/quarters/Q3/Q3Data.xlsx
+++ b/quarters/Q3/Q3Data.xlsx
@@ -31,6 +31,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_Financials" sheetId="23" state="visible" r:id="rId23"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_Unit_Economics" sheetId="24" state="visible" r:id="rId24"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q4_Planner" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_Industry_Graphs" sheetId="26" state="visible" r:id="rId26"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -43,7 +44,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="30">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -229,6 +230,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
     </font>
   </fonts>
   <fills count="33">
@@ -602,7 +607,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="16"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="16"/>
   </cellStyleXfs>
-  <cellXfs count="169">
+  <cellXfs count="171">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -834,6 +839,10 @@
     <xf numFmtId="0" fontId="28" fillId="30" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="31" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="32" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -18112,8 +18121,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" style="146" min="1" max="1"/>
+    <col width="16" customWidth="1" style="146" min="2" max="2"/>
+    <col width="26" customWidth="1" style="146" min="3" max="3"/>
+    <col width="24" customWidth="1" style="146" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="165" t="inlineStr">
@@ -18123,9 +18138,9 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Rule: OC/day = forecast demand / 65 * (1 + (1 - productivity)). Never schedule below forecast again.</t>
+      <c r="A2" s="170" t="inlineStr">
+        <is>
+          <t>Rule: OC/day = forecast demand / 65 * (1 + (1 - productivity)). Never schedule below forecast again. Q3 proof: OC 8/day vs 24 owned -&gt; 204 stock-outs AND labor cost/unit up $130-&gt;$205.</t>
         </is>
       </c>
     </row>
@@ -18187,7 +18202,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>YELLOW — more people, Rio live, ads maturing</t>
+          <t>Q3 demand growth was +235% (highest in industry) on 2 stores; 1.25x is conservative</t>
         </is>
       </c>
     </row>
@@ -18214,11 +18229,11 @@
         </is>
       </c>
       <c r="B8" s="168" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>YELLOW — raise with better pay</t>
+          <t>Graph-checked: industry runs 68-73%. Assume 74% WITH a pay raise. Never plan on 85%.</t>
         </is>
       </c>
     </row>
@@ -18466,6 +18481,2007 @@
       <c r="D25" t="inlineStr">
         <is>
           <t>Lowest in industry because volume is lowest</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="166" t="inlineStr">
+        <is>
+          <t>INDUSTRY BENCHMARKS FOR Q4 (from Strategic Graphs)</t>
+        </is>
+      </c>
+      <c r="B28" s="166" t="inlineStr">
+        <is>
+          <t>WeBike Q3</t>
+        </is>
+      </c>
+      <c r="C28" s="166" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="D28" s="166" t="inlineStr">
+        <is>
+          <t>Q4 target</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Scheduled operating capacity [units/day]</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>8</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>14 - 30</t>
+        </is>
+      </c>
+      <c r="D29" s="168" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Fixed capacity [units/day]</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>24</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>16 - 32</t>
+        </is>
+      </c>
+      <c r="D30" s="168" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Overtime capacity [units/day]</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0 - 7</t>
+        </is>
+      </c>
+      <c r="D31" s="168" t="inlineStr">
+        <is>
+          <t>0 - 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Average COGS per unit [$]</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>620</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>BB LLC lowest</t>
+        </is>
+      </c>
+      <c r="D32" s="168" t="inlineStr">
+        <is>
+          <t>&lt; 550</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Average labor cost per unit [$]</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>205</v>
+      </c>
+      <c r="D33" s="168" t="inlineStr">
+        <is>
+          <t>&lt; 150</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Sales compensation [$]</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>24425</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>22,000 - 27,000</t>
+        </is>
+      </c>
+      <c r="D34" s="168" t="n">
+        <v>26500</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Production compensation [$]</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>20757</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>20,500 - 23,500</t>
+        </is>
+      </c>
+      <c r="D35" s="168" t="n">
+        <v>22500</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Demand per sales person</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>45</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>60 typical / 72 best</t>
+        </is>
+      </c>
+      <c r="D36" s="168" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Store + web center spend [$]</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>121000</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>up to 360,000</t>
+        </is>
+      </c>
+      <c r="D37" s="168" t="inlineStr">
+        <is>
+          <t>raise — open city #3</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Organic SEM clicks</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>150</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>440 best</t>
+        </is>
+      </c>
+      <c r="D38" s="168" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Number of stores</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>2</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2 (all but Bike Bros)</t>
+        </is>
+      </c>
+      <c r="D39" s="168" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="165" t="inlineStr">
+        <is>
+          <t>UNIT-COST UPSIDE — why right-sizing OC pays twice</t>
+        </is>
+      </c>
+      <c r="B42" s="165" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Q3 COGS per unit</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Target COGS per unit at ~15/day scale</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Saving per unit</t>
+        </is>
+      </c>
+      <c r="B45">
+        <f>B43-B44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Q4 forecast units</t>
+        </is>
+      </c>
+      <c r="B46">
+        <f>B7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>COGS saving on forecast volume</t>
+        </is>
+      </c>
+      <c r="B47">
+        <f>B45*B46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>+ Gross margin recovered from ending stock-outs</t>
+        </is>
+      </c>
+      <c r="B48">
+        <f>Q3_Unit_Economics!I6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <f> Combined Q4 swing vs Q3 behaviour</f>
+        <v/>
+      </c>
+      <c r="B49" s="159">
+        <f>B47+B48</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F107"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" style="146" min="1" max="1"/>
+    <col width="16" customWidth="1" style="146" min="2" max="2"/>
+    <col width="16" customWidth="1" style="146" min="3" max="3"/>
+    <col width="22" customWidth="1" style="146" min="4" max="4"/>
+    <col width="22" customWidth="1" style="146" min="5" max="5"/>
+    <col width="60" customWidth="1" style="146" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="169" t="inlineStr">
+        <is>
+          <t>Q3 Strategic Graphs — industry comparison (WeBike vs 6 rivals)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="170" t="inlineStr">
+        <is>
+          <t>Source: Strategic Graphs &gt; Workspace, Quarter 4 view (shows Q0-Q3 actuals). Chart-read values are approximate; numeric report values live in Q3_BSC / Q3_Market / Q3_Financials.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="166" t="inlineStr">
+        <is>
+          <t>MANUFACTURING — capacity (units/day)</t>
+        </is>
+      </c>
+      <c r="B4" s="166" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="C4" s="166" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="D4" s="166" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>WeBike fixed capacity</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>24</v>
+      </c>
+      <c r="C5" t="n">
+        <v>24</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>3 printers; tied 2nd highest in industry</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>WeBike SCHEDULED operating capacity</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>20</v>
+      </c>
+      <c r="C6" s="167" t="n">
+        <v>8</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CONFIRMS the back-solve: we cut OC by 60%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>WeBike overtime capacity</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ran OT on top of a tiny base</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SpaceBikes operating capacity</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>20</v>
+      </c>
+      <c r="C8" t="n">
+        <v>30</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>leader — expanded fixed capacity to 32</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MILC Bikes operating capacity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>16</v>
+      </c>
+      <c r="C9" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Bike Bros operating capacity</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>10</v>
+      </c>
+      <c r="C10" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>LiteCycle operating capacity</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>8</v>
+      </c>
+      <c r="C11" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>BB LLC operating capacity</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>6</v>
+      </c>
+      <c r="C12" t="n">
+        <v>15</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>+ ~7 overtime — highest OT in industry</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Spoke'd Up operating capacity</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>WeBike RANK on operating capacity</t>
+        </is>
+      </c>
+      <c r="C14" s="167" t="inlineStr">
+        <is>
+          <t>LAST (7 of 7)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Only firm that REDUCED operating capacity in Q3</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="166" t="inlineStr">
+        <is>
+          <t>MANUFACTURING — WeBike unit costs</t>
+        </is>
+      </c>
+      <c r="B16" s="166" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="C16" s="166" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="D16" s="166" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Capacity utilization [%]</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>16</v>
+      </c>
+      <c r="C17" t="n">
+        <v>73</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Q2 = idle plant; Q3 = tight plant, but tiny plant</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Average labor cost per unit [$]</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>130</v>
+      </c>
+      <c r="C18" s="167" t="n">
+        <v>205</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ROSE 58% — small OC + overtime is expensive per unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Average cost of goods sold per unit [$]</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>520</v>
+      </c>
+      <c r="C19" s="167" t="n">
+        <v>620</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ROSE ~19% despite selling 4x the units</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Production cost [$]</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>100928</v>
+      </c>
+      <c r="C20" t="n">
+        <v>272340</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Stock-outs [units]</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" t="n">
+        <v>204</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>the whipsaw</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Excess capacity cost [$]</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>148652</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>the whipsaw, other direction</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Lesson</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Under-scheduling cost us BOTH revenue AND margin. Volume normally lowers unit cost; we broke that by running a sub-scale OC with overtime.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="166" t="inlineStr">
+        <is>
+          <t>MARKET — segment size (units)</t>
+        </is>
+      </c>
+      <c r="B25" s="166" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="C25" s="166" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="D25" s="166" t="inlineStr">
+        <is>
+          <t>Growth</t>
+        </is>
+      </c>
+      <c r="E25" s="166" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C26" t="n">
+        <v>2878</v>
+      </c>
+      <c r="D26">
+        <f>C25/B25-1</f>
+        <v/>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>LARGEST and fastest growing; all 7 firms compete</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1100</v>
+      </c>
+      <c r="C27" t="n">
+        <v>2060</v>
+      </c>
+      <c r="D27">
+        <f>C26/B26-1</f>
+        <v/>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>we do not compete</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1050</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1621</v>
+      </c>
+      <c r="D28">
+        <f>C27/B27-1</f>
+        <v/>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>SMALLEST and slowest; our primary; only 4 firms</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Total market</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>3700</v>
+      </c>
+      <c r="C29" t="n">
+        <v>6559</v>
+      </c>
+      <c r="D29">
+        <f>C28/B28-1</f>
+        <v/>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Strategic tension: our least-crowded segment is also the smallest and slowest-growing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="166" t="inlineStr">
+        <is>
+          <t>MARKET — searches (web interest, Q3)</t>
+        </is>
+      </c>
+      <c r="B31" s="166" t="inlineStr">
+        <is>
+          <t>Approx</t>
+        </is>
+      </c>
+      <c r="C31" s="166" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1350</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>highest search volume — segment we ignore</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>900</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>large demand but lowest search volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="166" t="inlineStr">
+        <is>
+          <t>MARKET — Q3 share by segment [%]</t>
+        </is>
+      </c>
+      <c r="B36" s="166" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="C36" s="166" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="D36" s="166" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="E36" s="166" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="F36" s="166" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="C37" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="D37" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="E37" t="n">
+        <v>23</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>LEADER — all 3 segments, dominates Mountain</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>SpaceBikes</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="E38" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>#2 — Rec + Speed only, no Mountain</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Spoke'd Up</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="E39" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>LiteCycle</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="C40" t="n">
+        <v>21</v>
+      </c>
+      <c r="D40" t="n">
+        <v>19</v>
+      </c>
+      <c r="E40" t="n">
+        <v>15</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>our closest Mountain rival</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>MILC Bikes</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="E41" t="n">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>WeBike</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C42" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="D42" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E42" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>#2 Mountain, 6th Speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Bike Bros</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C43" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="D43" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="E43" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>FALLING in every segment (Mtn 19-&gt;11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="166" t="inlineStr">
+        <is>
+          <t>MARKET — demand productivity per head (Q3, approx)</t>
+        </is>
+      </c>
+      <c r="B45" s="166" t="inlineStr">
+        <is>
+          <t>WeBike</t>
+        </is>
+      </c>
+      <c r="C45" s="166" t="inlineStr">
+        <is>
+          <t>Industry best</t>
+        </is>
+      </c>
+      <c r="D45" s="166" t="inlineStr">
+        <is>
+          <t>Industry typical</t>
+        </is>
+      </c>
+      <c r="E45" s="166" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Demand per sales person</t>
+        </is>
+      </c>
+      <c r="B46" s="167" t="n">
+        <v>45</v>
+      </c>
+      <c r="C46" t="n">
+        <v>72</v>
+      </c>
+      <c r="D46" t="n">
+        <v>60</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>LAST — every rival gets more demand per head</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Demand per store sales person</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>46</v>
+      </c>
+      <c r="C47" t="n">
+        <v>88</v>
+      </c>
+      <c r="D47" t="n">
+        <v>70</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>BB LLC ~88; our stores under-produce</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Demand per web sales center person</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>42</v>
+      </c>
+      <c r="C48" t="n">
+        <v>95</v>
+      </c>
+      <c r="D48" t="n">
+        <v>75</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>we CUT web staff in Q3 — wrong lever</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Total sales people</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>14</v>
+      </c>
+      <c r="C49" t="n">
+        <v>21</v>
+      </c>
+      <c r="D49" t="n">
+        <v>14</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>headcount is at parity; output per head is not</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="166" t="inlineStr">
+        <is>
+          <t>MARKET — demand vs units sold (the leakage)</t>
+        </is>
+      </c>
+      <c r="B51" s="166" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C51" s="166" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>WeBike share of total DEMAND [%]</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>what we created</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>WeBike share of UNITS SOLD [%]</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>what we captured</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Leakage [pct points]</t>
+        </is>
+      </c>
+      <c r="B54">
+        <f>B48-B49</f>
+        <v/>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>pure stock-out loss, visible in the graphs</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Q3 demand growth rate [%]</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>235</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>highest in industry — demand generation is NOT our problem</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="166" t="inlineStr">
+        <is>
+          <t>MARKETING INPUTS (Q3, approx)</t>
+        </is>
+      </c>
+      <c r="B57" s="166" t="inlineStr">
+        <is>
+          <t>WeBike</t>
+        </is>
+      </c>
+      <c r="C57" s="166" t="inlineStr">
+        <is>
+          <t>Industry high</t>
+        </is>
+      </c>
+      <c r="D57" s="166" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="E57" s="166" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Advertising expenses [$]</t>
+        </is>
+      </c>
+      <c r="B58" s="159" t="n">
+        <v>119165</v>
+      </c>
+      <c r="C58" t="n">
+        <v>145000</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>spend is competitive</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Total regional ads [count]</t>
+        </is>
+      </c>
+      <c r="B59" s="159" t="n">
+        <v>19</v>
+      </c>
+      <c r="C59" t="n">
+        <v>24</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>ad VOLUME is a strength</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Organic SEM clicks</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>150</v>
+      </c>
+      <c r="C60" t="n">
+        <v>440</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>weak; BB LLC 440, SpaceBikes 400</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Organic SEM expenses [$]</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C61" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Bike Bros spends 5k for 200 clicks — poor ROI benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Average price [$]</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>1400</v>
+      </c>
+      <c r="C62" t="n">
+        <v>1480</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>BB LLC prices HIGHER and still leads share</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Number of stores</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>2</v>
+      </c>
+      <c r="C63" t="n">
+        <v>2</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>tied</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>everyone but Bike Bros has 2 -&gt; city #3 is a differentiator</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Number of web sales centers</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C64" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>tied</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Store + web center expenses [$]</t>
+        </is>
+      </c>
+      <c r="B65" s="167" t="n">
+        <v>121000</v>
+      </c>
+      <c r="C65" t="n">
+        <v>360000</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>lowest</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>we UNDER-invest in channel</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="166" t="inlineStr">
+        <is>
+          <t>HUMAN RESOURCES (Q3, approx) — CORRECTS earlier read</t>
+        </is>
+      </c>
+      <c r="B67" s="166" t="inlineStr">
+        <is>
+          <t>WeBike</t>
+        </is>
+      </c>
+      <c r="C67" s="166" t="inlineStr">
+        <is>
+          <t>Industry range</t>
+        </is>
+      </c>
+      <c r="D67" s="166" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Production worker compensation [$]</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>20757</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>20,500 - 23,500</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>low end, not an outlier</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Sales force compensation [$]</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>24425</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>22,000 - 27,000</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>middle; MILC ~27k, BB LLC ~26.5k highest</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Production worker productivity [%]</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>72</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>68 - 73</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>MID-PACK, not behind</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Sales force productivity [%]</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>70</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>70 - 75</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>MID-PACK; BB LLC ~75 best</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Comp satisfaction</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>68</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>65 - 72</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="168" t="inlineStr">
+        <is>
+          <t>CORRECTION</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>The whole industry runs ~70%. Our 85% projection was never realistic. The error was PLANNING CAPACITY on 85%, not being badly underpaid. Pay raises buy a few points, not 15.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="166" t="inlineStr">
+        <is>
+          <t>BALANCED SCORECARD — Q3 by firm (approx from graph)</t>
+        </is>
+      </c>
+      <c r="B75" s="166" t="inlineStr">
+        <is>
+          <t>Total Perf</t>
+        </is>
+      </c>
+      <c r="C75" s="166" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="D75" s="166" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="E75" s="166" t="inlineStr">
+        <is>
+          <t>Asset Mgmt</t>
+        </is>
+      </c>
+      <c r="F75" s="166" t="inlineStr">
+        <is>
+          <t>Wealth</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>22</v>
+      </c>
+      <c r="C76" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>SpaceBikes</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>11</v>
+      </c>
+      <c r="C77" t="n">
+        <v>34</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>MILC Bikes</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C78" t="n">
+        <v>15</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Bike Bros</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C79" t="n">
+        <v>14</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>LiteCycle</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>2</v>
+      </c>
+      <c r="C80" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Spoke'd Up</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>1</v>
+      </c>
+      <c r="C81" t="n">
+        <v>6</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="167" t="inlineStr">
+        <is>
+          <t>WeBike</t>
+        </is>
+      </c>
+      <c r="B82" s="167" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="C82" s="167" t="n">
+        <v>5.319</v>
+      </c>
+      <c r="D82" s="167" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="E82" s="167" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="F82" s="167" t="n">
+        <v>0.668</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="166" t="inlineStr">
+        <is>
+          <t>CUMULATIVE BSC (approx)</t>
+        </is>
+      </c>
+      <c r="B84" s="166" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C84" s="166" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>SpaceBikes</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>cumulative leader</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>closing fast — Q3 single-quarter leader</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Bike Bros</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>MILC Bikes</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Spoke'd Up</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>LiteCycle</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>WeBike</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Q2 Manufacturing Productivity of 0.20 still poisons the cumulative product</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="166" t="inlineStr">
+        <is>
+          <t>RIVAL PROFILES — what to copy and what to avoid</t>
+        </is>
+      </c>
+      <c r="B93" s="166" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>BB LLC (leader)</t>
+        </is>
+      </c>
+      <c r="B94" s="170" t="inlineStr">
+        <is>
+          <t>All 3 segments. Highest price (~$1,480) AND highest share. Most regional ads (24). Asset Mgmt 0.920 — best capital efficiency. Runs heavy overtime (~7) on modest fixed capacity: buys flexibility instead of printers. 21 sales people, ~88 demand per store rep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>SpaceBikes (cumulative leader)</t>
+        </is>
+      </c>
+      <c r="B95" s="170" t="inlineStr">
+        <is>
+          <t>Skips Mountain entirely; owns Recreation (34.5%) + Speed (20.4%). Expanded fixed capacity to 32/day — the only firm that out-built us. Highest ad spend (~$145k). Wealth 0.95.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>LiteCycle</t>
+        </is>
+      </c>
+      <c r="B96" s="170" t="inlineStr">
+        <is>
+          <t>Our Mountain rival at 21.0%, plus 19.0% of Speed. Organic SEM clicks COLLAPSED 400-&gt;180.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Bike Bros (cautionary tale)</t>
+        </is>
+      </c>
+      <c r="B97" s="170" t="inlineStr">
+        <is>
+          <t>1 store, 0 web sales centers, 7 sales people. Share falling in all three segments (Mountain 19-&gt;11). Under-channeling is fatal — this is the risk of our 'cut web spend' instinct.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>MILC / Spoke'd Up</t>
+        </is>
+      </c>
+      <c r="B98" s="170" t="inlineStr">
+        <is>
+          <t>Mid-pack. Spoke'd Up has the highest market growth but lowest Marketing Effectiveness (0.66).</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="166" t="inlineStr">
+        <is>
+          <t>Q4 IMPLICATIONS FROM THE GRAPHS</t>
+        </is>
+      </c>
+      <c r="B100" s="166" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>1. Operating capacity</t>
+        </is>
+      </c>
+      <c r="B101" s="170" t="inlineStr">
+        <is>
+          <t>We were LAST at 8/day while owning 24. Schedule to forecast (~15/day). This is confirmed by the Operating Capacity chart, not just inferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2. Unit cost</t>
+        </is>
+      </c>
+      <c r="B102" s="170" t="inlineStr">
+        <is>
+          <t>Labor cost/unit rose $130-&gt;$205 and COGS/unit $520-&gt;$620 because OC was sub-scale. Right-sizing OC cuts unit cost AND ends stock-outs — one decision, two wins.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>3. Do NOT cut channel</t>
+        </is>
+      </c>
+      <c r="B103" s="170" t="inlineStr">
+        <is>
+          <t>Store+web spend is the LOWEST in industry and demand per head is LAST. Bike Bros shows where that path ends. Open city #3 and re-staff web.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>4. Pay expectations</t>
+        </is>
+      </c>
+      <c r="B104" s="170" t="inlineStr">
+        <is>
+          <t>Industry productivity is ~70% across the board. Raise pay to upper-quartile (sales ~$26-27k, production ~$22-23k) but PLAN on ~73-75%, not 85%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>5. Segment strategy</t>
+        </is>
+      </c>
+      <c r="B105" s="170" t="inlineStr">
+        <is>
+          <t>Mountain is the smallest, slowest segment (1,621) and BB LLC holds 46%. Speed is 2,878 and growing. Recreation has the most searches (1,350) and we hold 2.6%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>6. Price</t>
+        </is>
+      </c>
+      <c r="B106" s="170" t="inlineStr">
+        <is>
+          <t>BB LLC charges MORE than us and leads. Our ~$1,400 average is not the constraint — supply is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>7. Advertising</t>
+        </is>
+      </c>
+      <c r="B107" s="170" t="inlineStr">
+        <is>
+          <t>Ad count 2nd, spend 3rd, Marketing Effectiveness at par. Marketing is NOT the problem. Weakest marketing input is organic SEM clicks (150 vs 440).</t>
         </is>
       </c>
     </row>

--- a/quarters/Q3/Q3Data.xlsx
+++ b/quarters/Q3/Q3Data.xlsx
@@ -32,6 +32,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_Unit_Economics" sheetId="24" state="visible" r:id="rId24"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q4_Planner" sheetId="25" state="visible" r:id="rId25"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_Industry_Graphs" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_Brand_Judgment" sheetId="27" state="visible" r:id="rId27"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -236,7 +237,7 @@
       <sz val="13"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill/>
     </fill>
@@ -402,6 +403,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -607,7 +613,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="16"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="16"/>
   </cellStyleXfs>
-  <cellXfs count="171">
+  <cellXfs count="175">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -841,6 +847,12 @@
     <xf numFmtId="0" fontId="0" fillId="32" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="32" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -20490,6 +20502,1547 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H91"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" style="146" min="1" max="1"/>
+    <col width="18" customWidth="1" style="146" min="2" max="2"/>
+    <col width="16" customWidth="1" style="146" min="3" max="3"/>
+    <col width="20" customWidth="1" style="146" min="4" max="4"/>
+    <col width="70" customWidth="1" style="146" min="5" max="5"/>
+    <col width="14" customWidth="1" style="146" min="6" max="6"/>
+    <col width="12" customWidth="1" style="146" min="7" max="7"/>
+    <col width="20" customWidth="1" style="146" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="169" t="inlineStr">
+        <is>
+          <t>Brand Judgment — World Market, Q3 actual (all 20 industry brands)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="170" t="inlineStr">
+        <is>
+          <t>Score = segment appeal of the brand DESIGN (1 = no appeal). Exact figures from the sim report. A score of 1 means the brand is irrelevant to that segment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="166" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="B4" s="166" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C4" s="166" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="D4" s="166" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="E4" s="166" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="F4" s="166" t="inlineStr">
+        <is>
+          <t>Targets</t>
+        </is>
+      </c>
+      <c r="G4" s="166" t="inlineStr">
+        <is>
+          <t>Best score</t>
+        </is>
+      </c>
+      <c r="H4" s="166" t="inlineStr">
+        <is>
+          <t>Gap to segment best</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MACH I.I</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Bike Bros</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>12</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>77</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>77</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TERRAMAX</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Bike Bros</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>56</v>
+      </c>
+      <c r="D6" t="n">
+        <v>73</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>73</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Mach 0.6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Bike Bros</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>9</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>61</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>61</v>
+      </c>
+      <c r="H7" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TERRAMean</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Bike Bros</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>59</v>
+      </c>
+      <c r="D8" t="n">
+        <v>72</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>72</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MountainCruise1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Bike Bros</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>76</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>76</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>LiteSpeed Pro+</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>LiteCycle</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>77</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>77</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>LiteSpeed+</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>LiteCycle</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>7</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>74</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>74</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LiteTrail Pro</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>LiteCycle</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>58</v>
+      </c>
+      <c r="D12" t="n">
+        <v>70</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>70</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="171" t="inlineStr">
+        <is>
+          <t>Hike Bike</t>
+        </is>
+      </c>
+      <c r="B13" s="171" t="inlineStr">
+        <is>
+          <t>WeBike</t>
+        </is>
+      </c>
+      <c r="C13" s="171" t="n">
+        <v>56</v>
+      </c>
+      <c r="D13" s="171" t="n">
+        <v>73</v>
+      </c>
+      <c r="E13" s="171" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="171" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="G13" s="171" t="n">
+        <v>73</v>
+      </c>
+      <c r="H13" s="171" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="171" t="inlineStr">
+        <is>
+          <t>Swift Bike</t>
+        </is>
+      </c>
+      <c r="B14" s="171" t="inlineStr">
+        <is>
+          <t>WeBike</t>
+        </is>
+      </c>
+      <c r="C14" s="171" t="n">
+        <v>10</v>
+      </c>
+      <c r="D14" s="171" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="171" t="n">
+        <v>72</v>
+      </c>
+      <c r="F14" s="171" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="G14" s="171" t="n">
+        <v>72</v>
+      </c>
+      <c r="H14" s="171" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Blu Ruged Ballz</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>56</v>
+      </c>
+      <c r="D15" t="n">
+        <v>73</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>73</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Blu Aero Ballz</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>7</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>74</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>74</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Blu Tail Ballz</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>58</v>
+      </c>
+      <c r="D17" t="n">
+        <v>70</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>70</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Blu Tube Ballz</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>9</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>76</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>76</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Spoke'd Easy</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Spoke'd Up</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>73</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>73</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Spoke'd Speed</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Spoke'd Up</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>10</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>75</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>75</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>The Armstrong</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SpaceBikes</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>9</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>76</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>76</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Mars Rover</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SpaceBikes</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>73</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>73</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Whole MILC MKII</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>MILC Bikes</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>74</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>74</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Skim MILC MKII</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>MILC Bikes</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>9</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>76</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>76</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="166" t="inlineStr">
+        <is>
+          <t>SEGMENT CEILINGS — what the best design achieves</t>
+        </is>
+      </c>
+      <c r="B26" s="166" t="inlineStr">
+        <is>
+          <t>Best score</t>
+        </is>
+      </c>
+      <c r="C26" s="166" t="inlineStr">
+        <is>
+          <t>Who holds it</t>
+        </is>
+      </c>
+      <c r="D26" s="166" t="inlineStr">
+        <is>
+          <t>WeBike</t>
+        </is>
+      </c>
+      <c r="E26" s="166" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>73</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Hike Bike (WeBike), TERRAMAX (Bike Bros), Blu Ruged Ballz (BB LLC)</t>
+        </is>
+      </c>
+      <c r="D27" s="159" t="n">
+        <v>73</v>
+      </c>
+      <c r="E27" s="159" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>77</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>MACH I.I (Bike Bros), LiteSpeed Pro+ (LiteCycle)</t>
+        </is>
+      </c>
+      <c r="D28" s="167" t="n">
+        <v>72</v>
+      </c>
+      <c r="E28" s="167" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>76</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>MountainCruise1 (Bike Bros)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>n/a (56 spillover)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="172" t="inlineStr">
+        <is>
+          <t>HEADLINE — Hike Bike is tied for the BEST Mountain brand in the industry</t>
+        </is>
+      </c>
+      <c r="B32" s="172" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Hike Bike Mountain judgment</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>BB LLC Blu Ruged Ballz Mountain judgment</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Our Mountain share [%]</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>22.1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>BB LLC Mountain share [%]</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>46.3</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Share ratio on an IDENTICAL brand score</t>
+        </is>
+      </c>
+      <c r="B37">
+        <f>B36/B35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Conclusion</t>
+        </is>
+      </c>
+      <c r="B38" s="170" t="inlineStr">
+        <is>
+          <t>BB LLC takes 2.1x our Mountain share with a brand design scored EXACTLY the same as ours. The gap is therefore NOT product. It is supply (we stocked out 33%), sales coverage (21 sales people vs our 14, ~88 demand/store rep vs our 46) and ad volume (24 vs 19). Do not redesign Hike Bike. Feed it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="166" t="inlineStr">
+        <is>
+          <t>SPEED GAP — Swift Bike is the weakest real Speed brand</t>
+        </is>
+      </c>
+      <c r="B41" s="166" t="inlineStr">
+        <is>
+          <t>Rec</t>
+        </is>
+      </c>
+      <c r="C41" s="166" t="inlineStr">
+        <is>
+          <t>Mtn</t>
+        </is>
+      </c>
+      <c r="D41" s="166" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="E41" s="166" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>MACH I.I (Bike Bros)</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>12</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="n">
+        <v>77</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>co-best Speed design</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>LiteSpeed Pro+ (LiteCycle)</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>12</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" t="n">
+        <v>77</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>co-best Speed design</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Blu Tube Ballz (BB LLC)</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>9</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>The Armstrong (SpaceBikes)</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>9</v>
+      </c>
+      <c r="C45" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Skim MILC MKII (MILC)</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>9</v>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Spoke'd Speed (Spoke'd Up)</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>10</v>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>LiteSpeed+ (LiteCycle)</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>7</v>
+      </c>
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Blu Aero Ballz (BB LLC)</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>7</v>
+      </c>
+      <c r="C49" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="167" t="inlineStr">
+        <is>
+          <t>Swift Bike (WeBike)</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>10</v>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" s="167" t="n">
+        <v>72</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2nd WORST — 5 points off the ceiling</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Mach 0.6 (Bike Bros)</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>9</v>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" t="n">
+        <v>61</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>only brand worse than ours</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="E52" s="170" t="inlineStr">
+        <is>
+          <t>8 of 9 rival Speed brands beat Swift Bike. The winning profile (12/1/77) is nearly identical to ours (10/1/72) - so a modest redesign should close most of the 5-point gap. Combined with our Speed AD judgment of 70, weak product + weak ad explains 7.5% share in a 2,878-unit segment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="166" t="inlineStr">
+        <is>
+          <t>DESIGN CONVERGENCE — the market has found the optimal profiles</t>
+        </is>
+      </c>
+      <c r="B55" s="166" t="inlineStr">
+        <is>
+          <t>Brands sharing it</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>56 / 73 / 1  (Mountain optimum)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>TERRAMAX (Bike Bros), Hike Bike (WeBike), Blu Ruged Ballz (BB LLC)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>58 / 70 / 1  (Mountain, 2nd tier)</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>LiteTrail Pro (LiteCycle), Blu Tail Ballz (BB LLC)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>12 / 1 / 77  (Speed optimum)</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>MACH I.I (Bike Bros), LiteSpeed Pro+ (LiteCycle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>9 / 1 / 76   (Speed, 2nd tier)</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Blu Tube Ballz (BB LLC), The Armstrong (SpaceBikes), Skim MILC MKII (MILC)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>7 / 1 / 74   (Speed, 3rd tier)</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>LiteSpeed+ (LiteCycle), Blu Aero Ballz (BB LLC)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>73 / 1 / 1   (Recreation)</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Spoke'd Easy (Spoke'd Up), Mars Rover (SpaceBikes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="B62" s="170" t="inlineStr">
+        <is>
+          <t>Multiple firms have landed on byte-identical designs. Brand design is becoming COMMODITISED - no one can win on product alone. Nobody exceeds 73 in Mountain or 77 in Speed, so those look like hard ceilings. Differentiation must come from supply, channel, ads and price.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="166" t="inlineStr">
+        <is>
+          <t>PORTFOLIO BREADTH</t>
+        </is>
+      </c>
+      <c r="B65" s="166" t="inlineStr">
+        <is>
+          <t>Brands</t>
+        </is>
+      </c>
+      <c r="C65" s="166" t="inlineStr">
+        <is>
+          <t>Segments covered</t>
+        </is>
+      </c>
+      <c r="D65" s="166" t="inlineStr">
+        <is>
+          <t>Overall share [%]</t>
+        </is>
+      </c>
+      <c r="E65" s="166" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Bike Bros</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>5</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Rec + Mtn + Speed</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>MOST brands, LOWEST share - 1 store, 0 web centers</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>4</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Rec* + Mtn + Speed</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>23</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>leader; 2 Mtn + 2 Speed brands, Rec via spillover only</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>LiteCycle</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>3</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Mtn + Speed</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="173" t="inlineStr">
+        <is>
+          <t>WeBike</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>2</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Mtn + Speed</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>at parity on count</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Spoke'd Up</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>2</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Rec + Speed</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>SpaceBikes</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>2</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Rec + Speed</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>cumulative LEADER on just 2 brands - skips Mountain</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>MILC Bikes</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>2</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Rec + Speed</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="E73" s="170" t="inlineStr">
+        <is>
+          <t>Brand COUNT does not drive share: Bike Bros has 5 brands and last place; SpaceBikes has 2 and leads cumulatively. A 3rd brand is NOT our priority - filling demand for the 2 we have is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="166" t="inlineStr">
+        <is>
+          <t>RECREATION SPILLOVER — a free option we are not using</t>
+        </is>
+      </c>
+      <c r="B76" s="166" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Hike Bike appeal to Recreation buyers</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Best dedicated Recreation brand (MountainCruise1)</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Recreation segment size [units]</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>2060</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Recreation searches (highest of 3 segments)</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Our Recreation share [%]</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Our Recreation demand [units, untargeted]</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="B83" s="170" t="inlineStr">
+        <is>
+          <t>Hike Bike already scores 56 with Recreation buyers and pulled 54 units we never asked for. That is real latent demand in the LARGEST-search segment. But 56 vs 76 means we cannot win Recreation on spillover - it would need a dedicated brand. Park this as a Q5 option, not a Q4 one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="166" t="inlineStr">
+        <is>
+          <t>Q4 BRAND ACTIONS</t>
+        </is>
+      </c>
+      <c r="B86" s="166" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Hike Bike (Mountain)</t>
+        </is>
+      </c>
+      <c r="B87" s="174" t="inlineStr">
+        <is>
+          <t>DO NOT REDESIGN. Tied for best in industry at 73 - already at the ceiling. Every dollar should go to supplying and selling it, not improving it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Swift Bike (Speed)</t>
+        </is>
+      </c>
+      <c r="B88" s="174" t="inlineStr">
+        <is>
+          <t>REDESIGN toward the 12/1/77 profile. We are 5 points off the ceiling and 8 of 9 rival Speed brands beat us. Also strengthen the Speed ad (judgment 70).</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Third brand</t>
+        </is>
+      </c>
+      <c r="B89" s="174" t="inlineStr">
+        <is>
+          <t>NO. Bike Bros proves brand count does not buy share. Fix supply first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="B90" s="174" t="inlineStr">
+        <is>
+          <t>DEFER. Spillover of 56 is not competitive vs 76; revisit in Q5 with a dedicated design.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="B91" s="174" t="inlineStr">
+        <is>
+          <t>HOLD. Our Mountain brand matches the best design and BB LLC charges ~$1,480 - we have room at $1,365, not a reason to discount.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/quarters/Q3/Q3Data.xlsx
+++ b/quarters/Q3/Q3Data.xlsx
@@ -33,6 +33,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q4_Planner" sheetId="25" state="visible" r:id="rId25"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_Industry_Graphs" sheetId="26" state="visible" r:id="rId26"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_Brand_Judgment" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_Components" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_Design_Model" sheetId="29" state="visible" r:id="rId29"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -613,7 +615,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="16"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="16"/>
   </cellStyleXfs>
-  <cellXfs count="175">
+  <cellXfs count="179">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -854,6 +856,18 @@
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="32" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -22043,6 +22057,2160 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:V41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" style="146" min="1" max="1"/>
+    <col width="26" customWidth="1" style="146" min="2" max="2"/>
+    <col width="4.5" customWidth="1" style="146" min="3" max="3"/>
+    <col width="4.5" customWidth="1" style="146" min="4" max="4"/>
+    <col width="4.5" customWidth="1" style="146" min="5" max="5"/>
+    <col width="4.5" customWidth="1" style="146" min="6" max="6"/>
+    <col width="4.5" customWidth="1" style="146" min="7" max="7"/>
+    <col width="4.5" customWidth="1" style="146" min="8" max="8"/>
+    <col width="4.5" customWidth="1" style="146" min="9" max="9"/>
+    <col width="4.5" customWidth="1" style="146" min="10" max="10"/>
+    <col width="4.5" customWidth="1" style="146" min="11" max="11"/>
+    <col width="4.5" customWidth="1" style="146" min="12" max="12"/>
+    <col width="4.5" customWidth="1" style="146" min="13" max="13"/>
+    <col width="4.5" customWidth="1" style="146" min="14" max="14"/>
+    <col width="4.5" customWidth="1" style="146" min="15" max="15"/>
+    <col width="4.5" customWidth="1" style="146" min="16" max="16"/>
+    <col width="4.5" customWidth="1" style="146" min="17" max="17"/>
+    <col width="4.5" customWidth="1" style="146" min="18" max="18"/>
+    <col width="4.5" customWidth="1" style="146" min="19" max="19"/>
+    <col width="4.5" customWidth="1" style="146" min="20" max="20"/>
+    <col width="4.5" customWidth="1" style="146" min="21" max="21"/>
+    <col width="4.5" customWidth="1" style="146" min="22" max="22"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="169" t="inlineStr">
+        <is>
+          <t>Competitors' Brands — component teardown, Q3 actual (all 20 brands)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="170" t="inlineStr">
+        <is>
+          <t>1 = included, blank = not included. 'Base components' and 'Standard carbon fiber' are in every brand and omitted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="165" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C4" s="166" t="inlineStr">
+        <is>
+          <t>Bike Bros</t>
+        </is>
+      </c>
+      <c r="D4" s="166" t="inlineStr">
+        <is>
+          <t>Bike Bros</t>
+        </is>
+      </c>
+      <c r="E4" s="166" t="inlineStr">
+        <is>
+          <t>Bike Bros</t>
+        </is>
+      </c>
+      <c r="F4" s="166" t="inlineStr">
+        <is>
+          <t>Bike Bros</t>
+        </is>
+      </c>
+      <c r="G4" s="166" t="inlineStr">
+        <is>
+          <t>Bike Bros</t>
+        </is>
+      </c>
+      <c r="H4" s="166" t="inlineStr">
+        <is>
+          <t>LiteCycle</t>
+        </is>
+      </c>
+      <c r="I4" s="166" t="inlineStr">
+        <is>
+          <t>LiteCycle</t>
+        </is>
+      </c>
+      <c r="J4" s="166" t="inlineStr">
+        <is>
+          <t>LiteCycle</t>
+        </is>
+      </c>
+      <c r="K4" s="166" t="inlineStr">
+        <is>
+          <t>WeBike</t>
+        </is>
+      </c>
+      <c r="L4" s="166" t="inlineStr">
+        <is>
+          <t>WeBike</t>
+        </is>
+      </c>
+      <c r="M4" s="166" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="N4" s="166" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="O4" s="166" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="P4" s="166" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="Q4" s="166" t="inlineStr">
+        <is>
+          <t>Spoke'd Up</t>
+        </is>
+      </c>
+      <c r="R4" s="166" t="inlineStr">
+        <is>
+          <t>Spoke'd Up</t>
+        </is>
+      </c>
+      <c r="S4" s="166" t="inlineStr">
+        <is>
+          <t>SpaceBikes</t>
+        </is>
+      </c>
+      <c r="T4" s="166" t="inlineStr">
+        <is>
+          <t>SpaceBikes</t>
+        </is>
+      </c>
+      <c r="U4" s="166" t="inlineStr">
+        <is>
+          <t>MILC Bikes</t>
+        </is>
+      </c>
+      <c r="V4" s="166" t="inlineStr">
+        <is>
+          <t>MILC Bikes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="110" customHeight="1" s="146">
+      <c r="A5" s="165" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="C5" s="175" t="inlineStr">
+        <is>
+          <t>MACH I.I</t>
+        </is>
+      </c>
+      <c r="D5" s="175" t="inlineStr">
+        <is>
+          <t>TERRAMAX</t>
+        </is>
+      </c>
+      <c r="E5" s="175" t="inlineStr">
+        <is>
+          <t>Mach 0.6</t>
+        </is>
+      </c>
+      <c r="F5" s="175" t="inlineStr">
+        <is>
+          <t>TERRAMean</t>
+        </is>
+      </c>
+      <c r="G5" s="175" t="inlineStr">
+        <is>
+          <t>MountainCruise1</t>
+        </is>
+      </c>
+      <c r="H5" s="175" t="inlineStr">
+        <is>
+          <t>LiteSpeed Pro+</t>
+        </is>
+      </c>
+      <c r="I5" s="175" t="inlineStr">
+        <is>
+          <t>LiteSpeed+</t>
+        </is>
+      </c>
+      <c r="J5" s="175" t="inlineStr">
+        <is>
+          <t>LiteTrail Pro</t>
+        </is>
+      </c>
+      <c r="K5" s="176" t="inlineStr">
+        <is>
+          <t>Hike Bike</t>
+        </is>
+      </c>
+      <c r="L5" s="176" t="inlineStr">
+        <is>
+          <t>Swift Bike</t>
+        </is>
+      </c>
+      <c r="M5" s="175" t="inlineStr">
+        <is>
+          <t>Blu Ruged Ballz</t>
+        </is>
+      </c>
+      <c r="N5" s="175" t="inlineStr">
+        <is>
+          <t>Blu Aero Ballz</t>
+        </is>
+      </c>
+      <c r="O5" s="175" t="inlineStr">
+        <is>
+          <t>Blu Tail Ballz</t>
+        </is>
+      </c>
+      <c r="P5" s="175" t="inlineStr">
+        <is>
+          <t>Blu Tube Ballz</t>
+        </is>
+      </c>
+      <c r="Q5" s="175" t="inlineStr">
+        <is>
+          <t>Spoke'd Easy</t>
+        </is>
+      </c>
+      <c r="R5" s="175" t="inlineStr">
+        <is>
+          <t>Spoke'd Speed</t>
+        </is>
+      </c>
+      <c r="S5" s="175" t="inlineStr">
+        <is>
+          <t>The Armstrong</t>
+        </is>
+      </c>
+      <c r="T5" s="175" t="inlineStr">
+        <is>
+          <t>Mars Rover</t>
+        </is>
+      </c>
+      <c r="U5" s="175" t="inlineStr">
+        <is>
+          <t>Whole MILC MKII</t>
+        </is>
+      </c>
+      <c r="V5" s="175" t="inlineStr">
+        <is>
+          <t>Skim MILC MKII</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="165" t="inlineStr">
+        <is>
+          <t>Targets</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="K6" s="173" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="L6" s="173" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="165" t="inlineStr">
+        <is>
+          <t>Judgment in target segment</t>
+        </is>
+      </c>
+      <c r="C7" s="165" t="n">
+        <v>77</v>
+      </c>
+      <c r="D7" s="165" t="n">
+        <v>73</v>
+      </c>
+      <c r="E7" s="165" t="n">
+        <v>61</v>
+      </c>
+      <c r="F7" s="165" t="n">
+        <v>72</v>
+      </c>
+      <c r="G7" s="165" t="n">
+        <v>76</v>
+      </c>
+      <c r="H7" s="165" t="n">
+        <v>77</v>
+      </c>
+      <c r="I7" s="165" t="n">
+        <v>74</v>
+      </c>
+      <c r="J7" s="165" t="n">
+        <v>70</v>
+      </c>
+      <c r="K7" s="171" t="n">
+        <v>73</v>
+      </c>
+      <c r="L7" s="171" t="n">
+        <v>72</v>
+      </c>
+      <c r="M7" s="165" t="n">
+        <v>73</v>
+      </c>
+      <c r="N7" s="165" t="n">
+        <v>74</v>
+      </c>
+      <c r="O7" s="165" t="n">
+        <v>70</v>
+      </c>
+      <c r="P7" s="165" t="n">
+        <v>76</v>
+      </c>
+      <c r="Q7" s="165" t="n">
+        <v>73</v>
+      </c>
+      <c r="R7" s="165" t="n">
+        <v>75</v>
+      </c>
+      <c r="S7" s="165" t="n">
+        <v>76</v>
+      </c>
+      <c r="T7" s="165" t="n">
+        <v>73</v>
+      </c>
+      <c r="U7" s="165" t="n">
+        <v>74</v>
+      </c>
+      <c r="V7" s="165" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="166" t="inlineStr">
+        <is>
+          <t>Frame</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Comfort (relaxed)</t>
+        </is>
+      </c>
+      <c r="G9" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" s="177" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Rugged (rough terrain)</t>
+        </is>
+      </c>
+      <c r="D10" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="178" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" s="177" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Aerodynamic (speed)</t>
+        </is>
+      </c>
+      <c r="C11" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" s="178" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="P11" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" s="177" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="166" t="inlineStr">
+        <is>
+          <t>Tires</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Mountain - high grip</t>
+        </is>
+      </c>
+      <c r="D13" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" s="178" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" s="177" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Hybrid - road/off-road</t>
+        </is>
+      </c>
+      <c r="G14" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" s="177" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Racing - fast</t>
+        </is>
+      </c>
+      <c r="C15" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" s="178" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="P15" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" s="177" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="166" t="inlineStr">
+        <is>
+          <t>Brakes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="T17" s="177" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Precision</t>
+        </is>
+      </c>
+      <c r="C18" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" s="178" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="P18" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" s="177" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Standard disc</t>
+        </is>
+      </c>
+      <c r="D19" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" s="178" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" s="177" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="166" t="inlineStr">
+        <is>
+          <t>Handlebars</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Basic straight</t>
+        </is>
+      </c>
+      <c r="D21" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" s="178" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" s="177" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Comfort straight</t>
+        </is>
+      </c>
+      <c r="G22" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" s="177" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Basic drop down</t>
+        </is>
+      </c>
+      <c r="C23" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" s="178" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="P23" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="S23" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="V23" s="177" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="166" t="inlineStr">
+        <is>
+          <t>Gears</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>7 speed (1x7)</t>
+        </is>
+      </c>
+      <c r="E25" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q25" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" s="177" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>14 speed (2x7)</t>
+        </is>
+      </c>
+      <c r="C26" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="N26" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="P26" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="R26" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="S26" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="V26" s="177" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>24 speed (3x8)</t>
+        </is>
+      </c>
+      <c r="D27" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" s="178" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" s="178" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" s="177" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="166" t="inlineStr">
+        <is>
+          <t>Seat</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Polymer gel all-purpose</t>
+        </is>
+      </c>
+      <c r="D29" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" s="178" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" s="177" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Polymer gel comfort</t>
+        </is>
+      </c>
+      <c r="G30" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="O30" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q30" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="T30" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" s="177" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Polymer gel racing</t>
+        </is>
+      </c>
+      <c r="C31" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" s="178" t="n">
+        <v>1</v>
+      </c>
+      <c r="N31" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="P31" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="R31" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="S31" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="V31" s="177" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="166" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Reflectors</t>
+        </is>
+      </c>
+      <c r="C33" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="L33" s="178" t="n">
+        <v>1</v>
+      </c>
+      <c r="N33" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q33" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="R33" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="T33" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" s="177" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="166" t="inlineStr">
+        <is>
+          <t>Decals</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Colorful brushstrokes</t>
+        </is>
+      </c>
+      <c r="C35" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" s="178" t="n">
+        <v>1</v>
+      </c>
+      <c r="M35" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="P35" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q35" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="S35" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="V35" s="177" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="166" t="inlineStr">
+        <is>
+          <t>Lights</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="C37" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="L37" s="178" t="n">
+        <v>1</v>
+      </c>
+      <c r="P37" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="R37" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="S37" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="T37" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="V37" s="177" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="166" t="inlineStr">
+        <is>
+          <t>Carriers</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Plastic basket</t>
+        </is>
+      </c>
+      <c r="G39" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q39" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="T39" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" s="177" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="166" t="inlineStr">
+        <is>
+          <t>Suspension</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Front shocks</t>
+        </is>
+      </c>
+      <c r="D41" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" s="178" t="n">
+        <v>1</v>
+      </c>
+      <c r="M41" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="O41" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q41" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="T41" s="177" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" s="177" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D85"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" style="146" min="1" max="1"/>
+    <col width="30" customWidth="1" style="146" min="2" max="2"/>
+    <col width="34" customWidth="1" style="146" min="3" max="3"/>
+    <col width="10" customWidth="1" style="146" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="169" t="inlineStr">
+        <is>
+          <t>Reverse-engineered brand judgment model (fitted to all 20 brands)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="170" t="inlineStr">
+        <is>
+          <t>Every brand in each segment shares one base recipe; scores differ only by a few components. The point values below reproduce all 20 observed scores exactly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="166" t="inlineStr">
+        <is>
+          <t>SPEED — base recipe (all 10 Speed brands share this)</t>
+        </is>
+      </c>
+      <c r="B4" s="166" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Frame</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Aerodynamic</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Tires</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Racing - fast</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Brakes</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Precision</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Handlebars</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Basic drop down</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Seat</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Polymer gel racing</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Carriers / Suspension</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="166" t="inlineStr">
+        <is>
+          <t>SPEED — what the variable components are worth</t>
+        </is>
+      </c>
+      <c r="B13" s="166" t="inlineStr">
+        <is>
+          <t>Points</t>
+        </is>
+      </c>
+      <c r="C13" s="166" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Gears 14 speed (2x7)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="C14" s="170" t="inlineStr">
+        <is>
+          <t>all 8 top Speed brands use it</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Gears 24 speed (3x8) instead</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="C15" s="170" t="inlineStr">
+        <is>
+          <t>Swift Bike is the ONLY Speed brand with it</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Gears 7 speed (1x7) instead</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>-16</v>
+      </c>
+      <c r="C16" s="170" t="inlineStr">
+        <is>
+          <t>Mach 0.6 = 61 with an otherwise full kit</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Decals (colorful brushstrokes)</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" s="170" t="inlineStr">
+        <is>
+          <t>every 76-77 brand has them; every 72-75 brand lacks them</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Reflectors</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="170" t="inlineStr">
+        <is>
+          <t>MACH I.I 77 (with) vs Blu Tube 76 (without), else identical</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Lights</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="170" t="inlineStr">
+        <is>
+          <t>Blu Aero 74 lacks lights; otherwise matches 75-point kit</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>MAXIMUM ACHIEVABLE (Speed)</t>
+        </is>
+      </c>
+      <c r="B20" s="159" t="n">
+        <v>77</v>
+      </c>
+      <c r="C20" s="170" t="inlineStr">
+        <is>
+          <t>MACH I.I and LiteSpeed Pro+ both hit it</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="166" t="inlineStr">
+        <is>
+          <t>SWIFT BIKE — exact fix to reach the industry ceiling</t>
+        </is>
+      </c>
+      <c r="B23" s="166" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="C23" s="166" t="inlineStr">
+        <is>
+          <t>Change to</t>
+        </is>
+      </c>
+      <c r="D23" s="166" t="inlineStr">
+        <is>
+          <t>Points</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Frame</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Aerodynamic</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Tires</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Racing</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Brakes</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Precision</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Handlebars</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Basic drop down</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Seat</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Polymer gel racing</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Reflectors</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>included</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Lights</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>included</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Gears</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>24 speed (3x8)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>14 speed (2x7)</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Decals</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>not included</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ADD colorful brushstrokes</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Current judgment</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Projected judgment after both changes</t>
+        </is>
+      </c>
+      <c r="B34">
+        <f>B33+SUM(D32:D33)</f>
+        <v/>
+      </c>
+      <c r="C34">
+        <f> industry ceiling (tied best)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="166" t="inlineStr">
+        <is>
+          <t>Why the gears mistake happened</t>
+        </is>
+      </c>
+      <c r="B37" s="166" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Root cause</t>
+        </is>
+      </c>
+      <c r="B38" s="170" t="inlineStr">
+        <is>
+          <t>Swift Bike inherited the 24-speed (3x8) mountain drivetrain from Hike Bike. 24-speed is OPTIMAL in Mountain (all 6 Mountain brands use it) and WRONG in Speed (all 8 leading Speed brands use 14-speed). We copied our Mountain spec into a Speed bike.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Cost side effect</t>
+        </is>
+      </c>
+      <c r="B39" s="170" t="inlineStr">
+        <is>
+          <t>14 speed (2x7) is a simpler drivetrain than 24 speed (3x8), so this change should also LOWER unit cost. Verify against the component price list before locking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="166" t="inlineStr">
+        <is>
+          <t>MOUNTAIN — base recipe (all 6 Mountain brands share this)</t>
+        </is>
+      </c>
+      <c r="B42" s="166" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Frame</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Rugged</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Tires</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Mountain - high grip</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Brakes</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Standard disc</t>
+        </is>
+      </c>
+      <c r="C45" s="168" t="n"/>
+      <c r="D45" s="168" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Handlebars</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Basic straight</t>
+        </is>
+      </c>
+      <c r="C46" s="168" t="n"/>
+      <c r="D46" s="168" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gears</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>24 speed (3x8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Suspension</t>
+        </is>
+      </c>
+      <c r="B48" s="172" t="inlineStr">
+        <is>
+          <t>Front shocks</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Decals</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Colorful brushstrokes</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Lights / Carriers</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="166" t="inlineStr">
+        <is>
+          <t>MOUNTAIN — what the variable components are worth</t>
+        </is>
+      </c>
+      <c r="B53" s="166" t="inlineStr">
+        <is>
+          <t>Points</t>
+        </is>
+      </c>
+      <c r="C53" s="166" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Seat: Polymer gel ALL-PURPOSE</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="C54" s="170" t="inlineStr">
+        <is>
+          <t>Hike Bike, TERRAMAX, Blu Ruged Ballz all = 73</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Seat: Polymer gel COMFORT instead</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>-3</v>
+      </c>
+      <c r="C55" s="170" t="inlineStr">
+        <is>
+          <t>LiteTrail Pro and Blu Tail Ballz both = 70</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Reflectors added</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C56" s="170" t="inlineStr">
+        <is>
+          <t>TERRAMean = 72; identical to Hike Bike except reflectors</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>MAXIMUM ACHIEVABLE (Mountain)</t>
+        </is>
+      </c>
+      <c r="B57" s="159" t="n">
+        <v>73</v>
+      </c>
+      <c r="C57" s="170" t="inlineStr">
+        <is>
+          <t>Hike Bike already there</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="167" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="166" t="inlineStr">
+        <is>
+          <t>HIKE BIKE — verified optimal, do not touch</t>
+        </is>
+      </c>
+      <c r="B60" s="166" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Seat</t>
+        </is>
+      </c>
+      <c r="B61" s="170" t="inlineStr">
+        <is>
+          <t>Polymer gel all-purpose = correct (comfort seat would cost 3 points)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Reflectors</t>
+        </is>
+      </c>
+      <c r="B62" s="170" t="inlineStr">
+        <is>
+          <t>correctly EXCLUDED (adding them costs 1 point - they are a Recreation cue)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Lights</t>
+        </is>
+      </c>
+      <c r="B63" s="170" t="inlineStr">
+        <is>
+          <t>correctly excluded</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="B64" s="170" t="inlineStr">
+        <is>
+          <t>73 of a possible 73 - nothing left to gain from redesign</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Implication</t>
+        </is>
+      </c>
+      <c r="B65" s="170" t="inlineStr">
+        <is>
+          <t>Any Q4 budget aimed at improving Hike Bike is wasted. Spend it on capacity, sales coverage and ads instead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="166" t="inlineStr">
+        <is>
+          <t>RECREATION — blueprint if we ever enter (Q5 option)</t>
+        </is>
+      </c>
+      <c r="B68" s="166" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Frame</t>
+        </is>
+      </c>
+      <c r="B69" s="170" t="inlineStr">
+        <is>
+          <t>Comfort (relaxed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Tires</t>
+        </is>
+      </c>
+      <c r="B70" s="170" t="inlineStr">
+        <is>
+          <t>Hybrid - road/off-road</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Brakes</t>
+        </is>
+      </c>
+      <c r="B71" s="170" t="inlineStr">
+        <is>
+          <t>Standard disc  &lt;-- NOT precision (costs 2) and NOT standard (costs 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Handlebars</t>
+        </is>
+      </c>
+      <c r="B72" s="170" t="inlineStr">
+        <is>
+          <t>Comfort straight</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Gears</t>
+        </is>
+      </c>
+      <c r="B73" s="170" t="inlineStr">
+        <is>
+          <t>7 speed (1x7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Seat</t>
+        </is>
+      </c>
+      <c r="B74" s="170" t="inlineStr">
+        <is>
+          <t>Polymer gel comfort</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="B75" s="170" t="inlineStr">
+        <is>
+          <t>Reflectors + Decals + Lights + Plastic basket + Front shocks</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="B76" s="170" t="inlineStr">
+        <is>
+          <t>76 = MountainCruise1 (Bike Bros), the only brand at the Recreation ceiling</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>CAUTION</t>
+        </is>
+      </c>
+      <c r="B77" s="170" t="inlineStr">
+        <is>
+          <t>Only 4 Recreation brands exist and they differ in 3 places (brakes, decals, lights), so the individual penalties are NOT uniquely identifiable. Observed constraints: precision+no-decals = 2 - precision+no-lights = 3 - standard-brakes+no-decals = 3. What IS certain: standard disc brakes are optimal, and MountainCruise1's exact recipe scores 76.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="166" t="inlineStr">
+        <is>
+          <t>CROSS-SEGMENT RULE OF THUMB</t>
+        </is>
+      </c>
+      <c r="B80" s="166" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Reflectors</t>
+        </is>
+      </c>
+      <c r="B81" s="170" t="inlineStr">
+        <is>
+          <t>+1 in Speed, -1 in Mountain, required in Recreation. Segment-dependent, not universally good.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Decals</t>
+        </is>
+      </c>
+      <c r="B82" s="170" t="inlineStr">
+        <is>
+          <t>+2 in Speed, required in Mountain and Recreation. Cheap and always worth having except where noted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Lights</t>
+        </is>
+      </c>
+      <c r="B83" s="170" t="inlineStr">
+        <is>
+          <t>+1 in Speed, excluded in Mountain, required in Recreation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Gears</t>
+        </is>
+      </c>
+      <c r="B84" s="170" t="inlineStr">
+        <is>
+          <t>The single biggest lever in Speed: 7sp = -16, 24sp = -3, 14sp = optimal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Seat</t>
+        </is>
+      </c>
+      <c r="B85" s="170" t="inlineStr">
+        <is>
+          <t>The single biggest lever in Mountain: comfort seat = -3 vs all-purpose.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/quarters/Q3/Q3Data.xlsx
+++ b/quarters/Q3/Q3Data.xlsx
@@ -35,6 +35,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_Brand_Judgment" sheetId="27" state="visible" r:id="rId27"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_Components" sheetId="28" state="visible" r:id="rId28"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_Design_Model" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_City_Demand" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_City_Strategy" sheetId="31" state="visible" r:id="rId31"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -615,7 +617,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="16"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="16"/>
   </cellStyleXfs>
-  <cellXfs count="179">
+  <cellXfs count="182">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -868,6 +870,11 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="31" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="33" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -24522,6 +24529,3029 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G69"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" style="146" min="1" max="1"/>
+    <col width="13" customWidth="1" style="146" min="2" max="2"/>
+    <col width="16" customWidth="1" style="146" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="169" t="inlineStr">
+        <is>
+          <t>Detailed Brand Demand — World Market by city, Q3 actual</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reconciles exactly to 6,559 total / 627 WeBike / 412 Hike Bike / 215 Swift Bike.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="166" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="B4" s="166" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C4" s="166" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="D4" s="166" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="E4" s="166" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="F4" s="166" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="G4" s="166" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>LiteSpeed Pro+</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>LiteCycle</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>39</v>
+      </c>
+      <c r="G5" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>LiteSpeed+</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LiteCycle</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>29</v>
+      </c>
+      <c r="G6" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>LiteTrail Pro</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>LiteCycle</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>13</v>
+      </c>
+      <c r="E7" t="n">
+        <v>62</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="171" t="inlineStr">
+        <is>
+          <t>Hike Bike</t>
+        </is>
+      </c>
+      <c r="B8" s="171" t="inlineStr">
+        <is>
+          <t>WeBike</t>
+        </is>
+      </c>
+      <c r="C8" s="171" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="D8" s="171" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="171" t="n">
+        <v>23</v>
+      </c>
+      <c r="F8" s="171" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="171" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="171" t="inlineStr">
+        <is>
+          <t>Swift Bike</t>
+        </is>
+      </c>
+      <c r="B9" s="171" t="inlineStr">
+        <is>
+          <t>WeBike</t>
+        </is>
+      </c>
+      <c r="C9" s="171" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="D9" s="171" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="171" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="171" t="n">
+        <v>12</v>
+      </c>
+      <c r="G9" s="171" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Blu Ruged Ballz</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>19</v>
+      </c>
+      <c r="E10" t="n">
+        <v>265</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Blu Aero Ballz</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>135</v>
+      </c>
+      <c r="G11" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Blu Tail Ballz</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>22</v>
+      </c>
+      <c r="E12" t="n">
+        <v>145</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Blu Tube Ballz</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>166</v>
+      </c>
+      <c r="G13" t="n">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Spoke'd Easy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Spoke'd Up</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>237</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Spoke'd Speed</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Spoke'd Up</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>175</v>
+      </c>
+      <c r="G15" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>The Armstrong</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SpaceBikes</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>272</v>
+      </c>
+      <c r="G16" t="n">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Mars Rover</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>SpaceBikes</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>302</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Whole MILC MKII</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>MILC Bikes</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>68</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Skim MILC MKII</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>MILC Bikes</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>52</v>
+      </c>
+      <c r="G19" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>LiteSpeed Pro+</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>LiteCycle</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>27</v>
+      </c>
+      <c r="G20" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>LiteSpeed+</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>LiteCycle</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>20</v>
+      </c>
+      <c r="G21" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>LiteTrail Pro</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>LiteCycle</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>13</v>
+      </c>
+      <c r="E22" t="n">
+        <v>46</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="171" t="inlineStr">
+        <is>
+          <t>Hike Bike</t>
+        </is>
+      </c>
+      <c r="B23" s="171" t="inlineStr">
+        <is>
+          <t>WeBike</t>
+        </is>
+      </c>
+      <c r="C23" s="171" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="D23" s="171" t="n">
+        <v>25</v>
+      </c>
+      <c r="E23" s="171" t="n">
+        <v>166</v>
+      </c>
+      <c r="F23" s="171" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="171" t="n">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="171" t="inlineStr">
+        <is>
+          <t>Swift Bike</t>
+        </is>
+      </c>
+      <c r="B24" s="171" t="inlineStr">
+        <is>
+          <t>WeBike</t>
+        </is>
+      </c>
+      <c r="C24" s="171" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="D24" s="171" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="171" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="171" t="n">
+        <v>79</v>
+      </c>
+      <c r="G24" s="171" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Blu Ruged Ballz</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>6</v>
+      </c>
+      <c r="E25" t="n">
+        <v>48</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Blu Aero Ballz</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>23</v>
+      </c>
+      <c r="G26" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Blu Tail Ballz</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>7</v>
+      </c>
+      <c r="E27" t="n">
+        <v>26</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Blu Tube Ballz</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>29</v>
+      </c>
+      <c r="G28" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Spoke'd Easy</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Spoke'd Up</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>21</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Spoke'd Speed</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Spoke'd Up</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>11</v>
+      </c>
+      <c r="G30" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>The Armstrong</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>SpaceBikes</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>43</v>
+      </c>
+      <c r="G31" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Mars Rover</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>SpaceBikes</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>77</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Whole MILC MKII</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>MILC Bikes</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>70</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Skim MILC MKII</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>MILC Bikes</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>37</v>
+      </c>
+      <c r="G34" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>MACH I.I</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Bike Bros</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>155</v>
+      </c>
+      <c r="G35" t="n">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>TERRAMAX</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Bike Bros</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>6</v>
+      </c>
+      <c r="E36" t="n">
+        <v>92</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Mach 0.6</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Bike Bros</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>25</v>
+      </c>
+      <c r="G37" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>TERRAMean</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Bike Bros</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="n">
+        <v>80</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>MountainCruise1</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Bike Bros</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>122</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>LiteSpeed Pro+</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>LiteCycle</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>126</v>
+      </c>
+      <c r="G40" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>LiteSpeed+</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>LiteCycle</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>93</v>
+      </c>
+      <c r="G41" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>LiteTrail Pro</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>LiteCycle</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>36</v>
+      </c>
+      <c r="E42" t="n">
+        <v>110</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="171" t="inlineStr">
+        <is>
+          <t>Hike Bike</t>
+        </is>
+      </c>
+      <c r="B43" s="171" t="inlineStr">
+        <is>
+          <t>WeBike</t>
+        </is>
+      </c>
+      <c r="C43" s="171" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="D43" s="171" t="n">
+        <v>24</v>
+      </c>
+      <c r="E43" s="171" t="n">
+        <v>156</v>
+      </c>
+      <c r="F43" s="171" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="171" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="171" t="inlineStr">
+        <is>
+          <t>Swift Bike</t>
+        </is>
+      </c>
+      <c r="B44" s="171" t="inlineStr">
+        <is>
+          <t>WeBike</t>
+        </is>
+      </c>
+      <c r="C44" s="171" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="D44" s="171" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="171" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="171" t="n">
+        <v>115</v>
+      </c>
+      <c r="G44" s="171" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Blu Ruged Ballz</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>16</v>
+      </c>
+      <c r="E45" t="n">
+        <v>137</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Blu Aero Ballz</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>110</v>
+      </c>
+      <c r="G46" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Blu Tail Ballz</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>19</v>
+      </c>
+      <c r="E47" t="n">
+        <v>75</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Blu Tube Ballz</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>136</v>
+      </c>
+      <c r="G48" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Spoke'd Easy</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Spoke'd Up</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>217</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="n">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Spoke'd Speed</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Spoke'd Up</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>163</v>
+      </c>
+      <c r="G50" t="n">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>The Armstrong</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>SpaceBikes</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>223</v>
+      </c>
+      <c r="G51" t="n">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Mars Rover</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>SpaceBikes</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>267</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Whole MILC MKII</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>MILC Bikes</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>275</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="n">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Skim MILC MKII</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>MILC Bikes</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="n">
+        <v>197</v>
+      </c>
+      <c r="G54" t="n">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>LiteSpeed Pro+</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>LiteCycle</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>123</v>
+      </c>
+      <c r="G55" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>LiteSpeed+</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>LiteCycle</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="n">
+        <v>91</v>
+      </c>
+      <c r="G56" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>LiteTrail Pro</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>LiteCycle</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>34</v>
+      </c>
+      <c r="E57" t="n">
+        <v>122</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="171" t="inlineStr">
+        <is>
+          <t>Hike Bike</t>
+        </is>
+      </c>
+      <c r="B58" s="171" t="inlineStr">
+        <is>
+          <t>WeBike</t>
+        </is>
+      </c>
+      <c r="C58" s="171" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
+      <c r="D58" s="171" t="n">
+        <v>2</v>
+      </c>
+      <c r="E58" s="171" t="n">
+        <v>13</v>
+      </c>
+      <c r="F58" s="171" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="171" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="171" t="inlineStr">
+        <is>
+          <t>Swift Bike</t>
+        </is>
+      </c>
+      <c r="B59" s="171" t="inlineStr">
+        <is>
+          <t>WeBike</t>
+        </is>
+      </c>
+      <c r="C59" s="171" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
+      <c r="D59" s="171" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="171" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="171" t="n">
+        <v>9</v>
+      </c>
+      <c r="G59" s="171" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Blu Ruged Ballz</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>5</v>
+      </c>
+      <c r="E60" t="n">
+        <v>36</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Blu Aero Ballz</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="n">
+        <v>26</v>
+      </c>
+      <c r="G61" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Blu Tail Ballz</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>5</v>
+      </c>
+      <c r="E62" t="n">
+        <v>19</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Blu Tube Ballz</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="n">
+        <v>32</v>
+      </c>
+      <c r="G63" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Spoke'd Easy</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Spoke'd Up</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>17</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Spoke'd Speed</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Spoke'd Up</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" t="n">
+        <v>13</v>
+      </c>
+      <c r="G65" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>The Armstrong</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>SpaceBikes</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="n">
+        <v>50</v>
+      </c>
+      <c r="G66" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Mars Rover</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>SpaceBikes</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>64</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Whole MILC MKII</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>MILC Bikes</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>58</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Skim MILC MKII</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>MILC Bikes</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" t="n">
+        <v>42</v>
+      </c>
+      <c r="G69" t="n">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H76"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" style="146" min="1" max="1"/>
+    <col width="30" customWidth="1" style="146" min="2" max="2"/>
+    <col width="30" customWidth="1" style="146" min="3" max="3"/>
+    <col width="16" customWidth="1" style="146" min="4" max="4"/>
+    <col width="16" customWidth="1" style="146" min="5" max="5"/>
+    <col width="16" customWidth="1" style="146" min="6" max="6"/>
+    <col width="16" customWidth="1" style="146" min="7" max="7"/>
+    <col width="16" customWidth="1" style="146" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="169" t="inlineStr">
+        <is>
+          <t>City-level competitive map and the City #3 decision</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="170" t="inlineStr">
+        <is>
+          <t>Amsterdam + New York are 77% of the entire market. We hold 9.9% of Amsterdam and 1.9% of New York, but 34.9% of Rio - the one city where we are the only firm with a store.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="166" t="inlineStr">
+        <is>
+          <t>CITY SIZE &amp; OUR POSITION</t>
+        </is>
+      </c>
+      <c r="B4" s="166" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="C4" s="166" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="D4" s="166" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="E4" s="166" t="inlineStr">
+        <is>
+          <t>Total demand</t>
+        </is>
+      </c>
+      <c r="F4" s="166" t="inlineStr">
+        <is>
+          <t>% of market</t>
+        </is>
+      </c>
+      <c r="G4" s="166" t="inlineStr">
+        <is>
+          <t>WeBike units</t>
+        </is>
+      </c>
+      <c r="H4" s="166" t="inlineStr">
+        <is>
+          <t>WeBike share</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>992</v>
+      </c>
+      <c r="C5" t="n">
+        <v>650</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1343</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2985</v>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>0.455099862783961</v>
+      </c>
+      <c r="G5" t="n">
+        <v>295</v>
+      </c>
+      <c r="H5" s="179" t="n">
+        <v>0.09882747068676717</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>664</v>
+      </c>
+      <c r="C6" t="n">
+        <v>495</v>
+      </c>
+      <c r="D6" t="n">
+        <v>880</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2039</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>0.3108705595365147</v>
+      </c>
+      <c r="G6" t="n">
+        <v>38</v>
+      </c>
+      <c r="H6" s="179" t="n">
+        <v>0.01863658656204022</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>219</v>
+      </c>
+      <c r="C7" t="n">
+        <v>286</v>
+      </c>
+      <c r="D7" t="n">
+        <v>269</v>
+      </c>
+      <c r="E7" t="n">
+        <v>774</v>
+      </c>
+      <c r="F7" s="10" t="n">
+        <v>0.1180057935660924</v>
+      </c>
+      <c r="G7" t="n">
+        <v>270</v>
+      </c>
+      <c r="H7" s="161" t="n">
+        <v>0.3488372093023256</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>185</v>
+      </c>
+      <c r="C8" t="n">
+        <v>190</v>
+      </c>
+      <c r="D8" t="n">
+        <v>386</v>
+      </c>
+      <c r="E8" t="n">
+        <v>761</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>0.1160237841134319</v>
+      </c>
+      <c r="G8" t="n">
+        <v>24</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>0.03153745072273324</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2060</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1621</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2878</v>
+      </c>
+      <c r="E9" t="n">
+        <v>6559</v>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>627</v>
+      </c>
+      <c r="H9" s="10" t="n">
+        <v>0.09559384052447019</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="166" t="inlineStr">
+        <is>
+          <t>SHARE BY CITY [%] — who owns what</t>
+        </is>
+      </c>
+      <c r="B12" s="166" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="C12" s="166" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="D12" s="166" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="E12" s="166" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="n">
+        <v>0.1651591289782245</v>
+      </c>
+      <c r="C13" s="10" t="n">
+        <v>0.3688082393330064</v>
+      </c>
+      <c r="D13" s="10" t="n">
+        <v>0.1795865633074935</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>0.1616294349540079</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SpaceBikes</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="n">
+        <v>0.1641541038525963</v>
+      </c>
+      <c r="C14" s="10" t="n">
+        <v>0.2815105443845022</v>
+      </c>
+      <c r="D14" s="10" t="n">
+        <v>0.1550387596899225</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>0.1498028909329829</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>LiteCycle</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="n">
+        <v>0.1222780569514238</v>
+      </c>
+      <c r="C15" s="10" t="n">
+        <v>0.07013241785188817</v>
+      </c>
+      <c r="D15" s="10" t="n">
+        <v>0.1369509043927649</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>0.4862023653088042</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Spoke'd Up</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="n">
+        <v>0.1273031825795645</v>
+      </c>
+      <c r="C16" s="10" t="n">
+        <v>0.2020598332515939</v>
+      </c>
+      <c r="D16" s="10" t="n">
+        <v>0.041343669250646</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>0.03942181340341656</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>MILC Bikes</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="n">
+        <v>0.1581239530988275</v>
+      </c>
+      <c r="C17" s="10" t="n">
+        <v>0.0588523786169691</v>
+      </c>
+      <c r="D17" s="10" t="n">
+        <v>0.1382428940568475</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>0.1314060446780552</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>WeBike</t>
+        </is>
+      </c>
+      <c r="B18" s="180" t="n">
+        <v>0.09882747068676717</v>
+      </c>
+      <c r="C18" s="180" t="n">
+        <v>0.01863658656204022</v>
+      </c>
+      <c r="D18" s="180" t="n">
+        <v>0.3488372093023256</v>
+      </c>
+      <c r="E18" s="180" t="n">
+        <v>0.03153745072273324</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Bike Bros</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="n">
+        <v>0.1641541038525963</v>
+      </c>
+      <c r="C19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="166" t="inlineStr">
+        <is>
+          <t>INFERRED STORE LOCATIONS (from demand concentration)</t>
+        </is>
+      </c>
+      <c r="B22" s="166" t="inlineStr">
+        <is>
+          <t>Firms with a store</t>
+        </is>
+      </c>
+      <c r="C22" s="166" t="inlineStr">
+        <is>
+          <t>City demand</t>
+        </is>
+      </c>
+      <c r="D22" s="166" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ALL SEVEN</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>2985</v>
+      </c>
+      <c r="D23" s="170" t="inlineStr">
+        <is>
+          <t>Most contested city AND the largest. Nobody exceeds 16.5%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="B24" s="167" t="inlineStr">
+        <is>
+          <t>BB LLC, SpaceBikes, Spoke'd Up</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>2039</v>
+      </c>
+      <c r="D24" s="170" t="inlineStr">
+        <is>
+          <t>2nd largest. We have NO store -&gt; only 1.9% share.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="B25" s="159" t="inlineStr">
+        <is>
+          <t>WeBike ONLY</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>774</v>
+      </c>
+      <c r="D25" s="170" t="inlineStr">
+        <is>
+          <t>Uncontested by any rival store -&gt; we take 34.9%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>LiteCycle ONLY</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>761</v>
+      </c>
+      <c r="D26" s="170" t="inlineStr">
+        <is>
+          <t>Uncontested by others -&gt; LiteCycle takes 48.6%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Bike Bros</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Amsterdam only (1 store, 0 web)</t>
+        </is>
+      </c>
+      <c r="D27" s="170" t="inlineStr">
+        <is>
+          <t>Appears in NO other city. Confirms the 1-store read.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="168" t="inlineStr">
+        <is>
+          <t>CAUTION</t>
+        </is>
+      </c>
+      <c r="D28" s="170" t="inlineStr">
+        <is>
+          <t>Store locations are INFERRED from demand patterns, not reported directly. MILC Bikes is Amsterdam-concentrated but its 2nd store is not identifiable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="166" t="inlineStr">
+        <is>
+          <t>THE STORE EFFECT — what a local store is worth</t>
+        </is>
+      </c>
+      <c r="B31" s="166" t="inlineStr">
+        <is>
+          <t>Share with store</t>
+        </is>
+      </c>
+      <c r="C31" s="166" t="inlineStr">
+        <is>
+          <t>Share without store</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>WeBike in Rio (only store in city)</t>
+        </is>
+      </c>
+      <c r="B32" s="161" t="n">
+        <v>0.349</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>LiteCycle in Bangalore (only store in city)</t>
+        </is>
+      </c>
+      <c r="B33" s="161" t="n">
+        <v>0.486</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>WeBike in Amsterdam (store, 6 rivals)</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="n">
+        <v>0.099</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>WeBike in New York City (no store)</t>
+        </is>
+      </c>
+      <c r="C35" s="179" t="n">
+        <v>0.019</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>WeBike in Bangalore (no store)</t>
+        </is>
+      </c>
+      <c r="C36" s="179" t="n">
+        <v>0.032</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="B37" s="170" t="inlineStr">
+        <is>
+          <t>A store is worth roughly 10x the share of web-only coverage (2-3% without, 10-35% with). An UNCONTESTED store is worth 35-49%. This is the highest-leverage decision we have.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="166" t="inlineStr">
+        <is>
+          <t>OUR PRIMARY SEGMENT (Mountain) BY CITY</t>
+        </is>
+      </c>
+      <c r="B40" s="166" t="inlineStr">
+        <is>
+          <t>Segment size</t>
+        </is>
+      </c>
+      <c r="C40" s="166" t="inlineStr">
+        <is>
+          <t>WeBike units</t>
+        </is>
+      </c>
+      <c r="D40" s="166" t="inlineStr">
+        <is>
+          <t>WeBike share</t>
+        </is>
+      </c>
+      <c r="E40" s="166" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="F40" s="166" t="inlineStr">
+        <is>
+          <t>Leader units</t>
+        </is>
+      </c>
+      <c r="G40" s="166" t="inlineStr">
+        <is>
+          <t>Leader share</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>650</v>
+      </c>
+      <c r="C41" t="n">
+        <v>156</v>
+      </c>
+      <c r="D41" s="10" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>WeBike</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>156</v>
+      </c>
+      <c r="G41" s="10" t="n">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>495</v>
+      </c>
+      <c r="C42" t="n">
+        <v>23</v>
+      </c>
+      <c r="D42" s="179" t="n">
+        <v>0.04646464646464647</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>BB LLC (both brands)</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>410</v>
+      </c>
+      <c r="G42" s="10" t="n">
+        <v>0.8282828282828283</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>286</v>
+      </c>
+      <c r="C43" t="n">
+        <v>166</v>
+      </c>
+      <c r="D43" s="161" t="n">
+        <v>0.5804195804195804</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>WeBike</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>166</v>
+      </c>
+      <c r="G43" s="10" t="n">
+        <v>0.5804195804195804</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>190</v>
+      </c>
+      <c r="C44" t="n">
+        <v>13</v>
+      </c>
+      <c r="D44" s="10" t="n">
+        <v>0.06842105263157895</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>LiteCycle</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>122</v>
+      </c>
+      <c r="G44" s="10" t="n">
+        <v>0.6421052631578947</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="166" t="inlineStr">
+        <is>
+          <t>CITY #3 DECISION — New York City vs Bangalore</t>
+        </is>
+      </c>
+      <c r="B47" s="166" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="C47" s="166" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total city demand (Q3)</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>2039</v>
+      </c>
+      <c r="C48" t="n">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of total market</t>
+        </is>
+      </c>
+      <c r="B49" s="10">
+        <f>B48/6559</f>
+        <v/>
+      </c>
+      <c r="C49" s="10">
+        <f>C48/6559</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Rival stores already there</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>3</v>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Our current share (web only)</t>
+        </is>
+      </c>
+      <c r="B51" s="10" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="C51" s="10" t="n">
+        <v>0.032</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Mountain segment size</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>495</v>
+      </c>
+      <c r="C52" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Mountain leader hold</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>BB LLC 82.8%</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>LiteCycle 64.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Speed segment size</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>880</v>
+      </c>
+      <c r="C54" t="n">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Recreation segment size (untapped)</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>664</v>
+      </c>
+      <c r="C55" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Units at a conservative 10% share</t>
+        </is>
+      </c>
+      <c r="B56">
+        <f>B48*0.10</f>
+        <v/>
+      </c>
+      <c r="C56">
+        <f>C48*0.10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Units at a Rio-like 25% share</t>
+        </is>
+      </c>
+      <c r="B57">
+        <f>B48*0.25</f>
+        <v/>
+      </c>
+      <c r="C57">
+        <f>C48*0.25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>VERDICT</t>
+        </is>
+      </c>
+      <c r="B58" s="181" t="inlineStr">
+        <is>
+          <t>LARGER PRIZE — 2.7x the demand. Even at a weak 10% it beats Bangalore at 25%. Fits our locked 'largest geos even if expensive' strategy.</t>
+        </is>
+      </c>
+      <c r="C58" s="170" t="inlineStr">
+        <is>
+          <t>SAFER but SMALLER — only LiteCycle to fight, yet the whole city is worth less than NYC's Speed segment alone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="166" t="inlineStr">
+        <is>
+          <t>CAPACITY CHECK — can we even serve a 3rd city?</t>
+        </is>
+      </c>
+      <c r="B61" s="166" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Fixed capacity per day</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Days per quarter</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Theoretical max units</t>
+        </is>
+      </c>
+      <c r="B64">
+        <f>B62*B63</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>At 74% worker productivity</t>
+        </is>
+      </c>
+      <c r="B65">
+        <f>B64*0.74</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Q4 forecast demand (existing cities, after ill will)</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Headroom for a new city</t>
+        </is>
+      </c>
+      <c r="B67" s="159">
+        <f>B65-B66</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="B68" s="170" t="inlineStr">
+        <is>
+          <t>We can absorb roughly 500 more units without buying a printer. A New York store at 10% (~204 units) fits comfortably. DO NOT repeat Q3 - schedule the operating capacity to match.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="166" t="inlineStr">
+        <is>
+          <t>RISKS &amp; PROTECTIONS</t>
+        </is>
+      </c>
+      <c r="B71" s="166" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Rio is our crown jewel</t>
+        </is>
+      </c>
+      <c r="B72" s="174" t="inlineStr">
+        <is>
+          <t>58.0% of Rio Mountain and 34.9% of the city. Hike Bike's single best market (166 Mountain units, more than Amsterdam's 156). The Q3 stock-out damaged our strongest position - ill will bites hardest exactly where we lead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Amsterdam is the biggest miss</t>
+        </is>
+      </c>
+      <c r="B73" s="170" t="inlineStr">
+        <is>
+          <t>2,985 units = 45.5% of the market and we hold only 9.9%. Adding sales coverage here may be cheaper per unit than a new city, and no rival exceeds 16.5% - it is genuinely open.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>New York is BB LLC's fortress</t>
+        </is>
+      </c>
+      <c r="B74" s="170" t="inlineStr">
+        <is>
+          <t>They take 36.9% of the city and 82.8% of its Mountain. Attack via SPEED (880 units, no single firm dominant) and Recreation, not head-on in Mountain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Bangalore is LiteCycle's fortress</t>
+        </is>
+      </c>
+      <c r="B75" s="170" t="inlineStr">
+        <is>
+          <t>48.6% city share, 64.2% of its Mountain - the most concentrated position any firm holds in any city.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Do not spread too thin</t>
+        </is>
+      </c>
+      <c r="B76" s="170" t="inlineStr">
+        <is>
+          <t>Bike Bros ran 5 brands from 1 store and finished last. Our constraint is supply and coverage depth, not map coverage.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/quarters/Q3/Q3Data.xlsx
+++ b/quarters/Q3/Q3Data.xlsx
@@ -37,6 +37,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_Design_Model" sheetId="29" state="visible" r:id="rId29"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_City_Demand" sheetId="30" state="visible" r:id="rId30"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_City_Strategy" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_Channel" sheetId="32" state="visible" r:id="rId32"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -617,7 +618,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="16"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="16"/>
   </cellStyleXfs>
-  <cellXfs count="182">
+  <cellXfs count="186">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -874,6 +875,12 @@
     <xf numFmtId="164" fontId="0" fillId="31" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="33" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="28" fillId="33" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="28" fillId="33" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -27552,6 +27559,1044 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J74"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="50" customWidth="1" style="146" min="1" max="1"/>
+    <col width="20" customWidth="1" style="146" min="2" max="2"/>
+    <col width="56" customWidth="1" style="146" min="3" max="3"/>
+    <col width="15" customWidth="1" style="146" min="4" max="4"/>
+    <col width="15" customWidth="1" style="146" min="5" max="5"/>
+    <col width="15" customWidth="1" style="146" min="6" max="6"/>
+    <col width="15" customWidth="1" style="146" min="7" max="7"/>
+    <col width="15" customWidth="1" style="146" min="8" max="8"/>
+    <col width="15" customWidth="1" style="146" min="9" max="9"/>
+    <col width="15" customWidth="1" style="146" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="169" t="inlineStr">
+        <is>
+          <t>Demand Distribution by Channel — Q3 actual</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="170" t="inlineStr">
+        <is>
+          <t>We cut web staff and spend in Q3. This is the bill: 120 web units, the lowest of any firm that operates a web centre, and 19.1% web mix against an industry average of 34.9%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="166" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B4" s="166" t="inlineStr">
+        <is>
+          <t>Store demand</t>
+        </is>
+      </c>
+      <c r="C4" s="166" t="inlineStr">
+        <is>
+          <t>Store %</t>
+        </is>
+      </c>
+      <c r="D4" s="166" t="inlineStr">
+        <is>
+          <t>Web demand</t>
+        </is>
+      </c>
+      <c r="E4" s="166" t="inlineStr">
+        <is>
+          <t>Web %</t>
+        </is>
+      </c>
+      <c r="F4" s="166" t="inlineStr">
+        <is>
+          <t>Total demand</t>
+        </is>
+      </c>
+      <c r="G4" s="166" t="inlineStr">
+        <is>
+          <t>Stores</t>
+        </is>
+      </c>
+      <c r="H4" s="166" t="inlineStr">
+        <is>
+          <t>Demand / store</t>
+        </is>
+      </c>
+      <c r="I4" s="166" t="inlineStr">
+        <is>
+          <t>Web centres</t>
+        </is>
+      </c>
+      <c r="J4" s="166" t="inlineStr">
+        <is>
+          <t>Demand / web centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>938</v>
+      </c>
+      <c r="C5" s="10" t="n">
+        <v>0.6224286662242866</v>
+      </c>
+      <c r="D5" t="n">
+        <v>569</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>0.3775713337757133</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1507</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" s="182" t="n">
+        <v>469</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="182" t="n">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SpaceBikes</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>807</v>
+      </c>
+      <c r="C6" s="10" t="n">
+        <v>0.6217257318952234</v>
+      </c>
+      <c r="D6" t="n">
+        <v>491</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>0.3782742681047766</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1298</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" s="182" t="n">
+        <v>403.5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="182" t="n">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>LiteCycle</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>549</v>
+      </c>
+      <c r="C7" s="10" t="n">
+        <v>0.5579268292682927</v>
+      </c>
+      <c r="D7" t="n">
+        <v>435</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>0.4420731707317073</v>
+      </c>
+      <c r="F7" t="n">
+        <v>984</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" s="182" t="n">
+        <v>274.5</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="182" t="n">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Spoke'd Up</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>716</v>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>0.8384074941451991</v>
+      </c>
+      <c r="D8" t="n">
+        <v>138</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>0.1615925058548009</v>
+      </c>
+      <c r="F8" t="n">
+        <v>854</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" s="182" t="n">
+        <v>358</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="182" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MILC Bikes</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>364</v>
+      </c>
+      <c r="C9" s="10" t="n">
+        <v>0.4555694618272841</v>
+      </c>
+      <c r="D9" t="n">
+        <v>435</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>0.5444305381727159</v>
+      </c>
+      <c r="F9" t="n">
+        <v>799</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="182" t="n">
+        <v>364</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="182" t="n">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="171" t="inlineStr">
+        <is>
+          <t>WeBike</t>
+        </is>
+      </c>
+      <c r="B10" s="171" t="n">
+        <v>507</v>
+      </c>
+      <c r="C10" s="183" t="n">
+        <v>0.8086124401913876</v>
+      </c>
+      <c r="D10" s="171" t="n">
+        <v>120</v>
+      </c>
+      <c r="E10" s="183" t="n">
+        <v>0.1913875598086124</v>
+      </c>
+      <c r="F10" s="171" t="n">
+        <v>627</v>
+      </c>
+      <c r="G10" s="171" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" s="184" t="n">
+        <v>253.5</v>
+      </c>
+      <c r="I10" s="171" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="184" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Bike Bros</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>490</v>
+      </c>
+      <c r="C11" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>490</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="182" t="n">
+        <v>490</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="182" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="166" t="inlineStr">
+        <is>
+          <t>OUR CHANNEL MIX vs INDUSTRY</t>
+        </is>
+      </c>
+      <c r="B14" s="166" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C14" s="166" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>WeBike web mix [%]</t>
+        </is>
+      </c>
+      <c r="B15" s="179" t="n">
+        <v>0.191</v>
+      </c>
+      <c r="C15" s="170" t="inlineStr">
+        <is>
+          <t>we CUT web staff and spend in Q3</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Industry average web mix [%] (firms with a web centre)</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="n">
+        <v>0.3492215627413878</v>
+      </c>
+      <c r="C16" s="170" t="inlineStr">
+        <is>
+          <t>MILC 54.4% - LiteCycle 44.2% - BB LLC 37.8% - SpaceBikes 37.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Gap [pct points]</t>
+        </is>
+      </c>
+      <c r="B17" s="10">
+        <f>C16-C15</f>
+        <v/>
+      </c>
+      <c r="C17" s="170" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>WeBike web demand [units]</t>
+        </is>
+      </c>
+      <c r="B18" s="167" t="n">
+        <v>120</v>
+      </c>
+      <c r="C18" s="170" t="inlineStr">
+        <is>
+          <t>LOWEST of any firm operating a web centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Industry web demand range</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>138 - 569</t>
+        </is>
+      </c>
+      <c r="C19" s="170" t="inlineStr">
+        <is>
+          <t>Spoke'd Up 138 is the only firm near us</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Rank on web demand</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>6 of 7</t>
+        </is>
+      </c>
+      <c r="C20" s="170" t="inlineStr">
+        <is>
+          <t>only Bike Bros is lower, and it has NO web centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="166" t="inlineStr">
+        <is>
+          <t>WHY WEB MATTERS MORE THAN WE THOUGHT</t>
+        </is>
+      </c>
+      <c r="B23" s="166" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="C23" s="166" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Our demand from New York City (no store)</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>38</v>
+      </c>
+      <c r="C24" s="170" t="inlineStr">
+        <is>
+          <t>web only</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Our demand from Bangalore (no store)</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>24</v>
+      </c>
+      <c r="C25" s="170" t="inlineStr">
+        <is>
+          <t>web only</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Subtotal from cities where we have NO store</t>
+        </is>
+      </c>
+      <c r="B26">
+        <f>B24+B25</f>
+        <v/>
+      </c>
+      <c r="C26" s="170" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Total web demand</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>120</v>
+      </c>
+      <c r="C27" s="170" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Share of web demand coming from non-store cities</t>
+        </is>
+      </c>
+      <c r="B28" s="10">
+        <f>B26/B27</f>
+        <v/>
+      </c>
+      <c r="C28" s="170" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Store demand (Amsterdam + Rio)</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>507</v>
+      </c>
+      <c r="C29" s="170" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Amsterdam + Rio total demand</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>565</v>
+      </c>
+      <c r="C30" s="170" t="inlineStr">
+        <is>
+          <t>so 58 units of web demand also came from store cities</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B31">
+        <f>B30-B29</f>
+        <v/>
+      </c>
+      <c r="C31" s="170" t="inlineStr">
+        <is>
+          <t>58 = web demand inside store cities; 58 + 62 = 120 web total</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="C32" s="174" t="inlineStr">
+        <is>
+          <t>The web centre is HALF our reach into cities where we have no store. It is the only way to touch New York and Bangalore today, and we shrank it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="166" t="inlineStr">
+        <is>
+          <t>THE WEB REBUILD CASE</t>
+        </is>
+      </c>
+      <c r="B35" s="166" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C35" s="166" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Current store demand [units]</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>507</v>
+      </c>
+      <c r="C36" s="170" t="inlineStr">
+        <is>
+          <t>hold constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Current web demand [units]</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>120</v>
+      </c>
+      <c r="C37" s="170" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Current total</t>
+        </is>
+      </c>
+      <c r="B38">
+        <f>B36+B37</f>
+        <v/>
+      </c>
+      <c r="C38" s="170" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>If web mix matched industry average (34.9%)</t>
+        </is>
+      </c>
+      <c r="C39" s="170" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  implied total demand</t>
+        </is>
+      </c>
+      <c r="B40">
+        <f>B36/(1-0.3492)</f>
+        <v/>
+      </c>
+      <c r="C40" s="170" t="inlineStr">
+        <is>
+          <t>store demand becomes 65.1% of total</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  implied web demand</t>
+        </is>
+      </c>
+      <c r="B41">
+        <f>B41-B36</f>
+        <v/>
+      </c>
+      <c r="C41" s="170" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ADDITIONAL demand vs today</t>
+        </is>
+      </c>
+      <c r="B42">
+        <f>B42-B37</f>
+        <v/>
+      </c>
+      <c r="C42" s="170" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Contribution per unit (Q3 actual, avg)</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>750</v>
+      </c>
+      <c r="C43" s="170" t="inlineStr">
+        <is>
+          <t>Hike Bike $747 / Swift Bike $756</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Gross margin opportunity</t>
+        </is>
+      </c>
+      <c r="B44">
+        <f>B43*B44</f>
+        <v/>
+      </c>
+      <c r="C44" s="170" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Cost of ~4 additional web staff per quarter</t>
+        </is>
+      </c>
+      <c r="B45" s="159" t="n">
+        <v>24425</v>
+      </c>
+      <c r="C45" s="170" t="inlineStr">
+        <is>
+          <t>$24,425/yr each = ~$6,106/qtr x 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Net quarterly gain</t>
+        </is>
+      </c>
+      <c r="B46">
+        <f>B45-B46</f>
+        <v/>
+      </c>
+      <c r="C46" s="170" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="B47" s="172" t="n"/>
+      <c r="C47" s="170" t="inlineStr">
+        <is>
+          <t>Web headcount is the cheapest demand in the game: no lease, no store setup, and it reaches all four cities. This is a far better first dollar than a third store.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" s="170" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="166" t="inlineStr">
+        <is>
+          <t>STORE PRODUCTIVITY — we under-staff what we own</t>
+        </is>
+      </c>
+      <c r="B50" s="166" t="inlineStr">
+        <is>
+          <t>Demand / store</t>
+        </is>
+      </c>
+      <c r="C50" s="166" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Bike Bros</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>490</v>
+      </c>
+      <c r="C51" s="170" t="inlineStr">
+        <is>
+          <t>ONE store, highest per-store demand in the industry</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>469</v>
+      </c>
+      <c r="C52" s="170" t="inlineStr">
+        <is>
+          <t>leader</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>SpaceBikes</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>404</v>
+      </c>
+      <c r="C53" s="170" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Spoke'd Up</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>358</v>
+      </c>
+      <c r="C54" s="170" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>LiteCycle</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>275</v>
+      </c>
+      <c r="C55" s="170" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>WeBike</t>
+        </is>
+      </c>
+      <c r="B56" s="167" t="n">
+        <v>254</v>
+      </c>
+      <c r="C56" s="170" t="inlineStr">
+        <is>
+          <t>LOWEST of the two-store firms</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>MILC Bikes</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>364</v>
+      </c>
+      <c r="C57" s="170" t="inlineStr">
+        <is>
+          <t>web-first model; Amsterdam store base</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="C58" s="170" t="inlineStr">
+        <is>
+          <t>BB LLC pulls 1.8x our demand from the same number of stores. Depth inside Amsterdam and Rio is unfinished business before we add a third location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="166" t="inlineStr">
+        <is>
+          <t>CHANNEL MODELS IN THIS INDUSTRY</t>
+        </is>
+      </c>
+      <c r="B61" s="166" t="inlineStr">
+        <is>
+          <t>Profile</t>
+        </is>
+      </c>
+      <c r="C61" s="166" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Web-first</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>MILC Bikes - 54.4% web, lowest store demand (364)</t>
+        </is>
+      </c>
+      <c r="C62" s="170" t="inlineStr">
+        <is>
+          <t>12.2% share on 1 store base</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Balanced</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>LiteCycle 44.2% - BB LLC 37.8% - SpaceBikes 37.8%</t>
+        </is>
+      </c>
+      <c r="C63" s="181" t="inlineStr">
+        <is>
+          <t>the three strongest firms sit here</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Store-heavy</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Spoke'd Up 83.8% - WeBike 80.9%</t>
+        </is>
+      </c>
+      <c r="C64" s="170" t="inlineStr">
+        <is>
+          <t>13.0% and 9.6% share</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Store-only</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Bike Bros 100% store, no web centre</t>
+        </is>
+      </c>
+      <c r="C65" s="185" t="inlineStr">
+        <is>
+          <t>7.5% share, LAST, falling everywhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="C66" s="170" t="inlineStr">
+        <is>
+          <t>The top three firms all run 38-44% web. Store-only is last. We are 80.9% store-heavy and drifting toward the Bike Bros failure mode.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="166" t="inlineStr">
+        <is>
+          <t>Q4 CHANNEL ACTIONS</t>
+        </is>
+      </c>
+      <c r="B69" s="166" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>1. Reverse the Q3 web cut</t>
+        </is>
+      </c>
+      <c r="B70" s="174" t="inlineStr">
+        <is>
+          <t>Rehire web sales + support toward 6 people. Cheapest demand available: no lease, no setup, reaches all 4 cities.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2. Restart page upgrades</t>
+        </is>
+      </c>
+      <c r="B71" s="174" t="inlineStr">
+        <is>
+          <t>We stopped this tactic in Q3. Toll-free stayed on. Both were cheap (~$3k and ~$6k/qtr) relative to ~$750 contribution per unit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>3. Deepen Amsterdam + Rio</t>
+        </is>
+      </c>
+      <c r="B72" s="174" t="inlineStr">
+        <is>
+          <t>254 demand/store vs BB LLC's 469. Add store sales staff before adding a third city - same money, faster payback.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>4. Re-evaluate city #3 order</t>
+        </is>
+      </c>
+      <c r="B73" s="174" t="inlineStr">
+        <is>
+          <t>Web already reaches New York (38 units). A store there is still the biggest prize, but web staff + store depth may be the better FIRST dollar this quarter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>5. Never cut channel again</t>
+        </is>
+      </c>
+      <c r="B74" s="174" t="inlineStr">
+        <is>
+          <t>Bike Bros is the control group: 100% store, no web, last place, share falling in all three segments.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/quarters/Q3/Q3Data.xlsx
+++ b/quarters/Q3/Q3Data.xlsx
@@ -38,6 +38,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_City_Demand" sheetId="30" state="visible" r:id="rId30"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_City_Strategy" sheetId="31" state="visible" r:id="rId31"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_Channel" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_Presence" sheetId="33" state="visible" r:id="rId33"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -618,7 +619,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="16"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="16"/>
   </cellStyleXfs>
-  <cellXfs count="186">
+  <cellXfs count="188">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -883,6 +884,8 @@
     <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="31" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="29" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -28597,6 +28600,1066 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I68"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" style="146" min="1" max="1"/>
+    <col width="34" customWidth="1" style="146" min="2" max="2"/>
+    <col width="46" customWidth="1" style="146" min="3" max="3"/>
+    <col width="15" customWidth="1" style="146" min="4" max="4"/>
+    <col width="15" customWidth="1" style="146" min="5" max="5"/>
+    <col width="15" customWidth="1" style="146" min="6" max="6"/>
+    <col width="15" customWidth="1" style="146" min="7" max="7"/>
+    <col width="15" customWidth="1" style="146" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="169" t="inlineStr">
+        <is>
+          <t>Competitors in City — CONFIRMED footprints, Q3</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="170" t="inlineStr">
+        <is>
+          <t>This report confirms every store location previously INFERRED from demand patterns. One correction: MILC Bikes has only ONE store (Amsterdam), not two.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="166" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="B4" s="166" t="inlineStr">
+        <is>
+          <t>Bike Bros</t>
+        </is>
+      </c>
+      <c r="C4" s="166" t="inlineStr">
+        <is>
+          <t>LiteCycle</t>
+        </is>
+      </c>
+      <c r="D4" s="166" t="inlineStr">
+        <is>
+          <t>WeBike</t>
+        </is>
+      </c>
+      <c r="E4" s="166" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="F4" s="166" t="inlineStr">
+        <is>
+          <t>Spoke'd Up</t>
+        </is>
+      </c>
+      <c r="G4" s="166" t="inlineStr">
+        <is>
+          <t>SpaceBikes</t>
+        </is>
+      </c>
+      <c r="H4" s="166" t="inlineStr">
+        <is>
+          <t>MILC Bikes</t>
+        </is>
+      </c>
+      <c r="I4" s="166" t="inlineStr">
+        <is>
+          <t>Store firms present</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="B5" s="159" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="C5" s="159" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D5" s="173" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E5" s="159" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F5" s="159" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G5" s="159" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H5" s="159" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E6" s="159" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F6" s="159" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G6" s="159" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D7" s="173" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C8" s="159" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Web Sales Centre</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C9" s="159" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D9" s="173" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E9" s="159" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F9" s="159" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G9" s="159" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H9" s="159" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="166" t="inlineStr">
+        <is>
+          <t>CONFIRMED FOOTPRINT</t>
+        </is>
+      </c>
+      <c r="B12" s="166" t="inlineStr">
+        <is>
+          <t>Stores</t>
+        </is>
+      </c>
+      <c r="C12" s="166" t="inlineStr">
+        <is>
+          <t>Cities</t>
+        </is>
+      </c>
+      <c r="D12" s="166" t="inlineStr">
+        <is>
+          <t>Web centre</t>
+        </is>
+      </c>
+      <c r="E12" s="166" t="inlineStr">
+        <is>
+          <t>Total demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Amsterdam, New York City</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1507</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SpaceBikes</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Amsterdam, New York City</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>LiteCycle</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Amsterdam, Bangalore</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Spoke'd Up</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Amsterdam, New York City</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>MILC Bikes</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="173" t="inlineStr">
+        <is>
+          <t>WeBike</t>
+        </is>
+      </c>
+      <c r="B18" s="173" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" s="173" t="inlineStr">
+        <is>
+          <t>Amsterdam, Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="D18" s="173" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E18" s="173" t="n">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Bike Bros</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="D19" s="167" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="166" t="inlineStr">
+        <is>
+          <t>MARKET STRUCTURE — a store never captures the whole city</t>
+        </is>
+      </c>
+      <c r="B22" s="166" t="inlineStr">
+        <is>
+          <t>Store firms</t>
+        </is>
+      </c>
+      <c r="C22" s="166" t="inlineStr">
+        <is>
+          <t>Store-firm demand</t>
+        </is>
+      </c>
+      <c r="D22" s="166" t="inlineStr">
+        <is>
+          <t>Store capture %</t>
+        </is>
+      </c>
+      <c r="E22" s="166" t="inlineStr">
+        <is>
+          <t>Web-only demand</t>
+        </is>
+      </c>
+      <c r="F22" s="166" t="inlineStr">
+        <is>
+          <t>Web-only %</t>
+        </is>
+      </c>
+      <c r="G22" s="166" t="inlineStr">
+        <is>
+          <t>Avg per store firm</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>7</v>
+      </c>
+      <c r="C23" t="n">
+        <v>2985</v>
+      </c>
+      <c r="D23" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="186" t="n">
+        <v>426.4285714285714</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1738</v>
+      </c>
+      <c r="D24" s="10" t="n">
+        <v>0.8523786169691026</v>
+      </c>
+      <c r="E24" t="n">
+        <v>301</v>
+      </c>
+      <c r="F24" s="10" t="n">
+        <v>0.1476213830308975</v>
+      </c>
+      <c r="G24" s="187" t="n">
+        <v>579.3333333333334</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="n">
+        <v>270</v>
+      </c>
+      <c r="D25" s="10" t="n">
+        <v>0.3488372093023256</v>
+      </c>
+      <c r="E25" t="n">
+        <v>504</v>
+      </c>
+      <c r="F25" s="10" t="n">
+        <v>0.6511627906976745</v>
+      </c>
+      <c r="G25" s="182" t="n">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="n">
+        <v>370</v>
+      </c>
+      <c r="D26" s="10" t="n">
+        <v>0.4862023653088042</v>
+      </c>
+      <c r="E26" t="n">
+        <v>391</v>
+      </c>
+      <c r="F26" s="10" t="n">
+        <v>0.5137976346911958</v>
+      </c>
+      <c r="G26" s="182" t="n">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="166" t="inlineStr">
+        <is>
+          <t>CORRECTION — Amsterdam is the MOST contested city, not an open one</t>
+        </is>
+      </c>
+      <c r="B29" s="166" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Earlier read</t>
+        </is>
+      </c>
+      <c r="B30" s="185" t="inlineStr">
+        <is>
+          <t>'No rival exceeds 16.5%, so Amsterdam is genuinely open.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>What the presence report shows</t>
+        </is>
+      </c>
+      <c r="B31" s="170" t="inlineStr">
+        <is>
+          <t>ALL SEVEN firms hold an Amsterdam store. Nobody exceeds 16.5% precisely BECAUSE all seven are there.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Avg demand per store firm - Amsterdam</t>
+        </is>
+      </c>
+      <c r="B32" s="170" t="n">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Avg demand per store firm - New York City</t>
+        </is>
+      </c>
+      <c r="B33" s="170" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Implication</t>
+        </is>
+      </c>
+      <c r="B34" s="181" t="inlineStr">
+        <is>
+          <t>A store in New York is worth MORE than deeper investment in Amsterdam. Amsterdam is 2,985 units split 7 ways; New York is 2,039 units split 3 ways. Gaining share in Amsterdam means taking it from six store-equipped rivals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="166" t="inlineStr">
+        <is>
+          <t>RIO — we under-exploit our monopoly</t>
+        </is>
+      </c>
+      <c r="B37" s="166" t="inlineStr">
+        <is>
+          <t>WeBike in Rio</t>
+        </is>
+      </c>
+      <c r="C37" s="166" t="inlineStr">
+        <is>
+          <t>LiteCycle in Bangalore</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Only firm with a store in the city</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>City demand</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>774</v>
+      </c>
+      <c r="C39" t="n">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Our / their units</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>270</v>
+      </c>
+      <c r="C40" t="n">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Share as sole store holder</t>
+        </is>
+      </c>
+      <c r="B41" s="179" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="C41" s="161" t="n">
+        <v>0.486</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="B42">
+        <f>C41-B41</f>
+        <v/>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>13.7 pts of share we leave on the table</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Web-only rivals take</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>504</v>
+      </c>
+      <c r="C43" t="n">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Web-only rivals' capture %</t>
+        </is>
+      </c>
+      <c r="B44" s="10">
+        <f>B43/B39</f>
+        <v/>
+      </c>
+      <c r="C44" s="10">
+        <f>C43/C39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="C45" s="174" t="inlineStr">
+        <is>
+          <t>Same structural position, nearly identical city size - LiteCycle extracts 13.7 more points than we do. Rio opened only in Q3 and we stocked out, so some of this is timing. But 65% of OUR exclusive city still goes to rivals who have no store there at all.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="166" t="inlineStr">
+        <is>
+          <t>WHY THE WEB CASE IS NOW STRONGER</t>
+        </is>
+      </c>
+      <c r="B48" s="166" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="B49" s="170" t="inlineStr">
+        <is>
+          <t>BB LLC pulls 139 units out of Rio with NO store there - 51% of what we get WITH a store. SpaceBikes 120, MILC 107, LiteCycle 106. Web-only rivals took 504 of Rio's 774 units.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Our mirror position</t>
+        </is>
+      </c>
+      <c r="B50" s="170" t="inlineStr">
+        <is>
+          <t>We pull only 38 from New York and 24 from Bangalore by web. Rivals do 3-5x better at the same trick.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Conclusion</t>
+        </is>
+      </c>
+      <c r="B51" s="174" t="inlineStr">
+        <is>
+          <t>Web reach is not a consolation prize for cities we skip - it is how the strong firms raid cities they never entered. Our 19.1% web mix is costing us in all four cities, including the two where we have stores.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="166" t="inlineStr">
+        <is>
+          <t>CITY #3 — updated read</t>
+        </is>
+      </c>
+      <c r="B54" s="166" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="C54" s="166" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>City demand</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>2039</v>
+      </c>
+      <c r="C55" t="n">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Store firms already present</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>3</v>
+      </c>
+      <c r="C56" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Avg demand per store firm today</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>579</v>
+      </c>
+      <c r="C57" t="n">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Weakest incumbent store firm</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Spoke'd Up 412</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Our current web-only demand there</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>38</v>
+      </c>
+      <c r="C59" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Plausible units with a store</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>412 - 574 (match Spoke'd Up or SpaceBikes)</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>~250 (split LiteCycle's monopoly)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+      <c r="B61" s="181" t="inlineStr">
+        <is>
+          <t>STILL THE BEST STORE TARGET. 2.7x the demand, and only 3 rivals hold stores vs Amsterdam's 7. Enter via SPEED (880 units, no dominant firm) - BB LLC holds 82.8% of NYC Mountain.</t>
+        </is>
+      </c>
+      <c r="C61" s="170" t="inlineStr">
+        <is>
+          <t>Smallest prize. LiteCycle's 48.6% monopoly is the industry's most concentrated position.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="166" t="inlineStr">
+        <is>
+          <t>Q4 SEQUENCING — reconciling depth vs breadth</t>
+        </is>
+      </c>
+      <c r="B64" s="166" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>1st dollar: web rebuild</t>
+        </is>
+      </c>
+      <c r="B65" s="174" t="inlineStr">
+        <is>
+          <t>Cheapest demand, reaches all 4 cities, pays back in-quarter (~+$89,600). Rivals prove web raids cities you never enter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2nd dollar: Rio depth</t>
+        </is>
+      </c>
+      <c r="B66" s="174" t="inlineStr">
+        <is>
+          <t>We are the ONLY store in Rio and extract just 34.9% vs LiteCycle's 48.6% in the same position. Closing that gap is ~106 units with no new lease.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>3rd dollar: New York store</t>
+        </is>
+      </c>
+      <c r="B67" s="174" t="inlineStr">
+        <is>
+          <t>Biggest single prize (2,039 units, only 3 store rivals). Enter through Speed once Swift Bike is fixed to 77.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>NOT a priority</t>
+        </is>
+      </c>
+      <c r="B68" s="174" t="inlineStr">
+        <is>
+          <t>Deepening Amsterdam against 6 store-equipped rivals; opening Bangalore against LiteCycle's entrenched 48.6%.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/quarters/Q3/Q3Data.xlsx
+++ b/quarters/Q3/Q3Data.xlsx
@@ -39,6 +39,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_City_Strategy" sheetId="31" state="visible" r:id="rId31"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_Channel" sheetId="32" state="visible" r:id="rId32"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_Presence" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_Staffing" sheetId="34" state="visible" r:id="rId34"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -619,7 +620,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="16"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="16"/>
   </cellStyleXfs>
-  <cellXfs count="188">
+  <cellXfs count="192">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -886,6 +887,10 @@
     </xf>
     <xf numFmtId="1" fontId="0" fillId="31" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="29" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="28" fillId="31" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="31" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -29660,6 +29665,1611 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J90"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" style="146" min="1" max="1"/>
+    <col width="40" customWidth="1" style="146" min="2" max="2"/>
+    <col width="34" customWidth="1" style="146" min="3" max="3"/>
+    <col width="30" customWidth="1" style="146" min="4" max="4"/>
+    <col width="13" customWidth="1" style="146" min="5" max="5"/>
+    <col width="13" customWidth="1" style="146" min="6" max="6"/>
+    <col width="13" customWidth="1" style="146" min="7" max="7"/>
+    <col width="13" customWidth="1" style="146" min="8" max="8"/>
+    <col width="13" customWidth="1" style="146" min="9" max="9"/>
+    <col width="13" customWidth="1" style="146" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="169" t="inlineStr">
+        <is>
+          <t>Sales and Service People — World Market, Q3 actual</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="170" t="inlineStr">
+        <is>
+          <t>Two hard findings: 7 people per city is the cap (nobody exceeds it, and Amsterdam has us AT it), and we are the only firm besides Bike Bros carrying UNTRAINED staff.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="166" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B4" s="166" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C4" s="166" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="D4" s="166" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="E4" s="166" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="F4" s="166" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="G4" s="166" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="H4" s="166" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="I4" s="166" t="inlineStr">
+        <is>
+          <t>UNTRAINED</t>
+        </is>
+      </c>
+      <c r="J4" s="166" t="inlineStr">
+        <is>
+          <t>At 7-cap?</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="n">
+        <v>7</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Spoke'd Up</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SpaceBikes</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" t="n">
+        <v>7</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="171" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="B8" s="171" t="inlineStr">
+        <is>
+          <t>WeBike</t>
+        </is>
+      </c>
+      <c r="C8" s="171" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" s="171" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="171" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="171" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="171" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="171" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" s="188" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="171" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Bike Bros</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>7</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>6</v>
+      </c>
+      <c r="I9" s="167" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>LiteCycle</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" t="n">
+        <v>5</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="171" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="B11" s="171" t="inlineStr">
+        <is>
+          <t>WeBike</t>
+        </is>
+      </c>
+      <c r="C11" s="171" t="n">
+        <v>7</v>
+      </c>
+      <c r="D11" s="171" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="171" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="171" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" s="171" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" s="171" t="n">
+        <v>6</v>
+      </c>
+      <c r="I11" s="188" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="171" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>7</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H12" t="n">
+        <v>7</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Spoke'd Up</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>6</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>6</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SpaceBikes</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>7</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>MILC Bikes</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>7</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H15" t="n">
+        <v>7</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>LiteCycle</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H16" t="n">
+        <v>5</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="166" t="inlineStr">
+        <is>
+          <t>FIRM ROLLUP</t>
+        </is>
+      </c>
+      <c r="B19" s="166" t="inlineStr">
+        <is>
+          <t>Store people</t>
+        </is>
+      </c>
+      <c r="C19" s="166" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="D19" s="166" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="E19" s="166" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="F19" s="166" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="G19" s="166" t="inlineStr">
+        <is>
+          <t>Untrained</t>
+        </is>
+      </c>
+      <c r="H19" s="166" t="inlineStr">
+        <is>
+          <t>Store demand</t>
+        </is>
+      </c>
+      <c r="I19" s="166" t="inlineStr">
+        <is>
+          <t>Demand / store person</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Bike Bros</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>7</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>490</v>
+      </c>
+      <c r="I20" s="189" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>14</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>6</v>
+      </c>
+      <c r="F21" t="n">
+        <v>6</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>938</v>
+      </c>
+      <c r="I21" s="189" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Spoke'd Up</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>11</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" t="n">
+        <v>4</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>5</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>716</v>
+      </c>
+      <c r="I22" s="189" t="n">
+        <v>65.09090909090909</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SpaceBikes</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>14</v>
+      </c>
+      <c r="C23" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" t="n">
+        <v>4</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>6</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>807</v>
+      </c>
+      <c r="I23" s="189" t="n">
+        <v>57.64285714285715</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>LiteCycle</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>10</v>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" t="n">
+        <v>6</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>549</v>
+      </c>
+      <c r="I24" s="189" t="n">
+        <v>54.9</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>MILC Bikes</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>7</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>3</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>364</v>
+      </c>
+      <c r="I25" s="189" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="171" t="inlineStr">
+        <is>
+          <t>WeBike</t>
+        </is>
+      </c>
+      <c r="B26" s="171" t="n">
+        <v>11</v>
+      </c>
+      <c r="C26" s="171" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" s="171" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="171" t="n">
+        <v>4</v>
+      </c>
+      <c r="F26" s="171" t="n">
+        <v>3</v>
+      </c>
+      <c r="G26" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" s="171" t="n">
+        <v>507</v>
+      </c>
+      <c r="I26" s="190" t="n">
+        <v>46.09090909090909</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="166" t="inlineStr">
+        <is>
+          <t>PRODUCTIVITY GAP</t>
+        </is>
+      </c>
+      <c r="B29" s="166" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C29" s="166" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>WeBike demand per store person</t>
+        </is>
+      </c>
+      <c r="B30" s="191" t="n">
+        <v>46.09090909090909</v>
+      </c>
+      <c r="C30" s="170" t="inlineStr">
+        <is>
+          <t>LOWEST in the industry</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Industry average (excl. us)</t>
+        </is>
+      </c>
+      <c r="B31" s="160" t="n">
+        <v>61.1056277056277</v>
+      </c>
+      <c r="C31" s="170" t="inlineStr">
+        <is>
+          <t>Bike Bros 70.0 is best; BB LLC 67.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Shortfall per person</t>
+        </is>
+      </c>
+      <c r="B32" s="189">
+        <f>C31-C30</f>
+        <v/>
+      </c>
+      <c r="C32" s="170" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Our store people</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>11</v>
+      </c>
+      <c r="C33" s="170" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Store demand if we matched the average</t>
+        </is>
+      </c>
+      <c r="B34">
+        <f>C31*C33</f>
+        <v/>
+      </c>
+      <c r="C34" s="170" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Additional units available at current headcount</t>
+        </is>
+      </c>
+      <c r="B35" s="159">
+        <f>C34-507</f>
+        <v/>
+      </c>
+      <c r="C35" s="170" t="inlineStr">
+        <is>
+          <t>no new hires needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="166" t="inlineStr">
+        <is>
+          <t>THE 7-PERSON CITY CAP — this settles depth vs breadth</t>
+        </is>
+      </c>
+      <c r="B38" s="166" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C38" s="166" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Maximum staff observed in any city (all 12 rows)</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>7</v>
+      </c>
+      <c r="C39" s="170" t="inlineStr">
+        <is>
+          <t>BB LLC, SpaceBikes, Bike Bros, MILC and our own Amsterdam all sit at 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>WeBike Amsterdam headcount</t>
+        </is>
+      </c>
+      <c r="B40" s="167" t="n">
+        <v>7</v>
+      </c>
+      <c r="C40" s="170" t="inlineStr">
+        <is>
+          <t>AT THE CAP - we cannot add a single person there</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>WeBike Rio headcount</t>
+        </is>
+      </c>
+      <c r="B41" s="159" t="n">
+        <v>4</v>
+      </c>
+      <c r="C41" s="170" t="inlineStr">
+        <is>
+          <t>3 SLOTS OPEN - the only store depth available to us</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="C42" s="174" t="inlineStr">
+        <is>
+          <t>'Deepen Amsterdam' is not a legal move. Amsterdam is maxed at 7. The only ways to add store selling capacity are (a) fill Rio's 3 open slots, or (b) open a new city, which unlocks 7 more.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="166" t="inlineStr">
+        <is>
+          <t>RIO vs AMSTERDAM — where a body is worth more</t>
+        </is>
+      </c>
+      <c r="B45" s="166" t="inlineStr">
+        <is>
+          <t>Rio</t>
+        </is>
+      </c>
+      <c r="C45" s="166" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Store people</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>4</v>
+      </c>
+      <c r="C46" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>City demand (all channels)</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>270</v>
+      </c>
+      <c r="C47" t="n">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Demand per person</t>
+        </is>
+      </c>
+      <c r="B48" s="160">
+        <f>C47/C46</f>
+        <v/>
+      </c>
+      <c r="C48" s="191">
+        <f>D47/D46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rival stores in city</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Open slots to the 7-cap</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>3</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="B51" s="174" t="inlineStr">
+        <is>
+          <t>A Rio head is worth ~60% more than an Amsterdam head because Rio has no rival store. Filling the 3 open Rio slots is the highest-return staffing move on the board.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>CAVEAT</t>
+        </is>
+      </c>
+      <c r="B52" s="170" t="inlineStr">
+        <is>
+          <t>City demand includes web orders, so per-person figures are directional rather than pure store productivity. The ranking is robust; the exact multiple is not.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="166" t="inlineStr">
+        <is>
+          <t>UNTRAINED STAFF — a free win we skipped</t>
+        </is>
+      </c>
+      <c r="B55" s="166" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C55" s="166" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>WeBike untrained people</t>
+        </is>
+      </c>
+      <c r="B56" s="167" t="n">
+        <v>2</v>
+      </c>
+      <c r="C56" s="170" t="inlineStr">
+        <is>
+          <t>1 in Rio, 1 in Amsterdam</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Firms with any untrained staff</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>WeBike (2), Bike Bros (1)</t>
+        </is>
+      </c>
+      <c r="C57" s="170" t="inlineStr">
+        <is>
+          <t>the other five are 100% trained</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Mountain training cost</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>400</v>
+      </c>
+      <c r="C58" s="170" t="inlineStr">
+        <is>
+          <t>per quarter</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Speed training cost</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>400</v>
+      </c>
+      <c r="C59" s="170" t="inlineStr">
+        <is>
+          <t>per quarter</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Cost to train both</t>
+        </is>
+      </c>
+      <c r="B60" s="159" t="n">
+        <v>800</v>
+      </c>
+      <c r="C60" s="170" t="inlineStr">
+        <is>
+          <t>trivial against ~$750 contribution PER UNIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="C61" s="174" t="inlineStr">
+        <is>
+          <t>We are paying two full salaries ($24,425/yr each) for untrained sellers while every serious competitor trains everyone. Fix this first - it costs $800.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="166" t="inlineStr">
+        <is>
+          <t>SPECIALISATION vs SEGMENT RESULT</t>
+        </is>
+      </c>
+      <c r="B64" s="166" t="inlineStr">
+        <is>
+          <t>Specialists</t>
+        </is>
+      </c>
+      <c r="C64" s="166" t="inlineStr">
+        <is>
+          <t>Segment demand</t>
+        </is>
+      </c>
+      <c r="D64" s="166" t="inlineStr">
+        <is>
+          <t>Demand per specialist</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="166" t="inlineStr">
+        <is>
+          <t>MOUNTAIN</t>
+        </is>
+      </c>
+      <c r="D65" s="189" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>LiteCycle</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>2</v>
+      </c>
+      <c r="C66" t="n">
+        <v>340</v>
+      </c>
+      <c r="D66" s="189">
+        <f>C66/B66</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>6</v>
+      </c>
+      <c r="C67" t="n">
+        <v>751</v>
+      </c>
+      <c r="D67" s="189">
+        <f>C67/B67</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="173" t="inlineStr">
+        <is>
+          <t>WeBike</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>4</v>
+      </c>
+      <c r="C68" t="n">
+        <v>358</v>
+      </c>
+      <c r="D68" s="189">
+        <f>C68/B68</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Bike Bros</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>2</v>
+      </c>
+      <c r="C69" t="n">
+        <v>172</v>
+      </c>
+      <c r="D69" s="189">
+        <f>C69/B69</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="166" t="inlineStr">
+        <is>
+          <t>SPEED</t>
+        </is>
+      </c>
+      <c r="D70" s="189" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>6</v>
+      </c>
+      <c r="C71" t="n">
+        <v>657</v>
+      </c>
+      <c r="D71" s="189">
+        <f>C71/B71</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>MILC Bikes</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>3</v>
+      </c>
+      <c r="C72" t="n">
+        <v>328</v>
+      </c>
+      <c r="D72" s="189">
+        <f>C72/B72</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>SpaceBikes</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>6</v>
+      </c>
+      <c r="C73" t="n">
+        <v>588</v>
+      </c>
+      <c r="D73" s="189">
+        <f>C73/B73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>LiteCycle</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>6</v>
+      </c>
+      <c r="C74" t="n">
+        <v>548</v>
+      </c>
+      <c r="D74" s="189">
+        <f>C74/B74</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Spoke'd Up</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>5</v>
+      </c>
+      <c r="C75" t="n">
+        <v>362</v>
+      </c>
+      <c r="D75" s="189">
+        <f>C75/B75</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="173" t="inlineStr">
+        <is>
+          <t>WeBike</t>
+        </is>
+      </c>
+      <c r="B76" s="167" t="n">
+        <v>3</v>
+      </c>
+      <c r="C76" t="n">
+        <v>215</v>
+      </c>
+      <c r="D76" s="189">
+        <f>C76/B76</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="166" t="inlineStr">
+        <is>
+          <t>RECREATION</t>
+        </is>
+      </c>
+      <c r="D77" s="189" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>SpaceBikes</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>4</v>
+      </c>
+      <c r="C78" t="n">
+        <v>710</v>
+      </c>
+      <c r="D78" s="189">
+        <f>C78/B78</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>MILC Bikes</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>3</v>
+      </c>
+      <c r="C79" t="n">
+        <v>471</v>
+      </c>
+      <c r="D79" s="189">
+        <f>C79/B79</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Spoke'd Up</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>4</v>
+      </c>
+      <c r="C80" t="n">
+        <v>492</v>
+      </c>
+      <c r="D80" s="189">
+        <f>C80/B80</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="173" t="inlineStr">
+        <is>
+          <t>WeBike</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" t="n">
+        <v>54</v>
+      </c>
+      <c r="D81" s="189" t="inlineStr">
+        <is>
+          <t>spillover only - no Rec specialists</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="166" t="inlineStr">
+        <is>
+          <t>Q4 STAFFING PLAN</t>
+        </is>
+      </c>
+      <c r="B84" s="166" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C84" s="166" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="D84" s="166" t="inlineStr">
+        <is>
+          <t>Expected units</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>1. Train the 2 untrained</t>
+        </is>
+      </c>
+      <c r="B85" s="174" t="inlineStr">
+        <is>
+          <t>1 Mountain (Rio) + 1 Speed (Amsterdam)</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>800</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>free productivity</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2. Fill Rio to the 7-cap</t>
+        </is>
+      </c>
+      <c r="B86" s="174" t="inlineStr">
+        <is>
+          <t>+3 people: 1 Mountain, 1 Speed, 1 Service</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>~$18,300/qtr salary + hire + train</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>~+200 at Rio's ~67/head</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>3. Rebuild web staff</t>
+        </is>
+      </c>
+      <c r="B87" s="174" t="inlineStr">
+        <is>
+          <t>3 -&gt; 6 web sales/support</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>~$18,300/qtr</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>~+152 (see Q3_Channel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>4. Add Speed specialists</t>
+        </is>
+      </c>
+      <c r="B88" s="174" t="inlineStr">
+        <is>
+          <t>we have 3 vs BB LLC/LiteCycle/SpaceBikes 6</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>included above</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Speed is our weakest segment AND the largest</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>5. New York store (if funded)</t>
+        </is>
+      </c>
+      <c r="B89" s="174" t="inlineStr">
+        <is>
+          <t>unlocks 7 fresh slots; staff Speed-heavy</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>setup + lease + salaries</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>~400-570 at incumbent rates</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>NOT possible</t>
+        </is>
+      </c>
+      <c r="B90" s="185" t="inlineStr">
+        <is>
+          <t>Adding anyone in Amsterdam - we are at the 7-person cap</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/quarters/Q3/Q3Data.xlsx
+++ b/quarters/Q3/Q3Data.xlsx
@@ -40,6 +40,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_Channel" sheetId="32" state="visible" r:id="rId32"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_Presence" sheetId="33" state="visible" r:id="rId33"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_Staffing" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_Web_Ops" sheetId="35" state="visible" r:id="rId35"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -52,7 +53,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="31">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -242,6 +243,10 @@
     <font>
       <b val="1"/>
       <sz val="13"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="34">
@@ -620,7 +625,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="16"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="16"/>
   </cellStyleXfs>
-  <cellXfs count="192">
+  <cellXfs count="193">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -891,6 +896,7 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="28" fillId="31" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="31" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="29" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -18169,7 +18175,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" style="146" min="1" max="1"/>
@@ -18188,7 +18194,7 @@
     <row r="2">
       <c r="A2" s="170" t="inlineStr">
         <is>
-          <t>Rule: OC/day = forecast demand / 65 * (1 + (1 - productivity)). Never schedule below forecast again. Q3 proof: OC 8/day vs 24 owned -&gt; 204 stock-outs AND labor cost/unit up $130-&gt;$205.</t>
+          <t>Rule: required OC/day = forecast units / (productivity x 65 days). Never schedule below the forecast again. Q3 proof: OC 8/day vs 24 owned -&gt; 204 stock-outs AND labour cost/unit up $130 -&gt; $205.</t>
         </is>
       </c>
     </row>
@@ -18288,12 +18294,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Productivity pad</t>
-        </is>
-      </c>
-      <c r="B9">
-        <f>1+(1-B8)</f>
-        <v/>
+          <t>Capacity factor (1 / productivity)</t>
+        </is>
+      </c>
+      <c r="B9" s="159">
+        <f>1/B8</f>
+        <v/>
+      </c>
+      <c r="C9" s="170" t="inlineStr">
+        <is>
+          <t>CORRECTED: was 1+(1-p)=1.26, which understated the requirement. 1/0.74 = 1.35.</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -18303,12 +18314,12 @@
         </is>
       </c>
       <c r="B10">
-        <f>B7/65*B9</f>
+        <f>B7/(B8*65)</f>
         <v/>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>schedule AT LEAST this</t>
+          <t>units / (productivity x days) - schedule AT LEAST this</t>
         </is>
       </c>
     </row>
@@ -18795,46 +18806,431 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Q4 forecast units</t>
-        </is>
-      </c>
-      <c r="B46">
-        <f>B7</f>
-        <v/>
+      <c r="A46" s="166" t="inlineStr">
+        <is>
+          <t>DEMAND SCENARIOS -&gt; REQUIRED OPERATING CAPACITY</t>
+        </is>
+      </c>
+      <c r="B46" s="166" t="inlineStr">
+        <is>
+          <t>Demand</t>
+        </is>
+      </c>
+      <c r="C46" s="166" t="inlineStr">
+        <is>
+          <t>Required OC/day</t>
+        </is>
+      </c>
+      <c r="D46" s="166" t="inlineStr">
+        <is>
+          <t>Fits in 24/day?</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>COGS saving on forecast volume</t>
-        </is>
-      </c>
-      <c r="B47">
-        <f>B45*B46</f>
+          <t>A. Do nothing (Q3 demand less 16.3% ill will)</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>525</v>
+      </c>
+      <c r="C47" s="189">
+        <f>B48/(0.74*65)</f>
+        <v/>
+      </c>
+      <c r="D47">
+        <f>IF(C48&lt;=24,"yes","NO")</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>+ Gross margin recovered from ending stock-outs</t>
+          <t>B. Base forecast (planner B7)</t>
         </is>
       </c>
       <c r="B48">
-        <f>Q3_Unit_Economics!I6</f>
+        <f>B7</f>
+        <v/>
+      </c>
+      <c r="C48" s="189">
+        <f>B49/(0.74*65)</f>
+        <v/>
+      </c>
+      <c r="D48">
+        <f>IF(C49&lt;=24,"yes","NO")</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <f> Combined Q4 swing vs Q3 behaviour</f>
-        <v/>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>C. + fill Rio to the 7-person cap</t>
+        </is>
       </c>
       <c r="B49" s="159">
-        <f>B47+B48</f>
-        <v/>
+        <f>B49+200</f>
+        <v/>
+      </c>
+      <c r="C49" s="189">
+        <f>B50/(0.74*65)</f>
+        <v/>
+      </c>
+      <c r="D49">
+        <f>IF(C50&lt;=24,"yes","NO")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>D. + full web rebuild (7 staff, 4 tactics)</t>
+        </is>
+      </c>
+      <c r="B50">
+        <f>B50+315</f>
+        <v/>
+      </c>
+      <c r="C50" s="189">
+        <f>B51/(0.74*65)</f>
+        <v/>
+      </c>
+      <c r="D50">
+        <f>IF(C51&lt;=24,"yes","NO")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>E. + New York store</t>
+        </is>
+      </c>
+      <c r="B51">
+        <f>B51+400</f>
+        <v/>
+      </c>
+      <c r="C51" s="189">
+        <f>B52/(0.74*65)</f>
+        <v/>
+      </c>
+      <c r="D51" s="167">
+        <f>IF(C52&lt;=24,"yes","NO")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Max units at 24/day and 74% productivity</t>
+        </is>
+      </c>
+      <c r="B52" s="159">
+        <f>24*0.74*65</f>
+        <v/>
+      </c>
+      <c r="D52" s="167" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D53" s="185" t="inlineStr">
+        <is>
+          <t>Scenario C (Rio fill) fits comfortably at 17.8/day. Scenario D (Rio + full web rebuild) needs 24.3/day and EXCEEDS our 24/day fixed capacity by a hair. Scenario E (plus New York) needs 32.7/day. Capacity - not demand, not product - is now the binding constraint on growth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="166" t="inlineStr">
+        <is>
+          <t>WEB &amp; STAFFING TARGETS (from Q3_Web_Ops / Q3_Staffing)</t>
+        </is>
+      </c>
+      <c r="B56" s="166" t="inlineStr">
+        <is>
+          <t>WeBike Q3</t>
+        </is>
+      </c>
+      <c r="C56" s="166" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="D56" s="166" t="inlineStr">
+        <is>
+          <t>Q4 target</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Web staff (cap is 7)</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>3</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>7 (four firms)</t>
+        </is>
+      </c>
+      <c r="D57" s="168" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Web productivity tactics funded (of 4)</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" t="n">
+        <v>4</v>
+      </c>
+      <c r="D58" s="168" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Web productivity budget</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>24,000 - 33,000</t>
+        </is>
+      </c>
+      <c r="D59" s="168" t="n">
+        <v>28000</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Web demand</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>120</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>435 - 569</t>
+        </is>
+      </c>
+      <c r="D60" s="168" t="n">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Rio store staff (cap is 7)</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>4</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D61" s="168" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Amsterdam store staff (cap is 7)</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>7</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D62" s="168" t="inlineStr">
+        <is>
+          <t>7 (AT CAP - no room)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Untrained staff</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>2</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" s="167" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="166" t="inlineStr">
+        <is>
+          <t>CAPACITY IS NOW THE BINDING CONSTRAINT — and idle cash is the cure</t>
+        </is>
+      </c>
+      <c r="B66" s="166" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C66" s="166" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Cash sitting idle</t>
+        </is>
+      </c>
+      <c r="B67" s="167" t="n">
+        <v>1010838</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>the direct cause of Asset Management 0.353 (LAST place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Fixed capacity today</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>24</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>3 printers, $720,000 original cost -&gt; ~$240,000 each</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Max units at 24/day and 74% productivity</t>
+        </is>
+      </c>
+      <c r="B69">
+        <f>24*0.74*65</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Demand if we fill Rio AND rebuild web</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>1171</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>exceeds the ceiling by ~17 units</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>A 4th printer would give</t>
+        </is>
+      </c>
+      <c r="B71" s="159" t="n">
+        <v>32</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>units/day -&gt; max ~1,539 units</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Approx capital cost</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>240000</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>24% of idle cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Approx added depreciation</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>per quarter</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="C74" s="174" t="inlineStr">
+        <is>
+          <t>Buying capacity solves TWO problems at once: it lifts the growth ceiling AND converts idle cash into revenue-producing assets, which is exactly what Asset Management 0.353 is punishing. Note that owning capacity is NOT what caused Q2's $148,652 excess-capacity charge - that came from SCHEDULING operating capacity we did not use. Depreciation is the only carrying cost of ownership.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Decision framing</t>
+        </is>
+      </c>
+      <c r="C75" s="174" t="inlineStr">
+        <is>
+          <t>If we want Rio + web + New York we need roughly 33/day, i.e. 2 more printers. If we want Rio + web only, 1 more printer gives comfortable slack. Doing nothing caps us at ~1,154 units.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -29822,7 +30218,6 @@
       <c r="I6" t="n">
         <v>0</v>
       </c>
-      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -29966,7 +30361,6 @@
       <c r="I10" t="n">
         <v>0</v>
       </c>
-      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="171" t="inlineStr">
@@ -30076,7 +30470,6 @@
       <c r="I13" t="n">
         <v>0</v>
       </c>
-      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -30186,7 +30579,6 @@
       <c r="I16" t="n">
         <v>0</v>
       </c>
-      <c r="J16" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="166" t="inlineStr">
@@ -31262,6 +31654,1134 @@
       <c r="B90" s="185" t="inlineStr">
         <is>
           <t>Adding anyone in Amsterdam - we are at the 7-person cap</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H74"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="50" customWidth="1" style="146" min="1" max="1"/>
+    <col width="16" customWidth="1" style="146" min="2" max="2"/>
+    <col width="20" customWidth="1" style="146" min="3" max="3"/>
+    <col width="58" customWidth="1" style="146" min="4" max="4"/>
+    <col width="14" customWidth="1" style="146" min="5" max="5"/>
+    <col width="14" customWidth="1" style="146" min="6" max="6"/>
+    <col width="14" customWidth="1" style="146" min="7" max="7"/>
+    <col width="14" customWidth="1" style="146" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="169" t="inlineStr">
+        <is>
+          <t>Web Sales &amp; Service + Web Productivity Budgets — Q3 actual</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="170" t="inlineStr">
+        <is>
+          <t>Two findings: web staff is ALSO capped at 7 and we sit at 3, and there are FOUR web productivity tactics of which we fund ONE. Every firm running all four gets 435-569 web units; the two running fewer get 120-138.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="166" t="inlineStr">
+        <is>
+          <t>WEB STAFF</t>
+        </is>
+      </c>
+      <c r="B4" s="166" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="C4" s="166" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="D4" s="166" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E4" s="166" t="inlineStr">
+        <is>
+          <t>Web demand</t>
+        </is>
+      </c>
+      <c r="F4" s="166" t="inlineStr">
+        <is>
+          <t>Demand / web head</t>
+        </is>
+      </c>
+      <c r="G4" s="166" t="inlineStr">
+        <is>
+          <t>Slots open to 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E5" t="n">
+        <v>569</v>
+      </c>
+      <c r="F5" s="189" t="n">
+        <v>81.28571428571429</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SpaceBikes</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" t="n">
+        <v>491</v>
+      </c>
+      <c r="F6" s="189" t="n">
+        <v>70.14285714285714</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>LiteCycle</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" t="n">
+        <v>435</v>
+      </c>
+      <c r="F7" s="189" t="n">
+        <v>62.14285714285715</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>MILC Bikes</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" t="n">
+        <v>435</v>
+      </c>
+      <c r="F8" s="189" t="n">
+        <v>62.14285714285715</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Spoke'd Up</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>138</v>
+      </c>
+      <c r="F9" s="189" t="n">
+        <v>46</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="171" t="inlineStr">
+        <is>
+          <t>WeBike</t>
+        </is>
+      </c>
+      <c r="B10" s="171" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="171" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="171" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" s="171" t="n">
+        <v>120</v>
+      </c>
+      <c r="F10" s="190" t="n">
+        <v>40</v>
+      </c>
+      <c r="G10" s="188" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Bike Bros</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="189" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>no web centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="166" t="inlineStr">
+        <is>
+          <t>THE WEB STAFF CAP</t>
+        </is>
+      </c>
+      <c r="B14" s="166" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C14" s="166" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Max web staff observed</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>7</v>
+      </c>
+      <c r="C15" s="170" t="inlineStr">
+        <is>
+          <t>LiteCycle, BB LLC, SpaceBikes and MILC all sit exactly at 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>WeBike web staff</t>
+        </is>
+      </c>
+      <c r="B16" s="167" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" s="170" t="inlineStr">
+        <is>
+          <t>2 sales + 1 service - we CUT to this in Q3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Slots open</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C17" s="170" t="inlineStr">
+        <is>
+          <t>same 7-person ceiling as the city stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Our demand per web head</t>
+        </is>
+      </c>
+      <c r="B18" s="167" t="n">
+        <v>40</v>
+      </c>
+      <c r="C18" s="170" t="inlineStr">
+        <is>
+          <t>LOWEST of all six firms with a web centre</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Leader demand per web head</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>81.3</v>
+      </c>
+      <c r="C19" s="170" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="C20" s="174" t="inlineStr">
+        <is>
+          <t>The web centre has the same 7-person ceiling as a store, but unlike Amsterdam we are nowhere near it. Four open slots and the worst output per head is the largest single pool of unclaimed demand we have found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="166" t="inlineStr">
+        <is>
+          <t>WEB PRODUCTIVITY BUDGETS</t>
+        </is>
+      </c>
+      <c r="B23" s="166" t="inlineStr">
+        <is>
+          <t>LiteCycle</t>
+        </is>
+      </c>
+      <c r="C23" s="166" t="inlineStr">
+        <is>
+          <t>WeBike</t>
+        </is>
+      </c>
+      <c r="D23" s="166" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="E23" s="166" t="inlineStr">
+        <is>
+          <t>Spoke'd Up</t>
+        </is>
+      </c>
+      <c r="F23" s="166" t="inlineStr">
+        <is>
+          <t>SpaceBikes</t>
+        </is>
+      </c>
+      <c r="G23" s="166" t="inlineStr">
+        <is>
+          <t>MILC Bikes</t>
+        </is>
+      </c>
+      <c r="H23" s="166" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Toll-free phone advising / service calls</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>7000</v>
+      </c>
+      <c r="C24" s="171" t="n">
+        <v>6000</v>
+      </c>
+      <c r="D24" t="n">
+        <v>9000</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F24" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G24" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H24" t="n">
+        <v>5667</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Advanced shopping cart &amp; checkout</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>7000</v>
+      </c>
+      <c r="C25" s="188" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>7000</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>7000</v>
+      </c>
+      <c r="G25" t="n">
+        <v>7000</v>
+      </c>
+      <c r="H25" t="n">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Continuous page upgrades (content, appeal, navigation)</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>7000</v>
+      </c>
+      <c r="C26" s="188" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>9000</v>
+      </c>
+      <c r="E26" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F26" t="n">
+        <v>12000</v>
+      </c>
+      <c r="G26" t="n">
+        <v>6000</v>
+      </c>
+      <c r="H26" t="n">
+        <v>6667</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Order tracking software</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C27" s="188" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>8000</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>8000</v>
+      </c>
+      <c r="G27" t="n">
+        <v>8000</v>
+      </c>
+      <c r="H27" t="n">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>29000</v>
+      </c>
+      <c r="C28" s="171" t="n">
+        <v>6000</v>
+      </c>
+      <c r="D28" t="n">
+        <v>33000</v>
+      </c>
+      <c r="E28" t="n">
+        <v>9000</v>
+      </c>
+      <c r="F28" t="n">
+        <v>33000</v>
+      </c>
+      <c r="G28" t="n">
+        <v>24000</v>
+      </c>
+      <c r="H28" t="n">
+        <v>27334</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Tactics funded (of 4)</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>4</v>
+      </c>
+      <c r="C29" s="171" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>4</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4</v>
+      </c>
+      <c r="G29" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Web demand</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>435</v>
+      </c>
+      <c r="C30" s="171" t="n">
+        <v>120</v>
+      </c>
+      <c r="D30" t="n">
+        <v>569</v>
+      </c>
+      <c r="E30" t="n">
+        <v>138</v>
+      </c>
+      <c r="F30" t="n">
+        <v>491</v>
+      </c>
+      <c r="G30" t="n">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="166" t="inlineStr">
+        <is>
+          <t>THE PATTERN IS ALMOST PERFECT</t>
+        </is>
+      </c>
+      <c r="B33" s="166" t="inlineStr">
+        <is>
+          <t>Tactics funded</t>
+        </is>
+      </c>
+      <c r="C33" s="166" t="inlineStr">
+        <is>
+          <t>Total budget</t>
+        </is>
+      </c>
+      <c r="D33" s="166" t="inlineStr">
+        <is>
+          <t>Web demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C34" t="n">
+        <v>33000</v>
+      </c>
+      <c r="D34" s="159" t="n">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>SpaceBikes</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>4</v>
+      </c>
+      <c r="C35" t="n">
+        <v>33000</v>
+      </c>
+      <c r="D35" s="159" t="n">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>LiteCycle</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>4</v>
+      </c>
+      <c r="C36" t="n">
+        <v>29000</v>
+      </c>
+      <c r="D36" s="159" t="n">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>MILC Bikes</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>4</v>
+      </c>
+      <c r="C37" t="n">
+        <v>24000</v>
+      </c>
+      <c r="D37" s="159" t="n">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Spoke'd Up</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>2</v>
+      </c>
+      <c r="C38" t="n">
+        <v>9000</v>
+      </c>
+      <c r="D38" s="167" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>WeBike</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" t="n">
+        <v>6000</v>
+      </c>
+      <c r="D39" s="167" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D40" s="174" t="inlineStr">
+        <is>
+          <t>Every firm funding all four tactics ($24k-33k) lands at 435-569 web units. Both firms funding fewer land at 120-138. Headcount moves with budget (7 vs 3) so the two effects cannot be fully separated - but we are at the bottom of BOTH.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="166" t="inlineStr">
+        <is>
+          <t>WHAT WE NEVER STARTED</t>
+        </is>
+      </c>
+      <c r="B43" s="166" t="inlineStr">
+        <is>
+          <t>Our budget</t>
+        </is>
+      </c>
+      <c r="C43" s="166" t="inlineStr">
+        <is>
+          <t>Industry average</t>
+        </is>
+      </c>
+      <c r="D43" s="166" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Toll-free phone</t>
+        </is>
+      </c>
+      <c r="B44" s="159" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C44" t="n">
+        <v>5667</v>
+      </c>
+      <c r="D44" s="170" t="inlineStr">
+        <is>
+          <t>ABOVE average - our one good web decision (raised from $3k)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Advanced shopping cart &amp; checkout</t>
+        </is>
+      </c>
+      <c r="B45" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" t="n">
+        <v>7000</v>
+      </c>
+      <c r="D45" s="170" t="inlineStr">
+        <is>
+          <t>NEVER STARTED - 4 of 6 firms fund it at $7,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Continuous page upgrades</t>
+        </is>
+      </c>
+      <c r="B46" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" t="n">
+        <v>6667</v>
+      </c>
+      <c r="D46" s="170" t="inlineStr">
+        <is>
+          <t>WE STOPPED THIS IN Q3 - SpaceBikes funds it at $12,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Order tracking software</t>
+        </is>
+      </c>
+      <c r="B47" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" t="n">
+        <v>8000</v>
+      </c>
+      <c r="D47" s="170" t="inlineStr">
+        <is>
+          <t>NEVER STARTED - 4 of 6 firms fund it at $8,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Our total</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C48" t="n">
+        <v>27500</v>
+      </c>
+      <c r="D48" s="170" t="inlineStr">
+        <is>
+          <t>average of the four full-tactic firms</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="166" t="inlineStr">
+        <is>
+          <t>THE FULL WEB REBUILD CASE</t>
+        </is>
+      </c>
+      <c r="B51" s="166" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C51" s="166" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Current web demand</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>120</v>
+      </c>
+      <c r="C52" s="170" t="inlineStr">
+        <is>
+          <t>3 staff, 1 tactic, $6,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Full-tactic cohort web demand range</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>435 - 569</t>
+        </is>
+      </c>
+      <c r="C53" s="170" t="inlineStr">
+        <is>
+          <t>7 staff, 4 tactics, $24k-33k</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Conservative target (cohort floor)</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>435</v>
+      </c>
+      <c r="C54" s="170" t="inlineStr">
+        <is>
+          <t>LiteCycle / MILC level</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Additional demand</t>
+        </is>
+      </c>
+      <c r="B55">
+        <f>C54-C52</f>
+        <v/>
+      </c>
+      <c r="C55" s="170" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Contribution per unit</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>750</v>
+      </c>
+      <c r="C56" s="170" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Gross margin opportunity</t>
+        </is>
+      </c>
+      <c r="B57" s="159">
+        <f>C55*C56</f>
+        <v/>
+      </c>
+      <c r="C57" s="170" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Cost: +4 web staff per quarter</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>24425</v>
+      </c>
+      <c r="C58" s="170" t="inlineStr">
+        <is>
+          <t>4 x $24,425/yr = ~$6,106/qtr each</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Cost: raise web budget $6,000 -&gt; $28,000</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>22000</v>
+      </c>
+      <c r="C59" s="170" t="inlineStr">
+        <is>
+          <t>add 3 tactics, top up toll-free</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Total incremental cost</t>
+        </is>
+      </c>
+      <c r="B60">
+        <f>C58+C59</f>
+        <v/>
+      </c>
+      <c r="C60" s="170" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>NET QUARTERLY GAIN</t>
+        </is>
+      </c>
+      <c r="B61" s="192">
+        <f>C57-C60</f>
+        <v/>
+      </c>
+      <c r="C61" s="170" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="C62" s="170" t="inlineStr">
+        <is>
+          <t>This supersedes the earlier +$89,600 estimate, which only modelled matching the average web MIX. Matching the leaders' web OPERATION is worth far more.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="166" t="inlineStr">
+        <is>
+          <t>CAPACITY WARNING</t>
+        </is>
+      </c>
+      <c r="B65" s="166" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="C65" s="166" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Store demand today</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>507</v>
+      </c>
+      <c r="C66" s="170" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Rio +3 staff at ~67/head</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>200</v>
+      </c>
+      <c r="C67" s="170" t="inlineStr">
+        <is>
+          <t>see Q3_Staffing</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Web at cohort floor</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>435</v>
+      </c>
+      <c r="C68" s="170" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Indicative total demand</t>
+        </is>
+      </c>
+      <c r="B69">
+        <f>C66+C67+C68</f>
+        <v/>
+      </c>
+      <c r="C69" s="170" t="inlineStr">
+        <is>
+          <t>before ill will</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Max units at 24/day, 65 days, 74% productivity</t>
+        </is>
+      </c>
+      <c r="B70">
+        <f>24*65*0.74</f>
+        <v/>
+      </c>
+      <c r="C70" s="170" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Required scheduled OC per day</t>
+        </is>
+      </c>
+      <c r="B71" s="168">
+        <f>C69/(0.74*65)</f>
+        <v/>
+      </c>
+      <c r="C71" s="170" t="inlineStr">
+        <is>
+          <t>units / (productivity x days)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Fixed capacity per day</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>24</v>
+      </c>
+      <c r="C72" s="170" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Headroom</t>
+        </is>
+      </c>
+      <c r="B73">
+        <f>C72-C71</f>
+        <v/>
+      </c>
+      <c r="C73" s="170" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="C74" s="174" t="inlineStr">
+        <is>
+          <t>Doing all of this at once pushes demand toward ~1,140 and required OC to roughly 21/day - inside our 24/day fixed capacity, but with little slack. Schedule OC to the FORECAST and re-run the production simulation before committing.</t>
         </is>
       </c>
     </row>

--- a/quarters/Q3/Q3Data.xlsx
+++ b/quarters/Q3/Q3Data.xlsx
@@ -41,6 +41,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_Presence" sheetId="33" state="visible" r:id="rId33"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_Staffing" sheetId="34" state="visible" r:id="rId34"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_Web_Ops" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_Price_Judgment" sheetId="36" state="visible" r:id="rId36"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -625,7 +626,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="16"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="16"/>
   </cellStyleXfs>
-  <cellXfs count="193">
+  <cellXfs count="194">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -897,6 +898,9 @@
     <xf numFmtId="165" fontId="28" fillId="31" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="31" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="30" fillId="29" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -32790,6 +32794,1691 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H96"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="52" customWidth="1" style="146" min="1" max="1"/>
+    <col width="22" customWidth="1" style="146" min="2" max="2"/>
+    <col width="30" customWidth="1" style="146" min="3" max="3"/>
+    <col width="60" customWidth="1" style="146" min="4" max="4"/>
+    <col width="56" customWidth="1" style="146" min="5" max="5"/>
+    <col width="16" customWidth="1" style="146" min="6" max="6"/>
+    <col width="16" customWidth="1" style="146" min="7" max="7"/>
+    <col width="16" customWidth="1" style="146" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="169" t="inlineStr">
+        <is>
+          <t>Price Judgment — World Market, Q3 actual</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="170" t="inlineStr">
+        <is>
+          <t>100 = no price resistance. Lower = buyers find the price high. Because the score depends only on price vs segment willingness-to-pay, identical triplets imply identical prices - which lets us rank every rival's price without seeing the price list.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="166" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="B4" s="166" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C4" s="166" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="D4" s="166" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="E4" s="166" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="F4" s="166" t="inlineStr">
+        <is>
+          <t>Targets</t>
+        </is>
+      </c>
+      <c r="G4" s="166" t="inlineStr">
+        <is>
+          <t>Price judgment in target</t>
+        </is>
+      </c>
+      <c r="H4" s="166" t="inlineStr">
+        <is>
+          <t>Resistance?</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MACH I.I</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Bike Bros</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>63</v>
+      </c>
+      <c r="D5" t="n">
+        <v>78</v>
+      </c>
+      <c r="E5" t="n">
+        <v>90</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="G5" s="167" t="n">
+        <v>90</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TERRAMAX</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Bike Bros</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>73</v>
+      </c>
+      <c r="D6" t="n">
+        <v>91</v>
+      </c>
+      <c r="E6" t="n">
+        <v>100</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="G6" s="167" t="n">
+        <v>91</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Mach 0.6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Bike Bros</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>70</v>
+      </c>
+      <c r="D7" t="n">
+        <v>86</v>
+      </c>
+      <c r="E7" t="n">
+        <v>100</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="G7" s="159" t="n">
+        <v>100</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TERRAMean</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Bike Bros</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>82</v>
+      </c>
+      <c r="D8" t="n">
+        <v>100</v>
+      </c>
+      <c r="E8" t="n">
+        <v>100</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="G8" s="159" t="n">
+        <v>100</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MountainCruise1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Bike Bros</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>92</v>
+      </c>
+      <c r="D9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" t="n">
+        <v>100</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="G9" s="167" t="n">
+        <v>92</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>LiteSpeed Pro+</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>LiteCycle</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>73</v>
+      </c>
+      <c r="D10" t="n">
+        <v>90</v>
+      </c>
+      <c r="E10" t="n">
+        <v>100</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="G10" s="159" t="n">
+        <v>100</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>LiteSpeed+</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>LiteCycle</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>83</v>
+      </c>
+      <c r="D11" t="n">
+        <v>100</v>
+      </c>
+      <c r="E11" t="n">
+        <v>100</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="G11" s="159" t="n">
+        <v>100</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LiteTrail Pro</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>LiteCycle</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>85</v>
+      </c>
+      <c r="D12" t="n">
+        <v>100</v>
+      </c>
+      <c r="E12" t="n">
+        <v>100</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="G12" s="159" t="n">
+        <v>100</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="171" t="inlineStr">
+        <is>
+          <t>Hike Bike</t>
+        </is>
+      </c>
+      <c r="B13" s="171" t="inlineStr">
+        <is>
+          <t>WeBike</t>
+        </is>
+      </c>
+      <c r="C13" s="171" t="n">
+        <v>81</v>
+      </c>
+      <c r="D13" s="171" t="n">
+        <v>100</v>
+      </c>
+      <c r="E13" s="171" t="n">
+        <v>100</v>
+      </c>
+      <c r="F13" s="171" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="G13" s="172" t="n">
+        <v>100</v>
+      </c>
+      <c r="H13" s="171" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="171" t="inlineStr">
+        <is>
+          <t>Swift Bike</t>
+        </is>
+      </c>
+      <c r="B14" s="171" t="inlineStr">
+        <is>
+          <t>WeBike</t>
+        </is>
+      </c>
+      <c r="C14" s="171" t="n">
+        <v>76</v>
+      </c>
+      <c r="D14" s="171" t="n">
+        <v>94</v>
+      </c>
+      <c r="E14" s="171" t="n">
+        <v>100</v>
+      </c>
+      <c r="F14" s="171" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="G14" s="172" t="n">
+        <v>100</v>
+      </c>
+      <c r="H14" s="171" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Blu Ruged Ballz</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>81</v>
+      </c>
+      <c r="D15" t="n">
+        <v>100</v>
+      </c>
+      <c r="E15" t="n">
+        <v>100</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="G15" s="159" t="n">
+        <v>100</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Blu Aero Ballz</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>70</v>
+      </c>
+      <c r="D16" t="n">
+        <v>86</v>
+      </c>
+      <c r="E16" t="n">
+        <v>100</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="G16" s="159" t="n">
+        <v>100</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Blu Tail Ballz</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>81</v>
+      </c>
+      <c r="D17" t="n">
+        <v>100</v>
+      </c>
+      <c r="E17" t="n">
+        <v>100</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="G17" s="159" t="n">
+        <v>100</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Blu Tube Ballz</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>70</v>
+      </c>
+      <c r="D18" t="n">
+        <v>86</v>
+      </c>
+      <c r="E18" t="n">
+        <v>100</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="G18" s="159" t="n">
+        <v>100</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Spoke'd Easy</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Spoke'd Up</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>100</v>
+      </c>
+      <c r="D19" t="n">
+        <v>100</v>
+      </c>
+      <c r="E19" t="n">
+        <v>100</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="G19" s="159" t="n">
+        <v>100</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Spoke'd Speed</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Spoke'd Up</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>73</v>
+      </c>
+      <c r="D20" t="n">
+        <v>91</v>
+      </c>
+      <c r="E20" t="n">
+        <v>100</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="G20" s="159" t="n">
+        <v>100</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>The Armstrong</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SpaceBikes</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>70</v>
+      </c>
+      <c r="D21" t="n">
+        <v>86</v>
+      </c>
+      <c r="E21" t="n">
+        <v>100</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="G21" s="159" t="n">
+        <v>100</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Mars Rover</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SpaceBikes</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>100</v>
+      </c>
+      <c r="D22" t="n">
+        <v>100</v>
+      </c>
+      <c r="E22" t="n">
+        <v>100</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="G22" s="159" t="n">
+        <v>100</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Whole MILC MKII</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>MILC Bikes</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>100</v>
+      </c>
+      <c r="D23" t="n">
+        <v>100</v>
+      </c>
+      <c r="E23" t="n">
+        <v>100</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="G23" s="159" t="n">
+        <v>100</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Skim MILC MKII</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>MILC Bikes</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>76</v>
+      </c>
+      <c r="D24" t="n">
+        <v>94</v>
+      </c>
+      <c r="E24" t="n">
+        <v>100</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="G24" s="159" t="n">
+        <v>100</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="166" t="inlineStr">
+        <is>
+          <t>INFERRED PRICE TIERS (cheapest first)</t>
+        </is>
+      </c>
+      <c r="B27" s="166" t="inlineStr">
+        <is>
+          <t>Rec</t>
+        </is>
+      </c>
+      <c r="C27" s="166" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="D27" s="166" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="E27" s="166" t="inlineStr">
+        <is>
+          <t>Brands at this price</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>tier 100</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>100</v>
+      </c>
+      <c r="C28" t="n">
+        <v>100</v>
+      </c>
+      <c r="D28" t="n">
+        <v>100</v>
+      </c>
+      <c r="E28" s="170" t="inlineStr">
+        <is>
+          <t>Spoke'd Easy (Spoke'd Up), Mars Rover (SpaceBikes), Whole MILC MKII (MILC Bikes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>tier 92</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>92</v>
+      </c>
+      <c r="C29" t="n">
+        <v>100</v>
+      </c>
+      <c r="D29" t="n">
+        <v>100</v>
+      </c>
+      <c r="E29" s="170" t="inlineStr">
+        <is>
+          <t>MountainCruise1 (Bike Bros)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>tier 85</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>85</v>
+      </c>
+      <c r="C30" t="n">
+        <v>100</v>
+      </c>
+      <c r="D30" t="n">
+        <v>100</v>
+      </c>
+      <c r="E30" s="170" t="inlineStr">
+        <is>
+          <t>LiteTrail Pro (LiteCycle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>tier 83</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>83</v>
+      </c>
+      <c r="C31" t="n">
+        <v>100</v>
+      </c>
+      <c r="D31" t="n">
+        <v>100</v>
+      </c>
+      <c r="E31" s="170" t="inlineStr">
+        <is>
+          <t>LiteSpeed+ (LiteCycle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>tier 82</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>82</v>
+      </c>
+      <c r="C32" t="n">
+        <v>100</v>
+      </c>
+      <c r="D32" t="n">
+        <v>100</v>
+      </c>
+      <c r="E32" s="170" t="inlineStr">
+        <is>
+          <t>TERRAMean (Bike Bros)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="173" t="inlineStr">
+        <is>
+          <t>tier 81</t>
+        </is>
+      </c>
+      <c r="B33" s="173" t="n">
+        <v>81</v>
+      </c>
+      <c r="C33" s="173" t="n">
+        <v>100</v>
+      </c>
+      <c r="D33" s="173" t="n">
+        <v>100</v>
+      </c>
+      <c r="E33" s="193" t="inlineStr">
+        <is>
+          <t>Hike Bike (WeBike), Blu Ruged Ballz (BB LLC), Blu Tail Ballz (BB LLC)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="173" t="inlineStr">
+        <is>
+          <t>tier 76</t>
+        </is>
+      </c>
+      <c r="B34" s="173" t="n">
+        <v>76</v>
+      </c>
+      <c r="C34" s="173" t="n">
+        <v>94</v>
+      </c>
+      <c r="D34" s="173" t="n">
+        <v>100</v>
+      </c>
+      <c r="E34" s="193" t="inlineStr">
+        <is>
+          <t>Swift Bike (WeBike), Skim MILC MKII (MILC Bikes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>tier 73</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>73</v>
+      </c>
+      <c r="C35" t="n">
+        <v>91</v>
+      </c>
+      <c r="D35" t="n">
+        <v>100</v>
+      </c>
+      <c r="E35" s="170" t="inlineStr">
+        <is>
+          <t>TERRAMAX (Bike Bros), Spoke'd Speed (Spoke'd Up)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>tier 73</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>73</v>
+      </c>
+      <c r="C36" t="n">
+        <v>90</v>
+      </c>
+      <c r="D36" t="n">
+        <v>100</v>
+      </c>
+      <c r="E36" s="170" t="inlineStr">
+        <is>
+          <t>LiteSpeed Pro+ (LiteCycle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>tier 70</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>70</v>
+      </c>
+      <c r="C37" t="n">
+        <v>86</v>
+      </c>
+      <c r="D37" t="n">
+        <v>100</v>
+      </c>
+      <c r="E37" s="170" t="inlineStr">
+        <is>
+          <t>Mach 0.6 (Bike Bros), Blu Aero Ballz (BB LLC), Blu Tube Ballz (BB LLC), The Armstrong (SpaceBikes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>tier 63</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>63</v>
+      </c>
+      <c r="C38" t="n">
+        <v>78</v>
+      </c>
+      <c r="D38" t="n">
+        <v>90</v>
+      </c>
+      <c r="E38" s="170" t="inlineStr">
+        <is>
+          <t>MACH I.I (Bike Bros)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="166" t="inlineStr">
+        <is>
+          <t>SEGMENT PRICE SENSITIVITY — resistance sets in at different tiers</t>
+        </is>
+      </c>
+      <c r="B41" s="166" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="C41" s="166" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="D41" s="166" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>tier 100 (cheapest)</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>100</v>
+      </c>
+      <c r="C42" t="n">
+        <v>100</v>
+      </c>
+      <c r="D42" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>tier 92</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>100</v>
+      </c>
+      <c r="C43" t="n">
+        <v>100</v>
+      </c>
+      <c r="D43" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>tier 85</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>100</v>
+      </c>
+      <c r="C44" t="n">
+        <v>100</v>
+      </c>
+      <c r="D44" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>tier 83</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>100</v>
+      </c>
+      <c r="C45" t="n">
+        <v>100</v>
+      </c>
+      <c r="D45" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>tier 82</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>100</v>
+      </c>
+      <c r="C46" t="n">
+        <v>100</v>
+      </c>
+      <c r="D46" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>tier 81  &lt;- Hike Bike</t>
+        </is>
+      </c>
+      <c r="B47" s="159" t="n">
+        <v>100</v>
+      </c>
+      <c r="C47" t="n">
+        <v>100</v>
+      </c>
+      <c r="D47" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>tier 76  &lt;- Swift Bike</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>94</v>
+      </c>
+      <c r="C48" s="159" t="n">
+        <v>100</v>
+      </c>
+      <c r="D48" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>tier 73</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>91</v>
+      </c>
+      <c r="C49" t="n">
+        <v>100</v>
+      </c>
+      <c r="D49" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>tier 70</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>86</v>
+      </c>
+      <c r="C50" s="159" t="n">
+        <v>100</v>
+      </c>
+      <c r="D50" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>tier 63 (most expensive)</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>78</v>
+      </c>
+      <c r="C51" s="167" t="n">
+        <v>90</v>
+      </c>
+      <c r="D51" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D52" s="174" t="inlineStr">
+        <is>
+          <t>SPEED is the least price-sensitive segment in the game - it tolerates every price up to tier 70 with zero resistance. MOUNTAIN starts resisting immediately below tier 81. RECREATION resists almost everything.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="166" t="inlineStr">
+        <is>
+          <t>HIKE BIKE — price is already optimal, hold it</t>
+        </is>
+      </c>
+      <c r="B55" s="166" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C55" s="166" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1365</v>
+      </c>
+      <c r="C56" s="170" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Mountain price judgment</t>
+        </is>
+      </c>
+      <c r="B57" s="159" t="n">
+        <v>100</v>
+      </c>
+      <c r="C57" s="170" t="inlineStr">
+        <is>
+          <t>ZERO price resistance</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Price tier</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>81</v>
+      </c>
+      <c r="C58" s="170" t="inlineStr">
+        <is>
+          <t>the HIGHEST-priced tier that still scores 100 in Mountain</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Next tier up (73)</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>91</v>
+      </c>
+      <c r="C59" s="170" t="inlineStr">
+        <is>
+          <t>TERRAMAX sits there and takes a 9-point hit</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+      <c r="C60" s="181" t="inlineStr">
+        <is>
+          <t>We are extracting the maximum price Mountain will bear without penalty. Raising it drops us into the resistance band. HOLD $1,365.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="166" t="inlineStr">
+        <is>
+          <t>SWIFT BIKE — we are UNDER-priced in Speed</t>
+        </is>
+      </c>
+      <c r="B63" s="166" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C63" s="166" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>1450</v>
+      </c>
+      <c r="C64" s="170" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Speed price judgment</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>100</v>
+      </c>
+      <c r="C65" s="170" t="inlineStr">
+        <is>
+          <t>zero resistance</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Our price tier</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>76</v>
+      </c>
+      <c r="C66" s="170" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Tier 70 brands (Armstrong, Blu Tube, Blu Aero, Mach 0.6)</t>
+        </is>
+      </c>
+      <c r="B67" s="159" t="n">
+        <v>100</v>
+      </c>
+      <c r="C67" s="170" t="inlineStr">
+        <is>
+          <t>priced ABOVE us and STILL score 100 in Speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>First tier with Speed resistance</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>63</v>
+      </c>
+      <c r="C68" s="170" t="inlineStr">
+        <is>
+          <t>only MACH I.I, at 90</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Headroom</t>
+        </is>
+      </c>
+      <c r="C69" s="170" t="inlineStr">
+        <is>
+          <t>roughly 1-2 price tiers before Speed resistance appears</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Estimated tier-70 price</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>1595</v>
+      </c>
+      <c r="C70" s="170" t="inlineStr">
+        <is>
+          <t>INFERRED - see the estimate note below</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Potential price increase</t>
+        </is>
+      </c>
+      <c r="B71">
+        <f>C70-C64</f>
+        <v/>
+      </c>
+      <c r="C71" s="170" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>On Q3 volume (215 units)</t>
+        </is>
+      </c>
+      <c r="B72" s="159">
+        <f>C71*215</f>
+        <v/>
+      </c>
+      <c r="C72" s="170" t="inlineStr">
+        <is>
+          <t>pure margin - no cost change</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>On a rebuilt Speed volume (say 400 units)</t>
+        </is>
+      </c>
+      <c r="B73" s="159">
+        <f>C71*400</f>
+        <v/>
+      </c>
+      <c r="C73" s="170" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>CAVEAT</t>
+        </is>
+      </c>
+      <c r="C74" s="174" t="inlineStr">
+        <is>
+          <t>The $1,595 figure is inferred from BB LLC's ~$1,480 average price across 4 brands, two of which appear to sit at our $1,365 tier. VERIFY against the actual price list before locking. The DIRECTION (we have room to raise) is solid; the exact number is not.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="166" t="inlineStr">
+        <is>
+          <t>THE BB LLC COMPARISON IS NOW AIRTIGHT</t>
+        </is>
+      </c>
+      <c r="B77" s="166" t="inlineStr">
+        <is>
+          <t>Hike Bike (WeBike)</t>
+        </is>
+      </c>
+      <c r="C77" s="166" t="inlineStr">
+        <is>
+          <t>Blu Ruged Ballz (BB LLC)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Brand judgment - Mountain</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>73</v>
+      </c>
+      <c r="C78" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Component recipe</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>56/73/1</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>56/73/1 (identical)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Price judgment</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>81 / 100 / 100</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>81 / 100 / 100 (identical)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Implied price</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>$1,365</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>$1,365 (same tier)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Mountain share</t>
+        </is>
+      </c>
+      <c r="B82" s="179" t="n">
+        <v>0.221</v>
+      </c>
+      <c r="C82" s="161" t="n">
+        <v>0.463</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Conclusion</t>
+        </is>
+      </c>
+      <c r="C83" s="174" t="inlineStr">
+        <is>
+          <t>Same product, same price, same price perception - and they take 2.1x our share. There is now no product or pricing explanation left. The entire gap is SUPPLY (we stocked out 33%), COVERAGE (14 store staff vs 14 but 7 web vs our 3) and ADS (24 regional vs our 19).</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="166" t="inlineStr">
+        <is>
+          <t>ANOTHER REASON TO SKIP RECREATION</t>
+        </is>
+      </c>
+      <c r="B86" s="166" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C86" s="166" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Hike Bike Recreation price judgment</t>
+        </is>
+      </c>
+      <c r="B87" s="167" t="n">
+        <v>81</v>
+      </c>
+      <c r="C87" s="170" t="inlineStr">
+        <is>
+          <t>Rec buyers resist our $1,365</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>All three Recreation brands</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>100</v>
+      </c>
+      <c r="C88" s="170" t="inlineStr">
+        <is>
+          <t>Spoke'd Easy, Mars Rover, Whole MILC - all at tier 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="C89" s="170" t="inlineStr">
+        <is>
+          <t>Recreation is the most price-sensitive segment AND the winning brands are the cheapest in the game. Entering would mean a low-price, low-margin product - the opposite of our 'profit margin leader' strategy. Combined with the 56-vs-76 brand judgment gap, Recreation stays parked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="166" t="inlineStr">
+        <is>
+          <t>Q4 PRICING ACTIONS</t>
+        </is>
+      </c>
+      <c r="B92" s="166" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Hike Bike</t>
+        </is>
+      </c>
+      <c r="B93" s="174" t="inlineStr">
+        <is>
+          <t>HOLD $1,365. Mountain judgment 100 and we sit at the top tier that achieves it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Swift Bike</t>
+        </is>
+      </c>
+      <c r="B94" s="174" t="inlineStr">
+        <is>
+          <t>RAISE. Speed tolerates 1-2 tiers above us with zero resistance. Verify the exact price list, then move toward the Armstrong / Blu Tube tier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Sequencing note</t>
+        </is>
+      </c>
+      <c r="B95" s="174" t="inlineStr">
+        <is>
+          <t>Raise the Swift Bike price in the SAME quarter we fix its design to 77 - better product plus a price the segment does not resist is the cleanest margin gain available.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Capacity note</t>
+        </is>
+      </c>
+      <c r="B96" s="174" t="inlineStr">
+        <is>
+          <t>A price rise also RELIEVES the capacity squeeze: more margin per unit on the same 24/day. If we cannot build 1,171 units, we should at least earn more on the ones we do build.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/quarters/Q3/Q3Data.xlsx
+++ b/quarters/Q3/Q3Data.xlsx
@@ -42,6 +42,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_Staffing" sheetId="34" state="visible" r:id="rId34"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_Web_Ops" sheetId="35" state="visible" r:id="rId35"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_Price_Judgment" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_Prices" sheetId="37" state="visible" r:id="rId37"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -626,7 +627,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="16"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="16"/>
   </cellStyleXfs>
-  <cellXfs count="194">
+  <cellXfs count="195">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -899,6 +900,9 @@
     <xf numFmtId="165" fontId="0" fillId="31" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="30" fillId="29" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -34479,6 +34483,1947 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J100"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" style="146" min="1" max="1"/>
+    <col width="24" customWidth="1" style="146" min="2" max="2"/>
+    <col width="26" customWidth="1" style="146" min="3" max="3"/>
+    <col width="62" customWidth="1" style="146" min="4" max="4"/>
+    <col width="34" customWidth="1" style="146" min="5" max="5"/>
+    <col width="14" customWidth="1" style="146" min="6" max="6"/>
+    <col width="14" customWidth="1" style="146" min="7" max="7"/>
+    <col width="14" customWidth="1" style="146" min="8" max="8"/>
+    <col width="14" customWidth="1" style="146" min="9" max="9"/>
+    <col width="14" customWidth="1" style="146" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="169" t="inlineStr">
+        <is>
+          <t>Competitors' Prices — World Market, Q3 actual</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="170" t="inlineStr">
+        <is>
+          <t>Actual price list. It confirms the price tiers inferred from price judgment: every tier maps to a distinct price, monotonically, across all 11 tiers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="166" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="B4" s="166" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C4" s="166" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="D4" s="166" t="inlineStr">
+        <is>
+          <t>Rebate</t>
+        </is>
+      </c>
+      <c r="E4" s="166" t="inlineStr">
+        <is>
+          <t>Net price</t>
+        </is>
+      </c>
+      <c r="F4" s="166" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="G4" s="166" t="inlineStr">
+        <is>
+          <t>Segment</t>
+        </is>
+      </c>
+      <c r="H4" s="166" t="inlineStr">
+        <is>
+          <t>Brand judgment</t>
+        </is>
+      </c>
+      <c r="I4" s="166" t="inlineStr">
+        <is>
+          <t>Price judgment</t>
+        </is>
+      </c>
+      <c r="J4" s="166" t="inlineStr">
+        <is>
+          <t>Price tier</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MACH I.I</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Bike Bros</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1749</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1749</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>77</v>
+      </c>
+      <c r="I5" s="167" t="n">
+        <v>90</v>
+      </c>
+      <c r="J5" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Blu Aero Ballz</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1580</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1580</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>74</v>
+      </c>
+      <c r="I6" s="159" t="n">
+        <v>100</v>
+      </c>
+      <c r="J6" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Blu Tube Ballz</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1580</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1580</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>76</v>
+      </c>
+      <c r="I7" s="159" t="n">
+        <v>100</v>
+      </c>
+      <c r="J7" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>The Armstrong</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SpaceBikes</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1580</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1580</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>76</v>
+      </c>
+      <c r="I8" s="159" t="n">
+        <v>100</v>
+      </c>
+      <c r="J8" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Mach 0.6</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Bike Bros</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1579</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1579</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>61</v>
+      </c>
+      <c r="I9" s="159" t="n">
+        <v>100</v>
+      </c>
+      <c r="J9" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>LiteSpeed Pro+</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>LiteCycle</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1515</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1515</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>77</v>
+      </c>
+      <c r="I10" s="159" t="n">
+        <v>100</v>
+      </c>
+      <c r="J10" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TERRAMAX</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Bike Bros</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1499</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1499</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>73</v>
+      </c>
+      <c r="I11" s="167" t="n">
+        <v>91</v>
+      </c>
+      <c r="J11" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Spoke'd Speed</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Spoke'd Up</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1499</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1499</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>75</v>
+      </c>
+      <c r="I12" s="159" t="n">
+        <v>100</v>
+      </c>
+      <c r="J12" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="171" t="inlineStr">
+        <is>
+          <t>Swift Bike</t>
+        </is>
+      </c>
+      <c r="B13" s="171" t="inlineStr">
+        <is>
+          <t>WeBike</t>
+        </is>
+      </c>
+      <c r="C13" s="171" t="n">
+        <v>1450</v>
+      </c>
+      <c r="D13" s="171" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="171" t="n">
+        <v>1450</v>
+      </c>
+      <c r="F13" s="171" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" s="171" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="H13" s="171" t="n">
+        <v>72</v>
+      </c>
+      <c r="I13" s="172" t="n">
+        <v>100</v>
+      </c>
+      <c r="J13" s="171" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Skim MILC MKII</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>MILC Bikes</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1450</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1450</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>76</v>
+      </c>
+      <c r="I14" s="159" t="n">
+        <v>100</v>
+      </c>
+      <c r="J14" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="171" t="inlineStr">
+        <is>
+          <t>Hike Bike</t>
+        </is>
+      </c>
+      <c r="B15" s="171" t="inlineStr">
+        <is>
+          <t>WeBike</t>
+        </is>
+      </c>
+      <c r="C15" s="171" t="n">
+        <v>1365</v>
+      </c>
+      <c r="D15" s="171" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="171" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F15" s="171" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="171" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="H15" s="171" t="n">
+        <v>73</v>
+      </c>
+      <c r="I15" s="172" t="n">
+        <v>100</v>
+      </c>
+      <c r="J15" s="171" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Blu Ruged Ballz</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1365</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>73</v>
+      </c>
+      <c r="I16" s="159" t="n">
+        <v>100</v>
+      </c>
+      <c r="J16" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Blu Tail Ballz</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1365</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F17" t="n">
+        <v>4</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>70</v>
+      </c>
+      <c r="I17" s="159" t="n">
+        <v>100</v>
+      </c>
+      <c r="J17" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TERRAMean</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Bike Bros</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1349</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1349</v>
+      </c>
+      <c r="F18" t="n">
+        <v>4</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>72</v>
+      </c>
+      <c r="I18" s="159" t="n">
+        <v>100</v>
+      </c>
+      <c r="J18" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>LiteSpeed+</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>LiteCycle</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1325</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1325</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>74</v>
+      </c>
+      <c r="I19" s="159" t="n">
+        <v>100</v>
+      </c>
+      <c r="J19" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>LiteTrail Pro</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>LiteCycle</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F20" t="n">
+        <v>3</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>70</v>
+      </c>
+      <c r="I20" s="159" t="n">
+        <v>100</v>
+      </c>
+      <c r="J20" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>MountainCruise1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Bike Bros</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1199</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1199</v>
+      </c>
+      <c r="F21" t="n">
+        <v>5</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>76</v>
+      </c>
+      <c r="I21" s="167" t="n">
+        <v>92</v>
+      </c>
+      <c r="J21" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Mars Rover</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SpaceBikes</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1100</v>
+      </c>
+      <c r="D22" t="n">
+        <v>50</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>73</v>
+      </c>
+      <c r="I22" s="159" t="n">
+        <v>100</v>
+      </c>
+      <c r="J22" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Spoke'd Easy</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Spoke'd Up</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>999</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>999</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>73</v>
+      </c>
+      <c r="I23" s="159" t="n">
+        <v>100</v>
+      </c>
+      <c r="J23" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Whole MILC MKII</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>MILC Bikes</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1050</v>
+      </c>
+      <c r="D24" t="n">
+        <v>100</v>
+      </c>
+      <c r="E24" t="n">
+        <v>950</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>74</v>
+      </c>
+      <c r="I24" s="159" t="n">
+        <v>100</v>
+      </c>
+      <c r="J24" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="166" t="inlineStr">
+        <is>
+          <t>TIER VALIDATION — inferred tier vs actual net price</t>
+        </is>
+      </c>
+      <c r="B27" s="166" t="inlineStr">
+        <is>
+          <t>Net price range</t>
+        </is>
+      </c>
+      <c r="C27" s="166" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="D27" s="166" t="inlineStr">
+        <is>
+          <t>Brands</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>tier 100</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>950 - 1,050</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>100</v>
+      </c>
+      <c r="D28" s="170" t="inlineStr">
+        <is>
+          <t>Spoke'd Easy, Mars Rover, Whole MILC MKII</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>tier 92</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1,199 - 1,199</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="170" t="inlineStr">
+        <is>
+          <t>MountainCruise1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>tier 85</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1,300 - 1,300</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="170" t="inlineStr">
+        <is>
+          <t>LiteTrail Pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>tier 83</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1,325 - 1,325</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="170" t="inlineStr">
+        <is>
+          <t>LiteSpeed+</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>tier 82</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1,349 - 1,349</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="170" t="inlineStr">
+        <is>
+          <t>TERRAMean</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>tier 81</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>1,365 - 1,365</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="170" t="inlineStr">
+        <is>
+          <t>Hike Bike, Blu Ruged Ballz, Blu Tail Ballz</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>tier 76</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>1,450 - 1,450</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="170" t="inlineStr">
+        <is>
+          <t>Swift Bike, Skim MILC MKII</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>tier 73</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1,499 - 1,515</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>16</v>
+      </c>
+      <c r="D35" s="170" t="inlineStr">
+        <is>
+          <t>TERRAMAX, LiteSpeed Pro+, Spoke'd Speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>tier 70</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1,579 - 1,580</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="170" t="inlineStr">
+        <is>
+          <t>Mach 0.6, Blu Aero Ballz, Blu Tube Ballz, The Armstrong</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>tier 63</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1,749 - 1,749</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="170" t="inlineStr">
+        <is>
+          <t>MACH I.I</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="D38" s="181" t="inlineStr">
+        <is>
+          <t>Perfectly monotonic. Identical price judgment DID mean identical price in every case. Our earlier $1,595 estimate for tier 70 came in at $1,580 - off by $15 (0.9%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="166" t="inlineStr">
+        <is>
+          <t>SPEED PRICE LADDER — we are nearly the cheapest</t>
+        </is>
+      </c>
+      <c r="B41" s="166" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="C41" s="166" t="inlineStr">
+        <is>
+          <t>Brand judgment</t>
+        </is>
+      </c>
+      <c r="D41" s="166" t="inlineStr">
+        <is>
+          <t>Price judgment</t>
+        </is>
+      </c>
+      <c r="E41" s="166" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>MACH I.I</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1749</v>
+      </c>
+      <c r="C42" t="n">
+        <v>77</v>
+      </c>
+      <c r="D42" t="n">
+        <v>90</v>
+      </c>
+      <c r="E42" s="170" t="inlineStr">
+        <is>
+          <t>only Speed brand with price resistance</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Blu Aero Ballz</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1580</v>
+      </c>
+      <c r="C43" t="n">
+        <v>74</v>
+      </c>
+      <c r="D43" t="n">
+        <v>100</v>
+      </c>
+      <c r="E43" s="170" t="inlineStr">
+        <is>
+          <t>highest price with ZERO resistance</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Blu Tube Ballz</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1580</v>
+      </c>
+      <c r="C44" t="n">
+        <v>76</v>
+      </c>
+      <c r="D44" t="n">
+        <v>100</v>
+      </c>
+      <c r="E44" s="170" t="inlineStr">
+        <is>
+          <t>highest price with ZERO resistance</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>The Armstrong</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1580</v>
+      </c>
+      <c r="C45" t="n">
+        <v>76</v>
+      </c>
+      <c r="D45" t="n">
+        <v>100</v>
+      </c>
+      <c r="E45" s="170" t="inlineStr">
+        <is>
+          <t>highest price with ZERO resistance</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Mach 0.6</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1579</v>
+      </c>
+      <c r="C46" t="n">
+        <v>61</v>
+      </c>
+      <c r="D46" t="n">
+        <v>100</v>
+      </c>
+      <c r="E46" s="170" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>LiteSpeed Pro+</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1515</v>
+      </c>
+      <c r="C47" t="n">
+        <v>77</v>
+      </c>
+      <c r="D47" t="n">
+        <v>100</v>
+      </c>
+      <c r="E47" s="170" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Spoke'd Speed</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1499</v>
+      </c>
+      <c r="C48" t="n">
+        <v>75</v>
+      </c>
+      <c r="D48" t="n">
+        <v>100</v>
+      </c>
+      <c r="E48" s="170" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="171" t="inlineStr">
+        <is>
+          <t>Swift Bike</t>
+        </is>
+      </c>
+      <c r="B49" s="171" t="n">
+        <v>1450</v>
+      </c>
+      <c r="C49" s="171" t="n">
+        <v>72</v>
+      </c>
+      <c r="D49" s="171" t="n">
+        <v>100</v>
+      </c>
+      <c r="E49" s="194" t="inlineStr">
+        <is>
+          <t>OURS - 2nd cheapest, 2nd worst product</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Skim MILC MKII</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1450</v>
+      </c>
+      <c r="C50" t="n">
+        <v>76</v>
+      </c>
+      <c r="D50" t="n">
+        <v>100</v>
+      </c>
+      <c r="E50" s="170" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>LiteSpeed+</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1325</v>
+      </c>
+      <c r="C51" t="n">
+        <v>74</v>
+      </c>
+      <c r="D51" t="n">
+        <v>100</v>
+      </c>
+      <c r="E51" s="170" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="166" t="inlineStr">
+        <is>
+          <t>SWIFT BIKE PRICE MOVE — now precise</t>
+        </is>
+      </c>
+      <c r="B54" s="166" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C54" s="166" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Current price</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1450</v>
+      </c>
+      <c r="C55" s="170" t="inlineStr">
+        <is>
+          <t>2nd cheapest of 10 Speed brands</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Speed median price</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1547</v>
+      </c>
+      <c r="C56" s="170" t="inlineStr">
+        <is>
+          <t>we sit $97 below the median</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Highest price with ZERO Speed resistance</t>
+        </is>
+      </c>
+      <c r="B57" s="159" t="n">
+        <v>1580</v>
+      </c>
+      <c r="C57" s="170" t="inlineStr">
+        <is>
+          <t>Mach 0.6, Blu Aero, Blu Tube, The Armstrong</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>First price WITH resistance</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1749</v>
+      </c>
+      <c r="C58" s="170" t="inlineStr">
+        <is>
+          <t>MACH I.I, judgment 90</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Safe increase</t>
+        </is>
+      </c>
+      <c r="B59" s="159">
+        <f>C57-C55</f>
+        <v/>
+      </c>
+      <c r="C59" s="170" t="inlineStr">
+        <is>
+          <t>proven safe by four rival brands</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>On Q3 volume (215 units)</t>
+        </is>
+      </c>
+      <c r="B60" s="159">
+        <f>C59*215</f>
+        <v/>
+      </c>
+      <c r="C60" s="170" t="inlineStr">
+        <is>
+          <t>pure margin, no cost change</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>On a rebuilt Speed volume (400 units)</t>
+        </is>
+      </c>
+      <c r="B61" s="159">
+        <f>C59*400</f>
+        <v/>
+      </c>
+      <c r="C61" s="170" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Untested zone</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>1,581 - 1,748</t>
+        </is>
+      </c>
+      <c r="C62" s="170" t="inlineStr">
+        <is>
+          <t>nobody prices here, so resistance onset is unknown. $1,580 is the evidence-backed target.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="166" t="inlineStr">
+        <is>
+          <t>HIKE BIKE — confirmed at the Mountain ceiling</t>
+        </is>
+      </c>
+      <c r="B65" s="166" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="C65" s="166" t="inlineStr">
+        <is>
+          <t>Mountain price judgment</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>LiteTrail Pro</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>1300</v>
+      </c>
+      <c r="C66" s="170" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>LiteSpeed+ (Speed brand)</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>1325</v>
+      </c>
+      <c r="C67" s="170" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>TERRAMean</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>1349</v>
+      </c>
+      <c r="C68" s="170" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Hike Bike / Blu Ruged Ballz / Blu Tail Ballz</t>
+        </is>
+      </c>
+      <c r="B69" s="159" t="n">
+        <v>1365</v>
+      </c>
+      <c r="C69" s="181" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Swift Bike / Skim MILC (tier above)</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>1450</v>
+      </c>
+      <c r="C70" s="185" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>TERRAMAX</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>1499</v>
+      </c>
+      <c r="C71" s="170" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="C72" s="170" t="inlineStr">
+        <is>
+          <t>Mountain resistance begins somewhere between $1,365 and $1,450. We sit at the top of the clean band. HOLD $1,365 - the $85 of untested space is not worth risking a judgment drop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="166" t="inlineStr">
+        <is>
+          <t>CONTRIBUTION PER UNIT — matters now that capacity binds</t>
+        </is>
+      </c>
+      <c r="B75" s="166" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="C75" s="166" t="inlineStr">
+        <is>
+          <t>Q3 unit cost</t>
+        </is>
+      </c>
+      <c r="D75" s="166" t="inlineStr">
+        <is>
+          <t>Contribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Hike Bike</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>1365</v>
+      </c>
+      <c r="C76" t="n">
+        <v>618</v>
+      </c>
+      <c r="D76" s="170">
+        <f>B76-C76</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Swift Bike (today)</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>1450</v>
+      </c>
+      <c r="C77" t="n">
+        <v>694</v>
+      </c>
+      <c r="D77" s="170">
+        <f>B77-C77</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Swift Bike at $1,580</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>1580</v>
+      </c>
+      <c r="C78" t="n">
+        <v>694</v>
+      </c>
+      <c r="D78" s="181">
+        <f>B78-C78</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Swift Bike at $1,580 with 14-speed gears</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>1580</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="D79" s="170" t="inlineStr">
+        <is>
+          <t>higher still</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D80" s="174" t="inlineStr">
+        <is>
+          <t>At $1,580 Swift Bike becomes our MOST profitable unit ($886 vs Hike Bike's $747). Switching it to 14-speed (the design fix) should cut its cost too, widening the gap further.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="166" t="inlineStr">
+        <is>
+          <t>PRIORITY FIELD — a lever we have not thought about</t>
+        </is>
+      </c>
+      <c r="B83" s="166" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C83" s="166" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Our priority order</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>1 Hike Bike, 2 Swift Bike</t>
+        </is>
+      </c>
+      <c r="C84" s="170" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Q3 stock-out by brand</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Hike Bike 134/412 = 32.5%</t>
+        </is>
+      </c>
+      <c r="C85" s="170" t="inlineStr">
+        <is>
+          <t>Swift Bike 70/215 = 32.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="C86" s="170" t="inlineStr">
+        <is>
+          <t>Both brands lost almost exactly the same percentage, so priority 1 did NOT shield Hike Bike in Q3. Treat the mechanism as unverified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Why it matters in Q4</t>
+        </is>
+      </c>
+      <c r="C87" s="174" t="inlineStr">
+        <is>
+          <t>Capacity is now binding (see Q4_Planner). If we cannot build all demand, the priority order decides the mix. After the price rise, Swift Bike earns $886/unit vs Hike Bike's $747 - so a pure margin view argues for promoting Swift Bike.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Counter-argument</t>
+        </is>
+      </c>
+      <c r="C88" s="174" t="inlineStr">
+        <is>
+          <t>Mountain is our PRIMARY segment for the Balanced Scorecard's Market Performance, and we hold 22.1% there vs 7.5% in Speed. Starving Hike Bike would hurt the scorecard even if it helps the income statement. Decide deliberately - do not leave it on default.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Rebates</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>we use 0</t>
+        </is>
+      </c>
+      <c r="C89" s="170" t="inlineStr">
+        <is>
+          <t>Only the two Recreation leaders rebate: Mars Rover $50, Whole MILC $100. Rebates appear to be a Recreation/price-sensitive tool - no reason for us to start.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="166" t="inlineStr">
+        <is>
+          <t>HOW RIVALS PRICE BY SEGMENT — the pattern to copy</t>
+        </is>
+      </c>
+      <c r="B92" s="166" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="C92" s="166" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="D92" s="166" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>$1,365</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>$1,580</t>
+        </is>
+      </c>
+      <c r="D93" s="170" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>SpaceBikes</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>$1,580</t>
+        </is>
+      </c>
+      <c r="D94" s="170" t="inlineStr">
+        <is>
+          <t>$1,050 net</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>MILC Bikes</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>$1,450</t>
+        </is>
+      </c>
+      <c r="D95" s="170" t="inlineStr">
+        <is>
+          <t>$950 net</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>LiteCycle</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>$1,300</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>$1,325 - $1,515</t>
+        </is>
+      </c>
+      <c r="D96" s="170" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Bike Bros</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>$1,349 - $1,499</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>$1,579 - $1,749</t>
+        </is>
+      </c>
+      <c r="D97" s="170" t="inlineStr">
+        <is>
+          <t>$1,199</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Spoke'd Up</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>$1,499</t>
+        </is>
+      </c>
+      <c r="D98" s="170" t="inlineStr">
+        <is>
+          <t>$999</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="171" t="inlineStr">
+        <is>
+          <t>WeBike</t>
+        </is>
+      </c>
+      <c r="B99" s="171" t="inlineStr">
+        <is>
+          <t>$1,365</t>
+        </is>
+      </c>
+      <c r="C99" s="171" t="inlineStr">
+        <is>
+          <t>$1,450</t>
+        </is>
+      </c>
+      <c r="D99" s="194" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D100" s="174" t="inlineStr">
+        <is>
+          <t>The strong firms price Speed $200+ above Mountain and Recreation far below. BB LLC is the cleanest example: identical Mountain price to ours, Speed $215 higher. We copied their Mountain price correctly and missed their Speed price entirely.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/quarters/Q3/Q3Data.xlsx
+++ b/quarters/Q3/Q3Data.xlsx
@@ -43,6 +43,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_Web_Ops" sheetId="35" state="visible" r:id="rId35"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_Price_Judgment" sheetId="36" state="visible" r:id="rId36"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_Prices" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_Ad_Judgment" sheetId="38" state="visible" r:id="rId38"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -51,9 +52,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
   </numFmts>
   <fonts count="31">
     <font>
@@ -627,7 +629,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="16"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="16"/>
   </cellStyleXfs>
-  <cellXfs count="195">
+  <cellXfs count="199">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -905,6 +907,10 @@
     <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="28" fillId="33" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="31" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="28" fillId="29" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -36424,6 +36430,1558 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I84"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" style="146" min="1" max="1"/>
+    <col width="22" customWidth="1" style="146" min="2" max="2"/>
+    <col width="22" customWidth="1" style="146" min="3" max="3"/>
+    <col width="62" customWidth="1" style="146" min="4" max="4"/>
+    <col width="40" customWidth="1" style="146" min="5" max="5"/>
+    <col width="15" customWidth="1" style="146" min="6" max="6"/>
+    <col width="15" customWidth="1" style="146" min="7" max="7"/>
+    <col width="15" customWidth="1" style="146" min="8" max="8"/>
+    <col width="15" customWidth="1" style="146" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="169" t="inlineStr">
+        <is>
+          <t>Ad Judgment — World Market, Q3 actual</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="170" t="inlineStr">
+        <is>
+          <t>HikeBike 1 is essentially best-in-class (80 vs BB LLC's 81). The Swift Bike ad is 8th of 9 Speed ads and shows by far the highest off-target appeal in the industry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="166" t="inlineStr">
+        <is>
+          <t>Ad</t>
+        </is>
+      </c>
+      <c r="B4" s="166" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C4" s="166" t="inlineStr">
+        <is>
+          <t>Brand advertised</t>
+        </is>
+      </c>
+      <c r="D4" s="166" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="E4" s="166" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="F4" s="166" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="G4" s="166" t="inlineStr">
+        <is>
+          <t>Target segment</t>
+        </is>
+      </c>
+      <c r="H4" s="166" t="inlineStr">
+        <is>
+          <t>Score in target</t>
+        </is>
+      </c>
+      <c r="I4" s="166" t="inlineStr">
+        <is>
+          <t>Off-target leakage</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Excluspeedity</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Bike Bros</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>MACH I.I</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F5" t="n">
+        <v>72</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>72</v>
+      </c>
+      <c r="I5" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TerraTech</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Bike Bros</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>TERRAMAX</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>23</v>
+      </c>
+      <c r="E6" t="n">
+        <v>78</v>
+      </c>
+      <c r="F6" t="n">
+        <v>30</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>78</v>
+      </c>
+      <c r="I6" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Easy Rider</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Bike Bros</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>MountainCruise1</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>75</v>
+      </c>
+      <c r="E7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F7" t="n">
+        <v>17</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>75</v>
+      </c>
+      <c r="I7" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Mountainability</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Bike Bros</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>TERRAMAX</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>35</v>
+      </c>
+      <c r="E8" t="n">
+        <v>77</v>
+      </c>
+      <c r="F8" t="n">
+        <v>32</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>77</v>
+      </c>
+      <c r="I8" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AndStill</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Bike Bros</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>MACH I.I</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>22</v>
+      </c>
+      <c r="E9" t="n">
+        <v>24</v>
+      </c>
+      <c r="F9" t="n">
+        <v>78</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>78</v>
+      </c>
+      <c r="I9" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Speed of Lite 1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>LiteCycle</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>LiteSpeed Pro+</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" t="n">
+        <v>22</v>
+      </c>
+      <c r="F10" t="n">
+        <v>77</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>77</v>
+      </c>
+      <c r="I10" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Speed of Lite 2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>LiteCycle</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>LiteSpeed+</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>16</v>
+      </c>
+      <c r="E11" t="n">
+        <v>13</v>
+      </c>
+      <c r="F11" t="n">
+        <v>73</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>73</v>
+      </c>
+      <c r="I11" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Trail Blazing 1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>LiteCycle</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>LiteTrail Pro</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>18</v>
+      </c>
+      <c r="E12" t="n">
+        <v>79</v>
+      </c>
+      <c r="F12" t="n">
+        <v>34</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>79</v>
+      </c>
+      <c r="I12" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="171" t="inlineStr">
+        <is>
+          <t>HikeBike 1</t>
+        </is>
+      </c>
+      <c r="B13" s="171" t="inlineStr">
+        <is>
+          <t>WeBike</t>
+        </is>
+      </c>
+      <c r="C13" s="171" t="inlineStr">
+        <is>
+          <t>Hike Bike</t>
+        </is>
+      </c>
+      <c r="D13" s="171" t="n">
+        <v>33</v>
+      </c>
+      <c r="E13" s="171" t="n">
+        <v>80</v>
+      </c>
+      <c r="F13" s="171" t="n">
+        <v>26</v>
+      </c>
+      <c r="G13" s="171" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="H13" s="171" t="n">
+        <v>80</v>
+      </c>
+      <c r="I13" s="171" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="171" t="inlineStr">
+        <is>
+          <t>Swift Bike</t>
+        </is>
+      </c>
+      <c r="B14" s="171" t="inlineStr">
+        <is>
+          <t>WeBike</t>
+        </is>
+      </c>
+      <c r="C14" s="171" t="inlineStr">
+        <is>
+          <t>Swift Bike</t>
+        </is>
+      </c>
+      <c r="D14" s="171" t="n">
+        <v>52</v>
+      </c>
+      <c r="E14" s="171" t="n">
+        <v>36</v>
+      </c>
+      <c r="F14" s="171" t="n">
+        <v>70</v>
+      </c>
+      <c r="G14" s="171" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="H14" s="171" t="n">
+        <v>70</v>
+      </c>
+      <c r="I14" s="171" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>BB Big Momma</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Blu Ruged Ballz</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>28</v>
+      </c>
+      <c r="E15" t="n">
+        <v>81</v>
+      </c>
+      <c r="F15" t="n">
+        <v>27</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>81</v>
+      </c>
+      <c r="I15" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Unleash lil pap</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Blu Tube Ballz</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>15</v>
+      </c>
+      <c r="E16" t="n">
+        <v>16</v>
+      </c>
+      <c r="F16" t="n">
+        <v>76</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>76</v>
+      </c>
+      <c r="I16" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Spoke'd Easy</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Spoke'd Up</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Spoke'd Easy</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>59</v>
+      </c>
+      <c r="E17" t="n">
+        <v>27</v>
+      </c>
+      <c r="F17" t="n">
+        <v>21</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>59</v>
+      </c>
+      <c r="I17" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Spoke'd Speed</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Spoke'd Up</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Spoke'd Speed</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E18" t="n">
+        <v>18</v>
+      </c>
+      <c r="F18" t="n">
+        <v>57</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>57</v>
+      </c>
+      <c r="I18" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>The Armstrong 1</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SpaceBikes</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>The Armstrong</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>21</v>
+      </c>
+      <c r="F19" t="n">
+        <v>77</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>77</v>
+      </c>
+      <c r="I19" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Mars Rover 1</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>SpaceBikes</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Mars Rover</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>79</v>
+      </c>
+      <c r="E20" t="n">
+        <v>25</v>
+      </c>
+      <c r="F20" t="n">
+        <v>24</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>79</v>
+      </c>
+      <c r="I20" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Skim MILC MKII</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>MILC Bikes</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Skim MILC MKII</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="n">
+        <v>19</v>
+      </c>
+      <c r="F21" t="n">
+        <v>75</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>75</v>
+      </c>
+      <c r="I21" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Whole MILC MKII</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>MILC Bikes</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Whole MILC MKII</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>77</v>
+      </c>
+      <c r="E22" t="n">
+        <v>47</v>
+      </c>
+      <c r="F22" t="n">
+        <v>41</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>77</v>
+      </c>
+      <c r="I22" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="166" t="inlineStr">
+        <is>
+          <t>SPEED AD LADDER</t>
+        </is>
+      </c>
+      <c r="B25" s="166" t="inlineStr">
+        <is>
+          <t>Speed score</t>
+        </is>
+      </c>
+      <c r="C25" s="166" t="inlineStr">
+        <is>
+          <t>Off-target leakage</t>
+        </is>
+      </c>
+      <c r="D25" s="166" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>AndStill (Bike Bros)</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>78</v>
+      </c>
+      <c r="C26" t="n">
+        <v>46</v>
+      </c>
+      <c r="D26" s="170" t="inlineStr">
+        <is>
+          <t>BEST Speed ad in the industry</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Speed of Lite 1 (LiteCycle)</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>77</v>
+      </c>
+      <c r="C27" t="n">
+        <v>32</v>
+      </c>
+      <c r="D27" s="170" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>The Armstrong 1 (SpaceBikes)</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>77</v>
+      </c>
+      <c r="C28" t="n">
+        <v>23</v>
+      </c>
+      <c r="D28" s="170" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Unleash lil pap (BB LLC)</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>76</v>
+      </c>
+      <c r="C29" t="n">
+        <v>31</v>
+      </c>
+      <c r="D29" s="170" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Skim MILC MKII (MILC Bikes)</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>75</v>
+      </c>
+      <c r="C30" t="n">
+        <v>29</v>
+      </c>
+      <c r="D30" s="170" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Speed of Lite 2 (LiteCycle)</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>73</v>
+      </c>
+      <c r="C31" t="n">
+        <v>29</v>
+      </c>
+      <c r="D31" s="170" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Excluspeedity (Bike Bros)</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>72</v>
+      </c>
+      <c r="C32" t="n">
+        <v>12</v>
+      </c>
+      <c r="D32" s="170" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="171" t="inlineStr">
+        <is>
+          <t>Swift Bike (WeBike)</t>
+        </is>
+      </c>
+      <c r="B33" s="188" t="n">
+        <v>70</v>
+      </c>
+      <c r="C33" s="188" t="n">
+        <v>88</v>
+      </c>
+      <c r="D33" s="194" t="inlineStr">
+        <is>
+          <t>OURS - 8th of 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Spoke'd Speed (Spoke'd Up)</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>57</v>
+      </c>
+      <c r="C34" t="n">
+        <v>22</v>
+      </c>
+      <c r="D34" s="170" t="inlineStr">
+        <is>
+          <t>worst; drags Spoke'd Up to last on Marketing Effectiveness</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="166" t="inlineStr">
+        <is>
+          <t>MOUNTAIN AD LADDER</t>
+        </is>
+      </c>
+      <c r="B37" s="166" t="inlineStr">
+        <is>
+          <t>Mountain score</t>
+        </is>
+      </c>
+      <c r="C37" s="166" t="inlineStr">
+        <is>
+          <t>Off-target leakage</t>
+        </is>
+      </c>
+      <c r="D37" s="166" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>BB Big Momma (BB LLC)</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>81</v>
+      </c>
+      <c r="C38" t="n">
+        <v>55</v>
+      </c>
+      <c r="D38" s="170" t="inlineStr">
+        <is>
+          <t>BEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="171" t="inlineStr">
+        <is>
+          <t>HikeBike 1 (WeBike)</t>
+        </is>
+      </c>
+      <c r="B39" s="172" t="n">
+        <v>80</v>
+      </c>
+      <c r="C39" s="171" t="n">
+        <v>59</v>
+      </c>
+      <c r="D39" s="194" t="inlineStr">
+        <is>
+          <t>OURS - 1 point off best</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trail Blazing 1 (LiteCycle)</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>79</v>
+      </c>
+      <c r="C40" t="n">
+        <v>52</v>
+      </c>
+      <c r="D40" s="170" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>TerraTech (Bike Bros)</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>78</v>
+      </c>
+      <c r="C41" t="n">
+        <v>53</v>
+      </c>
+      <c r="D41" s="170" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Mountainability (Bike Bros)</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>77</v>
+      </c>
+      <c r="C42" t="n">
+        <v>67</v>
+      </c>
+      <c r="D42" s="170" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="166" t="inlineStr">
+        <is>
+          <t>MARKETING EFFECTIVENESS — formula verified against 3 reported values</t>
+        </is>
+      </c>
+      <c r="B45" s="166" t="inlineStr">
+        <is>
+          <t>Avg brand</t>
+        </is>
+      </c>
+      <c r="C45" s="166" t="inlineStr">
+        <is>
+          <t>Avg ad</t>
+        </is>
+      </c>
+      <c r="D45" s="166" t="inlineStr">
+        <is>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="E45" s="166" t="inlineStr">
+        <is>
+          <t>Reported</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="C46" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="D46" s="195" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="E46" s="170" t="n">
+        <v>0.765</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>SpaceBikes</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="C47" t="n">
+        <v>78</v>
+      </c>
+      <c r="D47" s="195" t="n">
+        <v>0.7625</v>
+      </c>
+      <c r="E47" s="170" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>MILC Bikes</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>75</v>
+      </c>
+      <c r="C48" t="n">
+        <v>76</v>
+      </c>
+      <c r="D48" s="195" t="n">
+        <v>0.755</v>
+      </c>
+      <c r="E48" s="170" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="171" t="inlineStr">
+        <is>
+          <t>WeBike</t>
+        </is>
+      </c>
+      <c r="B49" s="171" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="C49" s="171" t="n">
+        <v>75</v>
+      </c>
+      <c r="D49" s="196" t="n">
+        <v>0.7375</v>
+      </c>
+      <c r="E49" s="194" t="n">
+        <v>0.738</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Spoke'd Up</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>74</v>
+      </c>
+      <c r="C50" t="n">
+        <v>58</v>
+      </c>
+      <c r="D50" s="195" t="n">
+        <v>0.6599999999999999</v>
+      </c>
+      <c r="E50" s="170" t="n">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="E51" s="181" t="inlineStr">
+        <is>
+          <t>Industry min 0.660 (Spoke'd Up) and max 0.765 (BB LLC) both reproduce exactly, as does our 0.738. Formula confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="166" t="inlineStr">
+        <is>
+          <t>FIXING SWIFT BIKE — the Marketing Effectiveness payoff</t>
+        </is>
+      </c>
+      <c r="B54" s="166" t="inlineStr">
+        <is>
+          <t>Brand judgment</t>
+        </is>
+      </c>
+      <c r="C54" s="166" t="inlineStr">
+        <is>
+          <t>Ad judgment</t>
+        </is>
+      </c>
+      <c r="D54" s="166" t="inlineStr">
+        <is>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="E54" s="166" t="inlineStr">
+        <is>
+          <t>vs industry max 0.765</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Q3 actual</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>72</v>
+      </c>
+      <c r="C55" t="n">
+        <v>70</v>
+      </c>
+      <c r="D55" s="197" t="n">
+        <v>0.7375</v>
+      </c>
+      <c r="E55" s="170" t="inlineStr">
+        <is>
+          <t>below average (0.743)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Fix ad only</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>72</v>
+      </c>
+      <c r="C56" t="n">
+        <v>77</v>
+      </c>
+      <c r="D56" s="195" t="n">
+        <v>0.755</v>
+      </c>
+      <c r="E56" s="170" t="inlineStr">
+        <is>
+          <t>3rd best</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Fix brand only (14-speed + decals)</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>77</v>
+      </c>
+      <c r="C57" t="n">
+        <v>70</v>
+      </c>
+      <c r="D57" s="195" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E57" s="170" t="inlineStr">
+        <is>
+          <t>4th best</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>FIX BOTH</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>77</v>
+      </c>
+      <c r="C58" t="n">
+        <v>77</v>
+      </c>
+      <c r="D58" s="198" t="n">
+        <v>0.7675</v>
+      </c>
+      <c r="E58" s="181" t="inlineStr">
+        <is>
+          <t>NEW INDUSTRY BEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="166" t="inlineStr">
+        <is>
+          <t>DIAGNOSIS — the Swift Bike ad is unfocused</t>
+        </is>
+      </c>
+      <c r="B61" s="166" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C61" s="166" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Our Swift Bike ad: Recreation score</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>52</v>
+      </c>
+      <c r="C62" s="170" t="inlineStr">
+        <is>
+          <t>highest Rec score of ANY Speed ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Our Swift Bike ad: Mountain score</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>36</v>
+      </c>
+      <c r="C63" s="170" t="inlineStr">
+        <is>
+          <t>highest Mtn score of ANY Speed ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Total off-target leakage</t>
+        </is>
+      </c>
+      <c r="B64" s="167" t="n">
+        <v>88</v>
+      </c>
+      <c r="C64" s="170" t="inlineStr">
+        <is>
+          <t>next highest is AndStill at 46; The Armstrong 1 is just 23</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Leading Speed ads for comparison</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Rec 2-22, Mtn 13-24</t>
+        </is>
+      </c>
+      <c r="C65" s="170" t="inlineStr">
+        <is>
+          <t>The Armstrong 1 scores Rec 2 - almost zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Hypothesis</t>
+        </is>
+      </c>
+      <c r="C66" s="174" t="inlineStr">
+        <is>
+          <t>The ad appears to carry Mountain- and Recreation-flavoured benefit claims rather than Speed-specific ones. This MIRRORS the component error: Swift Bike inherited Hike Bike's 24-speed drivetrain AND, it seems, Hike Bike's messaging. Same root cause - we cloned our Mountain assets into a Speed launch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>CAUTION</t>
+        </is>
+      </c>
+      <c r="C67" s="174" t="inlineStr">
+        <is>
+          <t>Leakage does NOT cleanly predict score across the field (AndStill leaks 46 and scores best), so this is a strong hypothesis, not a solved model like the component analysis. Rebuild the ad around Speed cues and re-test in the ad designer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="166" t="inlineStr">
+        <is>
+          <t>AD PORTFOLIO PATTERNS</t>
+        </is>
+      </c>
+      <c r="B70" s="166" t="inlineStr">
+        <is>
+          <t>Ads</t>
+        </is>
+      </c>
+      <c r="C70" s="166" t="inlineStr">
+        <is>
+          <t>Brands</t>
+        </is>
+      </c>
+      <c r="D70" s="166" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Bike Bros</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>5</v>
+      </c>
+      <c r="C71" t="n">
+        <v>5</v>
+      </c>
+      <c r="D71" s="170" t="inlineStr">
+        <is>
+          <t>TWO ads each for MACH I.I and TERRAMAX - A/B testing. Still finished LAST.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>LiteCycle</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>3</v>
+      </c>
+      <c r="C72" t="n">
+        <v>3</v>
+      </c>
+      <c r="D72" s="170" t="inlineStr">
+        <is>
+          <t>one ad per brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>2</v>
+      </c>
+      <c r="C73" t="n">
+        <v>4</v>
+      </c>
+      <c r="D73" s="170" t="inlineStr">
+        <is>
+          <t>advertises only Blu Ruged Ballz + Blu Tube Ballz; Blu Aero and Blu Tail run with NO ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>WeBike</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>2</v>
+      </c>
+      <c r="C74" t="n">
+        <v>2</v>
+      </c>
+      <c r="D74" s="170" t="inlineStr">
+        <is>
+          <t>one per brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>SpaceBikes / MILC / Spoke'd Up</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>2</v>
+      </c>
+      <c r="C75" t="n">
+        <v>2</v>
+      </c>
+      <c r="D75" s="170" t="inlineStr">
+        <is>
+          <t>one per brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D76" s="174" t="inlineStr">
+        <is>
+          <t>The LEADER runs the FEWEST ads relative to its brand count - 2 ads for 4 brands - and both are best or near-best in class. Bike Bros runs the most ads and is last. Ad QUALITY beats ad COUNT. A second Swift Bike ad is not the answer; a better one is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Portfolio idea worth noting</t>
+        </is>
+      </c>
+      <c r="D77" s="170" t="inlineStr">
+        <is>
+          <t>BB LLC pairs an ADVERTISED brand with an UNADVERTISED second brand in each segment (Blu Ruged + Blu Tail in Mountain, Blu Tube + Blu Aero in Speed). The ad builds the segment and the second brand catches overflow at a higher price. Not a Q4 move for us - capacity binds - but note it for later.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="166" t="inlineStr">
+        <is>
+          <t>Q4 ADVERTISING ACTIONS</t>
+        </is>
+      </c>
+      <c r="B80" s="166" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>HikeBike 1</t>
+        </is>
+      </c>
+      <c r="B81" s="174" t="inlineStr">
+        <is>
+          <t>KEEP. 80 vs BB LLC's 81 - one point off the industry best. Redesign cost is not justified; put the money into media inserts and capacity instead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Swift Bike ad</t>
+        </is>
+      </c>
+      <c r="B82" s="174" t="inlineStr">
+        <is>
+          <t>REDESIGN around Speed cues. Strip Mountain/Recreation claims (aerodynamic, racing tires, precision brakes, drop bars, lightweight). Target 77 to match Speed of Lite 1 / The Armstrong 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Do NOT add more ads</t>
+        </is>
+      </c>
+      <c r="B83" s="174" t="inlineStr">
+        <is>
+          <t>The leader runs 2 ads for 4 brands; the last-place firm runs 5 for 5. Quality over count.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Combined payoff</t>
+        </is>
+      </c>
+      <c r="B84" s="174" t="inlineStr">
+        <is>
+          <t>Swift Bike brand 72-&gt;77 AND ad 70-&gt;77 lifts Marketing Effectiveness from 0.738 to 0.7675 - past BB LLC's 0.765 to become the industry best. Both fixes are cheap relative to capacity.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/quarters/Q3/Q3Data.xlsx
+++ b/quarters/Q3/Q3Data.xlsx
@@ -51,6 +51,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_Compensation" sheetId="43" state="visible" r:id="rId43"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_Ad_Judgment" sheetId="44" state="visible" r:id="rId44"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_Competitor_Ads" sheetId="45" state="visible" r:id="rId45"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q4_Copy_The_Leader" sheetId="46" state="visible" r:id="rId46"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -72,7 +73,7 @@
     <numFmt numFmtId="173" formatCode="+0.0%;-0.0%"/>
     <numFmt numFmtId="174" formatCode="+$#,##0"/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="33">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -270,6 +271,10 @@
     <font>
       <b val="1"/>
       <color rgb="009C0006"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
     </font>
   </fonts>
   <fills count="34">
@@ -662,7 +667,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="16"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="16"/>
   </cellStyleXfs>
-  <cellXfs count="257">
+  <cellXfs count="263">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1014,6 +1019,22 @@
     <xf numFmtId="172" fontId="0" fillId="32" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="174" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="32" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="32" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -51269,7 +51290,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="166" t="inlineStr">
         <is>
@@ -51983,8 +52003,6 @@
         <v>88</v>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24"/>
     <row r="25">
       <c r="A25" s="166" t="inlineStr">
         <is>
@@ -52145,8 +52163,6 @@
         </is>
       </c>
     </row>
-    <row r="35"/>
-    <row r="36"/>
     <row r="37">
       <c r="A37" s="166" t="inlineStr">
         <is>
@@ -52247,8 +52263,6 @@
       </c>
       <c r="D42" s="170" t="inlineStr"/>
     </row>
-    <row r="43"/>
-    <row r="44"/>
     <row r="45">
       <c r="A45" s="166" t="inlineStr">
         <is>
@@ -52379,8 +52393,6 @@
         </is>
       </c>
     </row>
-    <row r="52"/>
-    <row r="53"/>
     <row r="54">
       <c r="A54" s="166" t="inlineStr">
         <is>
@@ -52492,8 +52504,6 @@
         </is>
       </c>
     </row>
-    <row r="59"/>
-    <row r="60"/>
     <row r="61">
       <c r="A61" s="166" t="inlineStr">
         <is>
@@ -52597,8 +52607,6 @@
         </is>
       </c>
     </row>
-    <row r="68"/>
-    <row r="69"/>
     <row r="70">
       <c r="A70" s="166" t="inlineStr">
         <is>
@@ -52735,8 +52743,6 @@
         </is>
       </c>
     </row>
-    <row r="78"/>
-    <row r="79"/>
     <row r="80">
       <c r="A80" s="166" t="inlineStr">
         <is>
@@ -54366,6 +54372,2205 @@
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:I2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F113"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" style="146" min="1" max="1"/>
+    <col width="40" customWidth="1" style="146" min="2" max="2"/>
+    <col width="30" customWidth="1" style="146" min="3" max="3"/>
+    <col width="16" customWidth="1" style="146" min="4" max="4"/>
+    <col width="78" customWidth="1" style="146" min="5" max="5"/>
+    <col width="20" customWidth="1" style="146" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="257" t="inlineStr">
+        <is>
+          <t>Q4 — COPY BB LLC: complete change list</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="62" customHeight="1" s="146">
+      <c r="A2" s="258" t="inlineStr">
+        <is>
+          <t>BB LLC scored 22 on the Q3 quarterly scorecard (next best 11, WeBike 0) and targets the SAME two segments we do — Mountain and Speed. Their Mountain bike is byte-identical to ours: 56/73/1 components, brand judgment 73, price $1,365, price judgment 81/100/100. Same product, same price, 46.3% share vs our 22.1%. There is no product or pricing explanation left. Everything below is execution we can copy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="199" t="inlineStr">
+        <is>
+          <t>THE FULL GAP</t>
+        </is>
+      </c>
+      <c r="B4" s="199" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="C4" s="199" t="inlineStr">
+        <is>
+          <t>WeBike</t>
+        </is>
+      </c>
+      <c r="D4" s="199" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="E4" s="259" t="inlineStr">
+        <is>
+          <t>Copyable in Q4?</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="200" t="inlineStr">
+        <is>
+          <t>Q3 quarterly BSC</t>
+        </is>
+      </c>
+      <c r="B5" s="200" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C5" s="200" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="200" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E5" s="260" t="inlineStr">
+        <is>
+          <t>outcome</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="200" t="inlineStr">
+        <is>
+          <t>Total demand</t>
+        </is>
+      </c>
+      <c r="B6" s="200" t="inlineStr">
+        <is>
+          <t>1,507</t>
+        </is>
+      </c>
+      <c r="C6" s="200" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="D6" s="200" t="inlineStr">
+        <is>
+          <t>2.40x</t>
+        </is>
+      </c>
+      <c r="E6" s="260" t="inlineStr">
+        <is>
+          <t>outcome</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="200" t="inlineStr">
+        <is>
+          <t>Mountain demand (share)</t>
+        </is>
+      </c>
+      <c r="B7" s="200" t="inlineStr">
+        <is>
+          <t>751 (46.3%)</t>
+        </is>
+      </c>
+      <c r="C7" s="200" t="inlineStr">
+        <is>
+          <t>358 (22.1%)</t>
+        </is>
+      </c>
+      <c r="D7" s="200" t="inlineStr">
+        <is>
+          <t>+393 units</t>
+        </is>
+      </c>
+      <c r="E7" s="260" t="inlineStr">
+        <is>
+          <t>partly</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="200" t="inlineStr">
+        <is>
+          <t>Speed demand (share)</t>
+        </is>
+      </c>
+      <c r="B8" s="200" t="inlineStr">
+        <is>
+          <t>657 (22.8%)</t>
+        </is>
+      </c>
+      <c r="C8" s="200" t="inlineStr">
+        <is>
+          <t>216 (7.5%)</t>
+        </is>
+      </c>
+      <c r="D8" s="200" t="inlineStr">
+        <is>
+          <t>+441 units</t>
+        </is>
+      </c>
+      <c r="E8" s="260" t="inlineStr">
+        <is>
+          <t>partly</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="200" t="inlineStr">
+        <is>
+          <t>Demand actually served</t>
+        </is>
+      </c>
+      <c r="B9" s="200" t="inlineStr">
+        <is>
+          <t>99.9%</t>
+        </is>
+      </c>
+      <c r="C9" s="204" t="inlineStr">
+        <is>
+          <t>67.5%</t>
+        </is>
+      </c>
+      <c r="D9" s="200" t="inlineStr">
+        <is>
+          <t>204 units lost</t>
+        </is>
+      </c>
+      <c r="E9" s="261" t="inlineStr">
+        <is>
+          <t>YES — fully</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="200" t="inlineStr">
+        <is>
+          <t>Mountain brand judgment</t>
+        </is>
+      </c>
+      <c r="B10" s="206" t="inlineStr">
+        <is>
+          <t>73 (Blu Ruged)</t>
+        </is>
+      </c>
+      <c r="C10" s="206" t="inlineStr">
+        <is>
+          <t>73 (Hike Bike)</t>
+        </is>
+      </c>
+      <c r="D10" s="206" t="inlineStr">
+        <is>
+          <t>TIED</t>
+        </is>
+      </c>
+      <c r="E10" s="260" t="inlineStr">
+        <is>
+          <t>already equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="200" t="inlineStr">
+        <is>
+          <t>Mountain price</t>
+        </is>
+      </c>
+      <c r="B11" s="206" t="inlineStr">
+        <is>
+          <t>$1,365</t>
+        </is>
+      </c>
+      <c r="C11" s="206" t="inlineStr">
+        <is>
+          <t>$1,365</t>
+        </is>
+      </c>
+      <c r="D11" s="206" t="inlineStr">
+        <is>
+          <t>IDENTICAL</t>
+        </is>
+      </c>
+      <c r="E11" s="260" t="inlineStr">
+        <is>
+          <t>already equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="200" t="inlineStr">
+        <is>
+          <t>Speed brand judgment</t>
+        </is>
+      </c>
+      <c r="B12" s="200" t="inlineStr">
+        <is>
+          <t>76 (Blu Tube)</t>
+        </is>
+      </c>
+      <c r="C12" s="200" t="inlineStr">
+        <is>
+          <t>72 (Swift)</t>
+        </is>
+      </c>
+      <c r="D12" s="200" t="inlineStr">
+        <is>
+          <t>−4</t>
+        </is>
+      </c>
+      <c r="E12" s="260" t="inlineStr">
+        <is>
+          <t>YES — we can hit 77</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="200" t="inlineStr">
+        <is>
+          <t>Speed price</t>
+        </is>
+      </c>
+      <c r="B13" s="200" t="inlineStr">
+        <is>
+          <t>$1,580</t>
+        </is>
+      </c>
+      <c r="C13" s="200" t="inlineStr">
+        <is>
+          <t>$1,450</t>
+        </is>
+      </c>
+      <c r="D13" s="200" t="inlineStr">
+        <is>
+          <t>−$130</t>
+        </is>
+      </c>
+      <c r="E13" s="260" t="inlineStr">
+        <is>
+          <t>YES — exactly</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="200" t="inlineStr">
+        <is>
+          <t>Mountain ad judgment</t>
+        </is>
+      </c>
+      <c r="B14" s="200" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="C14" s="200" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D14" s="200" t="inlineStr">
+        <is>
+          <t>−1</t>
+        </is>
+      </c>
+      <c r="E14" s="260" t="inlineStr">
+        <is>
+          <t>YES — worth 122 clicks</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="200" t="inlineStr">
+        <is>
+          <t>Speed ad judgment</t>
+        </is>
+      </c>
+      <c r="B15" s="200" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="C15" s="200" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D15" s="200" t="inlineStr">
+        <is>
+          <t>−6</t>
+        </is>
+      </c>
+      <c r="E15" s="260" t="inlineStr">
+        <is>
+          <t>YES — we can hit 77</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="200" t="inlineStr">
+        <is>
+          <t>Media inserts / spend</t>
+        </is>
+      </c>
+      <c r="B16" s="200" t="inlineStr">
+        <is>
+          <t>24 / $108,000</t>
+        </is>
+      </c>
+      <c r="C16" s="204" t="inlineStr">
+        <is>
+          <t>19 / $116,000</t>
+        </is>
+      </c>
+      <c r="D16" s="200" t="inlineStr">
+        <is>
+          <t>we paid MORE for LESS</t>
+        </is>
+      </c>
+      <c r="E16" s="261" t="inlineStr">
+        <is>
+          <t>YES — and it SAVES $8,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="200" t="inlineStr">
+        <is>
+          <t>Inserts in Biking Magazines</t>
+        </is>
+      </c>
+      <c r="B17" s="200" t="inlineStr">
+        <is>
+          <t>24 (100%)</t>
+        </is>
+      </c>
+      <c r="C17" s="200" t="inlineStr">
+        <is>
+          <t>10 (53%)</t>
+        </is>
+      </c>
+      <c r="D17" s="200" t="inlineStr">
+        <is>
+          <t>−14</t>
+        </is>
+      </c>
+      <c r="E17" s="260" t="inlineStr">
+        <is>
+          <t>YES — exactly</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="200" t="inlineStr">
+        <is>
+          <t>Organic SEM clicks (same $2,000)</t>
+        </is>
+      </c>
+      <c r="B18" s="200" t="inlineStr">
+        <is>
+          <t>437</t>
+        </is>
+      </c>
+      <c r="C18" s="200" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D18" s="200" t="inlineStr">
+        <is>
+          <t>−293</t>
+        </is>
+      </c>
+      <c r="E18" s="260" t="inlineStr">
+        <is>
+          <t>partly</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="200" t="inlineStr">
+        <is>
+          <t>Organic rank Mountain / Speed</t>
+        </is>
+      </c>
+      <c r="B19" s="200" t="inlineStr">
+        <is>
+          <t>#1 / #1</t>
+        </is>
+      </c>
+      <c r="C19" s="200" t="inlineStr">
+        <is>
+          <t>#2 / #5</t>
+        </is>
+      </c>
+      <c r="D19" s="200" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E19" s="260" t="inlineStr">
+        <is>
+          <t>Mountain yes, Speed likely</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="200" t="inlineStr">
+        <is>
+          <t>Stores</t>
+        </is>
+      </c>
+      <c r="B20" s="200" t="inlineStr">
+        <is>
+          <t>2 (AMS + NYC)</t>
+        </is>
+      </c>
+      <c r="C20" s="200" t="inlineStr">
+        <is>
+          <t>2 (AMS + Rio)</t>
+        </is>
+      </c>
+      <c r="D20" s="200" t="inlineStr">
+        <is>
+          <t>same count</t>
+        </is>
+      </c>
+      <c r="E20" s="260" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="200" t="inlineStr">
+        <is>
+          <t>Store sales force</t>
+        </is>
+      </c>
+      <c r="B21" s="200" t="inlineStr">
+        <is>
+          <t>14 (7 + 7)</t>
+        </is>
+      </c>
+      <c r="C21" s="200" t="inlineStr">
+        <is>
+          <t>11 (7 + 4)</t>
+        </is>
+      </c>
+      <c r="D21" s="200" t="inlineStr">
+        <is>
+          <t>−3</t>
+        </is>
+      </c>
+      <c r="E21" s="260" t="inlineStr">
+        <is>
+          <t>YES — exactly 14</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="200" t="inlineStr">
+        <is>
+          <t>Store crew mix per city</t>
+        </is>
+      </c>
+      <c r="B22" s="200" t="inlineStr">
+        <is>
+          <t>1 Svc / 3 Mtn / 3 Speed</t>
+        </is>
+      </c>
+      <c r="C22" s="200" t="inlineStr">
+        <is>
+          <t>AMS 1/3/2+1 untrained</t>
+        </is>
+      </c>
+      <c r="D22" s="200" t="inlineStr">
+        <is>
+          <t>mix + training</t>
+        </is>
+      </c>
+      <c r="E22" s="260" t="inlineStr">
+        <is>
+          <t>YES — exactly</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="200" t="inlineStr">
+        <is>
+          <t>Web sales force</t>
+        </is>
+      </c>
+      <c r="B23" s="200" t="inlineStr">
+        <is>
+          <t>7 (5 + 2)</t>
+        </is>
+      </c>
+      <c r="C23" s="200" t="inlineStr">
+        <is>
+          <t>3 (2 + 1)</t>
+        </is>
+      </c>
+      <c r="D23" s="200" t="inlineStr">
+        <is>
+          <t>−4</t>
+        </is>
+      </c>
+      <c r="E23" s="260" t="inlineStr">
+        <is>
+          <t>YES — exactly</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="200" t="inlineStr">
+        <is>
+          <t>Web productivity tactics funded</t>
+        </is>
+      </c>
+      <c r="B24" s="200" t="inlineStr">
+        <is>
+          <t>4 of 4 ($33,000)</t>
+        </is>
+      </c>
+      <c r="C24" s="204" t="inlineStr">
+        <is>
+          <t>1 of 4 ($6,000)</t>
+        </is>
+      </c>
+      <c r="D24" s="200" t="inlineStr">
+        <is>
+          <t>−3 tactics</t>
+        </is>
+      </c>
+      <c r="E24" s="261" t="inlineStr">
+        <is>
+          <t>YES — exactly</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="200" t="inlineStr">
+        <is>
+          <t>Web units</t>
+        </is>
+      </c>
+      <c r="B25" s="200" t="inlineStr">
+        <is>
+          <t>569</t>
+        </is>
+      </c>
+      <c r="C25" s="204" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D25" s="200" t="inlineStr">
+        <is>
+          <t>−449</t>
+        </is>
+      </c>
+      <c r="E25" s="261" t="inlineStr">
+        <is>
+          <t>YES — pattern says 435+</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="200" t="inlineStr">
+        <is>
+          <t>Fixed capacity / day</t>
+        </is>
+      </c>
+      <c r="B26" s="206" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C26" s="206" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D26" s="206" t="inlineStr">
+        <is>
+          <t>IDENTICAL</t>
+        </is>
+      </c>
+      <c r="E26" s="260" t="inlineStr">
+        <is>
+          <t>already equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="200" t="inlineStr">
+        <is>
+          <t>Scheduled operating capacity / day</t>
+        </is>
+      </c>
+      <c r="B27" s="200" t="inlineStr">
+        <is>
+          <t>24 (100%)</t>
+        </is>
+      </c>
+      <c r="C27" s="204" t="inlineStr">
+        <is>
+          <t>8 (33%)</t>
+        </is>
+      </c>
+      <c r="D27" s="200" t="inlineStr">
+        <is>
+          <t>−16</t>
+        </is>
+      </c>
+      <c r="E27" s="261" t="inlineStr">
+        <is>
+          <t>YES — fully</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="200" t="inlineStr">
+        <is>
+          <t>Overtime / day</t>
+        </is>
+      </c>
+      <c r="B28" s="200" t="inlineStr">
+        <is>
+          <t>6.90</t>
+        </is>
+      </c>
+      <c r="C28" s="200" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="D28" s="200" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E28" s="262" t="inlineStr">
+        <is>
+          <t>DON'T copy (see below)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="200" t="inlineStr">
+        <is>
+          <t>Sales compensation / productivity</t>
+        </is>
+      </c>
+      <c r="B29" s="200" t="inlineStr">
+        <is>
+          <t>$27,402 / 78%</t>
+        </is>
+      </c>
+      <c r="C29" s="200" t="inlineStr">
+        <is>
+          <t>$24,425 / 70%</t>
+        </is>
+      </c>
+      <c r="D29" s="200" t="inlineStr">
+        <is>
+          <t>−$2,977 / −8 pts</t>
+        </is>
+      </c>
+      <c r="E29" s="260" t="inlineStr">
+        <is>
+          <t>YES — exactly</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="200" t="inlineStr">
+        <is>
+          <t>Worker compensation / productivity</t>
+        </is>
+      </c>
+      <c r="B30" s="200" t="inlineStr">
+        <is>
+          <t>$23,042 / 75%</t>
+        </is>
+      </c>
+      <c r="C30" s="200" t="inlineStr">
+        <is>
+          <t>$20,757 / 72%</t>
+        </is>
+      </c>
+      <c r="D30" s="200" t="inlineStr">
+        <is>
+          <t>−$2,285 / −3 pts</t>
+        </is>
+      </c>
+      <c r="E30" s="260" t="inlineStr">
+        <is>
+          <t>YES — exactly</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="200" t="inlineStr">
+        <is>
+          <t>Marketing Effectiveness</t>
+        </is>
+      </c>
+      <c r="B31" s="200" t="inlineStr">
+        <is>
+          <t>0.765 (max)</t>
+        </is>
+      </c>
+      <c r="C31" s="200" t="inlineStr">
+        <is>
+          <t>0.738</t>
+        </is>
+      </c>
+      <c r="D31" s="200" t="inlineStr">
+        <is>
+          <t>−0.027</t>
+        </is>
+      </c>
+      <c r="E31" s="260" t="inlineStr">
+        <is>
+          <t>YES — we can reach 0.7675</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="200" t="inlineStr">
+        <is>
+          <t>Asset Management</t>
+        </is>
+      </c>
+      <c r="B32" s="200" t="inlineStr">
+        <is>
+          <t>0.920</t>
+        </is>
+      </c>
+      <c r="C32" s="200" t="inlineStr">
+        <is>
+          <t>0.353</t>
+        </is>
+      </c>
+      <c r="D32" s="200" t="inlineStr">
+        <is>
+          <t>idle cash</t>
+        </is>
+      </c>
+      <c r="E32" s="260" t="inlineStr">
+        <is>
+          <t>YES — spend it on the above</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="199" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B35" s="199" t="inlineStr">
+        <is>
+          <t>CHANGE — enter these in the sim</t>
+        </is>
+      </c>
+      <c r="C35" s="199" t="inlineStr">
+        <is>
+          <t>Exact value</t>
+        </is>
+      </c>
+      <c r="D35" s="199" t="inlineStr">
+        <is>
+          <t>Cash / qtr</t>
+        </is>
+      </c>
+      <c r="E35" s="259" t="inlineStr">
+        <is>
+          <t>Why (evidence)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="200" t="n">
+        <v>1</v>
+      </c>
+      <c r="B36" s="222" t="inlineStr">
+        <is>
+          <t>Schedule operating capacity</t>
+        </is>
+      </c>
+      <c r="C36" s="200" t="inlineStr">
+        <is>
+          <t>24 / day (100% of owned)</t>
+        </is>
+      </c>
+      <c r="D36" s="200" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="E36" s="260" t="inlineStr">
+        <is>
+          <t>BB LLC schedules all 24 owned; we scheduled 8 and stocked out on 204 of 627 units. 24/day x 74% x 65 = 1,154 units, which covers the 1,171 forecast within 1.5%. Also cuts unit cost: under-scheduling pushed labour/unit from $130 to $205.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="200" t="n">
+        <v>2</v>
+      </c>
+      <c r="B37" s="222" t="inlineStr">
+        <is>
+          <t>Overtime</t>
+        </is>
+      </c>
+      <c r="C37" s="211" t="inlineStr">
+        <is>
+          <t>0.00 — do NOT copy BB LLC's 6.90</t>
+        </is>
+      </c>
+      <c r="D37" s="200" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="E37" s="260" t="inlineStr">
+        <is>
+          <t>Manufacturing Productivity = utilisation of scheduled OC minus half the OT ratio. BB LLC's 6.90 OT scores 0.856; scheduling 24 with zero OT scores 1.000. Copy SpaceBikes here, not BB LLC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="200" t="n">
+        <v>3</v>
+      </c>
+      <c r="B38" s="200" t="inlineStr">
+        <is>
+          <t>Printers</t>
+        </is>
+      </c>
+      <c r="C38" s="211" t="inlineStr">
+        <is>
+          <t>Buy NONE (unless NYC — then 1)</t>
+        </is>
+      </c>
+      <c r="D38" s="200" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="E38" s="260" t="inlineStr">
+        <is>
+          <t>We already own the same 24/day BB LLC does. The Q2 $148,652 excess-capacity charge came from SCHEDULING unused capacity, not owning it. Only scenario E (NYC) needs 32.7/day.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="200" t="n">
+        <v>4</v>
+      </c>
+      <c r="B39" s="200" t="inlineStr">
+        <is>
+          <t>Swift Bike design: gears</t>
+        </is>
+      </c>
+      <c r="C39" s="200" t="inlineStr">
+        <is>
+          <t>24-speed -&gt; 14-speed (2 x 7)</t>
+        </is>
+      </c>
+      <c r="D39" s="200" t="inlineStr">
+        <is>
+          <t>design fee</t>
+        </is>
+      </c>
+      <c r="E39" s="260" t="inlineStr">
+        <is>
+          <t>+3 judgment. Swift Bike is the ONLY Speed brand in the industry running a 24-speed mountain drivetrain — it inherited Hike Bike's. 14-speed is also simpler and should cut unit cost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="200" t="n">
+        <v>5</v>
+      </c>
+      <c r="B40" s="200" t="inlineStr">
+        <is>
+          <t>Swift Bike design: decals</t>
+        </is>
+      </c>
+      <c r="C40" s="200" t="inlineStr">
+        <is>
+          <t>ADD colourful thin brushstrokes</t>
+        </is>
+      </c>
+      <c r="D40" s="200" t="inlineStr">
+        <is>
+          <t>included</t>
+        </is>
+      </c>
+      <c r="E40" s="260" t="inlineStr">
+        <is>
+          <t>+2 judgment. Takes Swift Bike 72 -&gt; 77, tying the industry Speed ceiling and BEATING BB LLC's Blu Tube at 76. Verified against a model that reproduces all 16 Mountain/Speed scores exactly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="200" t="n">
+        <v>6</v>
+      </c>
+      <c r="B41" s="200" t="inlineStr">
+        <is>
+          <t>Hike Bike design</t>
+        </is>
+      </c>
+      <c r="C41" s="211" t="inlineStr">
+        <is>
+          <t>NO CHANGE — 56/73/1</t>
+        </is>
+      </c>
+      <c r="D41" s="200" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="E41" s="260" t="inlineStr">
+        <is>
+          <t>73 is the industry Mountain ceiling, tied with BB LLC's own Blu Ruged Ballz. Nothing to gain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="200" t="n">
+        <v>7</v>
+      </c>
+      <c r="B42" s="200" t="inlineStr">
+        <is>
+          <t>Swift Bike price</t>
+        </is>
+      </c>
+      <c r="C42" s="200" t="inlineStr">
+        <is>
+          <t>$1,450 -&gt; $1,580</t>
+        </is>
+      </c>
+      <c r="D42" s="200" t="inlineStr">
+        <is>
+          <t>revenue +</t>
+        </is>
+      </c>
+      <c r="E42" s="260" t="inlineStr">
+        <is>
+          <t>$1,580 is BB LLC's exact Speed price and draws ZERO Speed resistance (proven by Blu Aero, Blu Tube, Armstrong at the same price). Resistance starts at $1,749. Contribution $756 -&gt; $886.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="200" t="n">
+        <v>8</v>
+      </c>
+      <c r="B43" s="200" t="inlineStr">
+        <is>
+          <t>Hike Bike price</t>
+        </is>
+      </c>
+      <c r="C43" s="211" t="inlineStr">
+        <is>
+          <t>HOLD $1,365</t>
+        </is>
+      </c>
+      <c r="D43" s="200" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="E43" s="260" t="inlineStr">
+        <is>
+          <t>Identical to BB LLC's Mountain price, and tier 81 is the highest tier still scoring 100 in Mountain. Already optimal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="200" t="n">
+        <v>9</v>
+      </c>
+      <c r="B44" s="200" t="inlineStr">
+        <is>
+          <t>Brand priority</t>
+        </is>
+      </c>
+      <c r="C44" s="200" t="inlineStr">
+        <is>
+          <t>Hike Bike 1, Swift Bike 2 (unchanged)</t>
+        </is>
+      </c>
+      <c r="D44" s="200" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="E44" s="260" t="inlineStr">
+        <is>
+          <t>Same pattern BB LLC uses (Mountain brand at priority 1). Once OC is scheduled to the forecast, priority stops rationing anything.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="200" t="n">
+        <v>10</v>
+      </c>
+      <c r="B45" s="200" t="inlineStr">
+        <is>
+          <t>Swift Bike ad — REBUILD</t>
+        </is>
+      </c>
+      <c r="C45" s="200" t="inlineStr">
+        <is>
+          <t>7 benefits, ranked (see next block)</t>
+        </is>
+      </c>
+      <c r="D45" s="200" t="inlineStr">
+        <is>
+          <t>design fee</t>
+        </is>
+      </c>
+      <c r="E45" s="260" t="inlineStr">
+        <is>
+          <t>70 -&gt; target 77. Our ad is the only Speed ad in the industry selling lights, reflectors and 'great price'; it leaks 52 Rec / 36 Mtn against 12-46 for everyone else.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="200" t="n">
+        <v>11</v>
+      </c>
+      <c r="B46" s="200" t="inlineStr">
+        <is>
+          <t>HikeBike 1 ad — try to clear 82</t>
+        </is>
+      </c>
+      <c r="C46" s="211" t="inlineStr">
+        <is>
+          <t>add 'Highest rated Mountain bike' + 'Local sales &amp; service'</t>
+        </is>
+      </c>
+      <c r="D46" s="200" t="inlineStr">
+        <is>
+          <t>design fee</t>
+        </is>
+      </c>
+      <c r="E46" s="260" t="inlineStr">
+        <is>
+          <t>Mountain SERP rank is EXACTLY ad-judgment order (81&gt;80&gt;79&gt;78&gt;77). Beating BB Big Momma's 81 moves us from position 2 to 1: 115 -&gt; 237 clicks on a page we already pay $1,000 for. Both claims are legal (we are tied at 73) and BB LLC runs both. PREVIEW FIRST — keep Q3 copy if it drops.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="200" t="n">
+        <v>12</v>
+      </c>
+      <c r="B47" s="200" t="inlineStr">
+        <is>
+          <t>Media: HikeBike 1 inserts</t>
+        </is>
+      </c>
+      <c r="C47" s="200" t="inlineStr">
+        <is>
+          <t>Biking 12 — and nothing else</t>
+        </is>
+      </c>
+      <c r="D47" s="200" t="inlineStr">
+        <is>
+          <t>$54,000</t>
+        </is>
+      </c>
+      <c r="E47" s="260" t="inlineStr">
+        <is>
+          <t>Exactly BB LLC's BB Big Momma plan. We cut HikeBike 1 Biking from 12 to 6 in Q3 to 'diversify' and spent the money on Sport/News/Venture instead. Biking is the #1 Mountain medium.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="200" t="n">
+        <v>13</v>
+      </c>
+      <c r="B48" s="200" t="inlineStr">
+        <is>
+          <t>Media: Swift Bike inserts</t>
+        </is>
+      </c>
+      <c r="C48" s="200" t="inlineStr">
+        <is>
+          <t>Biking 12 — and nothing else</t>
+        </is>
+      </c>
+      <c r="D48" s="200" t="inlineStr">
+        <is>
+          <t>$54,000</t>
+        </is>
+      </c>
+      <c r="E48" s="260" t="inlineStr">
+        <is>
+          <t>Exactly BB LLC's Unleash lil pap plan. We ran only 4 Biking for Swift Bike. BB LLC owned 24 of the industry's 51 Biking pages; at 24 each we co-own the medium.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="200" t="n">
+        <v>14</v>
+      </c>
+      <c r="B49" s="222" t="inlineStr">
+        <is>
+          <t>Media total</t>
+        </is>
+      </c>
+      <c r="C49" s="200" t="inlineStr">
+        <is>
+          <t>24 inserts / $108,000 (was 19 / $116,000)</t>
+        </is>
+      </c>
+      <c r="D49" s="206" t="inlineStr">
+        <is>
+          <t>-$8,000</t>
+        </is>
+      </c>
+      <c r="E49" s="260" t="inlineStr">
+        <is>
+          <t>The winning media plan is CHEAPER than what we did. More inserts, best medium, less money. Strictly dominant — the single easiest change on this list.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="200" t="n">
+        <v>15</v>
+      </c>
+      <c r="B50" s="200" t="inlineStr">
+        <is>
+          <t>Web tactic: toll-free phone</t>
+        </is>
+      </c>
+      <c r="C50" s="200" t="inlineStr">
+        <is>
+          <t>$6,000 -&gt; $9,000</t>
+        </is>
+      </c>
+      <c r="D50" s="200" t="inlineStr">
+        <is>
+          <t>$3,000</t>
+        </is>
+      </c>
+      <c r="E50" s="260" t="inlineStr">
+        <is>
+          <t>BB LLC's level. Our one already-funded tactic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="200" t="n">
+        <v>16</v>
+      </c>
+      <c r="B51" s="200" t="inlineStr">
+        <is>
+          <t>Web tactic: advanced shopping cart</t>
+        </is>
+      </c>
+      <c r="C51" s="200" t="inlineStr">
+        <is>
+          <t>$0 -&gt; $7,000</t>
+        </is>
+      </c>
+      <c r="D51" s="200" t="inlineStr">
+        <is>
+          <t>$7,000</t>
+        </is>
+      </c>
+      <c r="E51" s="260" t="inlineStr">
+        <is>
+          <t>Never funded. BB LLC, LiteCycle, SpaceBikes and MILC all fund it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="200" t="n">
+        <v>17</v>
+      </c>
+      <c r="B52" s="200" t="inlineStr">
+        <is>
+          <t>Web tactic: page upgrades</t>
+        </is>
+      </c>
+      <c r="C52" s="200" t="inlineStr">
+        <is>
+          <t>$0 -&gt; $9,000</t>
+        </is>
+      </c>
+      <c r="D52" s="200" t="inlineStr">
+        <is>
+          <t>$9,000</t>
+        </is>
+      </c>
+      <c r="E52" s="260" t="inlineStr">
+        <is>
+          <t>We funded this in Q2 and STOPPED it in Q3. BB LLC spends $9,000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="200" t="n">
+        <v>18</v>
+      </c>
+      <c r="B53" s="200" t="inlineStr">
+        <is>
+          <t>Web tactic: order tracking</t>
+        </is>
+      </c>
+      <c r="C53" s="200" t="inlineStr">
+        <is>
+          <t>$0 -&gt; $8,000</t>
+        </is>
+      </c>
+      <c r="D53" s="200" t="inlineStr">
+        <is>
+          <t>$8,000</t>
+        </is>
+      </c>
+      <c r="E53" s="260" t="inlineStr">
+        <is>
+          <t>Never funded. Every firm that funds all four lands 435-569 web units; every firm that funds fewer lands 120-138. We are at 120.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="200" t="n">
+        <v>19</v>
+      </c>
+      <c r="B54" s="222" t="inlineStr">
+        <is>
+          <t>Web staff</t>
+        </is>
+      </c>
+      <c r="C54" s="200" t="inlineStr">
+        <is>
+          <t>3 -&gt; 7 (5 sales + 2 service)</t>
+        </is>
+      </c>
+      <c r="D54" s="200" t="inlineStr">
+        <is>
+          <t>~$27,400</t>
+        </is>
+      </c>
+      <c r="E54" s="260" t="inlineStr">
+        <is>
+          <t>BB LLC's exact web crew. 7 is the hard cap. Web demand per head: BB LLC 81.3, WeBike 40.0 (last).</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="200" t="n">
+        <v>20</v>
+      </c>
+      <c r="B55" s="200" t="inlineStr">
+        <is>
+          <t>Amsterdam store: train the untrained</t>
+        </is>
+      </c>
+      <c r="C55" s="200" t="inlineStr">
+        <is>
+          <t>1 untrained -&gt; SPEED specialist</t>
+        </is>
+      </c>
+      <c r="D55" s="200" t="inlineStr">
+        <is>
+          <t>$400</t>
+        </is>
+      </c>
+      <c r="E55" s="260" t="inlineStr">
+        <is>
+          <t>Gives 1 Service / 3 Mountain / 3 Speed = BB LLC's exact crew. Amsterdam is AT the 7-person cap, so training is the only legal move there.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="200" t="n">
+        <v>21</v>
+      </c>
+      <c r="B56" s="200" t="inlineStr">
+        <is>
+          <t>Rio store: train the untrained</t>
+        </is>
+      </c>
+      <c r="C56" s="200" t="inlineStr">
+        <is>
+          <t>1 untrained -&gt; MOUNTAIN specialist</t>
+        </is>
+      </c>
+      <c r="D56" s="200" t="inlineStr">
+        <is>
+          <t>$400</t>
+        </is>
+      </c>
+      <c r="E56" s="260" t="inlineStr">
+        <is>
+          <t>Only Bike Bros (last place) also carries untrained staff. The other five firms train everyone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="200" t="n">
+        <v>22</v>
+      </c>
+      <c r="B57" s="222" t="inlineStr">
+        <is>
+          <t>Rio store: hire 3</t>
+        </is>
+      </c>
+      <c r="C57" s="200" t="inlineStr">
+        <is>
+          <t>+1 Mountain, +2 Speed -&gt; 1 Svc / 3 Mtn / 3 Speed</t>
+        </is>
+      </c>
+      <c r="D57" s="200" t="inlineStr">
+        <is>
+          <t>~$20,600</t>
+        </is>
+      </c>
+      <c r="E57" s="260" t="inlineStr">
+        <is>
+          <t>Clones BB LLC's crew in our second store and takes total store force to 14 = BB LLC's 14. Rio measures 60 units/head (we are the ONLY store in the city) vs Amsterdam's 38, so this is our highest-return staffing move: roughly +180 store units.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="200" t="n">
+        <v>23</v>
+      </c>
+      <c r="B58" s="222" t="inlineStr">
+        <is>
+          <t>Sales compensation</t>
+        </is>
+      </c>
+      <c r="C58" s="200" t="inlineStr">
+        <is>
+          <t>$22,000 salary / Expanded / 2 wk / 4% = $27,402</t>
+        </is>
+      </c>
+      <c r="D58" s="200" t="inlineStr">
+        <is>
+          <t>~$15,600</t>
+        </is>
+      </c>
+      <c r="E58" s="260" t="inlineStr">
+        <is>
+          <t>BB LLC's exact package — the industry's best sales productivity at 78%. Drop Full coverage: MILC pays MORE ($27,630) on Full + 1 week and scores 8.4 points WORSE. Salary is the #1 lever (87).</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="200" t="n">
+        <v>24</v>
+      </c>
+      <c r="B59" s="200" t="inlineStr">
+        <is>
+          <t>Production compensation</t>
+        </is>
+      </c>
+      <c r="C59" s="200" t="inlineStr">
+        <is>
+          <t>$18,500 salary / Expanded / 2 wk / 4% = $23,042</t>
+        </is>
+      </c>
+      <c r="D59" s="200" t="inlineStr">
+        <is>
+          <t>~payroll</t>
+        </is>
+      </c>
+      <c r="E59" s="260" t="inlineStr">
+        <is>
+          <t>BB LLC's exact package — best worker productivity at 75%. Our mix is already right; we are simply under on salary.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="200" t="n">
+        <v>25</v>
+      </c>
+      <c r="B60" s="200" t="inlineStr">
+        <is>
+          <t>Productivity assumption in the planner</t>
+        </is>
+      </c>
+      <c r="C60" s="200" t="inlineStr">
+        <is>
+          <t>74% — NEVER 85%</t>
+        </is>
+      </c>
+      <c r="D60" s="200" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="E60" s="260" t="inlineStr">
+        <is>
+          <t>Q3 planned 85% and delivered 70/72. BB LLC's 78% sales is the industry ceiling. Pay buys a few HR points, not fifteen productivity points.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="200" t="n">
+        <v>26</v>
+      </c>
+      <c r="B61" s="200" t="inlineStr">
+        <is>
+          <t>Stock issue</t>
+        </is>
+      </c>
+      <c r="C61" s="211" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="D61" s="200" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="E61" s="260" t="inlineStr">
+        <is>
+          <t>$1,010,838 already sits idle; that is what Asset Management 0.353 punishes. Spend cash, don't raise more.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="200" t="n">
+        <v>27</v>
+      </c>
+      <c r="B62" s="200" t="inlineStr">
+        <is>
+          <t>Target segments</t>
+        </is>
+      </c>
+      <c r="C62" s="200" t="inlineStr">
+        <is>
+          <t>Mountain (primary) / Speed (secondary)</t>
+        </is>
+      </c>
+      <c r="D62" s="200" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="E62" s="260" t="inlineStr">
+        <is>
+          <t>Unchanged — identical to BB LLC's targeting. No action, just don't touch it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="200" t="n">
+        <v>28</v>
+      </c>
+      <c r="B63" s="200" t="inlineStr">
+        <is>
+          <t>Organic SEM pages</t>
+        </is>
+      </c>
+      <c r="C63" s="200" t="inlineStr">
+        <is>
+          <t>2 pages, $1,000 each (unchanged)</t>
+        </is>
+      </c>
+      <c r="D63" s="200" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="E63" s="260" t="inlineStr">
+        <is>
+          <t>BB LLC gets 437 clicks from the SAME 2 pages and SAME $2,000 we spend. Rank, not budget, is the gap — and rank follows ad judgment, so changes 10 and 11 are the SEM fix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="200" t="n">
+        <v>29</v>
+      </c>
+      <c r="B64" s="200" t="inlineStr">
+        <is>
+          <t>Rebates</t>
+        </is>
+      </c>
+      <c r="C64" s="200" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="D64" s="200" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="E64" s="260" t="inlineStr">
+        <is>
+          <t>Only the two Recreation price leaders use them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="200" t="n">
+        <v>30</v>
+      </c>
+      <c r="B65" s="200" t="inlineStr">
+        <is>
+          <t>Recreation brand</t>
+        </is>
+      </c>
+      <c r="C65" s="211" t="inlineStr">
+        <is>
+          <t>DO NOT ADD — park for Q5</t>
+        </is>
+      </c>
+      <c r="D65" s="200" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="E65" s="260" t="inlineStr">
+        <is>
+          <t>BB LLC has no Recreation brand scoring 70+ either. Brand count does not drive share: Bike Bros has 5 brands and finished last; SpaceBikes has 2 and leads cumulatively. Capacity binds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="199" t="inlineStr">
+        <is>
+          <t>SWIFT BIKE AD — rank order to enter (draft, preview before committing)</t>
+        </is>
+      </c>
+      <c r="B68" s="259" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="200" t="inlineStr">
+        <is>
+          <t>1. Mention brand name</t>
+        </is>
+      </c>
+      <c r="B69" s="260" t="inlineStr">
+        <is>
+          <t>fills the Ad/Brand columns; does NOT consume an organic snippet slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="200" t="inlineStr">
+        <is>
+          <t>2. Ride a wind-cheater</t>
+        </is>
+      </c>
+      <c r="B70" s="260" t="inlineStr">
+        <is>
+          <t>8 of 8 rival Speed ads run this; we were missing it. Aero frame makes it true.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="200" t="inlineStr">
+        <is>
+          <t>3. Roll fast with racing tires</t>
+        </is>
+      </c>
+      <c r="B71" s="260" t="inlineStr">
+        <is>
+          <t>7 of 8 rivals; the bike HAS racing tires</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="200" t="inlineStr">
+        <is>
+          <t>4. Elite look - a ride of distinction</t>
+        </is>
+      </c>
+      <c r="B72" s="260" t="inlineStr">
+        <is>
+          <t>6 of 8 rivals, including both 77-point ads</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="200" t="inlineStr">
+        <is>
+          <t>5. A tailor-made bike just for you! 3D printing</t>
+        </is>
+      </c>
+      <c r="B73" s="260" t="inlineStr">
+        <is>
+          <t>on both best ads; we actually 3D-print</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="200" t="inlineStr">
+        <is>
+          <t>6. Local sales &amp; service</t>
+        </is>
+      </c>
+      <c r="B74" s="260" t="inlineStr">
+        <is>
+          <t>we are 80.9% store — and never claimed it</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="200" t="inlineStr">
+        <is>
+          <t>7. Picture of road race</t>
+        </is>
+      </c>
+      <c r="B75" s="260" t="inlineStr">
+        <is>
+          <t>the one thing Q3 got right; ranked lower so text fills the snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="204" t="inlineStr">
+        <is>
+          <t>DROP: lights, reflectors, 'carbon fiber quality at a great price', carbon-light at #2</t>
+        </is>
+      </c>
+      <c r="B76" s="260" t="inlineStr">
+        <is>
+          <t>Zero of 8 rival Speed ads run lights, reflectors or great price. Ours ran all three. Do not sell 'great price' in the quarter we raise the price to $1,580.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="206" t="inlineStr">
+        <is>
+          <t>Resulting snippet: wind-cheater / racing tires / elite look</t>
+        </is>
+      </c>
+      <c r="B77" s="260" t="inlineStr">
+        <is>
+          <t>Identical to Unleash lil pap, the Speed SERP #1 with 200 clicks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="200" t="inlineStr">
+        <is>
+          <t>Do NOT add a second Swift Bike ad</t>
+        </is>
+      </c>
+      <c r="B78" s="260" t="inlineStr">
+        <is>
+          <t>BB LLC runs 2 ads for 4 brands and leads. Bike Bros runs 5 for 5 and is last.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="199" t="inlineStr">
+        <is>
+          <t>EXPECTED RESULT</t>
+        </is>
+      </c>
+      <c r="B81" s="199" t="inlineStr">
+        <is>
+          <t>Q3 actual</t>
+        </is>
+      </c>
+      <c r="C81" s="199" t="inlineStr">
+        <is>
+          <t>Q4 after the copy</t>
+        </is>
+      </c>
+      <c r="D81" s="259" t="inlineStr">
+        <is>
+          <t>Basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="200" t="inlineStr">
+        <is>
+          <t>Units built</t>
+        </is>
+      </c>
+      <c r="B82" s="200" t="inlineStr">
+        <is>
+          <t>423</t>
+        </is>
+      </c>
+      <c r="C82" s="222" t="inlineStr">
+        <is>
+          <t>~1,154</t>
+        </is>
+      </c>
+      <c r="D82" s="260" t="inlineStr">
+        <is>
+          <t>24/day x 74% x 65 days, zero overtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="200" t="inlineStr">
+        <is>
+          <t>Demand served</t>
+        </is>
+      </c>
+      <c r="B83" s="200" t="inlineStr">
+        <is>
+          <t>67.5%</t>
+        </is>
+      </c>
+      <c r="C83" s="222" t="inlineStr">
+        <is>
+          <t>~99%</t>
+        </is>
+      </c>
+      <c r="D83" s="260" t="inlineStr">
+        <is>
+          <t>capacity finally matches the forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="200" t="inlineStr">
+        <is>
+          <t>Web units</t>
+        </is>
+      </c>
+      <c r="B84" s="200" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="C84" s="222" t="inlineStr">
+        <is>
+          <t>435+</t>
+        </is>
+      </c>
+      <c r="D84" s="260" t="inlineStr">
+        <is>
+          <t>all 4 tactics + 7 staff — the pattern holds for 4 of 4 firms</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="200" t="inlineStr">
+        <is>
+          <t>Rio store units</t>
+        </is>
+      </c>
+      <c r="B85" s="200" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="C85" s="222" t="inlineStr">
+        <is>
+          <t>~420</t>
+        </is>
+      </c>
+      <c r="D85" s="260" t="inlineStr">
+        <is>
+          <t>3 more heads at Rio's measured 60/head</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="200" t="inlineStr">
+        <is>
+          <t>Mountain share</t>
+        </is>
+      </c>
+      <c r="B86" s="200" t="inlineStr">
+        <is>
+          <t>22.1%</t>
+        </is>
+      </c>
+      <c r="C86" s="222" t="inlineStr">
+        <is>
+          <t>~35%</t>
+        </is>
+      </c>
+      <c r="D86" s="260" t="inlineStr">
+        <is>
+          <t>supply + 12 Biking inserts + Rio depth (BB LLC proves 46.3% is reachable on this product)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="200" t="inlineStr">
+        <is>
+          <t>Speed share</t>
+        </is>
+      </c>
+      <c r="B87" s="200" t="inlineStr">
+        <is>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="C87" s="222" t="inlineStr">
+        <is>
+          <t>~17%</t>
+        </is>
+      </c>
+      <c r="D87" s="260" t="inlineStr">
+        <is>
+          <t>brand 77 + ad 77 + $1,580 + 12 Biking inserts + 3 Speed heads per store</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="200" t="inlineStr">
+        <is>
+          <t>Marketing Effectiveness</t>
+        </is>
+      </c>
+      <c r="B88" s="200" t="inlineStr">
+        <is>
+          <t>0.738</t>
+        </is>
+      </c>
+      <c r="C88" s="222" t="inlineStr">
+        <is>
+          <t>0.7675</t>
+        </is>
+      </c>
+      <c r="D88" s="260" t="inlineStr">
+        <is>
+          <t>arithmetic — formula verified on 3 firms</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="200" t="inlineStr">
+        <is>
+          <t>Manufacturing Productivity</t>
+        </is>
+      </c>
+      <c r="B89" s="200" t="inlineStr">
+        <is>
+          <t>0.938</t>
+        </is>
+      </c>
+      <c r="C89" s="222" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="D89" s="260" t="inlineStr">
+        <is>
+          <t>schedule to forecast with zero OT</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="200" t="inlineStr">
+        <is>
+          <t>Market Performance</t>
+        </is>
+      </c>
+      <c r="B90" s="200" t="inlineStr">
+        <is>
+          <t>0.098</t>
+        </is>
+      </c>
+      <c r="C90" s="222" t="inlineStr">
+        <is>
+          <t>~0.26</t>
+        </is>
+      </c>
+      <c r="D90" s="260" t="inlineStr">
+        <is>
+          <t>avg share ~26% x ~99% served (BB LLC scored ~0.345)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="200" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B91" s="200" t="inlineStr">
+        <is>
+          <t>$589,720</t>
+        </is>
+      </c>
+      <c r="C91" s="222" t="inlineStr">
+        <is>
+          <t>~$1.5-1.7M</t>
+        </is>
+      </c>
+      <c r="D91" s="260" t="inlineStr">
+        <is>
+          <t>600 Mountain at $1,365 + 450 Speed at $1,580</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="200" t="inlineStr">
+        <is>
+          <t>Asset Management</t>
+        </is>
+      </c>
+      <c r="B92" s="200" t="inlineStr">
+        <is>
+          <t>0.353</t>
+        </is>
+      </c>
+      <c r="C92" s="222" t="inlineStr">
+        <is>
+          <t>improves</t>
+        </is>
+      </c>
+      <c r="D92" s="260" t="inlineStr">
+        <is>
+          <t>idle cash converted into staff, web and inserts</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="199" t="inlineStr">
+        <is>
+          <t>WHAT WE DELIBERATELY DO NOT COPY</t>
+        </is>
+      </c>
+      <c r="B95" s="259" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="200" t="inlineStr">
+        <is>
+          <t>BB LLC's 6.90 overtime</t>
+        </is>
+      </c>
+      <c r="B96" s="262" t="inlineStr">
+        <is>
+          <t>It costs Manufacturing Productivity (0.856 vs 1.000). We own the same 24 printers — we can schedule to the forecast without it. SpaceBikes is the better model here: 32 owned, 30 scheduled, zero OT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="200" t="inlineStr">
+        <is>
+          <t>BB LLC's 4 brands</t>
+        </is>
+      </c>
+      <c r="B97" s="262" t="inlineStr">
+        <is>
+          <t>Their 3rd and 4th brands (Blu Tail, Blu Aero) run UNADVERTISED as overflow catchers at a higher price. That only works with spare capacity. Capacity binds for us in Q4. File it for Q5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="200" t="inlineStr">
+        <is>
+          <t>BB LLC's NYC store</t>
+        </is>
+      </c>
+      <c r="B98" s="262" t="inlineStr">
+        <is>
+          <t>Tier 2 — they hold 82.8% of NYC Mountain and it needs a printer plus 7 new hires. If we go, go via SPEED (880 units, no dominant firm, Spoke'd Up's Speed ad is under 70), not Mountain. Depth in Rio and the web pays back faster.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="200" t="inlineStr">
+        <is>
+          <t>Bike Bros' 5 ads and 5 brands</t>
+        </is>
+      </c>
+      <c r="B99" s="262" t="inlineStr">
+        <is>
+          <t>Most ads and most brands in the industry — and last place. Their two Speed pages cannibalise each other into positions 7 and 8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="200" t="inlineStr">
+        <is>
+          <t>MILC's compensation</t>
+        </is>
+      </c>
+      <c r="B100" s="262" t="inlineStr">
+        <is>
+          <t>Highest sales spend in the industry ($27,630) and 8.4 points WORSE satisfaction than BB LLC, because of Full coverage + 1 week vacation. Mix beats total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="199" t="inlineStr">
+        <is>
+          <t>UNVERIFIED / VOTE REQUIRED</t>
+        </is>
+      </c>
+      <c r="B103" s="259" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="200" t="inlineStr">
+        <is>
+          <t>Every item above</t>
+        </is>
+      </c>
+      <c r="B104" s="260" t="inlineStr">
+        <is>
+          <t>ANALYSIS ONLY — nothing is locked. Majority vote required before entry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="200" t="inlineStr">
+        <is>
+          <t>Swift Bike ad landing score</t>
+        </is>
+      </c>
+      <c r="B105" s="260" t="inlineStr">
+        <is>
+          <t>Draft ranks are modelled on the two 77-point ads. PREVIEW in the designer and read the score before committing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="200" t="inlineStr">
+        <is>
+          <t>HikeBike 1 modification</t>
+        </is>
+      </c>
+      <c r="B106" s="260" t="inlineStr">
+        <is>
+          <t>Only commit if the preview clears 82. If it drops below 80, keep the Q3 copy exactly as is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="200" t="inlineStr">
+        <is>
+          <t>Speed organic rank after the fix</t>
+        </is>
+      </c>
+      <c r="B107" s="260" t="inlineStr">
+        <is>
+          <t>Speed SERP does NOT follow ad judgment (AndStill scores 78 and sits 7th), so the landing position is unpredictable. Treat as upside, not forecast.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="200" t="inlineStr">
+        <is>
+          <t>Web tactic setup fees</t>
+        </is>
+      </c>
+      <c r="B108" s="260" t="inlineStr">
+        <is>
+          <t>Q2 charged setup equal to the first quarterly budget. Assume ~$27,000 one-time on the three restarts — CONFIRM in the sim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="200" t="inlineStr">
+        <is>
+          <t>Hiring, design and redesign fees</t>
+        </is>
+      </c>
+      <c r="B109" s="260" t="inlineStr">
+        <is>
+          <t>Estimated at ~$40,000 combined. Read the actual figures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="200" t="inlineStr">
+        <is>
+          <t>Production worker headcount</t>
+        </is>
+      </c>
+      <c r="B110" s="260" t="inlineStr">
+        <is>
+          <t>Not in the Competitors' Profiles report, so the production payroll delta is not costed. Check the pro forma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="200" t="inlineStr">
+        <is>
+          <t>Printer price</t>
+        </is>
+      </c>
+      <c r="B111" s="260" t="inlineStr">
+        <is>
+          <t>~$240,000 assumed for the NYC tier. Verify before any purchase.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="200" t="inlineStr">
+        <is>
+          <t>Share targets</t>
+        </is>
+      </c>
+      <c r="B112" s="260" t="inlineStr">
+        <is>
+          <t>Directional. They assume the unit build lands and the mix follows Q3 proportions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="200" t="inlineStr">
+        <is>
+          <t>Before advancing</t>
+        </is>
+      </c>
+      <c r="B113" s="260" t="inlineStr">
+        <is>
+          <t>Run Production Simulation, then Cash Flow and pro forma. Confirm ending Cash + CD &gt;= $300,000.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:F2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quarters/Q3/Q3Data.xlsx
+++ b/quarters/Q3/Q3Data.xlsx
@@ -52,6 +52,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_Ad_Judgment" sheetId="44" state="visible" r:id="rId44"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_Competitor_Ads" sheetId="45" state="visible" r:id="rId45"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q4_Copy_The_Leader" sheetId="46" state="visible" r:id="rId46"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q4_Brand_Count" sheetId="47" state="visible" r:id="rId47"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -667,7 +668,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="16"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="16"/>
   </cellStyleXfs>
-  <cellXfs count="263">
+  <cellXfs count="265">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1033,6 +1034,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="32" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -56576,6 +56583,1424 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G97"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="52" customWidth="1" style="146" min="1" max="1"/>
+    <col width="22" customWidth="1" style="146" min="2" max="2"/>
+    <col width="20" customWidth="1" style="146" min="3" max="3"/>
+    <col width="24" customWidth="1" style="146" min="4" max="4"/>
+    <col width="76" customWidth="1" style="146" min="5" max="5"/>
+    <col width="18" customWidth="1" style="146" min="6" max="6"/>
+    <col width="14" customWidth="1" style="146" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="169" t="inlineStr">
+        <is>
+          <t>Do we add more bikes?  ANSWER: not in Q4 — capacity binds. Spec for Q5 below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="46" customHeight="1" s="146">
+      <c r="A2" s="258" t="inlineStr">
+        <is>
+          <t>Brand count does not explain segment share anywhere in this industry. Effective capacity and sales coverage do. BB LLC's second brands work because they own 30.9 effective capacity and 21 sales people; Bike Bros' second brands do nothing because they own 15 and 7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="199" t="inlineStr">
+        <is>
+          <t>Segment</t>
+        </is>
+      </c>
+      <c r="B4" s="199" t="inlineStr">
+        <is>
+          <t>Firm</t>
+        </is>
+      </c>
+      <c r="C4" s="199" t="inlineStr">
+        <is>
+          <t>Brands in segment</t>
+        </is>
+      </c>
+      <c r="D4" s="199" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="E4" s="199" t="inlineStr">
+        <is>
+          <t>Share</t>
+        </is>
+      </c>
+      <c r="F4" s="199" t="inlineStr">
+        <is>
+          <t>Effective OC/day</t>
+        </is>
+      </c>
+      <c r="G4" s="199" t="inlineStr">
+        <is>
+          <t>Sales people</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="200" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="B5" s="200" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="C5" s="200" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="200" t="n">
+        <v>657</v>
+      </c>
+      <c r="E5" s="228" t="n">
+        <v>0.2283</v>
+      </c>
+      <c r="F5" s="225" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="G5" s="200" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="200" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="B6" s="200" t="inlineStr">
+        <is>
+          <t>SpaceBikes</t>
+        </is>
+      </c>
+      <c r="C6" s="200" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="200" t="n">
+        <v>588</v>
+      </c>
+      <c r="E6" s="228" t="n">
+        <v>0.2043</v>
+      </c>
+      <c r="F6" s="225" t="n">
+        <v>30</v>
+      </c>
+      <c r="G6" s="200" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="200" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="B7" s="200" t="inlineStr">
+        <is>
+          <t>LiteCycle</t>
+        </is>
+      </c>
+      <c r="C7" s="200" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="200" t="n">
+        <v>548</v>
+      </c>
+      <c r="E7" s="228" t="n">
+        <v>0.1904</v>
+      </c>
+      <c r="F7" s="225" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="G7" s="200" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="200" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="B8" s="200" t="inlineStr">
+        <is>
+          <t>Spoke'd Up</t>
+        </is>
+      </c>
+      <c r="C8" s="200" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="200" t="n">
+        <v>362</v>
+      </c>
+      <c r="E8" s="228" t="n">
+        <v>0.1258</v>
+      </c>
+      <c r="F8" s="225" t="n">
+        <v>16.88</v>
+      </c>
+      <c r="G8" s="200" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="200" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="B9" s="200" t="inlineStr">
+        <is>
+          <t>MILC Bikes</t>
+        </is>
+      </c>
+      <c r="C9" s="200" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="200" t="n">
+        <v>328</v>
+      </c>
+      <c r="E9" s="228" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="F9" s="225" t="n">
+        <v>17</v>
+      </c>
+      <c r="G9" s="200" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="209" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="B10" s="209" t="inlineStr">
+        <is>
+          <t>WeBike</t>
+        </is>
+      </c>
+      <c r="C10" s="209" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="209" t="n">
+        <v>215</v>
+      </c>
+      <c r="E10" s="246" t="n">
+        <v>0.0747</v>
+      </c>
+      <c r="F10" s="226" t="n">
+        <v>9</v>
+      </c>
+      <c r="G10" s="209" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="200" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="B11" s="200" t="inlineStr">
+        <is>
+          <t>Bike Bros</t>
+        </is>
+      </c>
+      <c r="C11" s="200" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" s="200" t="n">
+        <v>180</v>
+      </c>
+      <c r="E11" s="228" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="F11" s="225" t="n">
+        <v>15</v>
+      </c>
+      <c r="G11" s="200" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="200" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="B12" s="200" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="C12" s="200" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="200" t="n">
+        <v>751</v>
+      </c>
+      <c r="E12" s="228" t="n">
+        <v>0.4633</v>
+      </c>
+      <c r="F12" s="225" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="G12" s="200" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="209" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="B13" s="209" t="inlineStr">
+        <is>
+          <t>WeBike</t>
+        </is>
+      </c>
+      <c r="C13" s="209" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="209" t="n">
+        <v>358</v>
+      </c>
+      <c r="E13" s="246" t="n">
+        <v>0.2209</v>
+      </c>
+      <c r="F13" s="226" t="n">
+        <v>9</v>
+      </c>
+      <c r="G13" s="209" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="200" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="B14" s="200" t="inlineStr">
+        <is>
+          <t>LiteCycle</t>
+        </is>
+      </c>
+      <c r="C14" s="200" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="200" t="n">
+        <v>340</v>
+      </c>
+      <c r="E14" s="228" t="n">
+        <v>0.2097</v>
+      </c>
+      <c r="F14" s="225" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="G14" s="200" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="200" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="B15" s="200" t="inlineStr">
+        <is>
+          <t>Bike Bros</t>
+        </is>
+      </c>
+      <c r="C15" s="200" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="200" t="n">
+        <v>172</v>
+      </c>
+      <c r="E15" s="228" t="n">
+        <v>0.1061</v>
+      </c>
+      <c r="F15" s="225" t="n">
+        <v>15</v>
+      </c>
+      <c r="G15" s="200" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="200" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="B16" s="200" t="inlineStr">
+        <is>
+          <t>SpaceBikes</t>
+        </is>
+      </c>
+      <c r="C16" s="200" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="200" t="n">
+        <v>710</v>
+      </c>
+      <c r="E16" s="228" t="n">
+        <v>0.3447</v>
+      </c>
+      <c r="F16" s="225" t="n">
+        <v>30</v>
+      </c>
+      <c r="G16" s="200" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="200" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="B17" s="200" t="inlineStr">
+        <is>
+          <t>Spoke'd Up</t>
+        </is>
+      </c>
+      <c r="C17" s="200" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="200" t="n">
+        <v>492</v>
+      </c>
+      <c r="E17" s="228" t="n">
+        <v>0.2388</v>
+      </c>
+      <c r="F17" s="225" t="n">
+        <v>16.88</v>
+      </c>
+      <c r="G17" s="200" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="200" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="B18" s="200" t="inlineStr">
+        <is>
+          <t>MILC Bikes</t>
+        </is>
+      </c>
+      <c r="C18" s="200" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="200" t="n">
+        <v>471</v>
+      </c>
+      <c r="E18" s="228" t="n">
+        <v>0.2286</v>
+      </c>
+      <c r="F18" s="225" t="n">
+        <v>17</v>
+      </c>
+      <c r="G18" s="200" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="200" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="B19" s="200" t="inlineStr">
+        <is>
+          <t>Bike Bros</t>
+        </is>
+      </c>
+      <c r="C19" s="200" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="200" t="n">
+        <v>122</v>
+      </c>
+      <c r="E19" s="228" t="n">
+        <v>0.0592</v>
+      </c>
+      <c r="F19" s="225" t="n">
+        <v>15</v>
+      </c>
+      <c r="G19" s="200" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="199" t="inlineStr">
+        <is>
+          <t>THE COUNTEREXAMPLES THAT KILL THE 'MORE BRANDS' ARGUMENT</t>
+        </is>
+      </c>
+      <c r="B22" s="199" t="inlineStr">
+        <is>
+          <t>Brands</t>
+        </is>
+      </c>
+      <c r="C22" s="199" t="inlineStr">
+        <is>
+          <t>Share</t>
+        </is>
+      </c>
+      <c r="D22" s="199" t="inlineStr">
+        <is>
+          <t>Effective OC</t>
+        </is>
+      </c>
+      <c r="E22" s="259" t="inlineStr">
+        <is>
+          <t>Sales people</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="200" t="inlineStr">
+        <is>
+          <t>SpaceBikes in Speed</t>
+        </is>
+      </c>
+      <c r="B23" s="206" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="200" t="inlineStr">
+        <is>
+          <t>20.4%</t>
+        </is>
+      </c>
+      <c r="D23" s="200" t="n">
+        <v>30</v>
+      </c>
+      <c r="E23" s="260" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="200" t="inlineStr">
+        <is>
+          <t>LiteCycle in Speed</t>
+        </is>
+      </c>
+      <c r="B24" s="200" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" s="200" t="inlineStr">
+        <is>
+          <t>19.0%</t>
+        </is>
+      </c>
+      <c r="D24" s="200" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="E24" s="260" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="200" t="inlineStr">
+        <is>
+          <t>Bike Bros in Speed</t>
+        </is>
+      </c>
+      <c r="B25" s="204" t="n">
+        <v>2</v>
+      </c>
+      <c r="C25" s="200" t="inlineStr">
+        <is>
+          <t>6.3%</t>
+        </is>
+      </c>
+      <c r="D25" s="200" t="n">
+        <v>15</v>
+      </c>
+      <c r="E25" s="260" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="200" t="inlineStr">
+        <is>
+          <t>WeBike in Speed</t>
+        </is>
+      </c>
+      <c r="B26" s="200" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="200" t="inlineStr">
+        <is>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D26" s="200" t="n">
+        <v>9</v>
+      </c>
+      <c r="E26" s="260" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="200" t="inlineStr">
+        <is>
+          <t>LiteCycle in Mountain</t>
+        </is>
+      </c>
+      <c r="B27" s="200" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="200" t="inlineStr">
+        <is>
+          <t>21.0%</t>
+        </is>
+      </c>
+      <c r="D27" s="200" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="E27" s="260" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="200" t="inlineStr">
+        <is>
+          <t>Bike Bros in Mountain</t>
+        </is>
+      </c>
+      <c r="B28" s="206" t="n">
+        <v>2</v>
+      </c>
+      <c r="C28" s="200" t="inlineStr">
+        <is>
+          <t>10.6%</t>
+        </is>
+      </c>
+      <c r="D28" s="200" t="n">
+        <v>15</v>
+      </c>
+      <c r="E28" s="260" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="200" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="B29" s="200" t="n"/>
+      <c r="C29" s="200" t="n"/>
+      <c r="D29" s="204" t="n"/>
+      <c r="E29" s="260" t="inlineStr">
+        <is>
+          <t>One brand with capacity beats two without it, every time. Bike Bros runs the most brands in the industry (5) and finished last.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="199" t="inlineStr">
+        <is>
+          <t>BUT SECOND BRANDS ARE 41% OF THE LEADER'S DEMAND</t>
+        </is>
+      </c>
+      <c r="B32" s="199" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C32" s="199" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="D32" s="199" t="inlineStr">
+        <is>
+          <t>Advertised?</t>
+        </is>
+      </c>
+      <c r="E32" s="259" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="200" t="inlineStr">
+        <is>
+          <t>Blu Ruged Ballz (Mountain, lead)</t>
+        </is>
+      </c>
+      <c r="B33" s="200" t="n">
+        <v>73</v>
+      </c>
+      <c r="C33" s="200" t="n">
+        <v>1365</v>
+      </c>
+      <c r="D33" s="200" t="inlineStr">
+        <is>
+          <t>yes — BB Big Momma 81</t>
+        </is>
+      </c>
+      <c r="E33" s="260" t="n">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="200" t="inlineStr">
+        <is>
+          <t>Blu Tail Ballz (Mountain, second)</t>
+        </is>
+      </c>
+      <c r="B34" s="200" t="n">
+        <v>70</v>
+      </c>
+      <c r="C34" s="200" t="n">
+        <v>1365</v>
+      </c>
+      <c r="D34" s="211" t="inlineStr">
+        <is>
+          <t>NO AD AT ALL</t>
+        </is>
+      </c>
+      <c r="E34" s="260" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="200" t="inlineStr">
+        <is>
+          <t>Blu Tube Ballz (Speed, lead)</t>
+        </is>
+      </c>
+      <c r="B35" s="200" t="n">
+        <v>76</v>
+      </c>
+      <c r="C35" s="200" t="n">
+        <v>1580</v>
+      </c>
+      <c r="D35" s="200" t="inlineStr">
+        <is>
+          <t>yes — Unleash lil pap 76</t>
+        </is>
+      </c>
+      <c r="E35" s="260" t="n">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="200" t="inlineStr">
+        <is>
+          <t>Blu Aero Ballz (Speed, second)</t>
+        </is>
+      </c>
+      <c r="B36" s="200" t="n">
+        <v>74</v>
+      </c>
+      <c r="C36" s="200" t="n">
+        <v>1580</v>
+      </c>
+      <c r="D36" s="211" t="inlineStr">
+        <is>
+          <t>NO AD AT ALL</t>
+        </is>
+      </c>
+      <c r="E36" s="260" t="n">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="200" t="inlineStr">
+        <is>
+          <t>Second brands combined</t>
+        </is>
+      </c>
+      <c r="B37" s="200" t="n"/>
+      <c r="C37" s="200" t="n"/>
+      <c r="D37" s="200" t="n"/>
+      <c r="E37" s="263" t="n">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="200" t="inlineStr">
+        <is>
+          <t>Pattern</t>
+        </is>
+      </c>
+      <c r="B38" s="200" t="n"/>
+      <c r="C38" s="200" t="n"/>
+      <c r="D38" s="200" t="n"/>
+      <c r="E38" s="260" t="inlineStr">
+        <is>
+          <t>Same price as the lead brand — NOT higher. Slightly lower judgment. No advertising. 612 units, or 41% of their 1,507 total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="200" t="inlineStr">
+        <is>
+          <t>Hypothesis (UNVERIFIED)</t>
+        </is>
+      </c>
+      <c r="B39" s="200" t="n"/>
+      <c r="C39" s="200" t="n"/>
+      <c r="D39" s="200" t="n"/>
+      <c r="E39" s="262" t="inlineStr">
+        <is>
+          <t>The second brand omits accessories to cut unit cost while charging the same price, because Speed shows zero resistance to $1,580. Blu Aero drops decals AND lights; LiteSpeed+ drops decals AND reflectors. Alternative reading: they just didn't optimise brand #2. We have no component price list — read the costs on the Design Brand screen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="199" t="inlineStr">
+        <is>
+          <t>WHY NOT IN Q4 — the capacity arithmetic</t>
+        </is>
+      </c>
+      <c r="B42" s="199" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="C42" s="259" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="200" t="inlineStr">
+        <is>
+          <t>Q4 plan of record demand forecast</t>
+        </is>
+      </c>
+      <c r="B43" s="200" t="n">
+        <v>1171</v>
+      </c>
+      <c r="C43" s="260" t="inlineStr">
+        <is>
+          <t>Rio filled to cap + full web rebuild</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="200" t="inlineStr">
+        <is>
+          <t>Capacity: 24/day x 74% x 65 days</t>
+        </is>
+      </c>
+      <c r="B44" s="200" t="n">
+        <v>1154</v>
+      </c>
+      <c r="C44" s="260" t="inlineStr">
+        <is>
+          <t>100% of what we own, zero overtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="200" t="inlineStr">
+        <is>
+          <t>Slack before adding anything</t>
+        </is>
+      </c>
+      <c r="B45" s="204" t="n">
+        <v>-17</v>
+      </c>
+      <c r="C45" s="260" t="inlineStr">
+        <is>
+          <t>we are ALREADY 1.4% over — there is no room</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="200" t="inlineStr">
+        <is>
+          <t>A second Speed brand would add</t>
+        </is>
+      </c>
+      <c r="B46" s="200" t="n">
+        <v>363</v>
+      </c>
+      <c r="C46" s="260" t="inlineStr">
+        <is>
+          <t>74–81% of the lead brand, per BB LLC and LiteCycle</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="200" t="inlineStr">
+        <is>
+          <t>Resulting unfilled demand</t>
+        </is>
+      </c>
+      <c r="B47" s="204" t="n">
+        <v>380</v>
+      </c>
+      <c r="C47" s="260" t="inlineStr">
+        <is>
+          <t>25% stock-out rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="200" t="inlineStr">
+        <is>
+          <t>Resulting Q5 ill will</t>
+        </is>
+      </c>
+      <c r="B48" s="204" t="inlineStr">
+        <is>
+          <t>~12%</t>
+        </is>
+      </c>
+      <c r="C48" s="260" t="inlineStr">
+        <is>
+          <t>half the unmet percentage</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="200" t="inlineStr">
+        <is>
+          <t>Q3 for comparison</t>
+        </is>
+      </c>
+      <c r="B49" s="200" t="n">
+        <v>204</v>
+      </c>
+      <c r="C49" s="260" t="inlineStr">
+        <is>
+          <t>33% stock-out, 16.3% ill will, LAST place in the industry</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="200" t="inlineStr">
+        <is>
+          <t>Required operating capacity</t>
+        </is>
+      </c>
+      <c r="B50" s="200" t="inlineStr">
+        <is>
+          <t>31.9/day</t>
+        </is>
+      </c>
+      <c r="C50" s="260" t="inlineStr">
+        <is>
+          <t>needs a 4th printer (~$240,000) to serve it</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="200" t="inlineStr">
+        <is>
+          <t>VERDICT</t>
+        </is>
+      </c>
+      <c r="B51" s="200" t="n"/>
+      <c r="C51" s="260" t="inlineStr">
+        <is>
+          <t>Adding a brand in Q4 recreates the exact failure we are fixing. It is not a brand decision, it is a printer decision — and the printer money is better spent on Rio staff and the web rebuild, which need no capex at all.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="165" t="n"/>
+      <c r="C52" s="167" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="199" t="inlineStr">
+        <is>
+          <t>BRAND 3 — second SPEED brand (first to add, once capacity exists)</t>
+        </is>
+      </c>
+      <c r="B54" s="259" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="200" t="inlineStr">
+        <is>
+          <t>Why Speed</t>
+        </is>
+      </c>
+      <c r="B55" s="260" t="inlineStr">
+        <is>
+          <t>Largest segment at 2,878 vs Mountain's 1,621, we hold only 7.5%, and it is the least price-sensitive segment in the game — judgment holds at 100 up to $1,580 and resistance only starts at $1,749. Contribution at $1,580 is $886/unit, our best.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="200" t="inlineStr">
+        <is>
+          <t>Frame</t>
+        </is>
+      </c>
+      <c r="B56" s="260" t="inlineStr">
+        <is>
+          <t>Aerodynamic</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="200" t="inlineStr">
+        <is>
+          <t>Tires</t>
+        </is>
+      </c>
+      <c r="B57" s="260" t="inlineStr">
+        <is>
+          <t>Racing - fast</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="200" t="inlineStr">
+        <is>
+          <t>Brakes</t>
+        </is>
+      </c>
+      <c r="B58" s="260" t="inlineStr">
+        <is>
+          <t>Precision</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="200" t="inlineStr">
+        <is>
+          <t>Handlebars</t>
+        </is>
+      </c>
+      <c r="B59" s="260" t="inlineStr">
+        <is>
+          <t>Basic drop down</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="200" t="inlineStr">
+        <is>
+          <t>Seat</t>
+        </is>
+      </c>
+      <c r="B60" s="260" t="inlineStr">
+        <is>
+          <t>Polymer gel racing</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="200" t="inlineStr">
+        <is>
+          <t>Gears</t>
+        </is>
+      </c>
+      <c r="B61" s="260" t="inlineStr">
+        <is>
+          <t>14 speed (2x7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="200" t="inlineStr">
+        <is>
+          <t>Decals</t>
+        </is>
+      </c>
+      <c r="B62" s="261" t="inlineStr">
+        <is>
+          <t>Colorful thin brushstrokes — INCLUDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="200" t="inlineStr">
+        <is>
+          <t>Lights</t>
+        </is>
+      </c>
+      <c r="B63" s="261" t="inlineStr">
+        <is>
+          <t>Standard — INCLUDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="200" t="inlineStr">
+        <is>
+          <t>Reflectors</t>
+        </is>
+      </c>
+      <c r="B64" s="261" t="inlineStr">
+        <is>
+          <t>OMIT (this is what makes it 76 not 77)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="200" t="inlineStr">
+        <is>
+          <t>Carrier / suspension</t>
+        </is>
+      </c>
+      <c r="B65" s="260" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="200" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="B66" s="261" t="inlineStr">
+        <is>
+          <t>76 — copies Blu Tube Ballz, The Armstrong AND Skim MILC, three firms that independently converged on this exact spec. Add reflectors for 77 only if the screen shows they are cheap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="200" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="B67" s="261" t="inlineStr">
+        <is>
+          <t>$1,580 — identical to Swift Bike, exactly as BB LLC prices both of theirs</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="200" t="inlineStr">
+        <is>
+          <t>Advertising</t>
+        </is>
+      </c>
+      <c r="B68" s="261" t="inlineStr">
+        <is>
+          <t>NONE. BB LLC leaves both second brands unadvertised and leads the industry. Keep media concentrated on the two ads we already have.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="200" t="inlineStr">
+        <is>
+          <t>Trigger to build it</t>
+        </is>
+      </c>
+      <c r="B69" s="262" t="inlineStr">
+        <is>
+          <t>Owned capacity comfortably exceeds forecast demand AND both existing brands are fully supplied. Realistically Q5, after Q4 proves the supply fix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="199" t="inlineStr">
+        <is>
+          <t>BRAND 4 — second MOUNTAIN brand (lower priority)</t>
+        </is>
+      </c>
+      <c r="B72" s="259" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="200" t="inlineStr">
+        <is>
+          <t>Why later</t>
+        </is>
+      </c>
+      <c r="B73" s="260" t="inlineStr">
+        <is>
+          <t>Mountain is the smallest and slowest-growing segment (1,621) and we are already #2 at 22.1%. Speed has four times the headroom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="200" t="inlineStr">
+        <is>
+          <t>Spec</t>
+        </is>
+      </c>
+      <c r="B74" s="260" t="inlineStr">
+        <is>
+          <t>The exact Hike Bike recipe but with the polymer gel COMFORT seat instead of all-purpose (−3 → judgment 70). This is Blu Tail Ballz and LiteTrail Pro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="200" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="B75" s="260" t="inlineStr">
+        <is>
+          <t>$1,365 — identical to Hike Bike, as BB LLC does</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="200" t="inlineStr">
+        <is>
+          <t>Advertising</t>
+        </is>
+      </c>
+      <c r="B76" s="260" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="199" t="inlineStr">
+        <is>
+          <t>BRAND 5 — RECREATION (Q5+ at the earliest; fights our margin strategy)</t>
+        </is>
+      </c>
+      <c r="B79" s="259" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="200" t="inlineStr">
+        <is>
+          <t>Spec = MountainCruise1, the only brand at the Recreation ceiling</t>
+        </is>
+      </c>
+      <c r="B80" s="260" t="inlineStr">
+        <is>
+          <t>judgment 76</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="200" t="inlineStr">
+        <is>
+          <t>Frame</t>
+        </is>
+      </c>
+      <c r="B81" s="260" t="inlineStr">
+        <is>
+          <t>Comfort (relaxed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="200" t="inlineStr">
+        <is>
+          <t>Tires</t>
+        </is>
+      </c>
+      <c r="B82" s="260" t="inlineStr">
+        <is>
+          <t>Hybrid - road and off-road</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="200" t="inlineStr">
+        <is>
+          <t>Brakes</t>
+        </is>
+      </c>
+      <c r="B83" s="260" t="inlineStr">
+        <is>
+          <t>STANDARD DISC — not precision, not standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="200" t="inlineStr">
+        <is>
+          <t>Handlebars</t>
+        </is>
+      </c>
+      <c r="B84" s="260" t="inlineStr">
+        <is>
+          <t>Comfort straight</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="200" t="inlineStr">
+        <is>
+          <t>Gears</t>
+        </is>
+      </c>
+      <c r="B85" s="260" t="inlineStr">
+        <is>
+          <t>7 speed (1x7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="200" t="inlineStr">
+        <is>
+          <t>Seat</t>
+        </is>
+      </c>
+      <c r="B86" s="260" t="inlineStr">
+        <is>
+          <t>Polymer gel comfort</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="200" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="B87" s="260" t="inlineStr">
+        <is>
+          <t>Reflectors + decals + lights + plastic basket + front shocks — all of them</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="200" t="inlineStr">
+        <is>
+          <t>THE PROBLEM</t>
+        </is>
+      </c>
+      <c r="B88" s="264" t="inlineStr">
+        <is>
+          <t>Every Recreation winner sits at price judgment 100, which means cheapest in the game: Whole MILC $950 net, Spoke'd Easy $999, Mars Rover $1,050 net. Our $1,365 scores only 81 in Recreation. Entering means accepting low margin, which contradicts our locked profit-margin-leader intent. Hike Bike already scores 56 with Recreation buyers and pulled 54 units of pure spillover, so there is no cheap way in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="200" t="inlineStr">
+        <is>
+          <t>Caveat on the spec</t>
+        </is>
+      </c>
+      <c r="B89" s="262" t="inlineStr">
+        <is>
+          <t>Only 4 Recreation brands exist and they differ in 3 places, so individual penalties are NOT uniquely identifiable. MountainCruise1's exact recipe is known to score 76; the reason each component matters is not.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="199" t="inlineStr">
+        <is>
+          <t>WHAT WE DO INSTEAD IN Q4</t>
+        </is>
+      </c>
+      <c r="B92" s="259" t="inlineStr">
+        <is>
+          <t>Why it beats a third brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="200" t="inlineStr">
+        <is>
+          <t>Fill Rio to the 7-person cap</t>
+        </is>
+      </c>
+      <c r="B93" s="260" t="inlineStr">
+        <is>
+          <t>~+180 store units at Rio's measured 60/head. No design fee, no lease, no printer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="200" t="inlineStr">
+        <is>
+          <t>Rebuild the web (4 tactics + 7 staff)</t>
+        </is>
+      </c>
+      <c r="B94" s="260" t="inlineStr">
+        <is>
+          <t>120 → 435+ units. Every firm funding all four lands 435–569. No printer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="200" t="inlineStr">
+        <is>
+          <t>Swift Bike to 77 and $1,580</t>
+        </is>
+      </c>
+      <c r="B95" s="260" t="inlineStr">
+        <is>
+          <t>Raises share AND margin in the segment where a third brand would go — without adding a unit of demand we cannot build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="200" t="inlineStr">
+        <is>
+          <t>Restore Biking inserts to 12 + 12</t>
+        </is>
+      </c>
+      <c r="B96" s="260" t="inlineStr">
+        <is>
+          <t>Five more inserts than Q3 for $8,000 LESS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="200" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B97" s="260" t="inlineStr">
+        <is>
+          <t>Every one of these lifts the same segments a third brand would target, costs less, and does not create demand we would fail to serve. A third brand is a Q5 move that follows a printer.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:G2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/quarters/Q3/Q3Data.xlsx
+++ b/quarters/Q3/Q3Data.xlsx
@@ -53,6 +53,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_Competitor_Ads" sheetId="45" state="visible" r:id="rId45"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q4_Copy_The_Leader" sheetId="46" state="visible" r:id="rId46"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q4_Brand_Count" sheetId="47" state="visible" r:id="rId47"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q4_RD" sheetId="48" state="visible" r:id="rId48"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -668,7 +669,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="16"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="16"/>
   </cellStyleXfs>
-  <cellXfs count="265">
+  <cellXfs count="267">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1040,6 +1041,10 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="31" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="28" fillId="29" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -58001,6 +58006,1253 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I78"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" style="146" min="1" max="1"/>
+    <col width="14" customWidth="1" style="146" min="2" max="2"/>
+    <col width="14" customWidth="1" style="146" min="3" max="3"/>
+    <col width="88" customWidth="1" style="146" min="4" max="4"/>
+    <col width="13" customWidth="1" style="146" min="5" max="5"/>
+    <col width="13" customWidth="1" style="146" min="6" max="6"/>
+    <col width="13" customWidth="1" style="146" min="7" max="7"/>
+    <col width="13" customWidth="1" style="146" min="8" max="8"/>
+    <col width="60" customWidth="1" style="146" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="169" t="inlineStr">
+        <is>
+          <t>Q4 R&amp;D — 3 project slots, scored against segment needs importance</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="62" customHeight="1" s="146">
+      <c r="A2" s="258" t="inlineStr">
+        <is>
+          <t>EVERY rated brand in the industry is 'Acceptable' (70-77). Nobody has reached 'Good' (78-84), 'Very Good' (85-94) or 'Excellent' (95-100). The component ceilings are Mountain 73, Speed 77, Recreation 76 — all inside one band. R&amp;D is the only route into three unclaimed bands. Needs importance from Q1 market research (`Needs` sheet); feature-to-need mapping is our reading of the Workspace descriptions, NOT sim output.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="199" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="B4" s="199" t="inlineStr">
+        <is>
+          <t>Dev cost</t>
+        </is>
+      </c>
+      <c r="C4" s="199" t="inlineStr">
+        <is>
+          <t>Unit cost</t>
+        </is>
+      </c>
+      <c r="D4" s="199" t="inlineStr">
+        <is>
+          <t>Fits our bikes</t>
+        </is>
+      </c>
+      <c r="E4" s="199" t="inlineStr">
+        <is>
+          <t>Mtn score</t>
+        </is>
+      </c>
+      <c r="F4" s="199" t="inlineStr">
+        <is>
+          <t>Speed score</t>
+        </is>
+      </c>
+      <c r="G4" s="199" t="inlineStr">
+        <is>
+          <t>Usable score</t>
+        </is>
+      </c>
+      <c r="H4" s="199" t="inlineStr">
+        <is>
+          <t>Score per $100k</t>
+        </is>
+      </c>
+      <c r="I4" s="259" t="inlineStr">
+        <is>
+          <t>Needs claimed</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="222" t="inlineStr">
+        <is>
+          <t>Decals: bright, per segment</t>
+        </is>
+      </c>
+      <c r="B5" s="265" t="n">
+        <v>109155</v>
+      </c>
+      <c r="C5" s="222" t="n">
+        <v>8</v>
+      </c>
+      <c r="D5" s="222" t="inlineStr">
+        <is>
+          <t>BOTH</t>
+        </is>
+      </c>
+      <c r="E5" s="222" t="n">
+        <v>472</v>
+      </c>
+      <c r="F5" s="222" t="n">
+        <v>457</v>
+      </c>
+      <c r="G5" s="222" t="n">
+        <v>929</v>
+      </c>
+      <c r="H5" s="222" t="n">
+        <v>851.1</v>
+      </c>
+      <c r="I5" s="263" t="inlineStr">
+        <is>
+          <t>Colorful, Stylish, Fits rider's personality, Status symbol/exclusivity</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="222" t="inlineStr">
+        <is>
+          <t>Gears: 11 speed (1x11)</t>
+        </is>
+      </c>
+      <c r="B6" s="265" t="n">
+        <v>568514</v>
+      </c>
+      <c r="C6" s="222" t="n">
+        <v>50</v>
+      </c>
+      <c r="D6" s="222" t="inlineStr">
+        <is>
+          <t>BOTH</t>
+        </is>
+      </c>
+      <c r="E6" s="222" t="n">
+        <v>472</v>
+      </c>
+      <c r="F6" s="222" t="n">
+        <v>433</v>
+      </c>
+      <c r="G6" s="222" t="n">
+        <v>905</v>
+      </c>
+      <c r="H6" s="222" t="n">
+        <v>159.2</v>
+      </c>
+      <c r="I6" s="263" t="inlineStr">
+        <is>
+          <t>Shifts smoothly, Light weight, Easily handles change in incline, Simple to use</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="222" t="inlineStr">
+        <is>
+          <t>Enriched carbon fiber</t>
+        </is>
+      </c>
+      <c r="B7" s="265" t="n">
+        <v>1023325</v>
+      </c>
+      <c r="C7" s="222" t="n">
+        <v>40</v>
+      </c>
+      <c r="D7" s="222" t="inlineStr">
+        <is>
+          <t>BOTH</t>
+        </is>
+      </c>
+      <c r="E7" s="222" t="n">
+        <v>365</v>
+      </c>
+      <c r="F7" s="222" t="n">
+        <v>374</v>
+      </c>
+      <c r="G7" s="222" t="n">
+        <v>739</v>
+      </c>
+      <c r="H7" s="222" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="I7" s="263" t="inlineStr">
+        <is>
+          <t>Light weight, Durable, Provides competitive advantage</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="200" t="inlineStr">
+        <is>
+          <t>Performance bike computer</t>
+        </is>
+      </c>
+      <c r="B8" s="220" t="n">
+        <v>682217</v>
+      </c>
+      <c r="C8" s="200" t="n">
+        <v>60</v>
+      </c>
+      <c r="D8" s="200" t="inlineStr">
+        <is>
+          <t>BOTH</t>
+        </is>
+      </c>
+      <c r="E8" s="200" t="n">
+        <v>340</v>
+      </c>
+      <c r="F8" s="200" t="n">
+        <v>359</v>
+      </c>
+      <c r="G8" s="200" t="n">
+        <v>699</v>
+      </c>
+      <c r="H8" s="200" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="I8" s="260" t="inlineStr">
+        <is>
+          <t>Navigation assistance, Provides competitive advantage, Precise speed control-turns, hills</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="200" t="inlineStr">
+        <is>
+          <t>Puncture resistant slime</t>
+        </is>
+      </c>
+      <c r="B9" s="220" t="n">
+        <v>159184</v>
+      </c>
+      <c r="C9" s="200" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="200" t="inlineStr">
+        <is>
+          <t>BOTH</t>
+        </is>
+      </c>
+      <c r="E9" s="200" t="n">
+        <v>341</v>
+      </c>
+      <c r="F9" s="200" t="n">
+        <v>299</v>
+      </c>
+      <c r="G9" s="200" t="n">
+        <v>640</v>
+      </c>
+      <c r="H9" s="200" t="n">
+        <v>402.1</v>
+      </c>
+      <c r="I9" s="260" t="inlineStr">
+        <is>
+          <t>Durable, Safety, Simple to use</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="200" t="inlineStr">
+        <is>
+          <t>Tires: Racing sleek very fast</t>
+        </is>
+      </c>
+      <c r="B10" s="220" t="n">
+        <v>254694</v>
+      </c>
+      <c r="C10" s="200" t="n">
+        <v>35</v>
+      </c>
+      <c r="D10" s="200" t="inlineStr">
+        <is>
+          <t>Swift Bike</t>
+        </is>
+      </c>
+      <c r="E10" s="200" t="n">
+        <v>549</v>
+      </c>
+      <c r="F10" s="200" t="n">
+        <v>602</v>
+      </c>
+      <c r="G10" s="200" t="n">
+        <v>602</v>
+      </c>
+      <c r="H10" s="200" t="n">
+        <v>236.4</v>
+      </c>
+      <c r="I10" s="260" t="inlineStr">
+        <is>
+          <t>Speed, Can turn sharply, Durable, Sleek, Precise speed control-turns, hills</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="200" t="inlineStr">
+        <is>
+          <t>Suspension: full (front+back)</t>
+        </is>
+      </c>
+      <c r="B11" s="220" t="n">
+        <v>618543</v>
+      </c>
+      <c r="C11" s="200" t="n">
+        <v>85</v>
+      </c>
+      <c r="D11" s="200" t="inlineStr">
+        <is>
+          <t>Hike Bike</t>
+        </is>
+      </c>
+      <c r="E11" s="200" t="n">
+        <v>542</v>
+      </c>
+      <c r="F11" s="200" t="n">
+        <v>477</v>
+      </c>
+      <c r="G11" s="200" t="n">
+        <v>542</v>
+      </c>
+      <c r="H11" s="200" t="n">
+        <v>87.59999999999999</v>
+      </c>
+      <c r="I11" s="260" t="inlineStr">
+        <is>
+          <t>Soften the impact of rough terrain, Can handle rough terrain, Comfortable, Soft ride, Precise speed control-turns, hills</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="200" t="inlineStr">
+        <is>
+          <t>Bars: Power straight</t>
+        </is>
+      </c>
+      <c r="B12" s="220" t="n">
+        <v>181924</v>
+      </c>
+      <c r="C12" s="200" t="n">
+        <v>17</v>
+      </c>
+      <c r="D12" s="200" t="inlineStr">
+        <is>
+          <t>Hike Bike</t>
+        </is>
+      </c>
+      <c r="E12" s="200" t="n">
+        <v>509</v>
+      </c>
+      <c r="F12" s="200" t="n">
+        <v>438</v>
+      </c>
+      <c r="G12" s="200" t="n">
+        <v>509</v>
+      </c>
+      <c r="H12" s="200" t="n">
+        <v>279.8</v>
+      </c>
+      <c r="I12" s="260" t="inlineStr">
+        <is>
+          <t>Can handle rough terrain, Rider expertise required, Durable, Easily handles change in incline</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="200" t="inlineStr">
+        <is>
+          <t>Tires: Mountain super traction</t>
+        </is>
+      </c>
+      <c r="B13" s="220" t="n">
+        <v>254694</v>
+      </c>
+      <c r="C13" s="200" t="n">
+        <v>30</v>
+      </c>
+      <c r="D13" s="200" t="inlineStr">
+        <is>
+          <t>Hike Bike</t>
+        </is>
+      </c>
+      <c r="E13" s="200" t="n">
+        <v>502</v>
+      </c>
+      <c r="F13" s="200" t="n">
+        <v>424</v>
+      </c>
+      <c r="G13" s="200" t="n">
+        <v>502</v>
+      </c>
+      <c r="H13" s="200" t="n">
+        <v>197.1</v>
+      </c>
+      <c r="I13" s="260" t="inlineStr">
+        <is>
+          <t>Can handle rough terrain, Can turn sharply, Durable, Can stop quickly</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="200" t="inlineStr">
+        <is>
+          <t>Bars: Carbon aero drop down</t>
+        </is>
+      </c>
+      <c r="B14" s="220" t="n">
+        <v>336560</v>
+      </c>
+      <c r="C14" s="200" t="n">
+        <v>40</v>
+      </c>
+      <c r="D14" s="200" t="inlineStr">
+        <is>
+          <t>Swift Bike</t>
+        </is>
+      </c>
+      <c r="E14" s="200" t="n">
+        <v>387</v>
+      </c>
+      <c r="F14" s="200" t="n">
+        <v>475</v>
+      </c>
+      <c r="G14" s="200" t="n">
+        <v>475</v>
+      </c>
+      <c r="H14" s="200" t="n">
+        <v>141.1</v>
+      </c>
+      <c r="I14" s="260" t="inlineStr">
+        <is>
+          <t>Aerodynamic, Light weight, Sleek, Comfortable</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="200" t="inlineStr">
+        <is>
+          <t>Bars: Carbon fiber riser</t>
+        </is>
+      </c>
+      <c r="B15" s="220" t="n">
+        <v>227406</v>
+      </c>
+      <c r="C15" s="200" t="n">
+        <v>24</v>
+      </c>
+      <c r="D15" s="200" t="inlineStr">
+        <is>
+          <t>Hike Bike</t>
+        </is>
+      </c>
+      <c r="E15" s="200" t="n">
+        <v>464</v>
+      </c>
+      <c r="F15" s="200" t="n">
+        <v>439</v>
+      </c>
+      <c r="G15" s="200" t="n">
+        <v>464</v>
+      </c>
+      <c r="H15" s="200" t="n">
+        <v>204</v>
+      </c>
+      <c r="I15" s="260" t="inlineStr">
+        <is>
+          <t>Comfortable, Soften the impact of rough terrain, Can turn sharply, Light weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="200" t="inlineStr">
+        <is>
+          <t>Lights: high intensity LED</t>
+        </is>
+      </c>
+      <c r="B16" s="220" t="n">
+        <v>140991</v>
+      </c>
+      <c r="C16" s="200" t="n">
+        <v>13</v>
+      </c>
+      <c r="D16" s="200" t="inlineStr">
+        <is>
+          <t>Swift Bike</t>
+        </is>
+      </c>
+      <c r="E16" s="200" t="n">
+        <v>215</v>
+      </c>
+      <c r="F16" s="200" t="n">
+        <v>232</v>
+      </c>
+      <c r="G16" s="200" t="n">
+        <v>232</v>
+      </c>
+      <c r="H16" s="200" t="n">
+        <v>164.5</v>
+      </c>
+      <c r="I16" s="260" t="inlineStr">
+        <is>
+          <t>High visibility, Safety</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="200" t="inlineStr">
+        <is>
+          <t>Tires: Hybrid comfort</t>
+        </is>
+      </c>
+      <c r="B17" s="220" t="n">
+        <v>254694</v>
+      </c>
+      <c r="C17" s="200" t="n">
+        <v>14</v>
+      </c>
+      <c r="D17" s="204" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
+        </is>
+      </c>
+      <c r="E17" s="200" t="n">
+        <v>403</v>
+      </c>
+      <c r="F17" s="200" t="n">
+        <v>372</v>
+      </c>
+      <c r="G17" s="200" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="200" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="260" t="inlineStr">
+        <is>
+          <t>Comfortable, Soft ride, Can turn sharply, On-road and off-road capabilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="200" t="inlineStr">
+        <is>
+          <t>Pedal-powered charger</t>
+        </is>
+      </c>
+      <c r="B18" s="220" t="n">
+        <v>291079</v>
+      </c>
+      <c r="C18" s="200" t="n">
+        <v>28</v>
+      </c>
+      <c r="D18" s="204" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
+        </is>
+      </c>
+      <c r="E18" s="200" t="n">
+        <v>232</v>
+      </c>
+      <c r="F18" s="200" t="n">
+        <v>235</v>
+      </c>
+      <c r="G18" s="200" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="200" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="260" t="inlineStr">
+        <is>
+          <t>Navigation assistance, Feel young at heart</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="200" t="inlineStr">
+        <is>
+          <t>Carrier: mesh folding tote</t>
+        </is>
+      </c>
+      <c r="B19" s="220" t="n">
+        <v>90962</v>
+      </c>
+      <c r="C19" s="200" t="n">
+        <v>12</v>
+      </c>
+      <c r="D19" s="204" t="inlineStr">
+        <is>
+          <t>NEITHER</t>
+        </is>
+      </c>
+      <c r="E19" s="200" t="n">
+        <v>206</v>
+      </c>
+      <c r="F19" s="200" t="n">
+        <v>138</v>
+      </c>
+      <c r="G19" s="200" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="200" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="260" t="inlineStr">
+        <is>
+          <t>Can carry things, Simple to use</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="199" t="inlineStr">
+        <is>
+          <t>RECOMMENDED THREE — all usable on BOTH bikes</t>
+        </is>
+      </c>
+      <c r="B22" s="199" t="inlineStr">
+        <is>
+          <t>Dev cost</t>
+        </is>
+      </c>
+      <c r="C22" s="199" t="inlineStr">
+        <is>
+          <t>Unit cost</t>
+        </is>
+      </c>
+      <c r="D22" s="259" t="inlineStr">
+        <is>
+          <t>Why this one</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="200" t="inlineStr">
+        <is>
+          <t>Decals: bright, styled per segment &amp; frame</t>
+        </is>
+      </c>
+      <c r="B23" s="220" t="n">
+        <v>109155</v>
+      </c>
+      <c r="C23" s="200" t="n">
+        <v>8</v>
+      </c>
+      <c r="D23" s="260" t="inlineStr">
+        <is>
+          <t>Highest combined needs score on the entire list (929). Hits Colourful (Mtn 120), Status symbol (Mtn 121), Stylish (Mtn 118), Fits personality (Spd 116) — four needs all scoring 109-121 in BOTH segments. Cheapest project ($109,155) and cheapest component ($8). And decals are one of only two component classes our design model has MEASURED: worth +2 in Speed. Highest confidence per dollar on the board.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="200" t="inlineStr">
+        <is>
+          <t>Enriched carbon fiber</t>
+        </is>
+      </c>
+      <c r="B24" s="220" t="n">
+        <v>1023325</v>
+      </c>
+      <c r="C24" s="200" t="n">
+        <v>40</v>
+      </c>
+      <c r="D24" s="260" t="inlineStr">
+        <is>
+          <t>Hits Light weight (Speed's #2 need at 133, Mtn 121), Durable (Mountain's #3 at 127, Spd 117) and Provides competitive advantage (Spd 124, Mtn 117). Upgrades the material on BOTH bikes and every future brand, since every bike in the game carries carbon fiber. Also the single most on-strategy item we could fund — our entire company premise is licensed carbon-fiber 3D printing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="200" t="inlineStr">
+        <is>
+          <t>Gears: 11 speed (1x11)</t>
+        </is>
+      </c>
+      <c r="B25" s="220" t="n">
+        <v>568514</v>
+      </c>
+      <c r="C25" s="200" t="n">
+        <v>50</v>
+      </c>
+      <c r="D25" s="260" t="inlineStr">
+        <is>
+          <t>Hits Easily handles change in incline (Mountain's #1 need at 131), Light weight (121/133) and Shifts smoothly (118/118). Gears are the STRONGEST lever our model has measured — a 16-point swing in Speed between 14sp and 7sp. Highest variance of the three: 24-speed is currently optimal in Mountain and 11 is fewer gears, though the feature text answers that directly. Bonus if it lands: ONE drivetrain optimal on both bikes, eliminating the copy-paste error that cost Swift Bike 3 points.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="200" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B26" s="249" t="n">
+        <v>1700994</v>
+      </c>
+      <c r="C26" s="200" t="n">
+        <v>98</v>
+      </c>
+      <c r="D26" s="260" t="inlineStr">
+        <is>
+          <t>48.4% of the $3,510,838 available. Gross added component cost $98/unit, but all three are REPLACEMENT parts — the true increment is the difference from what we ship today and is smaller.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="199" t="inlineStr">
+        <is>
+          <t>SCHEDULING — 1 quarter or 2</t>
+        </is>
+      </c>
+      <c r="B29" s="259" t="inlineStr">
+        <is>
+          <t>Reasoning</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="200" t="inlineStr">
+        <is>
+          <t>Recommend 1-quarter (rapid) on all three</t>
+        </is>
+      </c>
+      <c r="B30" s="261" t="inlineStr">
+        <is>
+          <t>We are SLOT-constrained (3 projects), not cash-constrained ($3.5M available). When slots are scarce and money is not, buy speed: features land in Q5 designs instead of Q6, and Q5's expanded engineering capacity stays free for new projects.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="200" t="inlineStr">
+        <is>
+          <t>The listed prices are not final</t>
+        </is>
+      </c>
+      <c r="B31" s="260" t="inlineStr">
+        <is>
+          <t>The table shows 'Cost to finish' with no quarter selected. The tip says a 1-quarter schedule costs MORE in total than spreading over two, so the rapid prices will be higher than displayed. Read the real numbers after selecting a quarter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="200" t="inlineStr">
+        <is>
+          <t>If the total lands under the 50% floor</t>
+        </is>
+      </c>
+      <c r="B32" s="260" t="inlineStr">
+        <is>
+          <t>Close the gap by paying for rapid development, NOT by adding a weaker fourth-choice feature. Three good features delivered a quarter early beats four mediocre ones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="200" t="inlineStr">
+        <is>
+          <t>Ask the team</t>
+        </is>
+      </c>
+      <c r="B33" s="262" t="inlineStr">
+        <is>
+          <t>How many quarters remain in the simulation? If it ends at Q6, 1-quarter scheduling is mandatory — a Q6 feature would never ship. This is the one input we do not have.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="199" t="inlineStr">
+        <is>
+          <t>FUNDING</t>
+        </is>
+      </c>
+      <c r="B36" s="199" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="C36" s="259" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="200" t="inlineStr">
+        <is>
+          <t>Cash on hand</t>
+        </is>
+      </c>
+      <c r="B37" s="220" t="n">
+        <v>1010838</v>
+      </c>
+      <c r="C37" s="260" t="inlineStr">
+        <is>
+          <t>idle — this is what Asset Management 0.353 punishes</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="200" t="inlineStr">
+        <is>
+          <t>VC raise</t>
+        </is>
+      </c>
+      <c r="B38" s="220" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="C38" s="262" t="inlineStr">
+        <is>
+          <t>take the full amount. This RECONCILES with our earlier 'stop issuing stock' rule, which was conditional on the cash sitting idle. R&amp;D is the productive use that justifies a raise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="200" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="B39" s="220" t="n">
+        <v>3510838</v>
+      </c>
+      <c r="C39" s="260" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="200" t="inlineStr">
+        <is>
+          <t>50% guidance floor</t>
+        </is>
+      </c>
+      <c r="B40" s="220" t="n">
+        <v>1755419</v>
+      </c>
+      <c r="C40" s="260" t="inlineStr">
+        <is>
+          <t>instructor guidance: plan to spend 50-75% on R&amp;D</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="200" t="inlineStr">
+        <is>
+          <t>75% guidance ceiling</t>
+        </is>
+      </c>
+      <c r="B41" s="220" t="n">
+        <v>2633128</v>
+      </c>
+      <c r="C41" s="260" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="200" t="inlineStr">
+        <is>
+          <t>Recommended three (listed cost)</t>
+        </is>
+      </c>
+      <c r="B42" s="220" t="n">
+        <v>1700994</v>
+      </c>
+      <c r="C42" s="260" t="inlineStr">
+        <is>
+          <t>48.4% — just under the floor at listed prices; rapid scheduling should close it</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="200" t="inlineStr">
+        <is>
+          <t>Also committed this quarter</t>
+        </is>
+      </c>
+      <c r="B43" s="220" t="n">
+        <v>146000</v>
+      </c>
+      <c r="C43" s="260" t="inlineStr">
+        <is>
+          <t>the copy-the-leader operating plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="200" t="inlineStr">
+        <is>
+          <t>Hard floor</t>
+        </is>
+      </c>
+      <c r="B44" s="220" t="n">
+        <v>300000</v>
+      </c>
+      <c r="C44" s="260" t="inlineStr">
+        <is>
+          <t>ending Cash + CD must stay at or above this</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="199" t="inlineStr">
+        <is>
+          <t>BRAND P&amp;L — what it tells us about cost per unit</t>
+        </is>
+      </c>
+      <c r="B47" s="199" t="inlineStr">
+        <is>
+          <t>Hike Bike</t>
+        </is>
+      </c>
+      <c r="C47" s="259" t="inlineStr">
+        <is>
+          <t>Swift Bike</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="200" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="B48" s="220" t="n">
+        <v>278</v>
+      </c>
+      <c r="C48" s="266" t="n">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="200" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B49" s="220" t="n">
+        <v>379470</v>
+      </c>
+      <c r="C49" s="266" t="n">
+        <v>210250</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="200" t="inlineStr">
+        <is>
+          <t>COGS</t>
+        </is>
+      </c>
+      <c r="B50" s="220" t="n">
+        <v>171741</v>
+      </c>
+      <c r="C50" s="266" t="n">
+        <v>100599</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="200" t="inlineStr">
+        <is>
+          <t>COGS per unit</t>
+        </is>
+      </c>
+      <c r="B51" s="220" t="n">
+        <v>618</v>
+      </c>
+      <c r="C51" s="266" t="n">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="200" t="inlineStr">
+        <is>
+          <t>Gross margin per unit</t>
+        </is>
+      </c>
+      <c r="B52" s="220" t="n">
+        <v>747</v>
+      </c>
+      <c r="C52" s="266" t="n">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="200" t="inlineStr">
+        <is>
+          <t>Brand expense (ad + design)</t>
+        </is>
+      </c>
+      <c r="B53" s="220" t="n">
+        <v>68732</v>
+      </c>
+      <c r="C53" s="266" t="n">
+        <v>82433</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="200" t="inlineStr">
+        <is>
+          <t>Brand expense PER UNIT</t>
+        </is>
+      </c>
+      <c r="B54" s="220" t="n">
+        <v>247</v>
+      </c>
+      <c r="C54" s="266" t="n">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="200" t="inlineStr">
+        <is>
+          <t>Profit per unit</t>
+        </is>
+      </c>
+      <c r="B55" s="220" t="n">
+        <v>500</v>
+      </c>
+      <c r="C55" s="266" t="n">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="200" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="B56" s="200" t="n"/>
+      <c r="C56" s="262" t="inlineStr">
+        <is>
+          <t>Swift Bike's $188 is not structural. It carries a one-time $30,000 design fee and spreads $45,433 of advertising over only 145 units ($313/unit). At BB LLC's Speed volume of 363 the same ad dollars cost $125/unit. Advertising is FIXED — volume is what crushes cost per unit. Swift also costs $76 more per unit to build than Hike Bike, and the 14-speed swap should narrow that.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="199" t="inlineStr">
+        <is>
+          <t>HOLD FOR Q5 (engineering capacity expands next quarter)</t>
+        </is>
+      </c>
+      <c r="B59" s="259" t="inlineStr">
+        <is>
+          <t>Why not now</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="200" t="inlineStr">
+        <is>
+          <t>Carrier: mesh folding tote</t>
+        </is>
+      </c>
+      <c r="B60" s="264" t="inlineStr">
+        <is>
+          <t>Comfort frames ONLY - fits neither of our bikes. Hard exclusion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="200" t="inlineStr">
+        <is>
+          <t>Suspension: full (front+back)</t>
+        </is>
+      </c>
+      <c r="B61" s="260" t="inlineStr">
+        <is>
+          <t>Not compatible with Aerodynamic, so Hike Bike only. Highest unit cost on the list at $85 against a $747 margin, and $618,543 to develop. Strong Mountain needs (rough terrain 128, soften impact 124) but half the reach for more money.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="200" t="inlineStr">
+        <is>
+          <t>Tires: Hybrid comfort</t>
+        </is>
+      </c>
+      <c r="B62" s="260" t="inlineStr">
+        <is>
+          <t>Recreation feature. Comfortable scores 95 in Mountain and 101 in Speed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="200" t="inlineStr">
+        <is>
+          <t>Pedal-powered charger</t>
+        </is>
+      </c>
+      <c r="B63" s="260" t="inlineStr">
+        <is>
+          <t>Touches no top-10 need in either of our segments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="200" t="inlineStr">
+        <is>
+          <t>Performance bike computer</t>
+        </is>
+      </c>
+      <c r="B64" s="260" t="inlineStr">
+        <is>
+          <t>$60/unit and $682,217 to develop. Navigation assistance is only 117/118 - mid-tier - and no rival ad in the game claims anything like it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="200" t="inlineStr">
+        <is>
+          <t>Tires: Mountain super traction</t>
+        </is>
+      </c>
+      <c r="B65" s="260" t="inlineStr">
+        <is>
+          <t>Genuinely strong for Mountain (rough terrain 128, turn sharply 124, durable 127) but scores only 82 on rough terrain in Speed. Best single-segment option - hold for Q5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="200" t="inlineStr">
+        <is>
+          <t>Tires: Racing sleek very fast</t>
+        </is>
+      </c>
+      <c r="B66" s="260" t="inlineStr">
+        <is>
+          <t>Strong for Speed (Speed 134, sleek 119) and directly supports the new Swift ad copy. Best Speed-only option - hold for Q5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="200" t="inlineStr">
+        <is>
+          <t>Bars: Carbon aero drop down</t>
+        </is>
+      </c>
+      <c r="B67" s="260" t="inlineStr">
+        <is>
+          <t>Supports 'ride a wind-cheater', the one claim on 8 of 8 rival Speed ads. Aerodynamic scores 122 in Speed but 88 in Mountain. Hold for Q5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="200" t="inlineStr">
+        <is>
+          <t>Bars: Power straight / CF riser</t>
+        </is>
+      </c>
+      <c r="B68" s="260" t="inlineStr">
+        <is>
+          <t>Mountain and Recreation leaning, and the Power straight text admits a downside (reduced tree clearance).</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="200" t="inlineStr">
+        <is>
+          <t>Puncture resistant slime</t>
+        </is>
+      </c>
+      <c r="B69" s="260" t="inlineStr">
+        <is>
+          <t>Only $3/unit and $159,184 - the best value per unit on the list, hitting Durable (Mtn 127 / Spd 117) and Safety. It is the strongest CHEAP alternative if the team wants to conserve cash, but it touches only 2-3 needs, so it wastes a scarce slot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="200" t="inlineStr">
+        <is>
+          <t>Lights: high intensity LED</t>
+        </is>
+      </c>
+      <c r="B70" s="260" t="inlineStr">
+        <is>
+          <t>High visibility is 119 in Speed but 103 in Mountain, and no Mountain brand in the industry ships lights at all. Our own ad analysis says drop lights from Speed copy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="199" t="inlineStr">
+        <is>
+          <t>CAVEATS</t>
+        </is>
+      </c>
+      <c r="B73" s="259" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="200" t="inlineStr">
+        <is>
+          <t>Need mapping is our judgment</t>
+        </is>
+      </c>
+      <c r="B74" s="260" t="inlineStr">
+        <is>
+          <t>The sim has not told us which needs each component satisfies. These are readings of the Workspace feature text. Use the scores as a ranking aid, not a points prediction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="200" t="inlineStr">
+        <is>
+          <t>Only 5 components are MEASURED</t>
+        </is>
+      </c>
+      <c r="B75" s="260" t="inlineStr">
+        <is>
+          <t>Our design model derived point values for gears, seat, decals, reflectors and lights only. Frame, tires, brakes and handlebars never varied within a segment, so we have no measured evidence for upgrading them. Two of the three picks land on measured components.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="200" t="inlineStr">
+        <is>
+          <t>11-speed is the risk</t>
+        </is>
+      </c>
+      <c r="B76" s="260" t="inlineStr">
+        <is>
+          <t>24-speed is currently optimal in Mountain and our ad claims 'more gears'. The feature text answers this ('11 gears can do the job of 24... lighter, easier to shift, wide range') and 'easily handles change in incline' is Mountain's #1 need at 131 — but it is still an inference. Lower-variance swap: puncture resistant slime, $159,184 and $3/unit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="200" t="inlineStr">
+        <is>
+          <t>Replacement not addition</t>
+        </is>
+      </c>
+      <c r="B77" s="260" t="inlineStr">
+        <is>
+          <t>All three picks replace parts we already fit, so the incremental unit cost is less than the $98 sticker. Read the delta on the Design Brand screen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="200" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B78" s="260" t="inlineStr">
+        <is>
+          <t>ANALYSIS ONLY. Three slots, majority vote required.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:H2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/quarters/Q3/Q3Data.xlsx
+++ b/quarters/Q3/Q3Data.xlsx
@@ -54,6 +54,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q4_Copy_The_Leader" sheetId="46" state="visible" r:id="rId46"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q4_Brand_Count" sheetId="47" state="visible" r:id="rId47"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q4_RD" sheetId="48" state="visible" r:id="rId48"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q4_Financing" sheetId="49" state="visible" r:id="rId49"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -669,7 +670,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="16"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="16"/>
   </cellStyleXfs>
-  <cellXfs count="267">
+  <cellXfs count="269">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1045,6 +1046,10 @@
     </xf>
     <xf numFmtId="3" fontId="28" fillId="29" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="28" fillId="32" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -59253,6 +59258,635 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" style="146" min="1" max="1"/>
+    <col width="15" customWidth="1" style="146" min="2" max="2"/>
+    <col width="92" customWidth="1" style="146" min="3" max="3"/>
+    <col width="15" customWidth="1" style="146" min="4" max="4"/>
+    <col width="15" customWidth="1" style="146" min="5" max="5"/>
+    <col width="15" customWidth="1" style="146" min="6" max="6"/>
+    <col width="15" customWidth="1" style="146" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="169" t="inlineStr">
+        <is>
+          <t>Q4 financing — loan vs equity, sized to actual uses</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="48" customHeight="1" s="146">
+      <c r="A2" s="258" t="inlineStr">
+        <is>
+          <t>KEY CORRECTION: Wealth = (paid-in capital + retained earnings) / paid-in capital, which reconciles EXACTLY to the reported 0.668 from 25,000 shares at $100 and retained earnings of -$829,162. While retained earnings are negative, issuing equity RAISES Wealth by diluting the deficit. Earlier advice in this project said issuing shares would drag Wealth — that was wrong.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="199" t="inlineStr">
+        <is>
+          <t>Raise</t>
+        </is>
+      </c>
+      <c r="B4" s="199" t="inlineStr">
+        <is>
+          <t>New paid-in</t>
+        </is>
+      </c>
+      <c r="C4" s="199" t="inlineStr">
+        <is>
+          <t>Wealth (equity)</t>
+        </is>
+      </c>
+      <c r="D4" s="199" t="inlineStr">
+        <is>
+          <t>vs 0.668</t>
+        </is>
+      </c>
+      <c r="E4" s="199" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="F4" s="199" t="inlineStr">
+        <is>
+          <t>Fin Perf (equity)</t>
+        </is>
+      </c>
+      <c r="G4" s="199" t="inlineStr">
+        <is>
+          <t>vs 5.319</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="220" t="n">
+        <v>0</v>
+      </c>
+      <c r="B5" s="220" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="C5" s="206" t="n">
+        <v>0.668</v>
+      </c>
+      <c r="D5" s="242" t="n">
+        <v>0.0005017964071856174</v>
+      </c>
+      <c r="E5" s="220" t="n">
+        <v>25000</v>
+      </c>
+      <c r="F5" s="204" t="n">
+        <v>5.319</v>
+      </c>
+      <c r="G5" s="242" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="220" t="n">
+        <v>500000</v>
+      </c>
+      <c r="B6" s="220" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="C6" s="206" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="D6" s="242" t="n">
+        <v>0.08325249500998</v>
+      </c>
+      <c r="E6" s="220" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F6" s="204" t="n">
+        <v>4.433</v>
+      </c>
+      <c r="G6" s="242" t="n">
+        <v>-0.1666666666666666</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="220" t="n">
+        <v>750000</v>
+      </c>
+      <c r="B7" s="220" t="n">
+        <v>3250000</v>
+      </c>
+      <c r="C7" s="206" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="D7" s="242" t="n">
+        <v>0.1150796867802855</v>
+      </c>
+      <c r="E7" s="220" t="n">
+        <v>32500</v>
+      </c>
+      <c r="F7" s="204" t="n">
+        <v>4.092</v>
+      </c>
+      <c r="G7" s="242" t="n">
+        <v>-0.2307692307692307</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="220" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="B8" s="220" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="C8" s="206" t="n">
+        <v>0.763</v>
+      </c>
+      <c r="D8" s="242" t="n">
+        <v>0.142360136869119</v>
+      </c>
+      <c r="E8" s="220" t="n">
+        <v>35000</v>
+      </c>
+      <c r="F8" s="204" t="n">
+        <v>3.799</v>
+      </c>
+      <c r="G8" s="242" t="n">
+        <v>-0.2857142857142857</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="220" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="B9" s="220" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="C9" s="206" t="n">
+        <v>0.834</v>
+      </c>
+      <c r="D9" s="242" t="n">
+        <v>0.2487538922155688</v>
+      </c>
+      <c r="E9" s="220" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F9" s="204" t="n">
+        <v>2.659</v>
+      </c>
+      <c r="G9" s="242" t="n">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="170" t="inlineStr">
+        <is>
+          <t>Equity helps Wealth and hurts Financial Performance. A loan does the opposite: Wealth stays 0.668 (last, unchanged) and shares stay at 25,000, with only interest touching the numerator.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="199" t="inlineStr">
+        <is>
+          <t>SOURCES AND USES — Q4</t>
+        </is>
+      </c>
+      <c r="B12" s="199" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="C12" s="259" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="200" t="inlineStr">
+        <is>
+          <t>R&amp;D — decals + 11-speed, listed price</t>
+        </is>
+      </c>
+      <c r="B13" s="220" t="n">
+        <v>677669</v>
+      </c>
+      <c r="C13" s="260" t="inlineStr">
+        <is>
+          <t>rapid scheduling costs MORE; read the real number on screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="200" t="inlineStr">
+        <is>
+          <t>R&amp;D rapid premium, if ~30%</t>
+        </is>
+      </c>
+      <c r="B14" s="220" t="n">
+        <v>203301</v>
+      </c>
+      <c r="C14" s="260" t="inlineStr">
+        <is>
+          <t>ESTIMATE ONLY — the single biggest unknown in this table</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="200" t="inlineStr">
+        <is>
+          <t>Operating plan, recurring</t>
+        </is>
+      </c>
+      <c r="B15" s="220" t="n">
+        <v>146000</v>
+      </c>
+      <c r="C15" s="260" t="inlineStr">
+        <is>
+          <t>media +$27k, web tactics +$27k, web staff +$27.4k, Rio staff +$20.6k, comp +$10.4k, training +$2k</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="200" t="inlineStr">
+        <is>
+          <t>Operating plan, one-time</t>
+        </is>
+      </c>
+      <c r="B16" s="220" t="n">
+        <v>67000</v>
+      </c>
+      <c r="C16" s="260" t="inlineStr">
+        <is>
+          <t>hiring and setup estimates</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="200" t="inlineStr">
+        <is>
+          <t>Swift Bike brand redesign fee</t>
+        </is>
+      </c>
+      <c r="B17" s="220" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C17" s="260" t="inlineStr">
+        <is>
+          <t>14-speed + decals; Q3 new-design fee was $30,000, a modify may be less</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="200" t="inlineStr">
+        <is>
+          <t>Swift Bike ad redesign fee</t>
+        </is>
+      </c>
+      <c r="B18" s="220" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C18" s="260" t="inlineStr">
+        <is>
+          <t>estimate</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="200" t="inlineStr">
+        <is>
+          <t>Printer #4</t>
+        </is>
+      </c>
+      <c r="B19" s="220" t="n">
+        <v>240000</v>
+      </c>
+      <c r="C19" s="260" t="inlineStr">
+        <is>
+          <t>8 units/day. Online Q5. Pays back in ONE quarter (see below)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="200" t="inlineStr">
+        <is>
+          <t>Printer #5</t>
+        </is>
+      </c>
+      <c r="B20" s="220" t="n">
+        <v>240000</v>
+      </c>
+      <c r="C20" s="260" t="inlineStr">
+        <is>
+          <t>OPTIONAL — only if we commit to New York in Q5</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="200" t="inlineStr">
+        <is>
+          <t>TOTAL with 1 printer</t>
+        </is>
+      </c>
+      <c r="B21" s="220" t="n">
+        <v>1373970</v>
+      </c>
+      <c r="C21" s="260" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="200" t="inlineStr">
+        <is>
+          <t>TOTAL with 2 printers</t>
+        </is>
+      </c>
+      <c r="B22" s="220" t="n">
+        <v>1613970</v>
+      </c>
+      <c r="C22" s="260" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="200" t="inlineStr">
+        <is>
+          <t>Cash on hand</t>
+        </is>
+      </c>
+      <c r="B23" s="220" t="n">
+        <v>1010838</v>
+      </c>
+      <c r="C23" s="260" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="200" t="inlineStr">
+        <is>
+          <t>Hard floor (ending cash + CD)</t>
+        </is>
+      </c>
+      <c r="B24" s="220" t="n">
+        <v>300000</v>
+      </c>
+      <c r="C24" s="260" t="inlineStr">
+        <is>
+          <t>must not be broken</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="200" t="inlineStr">
+        <is>
+          <t>Deployable cash</t>
+        </is>
+      </c>
+      <c r="B25" s="220" t="n">
+        <v>710838</v>
+      </c>
+      <c r="C25" s="260" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="223" t="inlineStr">
+        <is>
+          <t>RAISE NEEDED — 1 printer</t>
+        </is>
+      </c>
+      <c r="B26" s="267" t="n">
+        <v>663132</v>
+      </c>
+      <c r="C26" s="268" t="inlineStr">
+        <is>
+          <t>~$500k</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="223" t="inlineStr">
+        <is>
+          <t>RAISE NEEDED — 2 printers</t>
+        </is>
+      </c>
+      <c r="B27" s="267" t="n">
+        <v>903132</v>
+      </c>
+      <c r="C27" s="268" t="inlineStr">
+        <is>
+          <t>this is where $750k-$1M came from — it is the two-printer case</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="199" t="inlineStr">
+        <is>
+          <t>PRINTER TIMING — resizes the whole plan</t>
+        </is>
+      </c>
+      <c r="B30" s="259" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="200" t="inlineStr">
+        <is>
+          <t>Printers arrive one quarter LATE</t>
+        </is>
+      </c>
+      <c r="B31" s="262" t="inlineStr">
+        <is>
+          <t>Our Q1 lock proves it: 3 printers bought in Q1 gave '+24/day online next quarter, Q1 available = 0'. A printer bought in Q4 produces nothing in Q4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="200" t="inlineStr">
+        <is>
+          <t>So New York CANNOT open in Q4</t>
+        </is>
+      </c>
+      <c r="B32" s="260" t="inlineStr">
+        <is>
+          <t>Q4 capacity is already committed at 24.35/day for Rio plus the web rebuild. Adding 340-570 NYC units against zero spare capacity earns another quarter of stock-out ill will, in the one city where BB LLC already holds 82.8% of Mountain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="200" t="inlineStr">
+        <is>
+          <t>Correct order</t>
+        </is>
+      </c>
+      <c r="B33" s="260" t="inlineStr">
+        <is>
+          <t>Q4 BUYS printers and funds R&amp;D. Q5 OPENS New York into capacity that already exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="200" t="inlineStr">
+        <is>
+          <t>Printer payback</t>
+        </is>
+      </c>
+      <c r="B34" s="260" t="inlineStr">
+        <is>
+          <t>8 units/day x 0.74 x 65 days = 385 units/quarter. At ~$800 contribution that is $307,840 per quarter against a $240,000 price — it repays itself in 0.78 of a quarter, then repeats.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="199" t="inlineStr">
+        <is>
+          <t>RECOMMENDATION — match the funding to the asset</t>
+        </is>
+      </c>
+      <c r="B37" s="259" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="200" t="inlineStr">
+        <is>
+          <t>EQUITY for R&amp;D + operating plan (~$700-900k)</t>
+        </is>
+      </c>
+      <c r="B38" s="261" t="inlineStr">
+        <is>
+          <t>Speculative spending with no contractual payback belongs on equity. And Wealth actively rewards it now: the accumulated deficit is what drags us to 0.668, and fresh paid-in capital dilutes it. A $1M raise takes Wealth 0.668 -&gt; 0.763.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="200" t="inlineStr">
+        <is>
+          <t>DEBT for printers (~$240-480k), if offered</t>
+        </is>
+      </c>
+      <c r="B39" s="261" t="inlineStr">
+        <is>
+          <t>A hard asset with a self-liquidating payback inside one quarter services its own interest many times over, and debt keeps those dollars out of the Financial Performance denominator where we are already last.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="200" t="inlineStr">
+        <is>
+          <t>NOT the full $2.5M in either form</t>
+        </is>
+      </c>
+      <c r="B40" s="260" t="inlineStr">
+        <is>
+          <t>Undeployed cash is exactly what put Asset Management at 0.353, last in the industry. Size the raise to the uses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="200" t="inlineStr">
+        <is>
+          <t>If no loan is available</t>
+        </is>
+      </c>
+      <c r="B41" s="260" t="inlineStr">
+        <is>
+          <t>Take $750,000 of equity and buy one printer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="200" t="inlineStr">
+        <is>
+          <t>If a loan IS available on fair terms</t>
+        </is>
+      </c>
+      <c r="B42" s="260" t="inlineStr">
+        <is>
+          <t>Split: ~$600,000 equity for R&amp;D and operations, ~$480,000 debt for two printers, then open New York in Q5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="199" t="inlineStr">
+        <is>
+          <t>MUST CHECK BEFORE VOTING</t>
+        </is>
+      </c>
+      <c r="B45" s="259" t="inlineStr">
+        <is>
+          <t>Why it matters</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="200" t="inlineStr">
+        <is>
+          <t>Is a loan even offered this quarter?</t>
+        </is>
+      </c>
+      <c r="B46" s="260" t="inlineStr">
+        <is>
+          <t>Everything the sim has shown us is a VC/equity round. The whole debt half of this analysis is moot if there is no debt window.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="200" t="inlineStr">
+        <is>
+          <t>Interest rate and any borrowing cap</t>
+        </is>
+      </c>
+      <c r="B47" s="260" t="inlineStr">
+        <is>
+          <t>The one input that could flip the comparison. This analysis assumes 10%/yr. At a punitive rate debt loses. With retained earnings at -$829,162 we may not qualify at all.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="200" t="inlineStr">
+        <is>
+          <t>Is R&amp;D EXPENSED in Q4 or capitalised?</t>
+        </is>
+      </c>
+      <c r="B48" s="262" t="inlineStr">
+        <is>
+          <t>THE NUMBER I WOULD MOST WANT. If the $677,669 is expensed, Q4 posts a large loss even with the volume fix, retained earnings fall further, and Wealth falls with them — which weakens the debt case and changes the raise size.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="200" t="inlineStr">
+        <is>
+          <t>Confirm the one-quarter printer delay</t>
+        </is>
+      </c>
+      <c r="B49" s="260" t="inlineStr">
+        <is>
+          <t>The entire New York sequence depends on it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="200" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B50" s="260" t="inlineStr">
+        <is>
+          <t>ANALYSIS ONLY — majority vote required.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:F2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/quarters/Q3/Q3Data.xlsx
+++ b/quarters/Q3/Q3Data.xlsx
@@ -670,7 +670,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="16"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="16"/>
   </cellStyleXfs>
-  <cellXfs count="269">
+  <cellXfs count="271">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1052,6 +1052,8 @@
     <xf numFmtId="0" fontId="28" fillId="32" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="31" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="31" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -59264,618 +59266,729 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" style="146" min="1" max="1"/>
-    <col width="15" customWidth="1" style="146" min="2" max="2"/>
-    <col width="92" customWidth="1" style="146" min="3" max="3"/>
-    <col width="15" customWidth="1" style="146" min="4" max="4"/>
-    <col width="15" customWidth="1" style="146" min="5" max="5"/>
-    <col width="15" customWidth="1" style="146" min="6" max="6"/>
-    <col width="15" customWidth="1" style="146" min="7" max="7"/>
+    <col width="46" customWidth="1" style="146" min="1" max="1"/>
+    <col width="16" customWidth="1" style="146" min="2" max="2"/>
+    <col width="96" customWidth="1" style="146" min="3" max="3"/>
+    <col width="14" customWidth="1" style="146" min="4" max="4"/>
+    <col width="14" customWidth="1" style="146" min="5" max="5"/>
+    <col width="14" customWidth="1" style="146" min="6" max="6"/>
+    <col width="14" customWidth="1" style="146" min="7" max="7"/>
+    <col width="14" customWidth="1" style="146" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="169" t="inlineStr">
         <is>
-          <t>Q4 financing — loan vs equity, sized to actual uses</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="48" customHeight="1" s="146">
+          <t>Q4 financing — DECIDED: borrow $950,000, issue no stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="62" customHeight="1" s="146">
       <c r="A2" s="258" t="inlineStr">
         <is>
-          <t>KEY CORRECTION: Wealth = (paid-in capital + retained earnings) / paid-in capital, which reconciles EXACTLY to the reported 0.668 from 25,000 shares at $100 and retained earnings of -$829,162. While retained earnings are negative, issuing equity RAISES Wealth by diluting the deficit. Earlier advice in this project said issuing shares would drag Wealth — that was wrong.</t>
+          <t>Two formulas now reconcile EXACTLY. Wealth = (paid-in + RE) / paid-in = 0.6683 vs reported 0.668. Debt capacity = 1.5 x (paid-in + RE) = $2,506,257 vs reported $2,506,258. Net equity is the Wealth numerator AND the debt-capacity base, so every $1 of equity buys $1.50 of borrowing room and every $1 of loss destroys $1.50 of it. At the actual 7% annual rate, DEBT IS 2.5x LESS DAMAGING TO THE SCORECARD THAN EQUITY, and 4x less damaging than the $2.5M VC issue currently sitting in the form.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="199" t="inlineStr">
         <is>
-          <t>Raise</t>
+          <t>LOAN TERMS (as offered)</t>
         </is>
       </c>
       <c r="B4" s="199" t="inlineStr">
         <is>
-          <t>New paid-in</t>
-        </is>
-      </c>
-      <c r="C4" s="199" t="inlineStr">
-        <is>
-          <t>Wealth (equity)</t>
-        </is>
-      </c>
-      <c r="D4" s="199" t="inlineStr">
-        <is>
-          <t>vs 0.668</t>
-        </is>
-      </c>
-      <c r="E4" s="199" t="inlineStr">
-        <is>
-          <t>Shares</t>
-        </is>
-      </c>
-      <c r="F4" s="199" t="inlineStr">
-        <is>
-          <t>Fin Perf (equity)</t>
-        </is>
-      </c>
-      <c r="G4" s="199" t="inlineStr">
-        <is>
-          <t>vs 5.319</t>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="220" t="n">
+      <c r="A5" s="200" t="inlineStr">
+        <is>
+          <t>Debt capacity = 1.5 x (Equity + RE)</t>
+        </is>
+      </c>
+      <c r="B5" s="220" t="n">
+        <v>2506258</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="200" t="inlineStr">
+        <is>
+          <t>Total debt to date</t>
+        </is>
+      </c>
+      <c r="B6" s="200" t="n">
         <v>0</v>
       </c>
-      <c r="B5" s="220" t="n">
-        <v>2500000</v>
-      </c>
-      <c r="C5" s="206" t="n">
-        <v>0.668</v>
-      </c>
-      <c r="D5" s="242" t="n">
-        <v>0.0005017964071856174</v>
-      </c>
-      <c r="E5" s="220" t="n">
-        <v>25000</v>
-      </c>
-      <c r="F5" s="204" t="n">
-        <v>5.319</v>
-      </c>
-      <c r="G5" s="242" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="220" t="n">
-        <v>500000</v>
-      </c>
-      <c r="B6" s="220" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="C6" s="206" t="n">
-        <v>0.724</v>
-      </c>
-      <c r="D6" s="242" t="n">
-        <v>0.08325249500998</v>
-      </c>
-      <c r="E6" s="220" t="n">
-        <v>30000</v>
-      </c>
-      <c r="F6" s="204" t="n">
-        <v>4.433</v>
-      </c>
-      <c r="G6" s="242" t="n">
-        <v>-0.1666666666666666</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" s="220" t="n">
-        <v>750000</v>
+      <c r="A7" s="200" t="inlineStr">
+        <is>
+          <t>Available to borrow</t>
+        </is>
       </c>
       <c r="B7" s="220" t="n">
-        <v>3250000</v>
-      </c>
-      <c r="C7" s="206" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="D7" s="242" t="n">
-        <v>0.1150796867802855</v>
-      </c>
-      <c r="E7" s="220" t="n">
-        <v>32500</v>
-      </c>
-      <c r="F7" s="204" t="n">
-        <v>4.092</v>
-      </c>
-      <c r="G7" s="242" t="n">
-        <v>-0.2307692307692307</v>
+        <v>2506258</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="220" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="B8" s="220" t="n">
-        <v>3500000</v>
-      </c>
-      <c r="C8" s="206" t="n">
-        <v>0.763</v>
-      </c>
-      <c r="D8" s="242" t="n">
-        <v>0.142360136869119</v>
-      </c>
-      <c r="E8" s="220" t="n">
-        <v>35000</v>
-      </c>
-      <c r="F8" s="204" t="n">
-        <v>3.799</v>
-      </c>
-      <c r="G8" s="242" t="n">
-        <v>-0.2857142857142857</v>
+      <c r="A8" s="200" t="inlineStr">
+        <is>
+          <t>Annual interest rate</t>
+        </is>
+      </c>
+      <c r="B8" s="200" t="inlineStr">
+        <is>
+          <t>7.00%</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="220" t="n">
-        <v>2500000</v>
-      </c>
-      <c r="B9" s="220" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="C9" s="206" t="n">
-        <v>0.834</v>
-      </c>
-      <c r="D9" s="242" t="n">
-        <v>0.2487538922155688</v>
-      </c>
-      <c r="E9" s="220" t="n">
-        <v>50000</v>
-      </c>
-      <c r="F9" s="204" t="n">
-        <v>2.659</v>
-      </c>
-      <c r="G9" s="242" t="n">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="170" t="inlineStr">
-        <is>
-          <t>Equity helps Wealth and hurts Financial Performance. A loan does the opposite: Wealth stays 0.668 (last, unchanged) and shares stay at 25,000, with only interest touching the numerator.</t>
+      <c r="A9" s="200" t="inlineStr">
+        <is>
+          <t>Quarterly interest rate</t>
+        </is>
+      </c>
+      <c r="B9" s="200" t="inlineStr">
+        <is>
+          <t>1.75%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="199" t="inlineStr">
         <is>
-          <t>SOURCES AND USES — Q4</t>
+          <t>STOCK HISTORY</t>
         </is>
       </c>
       <c r="B12" s="199" t="inlineStr">
         <is>
-          <t>Amount</t>
-        </is>
-      </c>
-      <c r="C12" s="259" t="inlineStr">
-        <is>
-          <t>Note</t>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="C12" s="199" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="D12" s="199" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="E12" s="199" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="F12" s="199" t="inlineStr">
+        <is>
+          <t>Quarter</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="200" t="inlineStr">
         <is>
-          <t>R&amp;D — decals + 11-speed, listed price</t>
-        </is>
-      </c>
-      <c r="B13" s="220" t="n">
-        <v>677669</v>
-      </c>
-      <c r="C13" s="260" t="inlineStr">
-        <is>
-          <t>rapid scheduling costs MORE; read the real number on screen</t>
-        </is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B13" s="200" t="inlineStr">
+        <is>
+          <t>Executive Team</t>
+        </is>
+      </c>
+      <c r="C13" s="220" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D13" s="200" t="n">
+        <v>100</v>
+      </c>
+      <c r="E13" s="220" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="F13" s="200" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="200" t="inlineStr">
         <is>
-          <t>R&amp;D rapid premium, if ~30%</t>
-        </is>
-      </c>
-      <c r="B14" s="220" t="n">
-        <v>203301</v>
-      </c>
-      <c r="C14" s="260" t="inlineStr">
-        <is>
-          <t>ESTIMATE ONLY — the single biggest unknown in this table</t>
-        </is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B14" s="200" t="inlineStr">
+        <is>
+          <t>Executive Team</t>
+        </is>
+      </c>
+      <c r="C14" s="220" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D14" s="200" t="n">
+        <v>100</v>
+      </c>
+      <c r="E14" s="220" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F14" s="200" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="200" t="inlineStr">
         <is>
-          <t>Operating plan, recurring</t>
-        </is>
-      </c>
-      <c r="B15" s="220" t="n">
-        <v>146000</v>
-      </c>
-      <c r="C15" s="260" t="inlineStr">
-        <is>
-          <t>media +$27k, web tactics +$27k, web staff +$27.4k, Rio staff +$20.6k, comp +$10.4k, training +$2k</t>
-        </is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B15" s="200" t="inlineStr">
+        <is>
+          <t>Executive Team</t>
+        </is>
+      </c>
+      <c r="C15" s="220" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D15" s="200" t="n">
+        <v>100</v>
+      </c>
+      <c r="E15" s="220" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F15" s="200" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="200" t="inlineStr">
-        <is>
-          <t>Operating plan, one-time</t>
-        </is>
-      </c>
-      <c r="B16" s="220" t="n">
-        <v>67000</v>
-      </c>
-      <c r="C16" s="260" t="inlineStr">
-        <is>
-          <t>hiring and setup estimates</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="200" t="inlineStr">
-        <is>
-          <t>Swift Bike brand redesign fee</t>
-        </is>
-      </c>
-      <c r="B17" s="220" t="n">
-        <v>30000</v>
-      </c>
-      <c r="C17" s="260" t="inlineStr">
-        <is>
-          <t>14-speed + decals; Q3 new-design fee was $30,000, a modify may be less</t>
-        </is>
+      <c r="A16" s="219" t="inlineStr">
+        <is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B16" s="219" t="inlineStr">
+        <is>
+          <t>VENTURE CAPITALISTS — CURRENTLY ENTERED, REDUCE TO $0</t>
+        </is>
+      </c>
+      <c r="C16" s="224" t="n">
+        <v>25000</v>
+      </c>
+      <c r="D16" s="219" t="n">
+        <v>100</v>
+      </c>
+      <c r="E16" s="224" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="F16" s="219" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="200" t="inlineStr">
-        <is>
-          <t>Swift Bike ad redesign fee</t>
-        </is>
-      </c>
-      <c r="B18" s="220" t="n">
-        <v>10000</v>
-      </c>
-      <c r="C18" s="260" t="inlineStr">
-        <is>
-          <t>estimate</t>
+      <c r="A18" s="170" t="inlineStr">
+        <is>
+          <t>Rows 1-3 sum to 25,000 shares and $2,500,000 paid-in — exactly what the Wealth reconciliation required, so the model is confirmed. Row 4 is a LIVE DECISION, not history: as entered it doubles the share count and hands VCs 50% of the company.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="200" t="inlineStr">
-        <is>
-          <t>Printer #4</t>
-        </is>
-      </c>
-      <c r="B19" s="220" t="n">
-        <v>240000</v>
-      </c>
-      <c r="C19" s="260" t="inlineStr">
-        <is>
-          <t>8 units/day. Online Q5. Pays back in ONE quarter (see below)</t>
+      <c r="A19" s="199" t="inlineStr">
+        <is>
+          <t>USES — Q4 (team voted 2 printers)</t>
+        </is>
+      </c>
+      <c r="B19" s="199" t="inlineStr">
+        <is>
+          <t>Amount</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="200" t="inlineStr">
         <is>
-          <t>Printer #5</t>
+          <t>R&amp;D — decals + 11-speed, listed</t>
         </is>
       </c>
       <c r="B20" s="220" t="n">
-        <v>240000</v>
-      </c>
-      <c r="C20" s="260" t="inlineStr">
-        <is>
-          <t>OPTIONAL — only if we commit to New York in Q5</t>
-        </is>
+        <v>677669</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="200" t="inlineStr">
         <is>
-          <t>TOTAL with 1 printer</t>
+          <t>R&amp;D rapid premium (~30% ESTIMATE)</t>
         </is>
       </c>
       <c r="B21" s="220" t="n">
-        <v>1373970</v>
-      </c>
-      <c r="C21" s="260" t="inlineStr"/>
+        <v>203301</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="200" t="inlineStr">
         <is>
-          <t>TOTAL with 2 printers</t>
+          <t>Operating plan, recurring</t>
         </is>
       </c>
       <c r="B22" s="220" t="n">
-        <v>1613970</v>
-      </c>
-      <c r="C22" s="260" t="inlineStr"/>
+        <v>146000</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="200" t="inlineStr">
         <is>
-          <t>Cash on hand</t>
+          <t>Operating plan, one-time</t>
         </is>
       </c>
       <c r="B23" s="220" t="n">
-        <v>1010838</v>
-      </c>
-      <c r="C23" s="260" t="inlineStr"/>
+        <v>67000</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="200" t="inlineStr">
         <is>
-          <t>Hard floor (ending cash + CD)</t>
+          <t>Swift Bike brand redesign fee</t>
         </is>
       </c>
       <c r="B24" s="220" t="n">
-        <v>300000</v>
-      </c>
-      <c r="C24" s="260" t="inlineStr">
-        <is>
-          <t>must not be broken</t>
-        </is>
+        <v>30000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="200" t="inlineStr">
         <is>
-          <t>Deployable cash</t>
+          <t>Swift Bike ad redesign fee</t>
         </is>
       </c>
       <c r="B25" s="220" t="n">
-        <v>710838</v>
-      </c>
-      <c r="C25" s="260" t="inlineStr"/>
+        <v>10000</v>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="223" t="inlineStr">
-        <is>
-          <t>RAISE NEEDED — 1 printer</t>
-        </is>
-      </c>
-      <c r="B26" s="267" t="n">
-        <v>663132</v>
-      </c>
-      <c r="C26" s="268" t="inlineStr">
-        <is>
-          <t>~$500k</t>
-        </is>
+      <c r="A26" s="200" t="inlineStr">
+        <is>
+          <t>Printer #4</t>
+        </is>
+      </c>
+      <c r="B26" s="220" t="n">
+        <v>240000</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="223" t="inlineStr">
-        <is>
-          <t>RAISE NEEDED — 2 printers</t>
-        </is>
-      </c>
-      <c r="B27" s="267" t="n">
-        <v>903132</v>
-      </c>
-      <c r="C27" s="268" t="inlineStr">
-        <is>
-          <t>this is where $750k-$1M came from — it is the two-printer case</t>
-        </is>
+      <c r="A27" s="200" t="inlineStr">
+        <is>
+          <t>Printer #5</t>
+        </is>
+      </c>
+      <c r="B27" s="220" t="n">
+        <v>240000</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="200" t="inlineStr">
+        <is>
+          <t>TOTAL USES</t>
+        </is>
+      </c>
+      <c r="B28" s="220" t="n">
+        <v>1613970</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="200" t="inlineStr">
+        <is>
+          <t>Cash on hand</t>
+        </is>
+      </c>
+      <c r="B29" s="220" t="n">
+        <v>1010838</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="199" t="inlineStr">
-        <is>
-          <t>PRINTER TIMING — resizes the whole plan</t>
-        </is>
-      </c>
-      <c r="B30" s="259" t="inlineStr">
-        <is>
-          <t>Detail</t>
-        </is>
+      <c r="A30" s="200" t="inlineStr">
+        <is>
+          <t>Hard floor</t>
+        </is>
+      </c>
+      <c r="B30" s="220" t="n">
+        <v>300000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="200" t="inlineStr">
         <is>
-          <t>Printers arrive one quarter LATE</t>
-        </is>
-      </c>
-      <c r="B31" s="262" t="inlineStr">
-        <is>
-          <t>Our Q1 lock proves it: 3 printers bought in Q1 gave '+24/day online next quarter, Q1 available = 0'. A printer bought in Q4 produces nothing in Q4.</t>
-        </is>
+          <t>Deployable cash</t>
+        </is>
+      </c>
+      <c r="B31" s="220" t="n">
+        <v>710838</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="200" t="inlineStr">
         <is>
-          <t>So New York CANNOT open in Q4</t>
-        </is>
-      </c>
-      <c r="B32" s="260" t="inlineStr">
-        <is>
-          <t>Q4 capacity is already committed at 24.35/day for Rio plus the web rebuild. Adding 340-570 NYC units against zero spare capacity earns another quarter of stock-out ill will, in the one city where BB LLC already holds 82.8% of Mountain.</t>
-        </is>
+          <t>FUNDING GAP</t>
+        </is>
+      </c>
+      <c r="B32" s="220" t="n">
+        <v>903132</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="200" t="inlineStr">
-        <is>
-          <t>Correct order</t>
-        </is>
-      </c>
-      <c r="B33" s="260" t="inlineStr">
-        <is>
-          <t>Q4 BUYS printers and funds R&amp;D. Q5 OPENS New York into capacity that already exists.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="200" t="inlineStr">
-        <is>
-          <t>Printer payback</t>
-        </is>
-      </c>
-      <c r="B34" s="260" t="inlineStr">
-        <is>
-          <t>8 units/day x 0.74 x 65 days = 385 units/quarter. At ~$800 contribution that is $307,840 per quarter against a $240,000 price — it repays itself in 0.78 of a quarter, then repeats.</t>
+      <c r="A33" s="222" t="inlineStr">
+        <is>
+          <t>RECOMMENDED BORROWING</t>
+        </is>
+      </c>
+      <c r="B33" s="265" t="n">
+        <v>950000</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="199" t="inlineStr">
+        <is>
+          <t>OPTION</t>
+        </is>
+      </c>
+      <c r="B36" s="199" t="inlineStr">
+        <is>
+          <t>Shares after</t>
+        </is>
+      </c>
+      <c r="C36" s="199" t="inlineStr">
+        <is>
+          <t>Qtrly interest</t>
+        </is>
+      </c>
+      <c r="D36" s="199" t="inlineStr">
+        <is>
+          <t>Wealth</t>
+        </is>
+      </c>
+      <c r="E36" s="199" t="inlineStr">
+        <is>
+          <t>vs 0.668</t>
+        </is>
+      </c>
+      <c r="F36" s="199" t="inlineStr">
+        <is>
+          <t>Fin Perf</t>
+        </is>
+      </c>
+      <c r="G36" s="199" t="inlineStr">
+        <is>
+          <t>vs 5.319</t>
+        </is>
+      </c>
+      <c r="H36" s="199" t="inlineStr">
+        <is>
+          <t>BSC combined</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="199" t="inlineStr">
-        <is>
-          <t>RECOMMENDATION — match the funding to the asset</t>
-        </is>
-      </c>
-      <c r="B37" s="259" t="inlineStr">
-        <is>
-          <t>Detail</t>
-        </is>
+      <c r="A37" s="206" t="inlineStr">
+        <is>
+          <t>ALL DEBT (recommended)</t>
+        </is>
+      </c>
+      <c r="B37" s="244" t="n">
+        <v>25000</v>
+      </c>
+      <c r="C37" s="244" t="n">
+        <v>15805</v>
+      </c>
+      <c r="D37" s="206" t="n">
+        <v>0.662</v>
+      </c>
+      <c r="E37" s="243" t="n">
+        <v>-0.008962161676646874</v>
+      </c>
+      <c r="F37" s="206" t="n">
+        <v>5.003</v>
+      </c>
+      <c r="G37" s="243" t="n">
+        <v>-0.05942774957698804</v>
+      </c>
+      <c r="H37" s="243" t="n">
+        <v>-0.06785731015384666</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="200" t="inlineStr">
         <is>
-          <t>EQUITY for R&amp;D + operating plan (~$700-900k)</t>
-        </is>
-      </c>
-      <c r="B38" s="261" t="inlineStr">
-        <is>
-          <t>Speculative spending with no contractual payback belongs on equity. And Wealth actively rewards it now: the accumulated deficit is what drags us to 0.668, and fresh paid-in capital dilutes it. A $1M raise takes Wealth 0.668 -&gt; 0.763.</t>
-        </is>
+          <t>ALL EQUITY</t>
+        </is>
+      </c>
+      <c r="B38" s="220" t="n">
+        <v>34031</v>
+      </c>
+      <c r="C38" s="220" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="200" t="n">
+        <v>0.756</v>
+      </c>
+      <c r="E38" s="228" t="n">
+        <v>0.1322619372931724</v>
+      </c>
+      <c r="F38" s="200" t="n">
+        <v>3.907</v>
+      </c>
+      <c r="G38" s="228" t="n">
+        <v>-0.2653756868737328</v>
+      </c>
+      <c r="H38" s="228" t="n">
+        <v>-0.1682128520369867</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="200" t="inlineStr">
-        <is>
-          <t>DEBT for printers (~$240-480k), if offered</t>
-        </is>
-      </c>
-      <c r="B39" s="261" t="inlineStr">
-        <is>
-          <t>A hard asset with a self-liquidating payback inside one quarter services its own interest many times over, and debt keeps those dollars out of the Financial Performance denominator where we are already last.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="200" t="inlineStr">
-        <is>
-          <t>NOT the full $2.5M in either form</t>
-        </is>
-      </c>
-      <c r="B40" s="260" t="inlineStr">
-        <is>
-          <t>Undeployed cash is exactly what put Asset Management at 0.353, last in the industry. Size the raise to the uses.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="200" t="inlineStr">
-        <is>
-          <t>If no loan is available</t>
-        </is>
-      </c>
-      <c r="B41" s="260" t="inlineStr">
-        <is>
-          <t>Take $750,000 of equity and buy one printer.</t>
-        </is>
+      <c r="A39" s="204" t="inlineStr">
+        <is>
+          <t>$2.5M VC as entered</t>
+        </is>
+      </c>
+      <c r="B39" s="269" t="n">
+        <v>50000</v>
+      </c>
+      <c r="C39" s="269" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="204" t="n">
+        <v>0.834</v>
+      </c>
+      <c r="E39" s="270" t="n">
+        <v>0.2487538922155688</v>
+      </c>
+      <c r="F39" s="204" t="n">
+        <v>2.659</v>
+      </c>
+      <c r="G39" s="270" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H39" s="270" t="n">
+        <v>-0.3756230538922156</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="200" t="inlineStr">
-        <is>
-          <t>If a loan IS available on fair terms</t>
-        </is>
-      </c>
-      <c r="B42" s="260" t="inlineStr">
-        <is>
-          <t>Split: ~$600,000 equity for R&amp;D and operations, ~$480,000 debt for two printers, then open New York in Q5.</t>
-        </is>
+      <c r="A42" s="199" t="inlineStr">
+        <is>
+          <t>RISK — losses shrink debt capacity 1.5x</t>
+        </is>
+      </c>
+      <c r="B42" s="199" t="inlineStr">
+        <is>
+          <t>New RE</t>
+        </is>
+      </c>
+      <c r="C42" s="199" t="inlineStr">
+        <is>
+          <t>New capacity</t>
+        </is>
+      </c>
+      <c r="D42" s="199" t="inlineStr">
+        <is>
+          <t>Borrowed $950k</t>
+        </is>
+      </c>
+      <c r="E42" s="199" t="inlineStr">
+        <is>
+          <t>Headroom</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="200" t="inlineStr">
+        <is>
+          <t>Q4 net loss of $0</t>
+        </is>
+      </c>
+      <c r="B43" s="220" t="n">
+        <v>-829162</v>
+      </c>
+      <c r="C43" s="220" t="n">
+        <v>2506257</v>
+      </c>
+      <c r="D43" s="220" t="n">
+        <v>950000</v>
+      </c>
+      <c r="E43" s="220" t="n">
+        <v>1556257</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="200" t="inlineStr">
+        <is>
+          <t>Q4 net loss of $300,000</t>
+        </is>
+      </c>
+      <c r="B44" s="220" t="n">
+        <v>-1129162</v>
+      </c>
+      <c r="C44" s="220" t="n">
+        <v>2056257</v>
+      </c>
+      <c r="D44" s="220" t="n">
+        <v>950000</v>
+      </c>
+      <c r="E44" s="220" t="n">
+        <v>1106257</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="199" t="inlineStr">
-        <is>
-          <t>MUST CHECK BEFORE VOTING</t>
-        </is>
-      </c>
-      <c r="B45" s="259" t="inlineStr">
-        <is>
-          <t>Why it matters</t>
-        </is>
+      <c r="A45" s="200" t="inlineStr">
+        <is>
+          <t>Q4 net loss of $500,000</t>
+        </is>
+      </c>
+      <c r="B45" s="220" t="n">
+        <v>-1329162</v>
+      </c>
+      <c r="C45" s="220" t="n">
+        <v>1756257</v>
+      </c>
+      <c r="D45" s="220" t="n">
+        <v>950000</v>
+      </c>
+      <c r="E45" s="220" t="n">
+        <v>806257</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="200" t="inlineStr">
         <is>
-          <t>Is a loan even offered this quarter?</t>
-        </is>
-      </c>
-      <c r="B46" s="260" t="inlineStr">
-        <is>
-          <t>Everything the sim has shown us is a VC/equity round. The whole debt half of this analysis is moot if there is no debt window.</t>
-        </is>
+          <t>Q4 net loss of $760,000</t>
+        </is>
+      </c>
+      <c r="B46" s="220" t="n">
+        <v>-1589162</v>
+      </c>
+      <c r="C46" s="220" t="n">
+        <v>1366257</v>
+      </c>
+      <c r="D46" s="220" t="n">
+        <v>950000</v>
+      </c>
+      <c r="E46" s="220" t="n">
+        <v>416257</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="200" t="inlineStr">
         <is>
-          <t>Interest rate and any borrowing cap</t>
-        </is>
-      </c>
-      <c r="B47" s="260" t="inlineStr">
-        <is>
-          <t>The one input that could flip the comparison. This analysis assumes 10%/yr. At a punitive rate debt loses. With retained earnings at -$829,162 we may not qualify at all.</t>
-        </is>
+          <t>Q4 net loss of $1,000,000</t>
+        </is>
+      </c>
+      <c r="B47" s="220" t="n">
+        <v>-1829162</v>
+      </c>
+      <c r="C47" s="220" t="n">
+        <v>1006257</v>
+      </c>
+      <c r="D47" s="220" t="n">
+        <v>950000</v>
+      </c>
+      <c r="E47" s="220" t="n">
+        <v>56257</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="200" t="inlineStr">
-        <is>
-          <t>Is R&amp;D EXPENSED in Q4 or capitalised?</t>
-        </is>
-      </c>
-      <c r="B48" s="262" t="inlineStr">
-        <is>
-          <t>THE NUMBER I WOULD MOST WANT. If the $677,669 is expensed, Q4 posts a large loss even with the volume fix, retained earnings fall further, and Wealth falls with them — which weakens the debt case and changes the raise size.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="200" t="inlineStr">
-        <is>
-          <t>Confirm the one-quarter printer delay</t>
-        </is>
-      </c>
-      <c r="B49" s="260" t="inlineStr">
-        <is>
-          <t>The entire New York sequence depends on it.</t>
-        </is>
+      <c r="A48" s="204" t="inlineStr">
+        <is>
+          <t>Q4 net loss of $1,200,000</t>
+        </is>
+      </c>
+      <c r="B48" s="269" t="n">
+        <v>-2029162</v>
+      </c>
+      <c r="C48" s="269" t="n">
+        <v>706257</v>
+      </c>
+      <c r="D48" s="269" t="n">
+        <v>950000</v>
+      </c>
+      <c r="E48" s="269" t="n">
+        <v>-243743</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="200" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="B50" s="260" t="inlineStr">
-        <is>
-          <t>ANALYSIS ONLY — majority vote required.</t>
+      <c r="A50" s="170" t="inlineStr">
+        <is>
+          <t>At plan (~1,154 units) gross margin ~$920k against ~$800k operating expense, so operations run near break-even BEFORE R&amp;D. Expensing ~$880k of R&amp;D puts the Q4 loss near $760k — still inside capacity. It only breaches if the volume plan ALSO underdelivers badly. HEDGE IF WANTED: $250,000 of equity buys $375,000 of extra capacity for only 2,500 shares.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="199" t="inlineStr">
+        <is>
+          <t>DECISION</t>
+        </is>
+      </c>
+      <c r="B51" s="259" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="200" t="inlineStr">
+        <is>
+          <t>1. Stock issue -&gt; $0</t>
+        </is>
+      </c>
+      <c r="B52" s="261" t="inlineStr">
+        <is>
+          <t>Delete the Q4 Venture Capitalists row. As entered it doubles shares 25,000 -&gt; 50,000, gives VCs half the company, permanently halves Financial Performance where we are already last, and raises $900k more than we can deploy — recreating the idle-cash problem behind Asset Management 0.353.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="200" t="inlineStr">
+        <is>
+          <t>2. Borrow $950,000</t>
+        </is>
+      </c>
+      <c r="B53" s="261" t="inlineStr">
+        <is>
+          <t>Covers the $903,132 gap plus a buffer for the unknown rapid-R&amp;D premium. Interest $16,625/quarter = 1.8% of planned gross margin, and 2.6x inside the $2,506,258 capacity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="200" t="inlineStr">
+        <is>
+          <t>3. Buy both printers ($480,000)</t>
+        </is>
+      </c>
+      <c r="B54" s="261" t="inlineStr">
+        <is>
+          <t>They arrive Q5, which is exactly when New York opens. Two printers earn $615,680/quarter against $8,400 of interest — they out-earn their own financing 73x.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="200" t="inlineStr">
+        <is>
+          <t>4. Accept that Wealth stays ~0.66</t>
+        </is>
+      </c>
+      <c r="B55" s="260" t="inlineStr">
+        <is>
+          <t>It remains our weakest indicator. The only real fix is retained earnings — actually making money. Equity would paper over it by diluting the deficit while wrecking Financial Performance to do so.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="200" t="inlineStr">
+        <is>
+          <t>Still worth confirming</t>
+        </is>
+      </c>
+      <c r="B56" s="262" t="inlineStr">
+        <is>
+          <t>Whether R&amp;D is expensed or capitalised in Q4. It does not change the debt-vs-equity answer, but it sets how much headroom Q5 has and whether the $250k equity hedge is worth taking.</t>
         </is>
       </c>
     </row>

--- a/quarters/Q3/Q3Data.xlsx
+++ b/quarters/Q3/Q3Data.xlsx
@@ -55,6 +55,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q4_Brand_Count" sheetId="47" state="visible" r:id="rId47"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q4_RD" sheetId="48" state="visible" r:id="rId48"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q4_Financing" sheetId="49" state="visible" r:id="rId49"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q4_Ads_SEO_Media" sheetId="50" state="visible" r:id="rId50"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -670,7 +671,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="16"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="16"/>
   </cellStyleXfs>
-  <cellXfs count="271">
+  <cellXfs count="272">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1054,6 +1055,7 @@
     </xf>
     <xf numFmtId="3" fontId="0" fillId="31" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="31" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="28" fillId="29" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -60193,6 +60195,1582 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H94"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" style="146" min="1" max="1"/>
+    <col width="17" customWidth="1" style="146" min="2" max="2"/>
+    <col width="100" customWidth="1" style="146" min="3" max="3"/>
+    <col width="13" customWidth="1" style="146" min="4" max="4"/>
+    <col width="13" customWidth="1" style="146" min="5" max="5"/>
+    <col width="13" customWidth="1" style="146" min="6" max="6"/>
+    <col width="13" customWidth="1" style="146" min="7" max="7"/>
+    <col width="70" customWidth="1" style="146" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="169" t="inlineStr">
+        <is>
+          <t>Q4 ad design, organic SEO and media placement</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="58" customHeight="1" s="146">
+      <c r="A2" s="258" t="inlineStr">
+        <is>
+          <t>THE ORGANISING PRINCIPLE: ad JUDGMENT is free of the capacity constraint (Marketing Effectiveness has no volume term), but media INSERT VOLUME is pure demand generation and Q4 output is hard-capped at 1,154 units against a forecast of 1,171. So improve the COPY aggressively and RESTRAIN the PLACEMENT. This supersedes the earlier Option B media recommendation, which was written before we established that printers arrive a quarter late.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="199" t="inlineStr">
+        <is>
+          <t>Segment</t>
+        </is>
+      </c>
+      <c r="B4" s="199" t="inlineStr">
+        <is>
+          <t>Pos</t>
+        </is>
+      </c>
+      <c r="C4" s="199" t="inlineStr">
+        <is>
+          <t>Ad</t>
+        </is>
+      </c>
+      <c r="D4" s="199" t="inlineStr">
+        <is>
+          <t>Ad judgment</t>
+        </is>
+      </c>
+      <c r="E4" s="199" t="inlineStr">
+        <is>
+          <t>Inserts</t>
+        </is>
+      </c>
+      <c r="F4" s="199" t="inlineStr">
+        <is>
+          <t>Clicks</t>
+        </is>
+      </c>
+      <c r="G4" s="199" t="inlineStr">
+        <is>
+          <t>Rank = judgment?</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="200" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="B5" s="200" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="200" t="inlineStr">
+        <is>
+          <t>Mars Rover 1 (SpaceBikes)</t>
+        </is>
+      </c>
+      <c r="D5" s="200" t="n">
+        <v>79</v>
+      </c>
+      <c r="E5" s="200" t="n">
+        <v>7</v>
+      </c>
+      <c r="F5" s="200" t="n">
+        <v>303</v>
+      </c>
+      <c r="G5" s="206" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="200" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="B6" s="200" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="200" t="inlineStr">
+        <is>
+          <t>Whole MILC MKII (MILC)</t>
+        </is>
+      </c>
+      <c r="D6" s="200" t="n">
+        <v>77</v>
+      </c>
+      <c r="E6" s="200" t="n">
+        <v>11</v>
+      </c>
+      <c r="F6" s="200" t="n">
+        <v>144</v>
+      </c>
+      <c r="G6" s="206" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="200" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="B7" s="200" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="200" t="inlineStr">
+        <is>
+          <t>Easy Rider (Bike Bros)</t>
+        </is>
+      </c>
+      <c r="D7" s="200" t="n">
+        <v>75</v>
+      </c>
+      <c r="E7" s="200" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="200" t="n">
+        <v>88</v>
+      </c>
+      <c r="G7" s="206" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="200" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="B8" s="200" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" s="200" t="inlineStr">
+        <is>
+          <t>Spoke'd Easy (Spoke'd Up)</t>
+        </is>
+      </c>
+      <c r="D8" s="200" t="n">
+        <v>59</v>
+      </c>
+      <c r="E8" s="200" t="n">
+        <v>7</v>
+      </c>
+      <c r="F8" s="200" t="n">
+        <v>61</v>
+      </c>
+      <c r="G8" s="206" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="200" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="B9" s="200" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="200" t="inlineStr">
+        <is>
+          <t>BB Big Momma (BB LLC)</t>
+        </is>
+      </c>
+      <c r="D9" s="200" t="n">
+        <v>81</v>
+      </c>
+      <c r="E9" s="200" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" s="200" t="n">
+        <v>237</v>
+      </c>
+      <c r="G9" s="206" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="248" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="B10" s="248" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="248" t="inlineStr">
+        <is>
+          <t>HikeBike 1 (WeBike)</t>
+        </is>
+      </c>
+      <c r="D10" s="248" t="n">
+        <v>80</v>
+      </c>
+      <c r="E10" s="248" t="n">
+        <v>11</v>
+      </c>
+      <c r="F10" s="248" t="n">
+        <v>115</v>
+      </c>
+      <c r="G10" s="222" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="200" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="B11" s="200" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" s="200" t="inlineStr">
+        <is>
+          <t>Trail Blazing 1 (LiteCycle)</t>
+        </is>
+      </c>
+      <c r="D11" s="200" t="n">
+        <v>79</v>
+      </c>
+      <c r="E11" s="200" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" s="200" t="n">
+        <v>69</v>
+      </c>
+      <c r="G11" s="206" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="200" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="B12" s="200" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" s="200" t="inlineStr">
+        <is>
+          <t>TerraTech (Bike Bros)</t>
+        </is>
+      </c>
+      <c r="D12" s="200" t="n">
+        <v>78</v>
+      </c>
+      <c r="E12" s="200" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" s="200" t="n">
+        <v>46</v>
+      </c>
+      <c r="G12" s="206" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="200" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="B13" s="200" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" s="200" t="inlineStr">
+        <is>
+          <t>Mountainability (Bike Bros)</t>
+        </is>
+      </c>
+      <c r="D13" s="200" t="n">
+        <v>77</v>
+      </c>
+      <c r="E13" s="200" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" s="200" t="n">
+        <v>33</v>
+      </c>
+      <c r="G13" s="206" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="200" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="B14" s="200" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="200" t="inlineStr">
+        <is>
+          <t>Unleash lil pap (BB LLC)</t>
+        </is>
+      </c>
+      <c r="D14" s="200" t="n">
+        <v>76</v>
+      </c>
+      <c r="E14" s="200" t="n">
+        <v>12</v>
+      </c>
+      <c r="F14" s="200" t="n">
+        <v>200</v>
+      </c>
+      <c r="G14" s="204" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="200" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="B15" s="200" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" s="200" t="inlineStr">
+        <is>
+          <t>The Armstrong 1 (SpaceBikes)</t>
+        </is>
+      </c>
+      <c r="D15" s="200" t="n">
+        <v>77</v>
+      </c>
+      <c r="E15" s="200" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" s="200" t="n">
+        <v>98</v>
+      </c>
+      <c r="G15" s="204" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="200" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="B16" s="200" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" s="200" t="inlineStr">
+        <is>
+          <t>Speed of Lite 1 (LiteCycle)</t>
+        </is>
+      </c>
+      <c r="D16" s="200" t="n">
+        <v>77</v>
+      </c>
+      <c r="E16" s="200" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" s="200" t="n">
+        <v>61</v>
+      </c>
+      <c r="G16" s="204" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="200" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="B17" s="200" t="n">
+        <v>4</v>
+      </c>
+      <c r="C17" s="200" t="inlineStr">
+        <is>
+          <t>Skim MILC MKII (MILC)</t>
+        </is>
+      </c>
+      <c r="D17" s="200" t="n">
+        <v>75</v>
+      </c>
+      <c r="E17" s="200" t="n">
+        <v>5</v>
+      </c>
+      <c r="F17" s="200" t="n">
+        <v>43</v>
+      </c>
+      <c r="G17" s="204" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="248" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="B18" s="248" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" s="248" t="inlineStr">
+        <is>
+          <t>Swift Bike (WeBike)</t>
+        </is>
+      </c>
+      <c r="D18" s="248" t="n">
+        <v>70</v>
+      </c>
+      <c r="E18" s="248" t="n">
+        <v>8</v>
+      </c>
+      <c r="F18" s="248" t="n">
+        <v>29</v>
+      </c>
+      <c r="G18" s="219" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="200" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="B19" s="200" t="n">
+        <v>6</v>
+      </c>
+      <c r="C19" s="200" t="inlineStr">
+        <is>
+          <t>Speed of Lite 2 (LiteCycle)</t>
+        </is>
+      </c>
+      <c r="D19" s="200" t="n">
+        <v>73</v>
+      </c>
+      <c r="E19" s="200" t="n">
+        <v>4</v>
+      </c>
+      <c r="F19" s="200" t="n">
+        <v>23</v>
+      </c>
+      <c r="G19" s="204" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="200" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="B20" s="200" t="n">
+        <v>7</v>
+      </c>
+      <c r="C20" s="200" t="inlineStr">
+        <is>
+          <t>AndStill (Bike Bros)</t>
+        </is>
+      </c>
+      <c r="D20" s="200" t="n">
+        <v>78</v>
+      </c>
+      <c r="E20" s="200" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" s="200" t="n">
+        <v>23</v>
+      </c>
+      <c r="G20" s="204" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="200" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="B21" s="200" t="n">
+        <v>8</v>
+      </c>
+      <c r="C21" s="200" t="inlineStr">
+        <is>
+          <t>Excluspeedity (Bike Bros)</t>
+        </is>
+      </c>
+      <c r="D21" s="200" t="n">
+        <v>72</v>
+      </c>
+      <c r="E21" s="200" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" s="200" t="n">
+        <v>23</v>
+      </c>
+      <c r="G21" s="204" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="200" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="B22" s="200" t="n">
+        <v>9</v>
+      </c>
+      <c r="C22" s="200" t="inlineStr">
+        <is>
+          <t>Spoke'd Speed (Spoke'd Up)</t>
+        </is>
+      </c>
+      <c r="D22" s="200" t="n">
+        <v>57</v>
+      </c>
+      <c r="E22" s="200" t="n">
+        <v>5</v>
+      </c>
+      <c r="F22" s="200" t="n">
+        <v>21</v>
+      </c>
+      <c r="G22" s="204" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="170" t="inlineStr">
+        <is>
+          <t>RECREATION IS THE PROOF that ad judgment sets rank and media spend does not: Whole MILC ran 11 inserts vs Mars Rover's 7 and still ranked below it (judgment 77 vs 79). In Mountain both explanations agree, so only Rec separates them. SPEED IS UNEXPLAINED — AndStill has the best Speed ad at 78 and sits 7th. Partial clue: Bike Bros runs two ads for the SAME brand (MACH I.I) and both sank to 7th/8th. But even excluding those, Speed is not monotonic. So treat Speed click gains as UPSIDE, never as a forecast.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="199" t="inlineStr">
+        <is>
+          <t>CTR by position (verified, near-identical across segments)</t>
+        </is>
+      </c>
+      <c r="B25" s="199" t="inlineStr">
+        <is>
+          <t>CTR</t>
+        </is>
+      </c>
+      <c r="C25" s="199" t="inlineStr">
+        <is>
+          <t>Mountain clicks at 1,027 searches</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="200" t="inlineStr">
+        <is>
+          <t>Position 1</t>
+        </is>
+      </c>
+      <c r="B26" s="228" t="n">
+        <v>0.228</v>
+      </c>
+      <c r="C26" s="200" t="n">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="200" t="inlineStr">
+        <is>
+          <t>Position 2</t>
+        </is>
+      </c>
+      <c r="B27" s="228" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="C27" s="200" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="200" t="inlineStr">
+        <is>
+          <t>Position 3</t>
+        </is>
+      </c>
+      <c r="B28" s="228" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="C28" s="200" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="200" t="inlineStr">
+        <is>
+          <t>Position 4</t>
+        </is>
+      </c>
+      <c r="B29" s="228" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="C29" s="200" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="200" t="inlineStr">
+        <is>
+          <t>Position 5</t>
+        </is>
+      </c>
+      <c r="B30" s="228" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="C30" s="200" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="222" t="inlineStr">
+        <is>
+          <t>HikeBike 1 moving position 2 -&gt; 1</t>
+        </is>
+      </c>
+      <c r="B31" s="271" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="C31" s="222" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="199" t="inlineStr">
+        <is>
+          <t>HIKEBIKE 1 — recommended stack (BB LLC's verbatim)</t>
+        </is>
+      </c>
+      <c r="B34" s="199" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="C34" s="259" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="200" t="inlineStr">
+        <is>
+          <t>1 Tackle steep climbs with more gears</t>
+        </is>
+      </c>
+      <c r="B35" s="211" t="inlineStr">
+        <is>
+          <t>keep, promote</t>
+        </is>
+      </c>
+      <c r="C35" s="260" t="inlineStr">
+        <is>
+          <t>Mountain's #1 need: easily handles change in incline, 131. 4 of 4 rivals run it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="200" t="inlineStr">
+        <is>
+          <t>2 Grab the path with high tread tires</t>
+        </is>
+      </c>
+      <c r="B36" s="211" t="inlineStr">
+        <is>
+          <t>keep, promote</t>
+        </is>
+      </c>
+      <c r="C36" s="260" t="inlineStr">
+        <is>
+          <t>Can handle rough terrain 128. 3 of 4 rivals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="200" t="inlineStr">
+        <is>
+          <t>3 Highest rated Mountain bike</t>
+        </is>
+      </c>
+      <c r="B37" s="206" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="C37" s="260" t="inlineStr">
+        <is>
+          <t>TRUE — Hike Bike is TIED for best Mountain at 73 with TERRAMAX and Blu Ruged Ballz, so the claim is legal. Hits Status symbol/exclusivity 121. This is BB LLC's differentiator.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="200" t="inlineStr">
+        <is>
+          <t>4 Local sales &amp; service</t>
+        </is>
+      </c>
+      <c r="B38" s="206" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="C38" s="260" t="inlineStr">
+        <is>
+          <t>TRUE — Amsterdam + Rio. Hits Repair/parts/support nearby 121. 3 of 4 rival Mountain ads run it and we never have, despite being 80.9% store.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="200" t="inlineStr">
+        <is>
+          <t>5 Mention brand name</t>
+        </is>
+      </c>
+      <c r="B39" s="211" t="inlineStr">
+        <is>
+          <t>keep, demote</t>
+        </is>
+      </c>
+      <c r="C39" s="260" t="inlineStr">
+        <is>
+          <t>Fills the Ad/Brand columns and does NOT consume a SERP snippet slot, so rank 1 was wasted on it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="200" t="inlineStr">
+        <is>
+          <t>6 Picture of a rider on a steep trail</t>
+        </is>
+      </c>
+      <c r="B40" s="211" t="inlineStr">
+        <is>
+          <t>keep, demote</t>
+        </is>
+      </c>
+      <c r="C40" s="260" t="inlineStr">
+        <is>
+          <t>DOES consume a snippet slot. Rec #1 and Mountain #1 both lead with a CLAIM, not a picture.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="200" t="inlineStr">
+        <is>
+          <t>-- Have an adventure on a carbon bike!</t>
+        </is>
+      </c>
+      <c r="B41" s="204" t="inlineStr">
+        <is>
+          <t>DROP</t>
+        </is>
+      </c>
+      <c r="C41" s="260" t="inlineStr">
+        <is>
+          <t>Only 2 of 4 rivals. BB LLC omits it and scores higher with fewer benefits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="200" t="inlineStr">
+        <is>
+          <t>-- Go anywhere on a tough carbon bike</t>
+        </is>
+      </c>
+      <c r="B42" s="204" t="inlineStr">
+        <is>
+          <t>DROP</t>
+        </is>
+      </c>
+      <c r="C42" s="260" t="inlineStr">
+        <is>
+          <t>Weakest adoption at 1 of 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="200" t="inlineStr">
+        <is>
+          <t>-- Mountains are no longer difficult</t>
+        </is>
+      </c>
+      <c r="B43" s="204" t="inlineStr">
+        <is>
+          <t>DROP, then TEST</t>
+        </is>
+      </c>
+      <c r="C43" s="260" t="inlineStr">
+        <is>
+          <t>Drop first. If the preview reads 81, add it back at rank 7 and preview again; keep the higher score.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="170" t="inlineStr">
+        <is>
+          <t>BB LLC wins with SIX benefits while we run SEVEN — more claims is not better. Spoke'd Speed has all the right Speed ingredients, uses the full 9-benefit cap, and scores 57, the worst in the game. PREVIEW BEFORE COMMITTING; revert to Q3 copy if it comes in under 80.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="199" t="inlineStr">
+        <is>
+          <t>SWIFT BIKE — recommended stack (AndStill's verbatim, the 78)</t>
+        </is>
+      </c>
+      <c r="B46" s="199" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="C46" s="259" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="200" t="inlineStr">
+        <is>
+          <t>1 Picture of road race</t>
+        </is>
+      </c>
+      <c r="B47" s="211" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="C47" s="260" t="inlineStr">
+        <is>
+          <t>8 of 8 rivals. The one line we already share with the best ad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="200" t="inlineStr">
+        <is>
+          <t>2 Mention brand name</t>
+        </is>
+      </c>
+      <c r="B48" s="211" t="inlineStr">
+        <is>
+          <t>promote</t>
+        </is>
+      </c>
+      <c r="C48" s="260" t="inlineStr">
+        <is>
+          <t>8 of 8 rivals rank it 2nd. Ours sat at 4. Does not consume a snippet slot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="200" t="inlineStr">
+        <is>
+          <t>3 Ride a wind-cheater</t>
+        </is>
+      </c>
+      <c r="B49" s="206" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="C49" s="260" t="inlineStr">
+        <is>
+          <t>8 of 8 rivals run it and we do not. Aerodynamic is Speed need #5 at 122, and the aero frame supports the claim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="200" t="inlineStr">
+        <is>
+          <t>4 Elite look - a ride of distinction</t>
+        </is>
+      </c>
+      <c r="B50" s="206" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="C50" s="260" t="inlineStr">
+        <is>
+          <t>6 of 8, including BOTH 77-point ads. Status symbol 116.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="200" t="inlineStr">
+        <is>
+          <t>5 A tailor-made bike just for you! 3D printing</t>
+        </is>
+      </c>
+      <c r="B51" s="206" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="C51" s="260" t="inlineStr">
+        <is>
+          <t>3 of 8, but on BOTH of the two best ads. We actually 3D-print — this is our licensed core capability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="200" t="inlineStr">
+        <is>
+          <t>6 Roll fast with racing tires</t>
+        </is>
+      </c>
+      <c r="B52" s="206" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="C52" s="260" t="inlineStr">
+        <is>
+          <t>7 of 8. The bike HAS racing tires. Speed's #1 need is Speed at 134.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="200" t="inlineStr">
+        <is>
+          <t>7 Local sales &amp; service</t>
+        </is>
+      </c>
+      <c r="B53" s="206" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="C53" s="260" t="inlineStr">
+        <is>
+          <t>3 of 8. We are 80.9% store and have never claimed it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="200" t="inlineStr">
+        <is>
+          <t>-- Carbon fiber quality at a GREAT PRICE</t>
+        </is>
+      </c>
+      <c r="B54" s="204" t="inlineStr">
+        <is>
+          <t>DROP</t>
+        </is>
+      </c>
+      <c r="C54" s="260" t="inlineStr">
+        <is>
+          <t>0 of 8 rivals. And we are raising Swift to $1,580 this quarter — the claim would contradict the price.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="200" t="inlineStr">
+        <is>
+          <t>-- Ride safely after dark with LIGHTS</t>
+        </is>
+      </c>
+      <c r="B55" s="204" t="inlineStr">
+        <is>
+          <t>DROP</t>
+        </is>
+      </c>
+      <c r="C55" s="260" t="inlineStr">
+        <is>
+          <t>0 of 8. A Recreation cue. The bike KEEPS its lights (+1 in the Speed recipe); we just stop advertising them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="200" t="inlineStr">
+        <is>
+          <t>-- Added safety - REFLECTORS everywhere</t>
+        </is>
+      </c>
+      <c r="B56" s="204" t="inlineStr">
+        <is>
+          <t>DROP</t>
+        </is>
+      </c>
+      <c r="C56" s="260" t="inlineStr">
+        <is>
+          <t>0 of 8. Same: keep the part, drop the claim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="200" t="inlineStr">
+        <is>
+          <t>-- Enjoy your ride - carbon fiber light</t>
+        </is>
+      </c>
+      <c r="B57" s="211" t="inlineStr">
+        <is>
+          <t>DEMOTE or drop</t>
+        </is>
+      </c>
+      <c r="C57" s="260" t="inlineStr">
+        <is>
+          <t>4 of 8 run it, but it was our rank 2 and reads as Recreation comfort.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="200" t="inlineStr">
+        <is>
+          <t>TEST: Highest rated Speed bike</t>
+        </is>
+      </c>
+      <c r="B58" s="211" t="inlineStr">
+        <is>
+          <t>TEST ONLY</t>
+        </is>
+      </c>
+      <c r="C58" s="260" t="inlineStr">
+        <is>
+          <t>The Armstrong runs it and sits position 2. Legal ONLY once Swift's design actually hits 77. The sim may validate against Q3 where Swift is 72 — so DESIGN THE BRAND FIRST, then the ad. If rejected, keep local sales &amp; service.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="170" t="inlineStr">
+        <is>
+          <t>Our current Speed ad shares exactly ONE line with the best Speed ad. The three claims nobody else runs (lights / reflectors / great price) are Recreation cues and are why the ad leaks 52 Rec and 36 Mtn units at a judgment of 70. DO BOTH the design fix (24sp-&gt;14sp +3, add decals +2 =&gt; 77) AND the ad fix in the SAME quarter: together Marketing Effectiveness hits 0.7675, past BB LLC's 0.765 for industry best. Ad alone = 0.755, design alone = 0.750.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="199" t="inlineStr">
+        <is>
+          <t>MEDIA — cost per insert</t>
+        </is>
+      </c>
+      <c r="B61" s="199" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="C61" s="259" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="206" t="inlineStr">
+        <is>
+          <t>Biking Magazines</t>
+        </is>
+      </c>
+      <c r="B62" s="244" t="n">
+        <v>4500</v>
+      </c>
+      <c r="C62" s="261" t="inlineStr">
+        <is>
+          <t>CHEAPEST and the top-preference medium for BOTH our segments (Mountain pref 134)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="200" t="inlineStr">
+        <is>
+          <t>New Venture</t>
+        </is>
+      </c>
+      <c r="B63" s="220" t="n">
+        <v>5500</v>
+      </c>
+      <c r="C63" s="260" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="200" t="inlineStr">
+        <is>
+          <t>Health &amp; Fitness</t>
+        </is>
+      </c>
+      <c r="B64" s="220" t="n">
+        <v>7000</v>
+      </c>
+      <c r="C64" s="260" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="200" t="inlineStr">
+        <is>
+          <t>General News</t>
+        </is>
+      </c>
+      <c r="B65" s="220" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C65" s="260" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="200" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="B66" s="220" t="n">
+        <v>9500</v>
+      </c>
+      <c r="C66" s="260" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="200" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B67" s="220" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C67" s="260" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="200" t="inlineStr">
+        <is>
+          <t>Leisure &amp; Entertainment</t>
+        </is>
+      </c>
+      <c r="B68" s="220" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C68" s="260" t="inlineStr">
+        <is>
+          <t>Rec-skewed — Mountain preference 60. Do not buy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="199" t="inlineStr">
+        <is>
+          <t>MEDIA OPTIONS</t>
+        </is>
+      </c>
+      <c r="B71" s="199" t="inlineStr">
+        <is>
+          <t>Hike Biking</t>
+        </is>
+      </c>
+      <c r="C71" s="199" t="inlineStr">
+        <is>
+          <t>Swift Biking</t>
+        </is>
+      </c>
+      <c r="D71" s="199" t="inlineStr">
+        <is>
+          <t>Inserts</t>
+        </is>
+      </c>
+      <c r="E71" s="199" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="F71" s="199" t="inlineStr">
+        <is>
+          <t>vs Q3</t>
+        </is>
+      </c>
+      <c r="G71" s="199" t="inlineStr">
+        <is>
+          <t>Biking total</t>
+        </is>
+      </c>
+      <c r="H71" s="259" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="204" t="inlineStr">
+        <is>
+          <t>Q3 actual (what we did)</t>
+        </is>
+      </c>
+      <c r="B72" s="204" t="n">
+        <v>11</v>
+      </c>
+      <c r="C72" s="204" t="n">
+        <v>8</v>
+      </c>
+      <c r="D72" s="204" t="n">
+        <v>19</v>
+      </c>
+      <c r="E72" s="269" t="n">
+        <v>116000</v>
+      </c>
+      <c r="F72" s="269" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="204" t="n">
+        <v>10</v>
+      </c>
+      <c r="H72" s="264" t="inlineStr">
+        <is>
+          <t>5 media, 53% Biking. The mix error.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="200" t="inlineStr">
+        <is>
+          <t>A. Copy BB LLC exactly</t>
+        </is>
+      </c>
+      <c r="B73" s="200" t="n">
+        <v>12</v>
+      </c>
+      <c r="C73" s="200" t="n">
+        <v>12</v>
+      </c>
+      <c r="D73" s="200" t="n">
+        <v>24</v>
+      </c>
+      <c r="E73" s="220" t="n">
+        <v>108000</v>
+      </c>
+      <c r="F73" s="220" t="n">
+        <v>-8000</v>
+      </c>
+      <c r="G73" s="200" t="n">
+        <v>24</v>
+      </c>
+      <c r="H73" s="260" t="inlineStr">
+        <is>
+          <t>Right mix, but +5 inserts of demand we cannot build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="204" t="inlineStr">
+        <is>
+          <t>B. My earlier rec (SUPERSEDED)</t>
+        </is>
+      </c>
+      <c r="B74" s="204" t="n">
+        <v>16</v>
+      </c>
+      <c r="C74" s="204" t="n">
+        <v>12</v>
+      </c>
+      <c r="D74" s="204" t="n">
+        <v>28</v>
+      </c>
+      <c r="E74" s="269" t="n">
+        <v>143000</v>
+      </c>
+      <c r="F74" s="269" t="n">
+        <v>27000</v>
+      </c>
+      <c r="G74" s="204" t="n">
+        <v>24</v>
+      </c>
+      <c r="H74" s="264" t="inlineStr">
+        <is>
+          <t>+$27,000 and the most demand. Wrong for a capped quarter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="222" t="inlineStr">
+        <is>
+          <t>C. MIX FIX ONLY (recommended)</t>
+        </is>
+      </c>
+      <c r="B75" s="222" t="n">
+        <v>12</v>
+      </c>
+      <c r="C75" s="222" t="n">
+        <v>4</v>
+      </c>
+      <c r="D75" s="222" t="n">
+        <v>16</v>
+      </c>
+      <c r="E75" s="265" t="n">
+        <v>72000</v>
+      </c>
+      <c r="F75" s="265" t="n">
+        <v>-44000</v>
+      </c>
+      <c r="G75" s="222" t="n">
+        <v>16</v>
+      </c>
+      <c r="H75" s="263" t="inlineStr">
+        <is>
+          <t>Matches BB LLC's 12 Biking on Mountain, holds Speed at Q3's 4, drops all off-Biking. -$44,000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="200" t="inlineStr">
+        <is>
+          <t>D. Minimum viable</t>
+        </is>
+      </c>
+      <c r="B76" s="200" t="n">
+        <v>8</v>
+      </c>
+      <c r="C76" s="200" t="n">
+        <v>4</v>
+      </c>
+      <c r="D76" s="200" t="n">
+        <v>12</v>
+      </c>
+      <c r="E76" s="220" t="n">
+        <v>54000</v>
+      </c>
+      <c r="F76" s="220" t="n">
+        <v>-62000</v>
+      </c>
+      <c r="G76" s="200" t="n">
+        <v>12</v>
+      </c>
+      <c r="H76" s="260" t="inlineStr">
+        <is>
+          <t>If the team wants to protect the loan headroom harder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="170" t="inlineStr">
+        <is>
+          <t>WHY VOLUME MUST BE RESTRAINED: Market Performance = (avg share in targeted segments) x (percent of demand served). Q4 output is capped at 1,154 units and the plan already forecasts 1,171. With output capped, extra demand CANNOT raise units sold, so it only lowers the percent-served term — strictly negative — and it earns Q5 ill will at half the unmet percentage. Fix the MIX, hold the VOLUME, and expand to the full 24-insert BB LLC buy in Q5 when the printers land.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="199" t="inlineStr">
+        <is>
+          <t>ORGANIC SEO — settled points</t>
+        </is>
+      </c>
+      <c r="B79" s="259" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="200" t="inlineStr">
+        <is>
+          <t>Page investment is not a lever</t>
+        </is>
+      </c>
+      <c r="B80" s="260" t="inlineStr">
+        <is>
+          <t>Every listing in the industry cost exactly $1,000 and nobody spent more. Leave both pages at $1,000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="200" t="inlineStr">
+        <is>
+          <t>Rank sets clicks; snippet wording does not</t>
+        </is>
+      </c>
+      <c r="B81" s="260" t="inlineStr">
+        <is>
+          <t>CTR is a step function of position only: 22.8% / 11.1% / 6.7% / 4.6% / 3.2%. So optimise for AD JUDGMENT, which sets position, not for snippet aesthetics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="200" t="inlineStr">
+        <is>
+          <t>Brand name is free on the SERP</t>
+        </is>
+      </c>
+      <c r="B82" s="260" t="inlineStr">
+        <is>
+          <t>'Mention brand name' fills the Ad/Brand columns and does NOT consume a snippet slot. A PICTURE does. Rec #1 and Mountain #1 both lead with a claim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="200" t="inlineStr">
+        <is>
+          <t>Never a second page in one segment</t>
+        </is>
+      </c>
+      <c r="B83" s="260" t="inlineStr">
+        <is>
+          <t>Bike Bros' two Mountain ads drew 79 clicks combined against our single page's 115, and their two MACH I.I Speed pages sank to positions 7 and 8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="200" t="inlineStr">
+        <is>
+          <t>No Recreation page</t>
+        </is>
+      </c>
+      <c r="B84" s="260" t="inlineStr">
+        <is>
+          <t>We have no Rec brand, and every Rec winner leads with comfort-seat copy we cannot truthfully run on Hike Bike.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="200" t="inlineStr">
+        <is>
+          <t>SEO is NOT our web problem</t>
+        </is>
+      </c>
+      <c r="B85" s="262" t="inlineStr">
+        <is>
+          <t>LiteCycle converts 153 clicks into 435 web units; we convert 144 into 120 — 3.6x worse on nearly identical traffic. The web rebuild (staff 3-&gt;7, all four tactics) is the fix, not more clicks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="199" t="inlineStr">
+        <is>
+          <t>Q4 DECISION SUMMARY</t>
+        </is>
+      </c>
+      <c r="B88" s="259" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="200" t="inlineStr">
+        <is>
+          <t>HikeBike 1 ad</t>
+        </is>
+      </c>
+      <c r="B89" s="260" t="inlineStr">
+        <is>
+          <t>Redesign to BB LLC's 6-benefit stack. Add 'Highest rated Mountain bike' and 'Local sales &amp; service'; drop adventure, tough carbon, mountains-easier. Preview and target 82 for position 1 — the payoff is deterministic in Mountain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="200" t="inlineStr">
+        <is>
+          <t>Swift Bike ad</t>
+        </is>
+      </c>
+      <c r="B90" s="260" t="inlineStr">
+        <is>
+          <t>Redesign to AndStill's 7-benefit stack. Drop lights, reflectors and great price. Design the brand FIRST so 'Highest rated Speed bike' can be tested.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="200" t="inlineStr">
+        <is>
+          <t>Organic SEO</t>
+        </is>
+      </c>
+      <c r="B91" s="260" t="inlineStr">
+        <is>
+          <t>Both pages stay at $1,000. No third page, no Rec page. Fix web OPERATIONS, not traffic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="200" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="B92" s="260" t="inlineStr">
+        <is>
+          <t>Option C — Biking only, HikeBike 12 + Swift 4 = 16 inserts, $72,000, down $44,000 from Q3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="200" t="inlineStr">
+        <is>
+          <t>Leave alone</t>
+        </is>
+      </c>
+      <c r="B93" s="260" t="inlineStr">
+        <is>
+          <t>Hike Bike's design (73, tied best, verified optimal) and its price ($1,365, already the optimal tier).</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="200" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B94" s="260" t="inlineStr">
+        <is>
+          <t>ANALYSIS ONLY — majority vote required. Preview every ad score in the designer before committing.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:G2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/quarters/Q3/Q3Data.xlsx
+++ b/quarters/Q3/Q3Data.xlsx
@@ -56,6 +56,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q4_RD" sheetId="48" state="visible" r:id="rId48"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q4_Financing" sheetId="49" state="visible" r:id="rId49"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q4_Ads_SEO_Media" sheetId="50" state="visible" r:id="rId50"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q4_Price_Priority" sheetId="51" state="visible" r:id="rId51"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -671,7 +672,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="16"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="16"/>
   </cellStyleXfs>
-  <cellXfs count="272">
+  <cellXfs count="274">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1056,6 +1057,8 @@
     <xf numFmtId="3" fontId="0" fillId="31" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="31" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="28" fillId="29" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="29" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="32" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -61771,6 +61774,533 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" style="146" min="1" max="1"/>
+    <col width="14" customWidth="1" style="146" min="2" max="2"/>
+    <col width="100" customWidth="1" style="146" min="3" max="3"/>
+    <col width="13" customWidth="1" style="146" min="4" max="4"/>
+    <col width="13" customWidth="1" style="146" min="5" max="5"/>
+    <col width="46" customWidth="1" style="146" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="169" t="inlineStr">
+        <is>
+          <t>Q4 World Market — retail price, rebate, sales priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="48" customHeight="1" s="146">
+      <c r="A2" s="258" t="inlineStr">
+        <is>
+          <t>BOTTOM LINE: hold Hike Bike at $1,365 (already the highest price that draws zero Mountain resistance), raise Swift Bike $1,450 -&gt; $1,580 (+$130, verified riskless by three rival brands at that exact price), keep both rebates at $0, and LEAVE the priority order alone. The priority reasoning changed: a Mountain unit is worth 1.78x a Speed unit for Market Performance because Mountain is the SMALLER segment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="199" t="inlineStr">
+        <is>
+          <t>WHAT TO ENTER</t>
+        </is>
+      </c>
+      <c r="B4" s="199" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="C4" s="199" t="inlineStr">
+        <is>
+          <t>Retail price</t>
+        </is>
+      </c>
+      <c r="D4" s="199" t="inlineStr">
+        <is>
+          <t>Rebate</t>
+        </is>
+      </c>
+      <c r="E4" s="259" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="200" t="inlineStr">
+        <is>
+          <t>Hike Bike</t>
+        </is>
+      </c>
+      <c r="B5" s="200" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="232" t="n">
+        <v>1365</v>
+      </c>
+      <c r="D5" s="232" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="260" t="inlineStr">
+        <is>
+          <t>NO CHANGE — Mountain price judgment is already 100 and the next step up drops it to 94</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="206" t="inlineStr">
+        <is>
+          <t>Swift Bike</t>
+        </is>
+      </c>
+      <c r="B6" s="206" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="272" t="n">
+        <v>1580</v>
+      </c>
+      <c r="D6" s="272" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="261" t="inlineStr">
+        <is>
+          <t>RAISE $130 from $1,450 — Speed judgment stays at 100, proven by Blu Aero, Blu Tube and The Armstrong</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="199" t="inlineStr">
+        <is>
+          <t>PRICE TIER LADDER (from Q3_Price_Judgment)</t>
+        </is>
+      </c>
+      <c r="B9" s="199" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="C9" s="199" t="inlineStr">
+        <is>
+          <t>Rec</t>
+        </is>
+      </c>
+      <c r="D9" s="199" t="inlineStr">
+        <is>
+          <t>Mtn</t>
+        </is>
+      </c>
+      <c r="E9" s="199" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="F9" s="259" t="inlineStr">
+        <is>
+          <t>Brands at this price</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="206" t="inlineStr"/>
+      <c r="B10" s="272" t="n">
+        <v>1365</v>
+      </c>
+      <c r="C10" s="206" t="n">
+        <v>81</v>
+      </c>
+      <c r="D10" s="206" t="n">
+        <v>100</v>
+      </c>
+      <c r="E10" s="206" t="n">
+        <v>100</v>
+      </c>
+      <c r="F10" s="261" t="inlineStr">
+        <is>
+          <t>Hike Bike, Blu Ruged Ballz, Blu Tail Ballz</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="200" t="inlineStr"/>
+      <c r="B11" s="232" t="n">
+        <v>1450</v>
+      </c>
+      <c r="C11" s="200" t="n">
+        <v>76</v>
+      </c>
+      <c r="D11" s="200" t="n">
+        <v>94</v>
+      </c>
+      <c r="E11" s="200" t="n">
+        <v>100</v>
+      </c>
+      <c r="F11" s="260" t="inlineStr">
+        <is>
+          <t>Swift Bike, Skim MILC MKII</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="200" t="inlineStr"/>
+      <c r="B12" s="232" t="n">
+        <v>1499</v>
+      </c>
+      <c r="C12" s="200" t="n">
+        <v>73</v>
+      </c>
+      <c r="D12" s="200" t="n">
+        <v>91</v>
+      </c>
+      <c r="E12" s="200" t="n">
+        <v>100</v>
+      </c>
+      <c r="F12" s="260" t="inlineStr">
+        <is>
+          <t>TERRAMAX, Spoke'd Speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="200" t="inlineStr"/>
+      <c r="B13" s="232" t="n">
+        <v>1515</v>
+      </c>
+      <c r="C13" s="200" t="n">
+        <v>73</v>
+      </c>
+      <c r="D13" s="200" t="n">
+        <v>91</v>
+      </c>
+      <c r="E13" s="200" t="n">
+        <v>100</v>
+      </c>
+      <c r="F13" s="260" t="inlineStr">
+        <is>
+          <t>LiteSpeed Pro+</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="200" t="inlineStr"/>
+      <c r="B14" s="232" t="n">
+        <v>1579</v>
+      </c>
+      <c r="C14" s="200" t="n">
+        <v>70</v>
+      </c>
+      <c r="D14" s="200" t="n">
+        <v>86</v>
+      </c>
+      <c r="E14" s="200" t="n">
+        <v>100</v>
+      </c>
+      <c r="F14" s="260" t="inlineStr">
+        <is>
+          <t>Mach 0.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="211" t="inlineStr"/>
+      <c r="B15" s="273" t="n">
+        <v>1580</v>
+      </c>
+      <c r="C15" s="211" t="n">
+        <v>70</v>
+      </c>
+      <c r="D15" s="211" t="n">
+        <v>86</v>
+      </c>
+      <c r="E15" s="211" t="n">
+        <v>100</v>
+      </c>
+      <c r="F15" s="262" t="inlineStr">
+        <is>
+          <t>Blu Aero Ballz, Blu Tube Ballz, The Armstrong</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="200" t="inlineStr"/>
+      <c r="B16" s="232" t="n">
+        <v>1749</v>
+      </c>
+      <c r="C16" s="200" t="n">
+        <v>63</v>
+      </c>
+      <c r="D16" s="200" t="n">
+        <v>78</v>
+      </c>
+      <c r="E16" s="200" t="n">
+        <v>90</v>
+      </c>
+      <c r="F16" s="260" t="inlineStr">
+        <is>
+          <t>MACH I.I — most expensive in the game</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="170" t="inlineStr">
+        <is>
+          <t>Speed is the least price-sensitive segment in the game: judgment holds at 100 all the way to $1,580 and only breaks at $1,749. Mountain holds 100 only to $1,365. Swift Bike is currently the 2nd CHEAPEST of 10 Speed brands while carrying the 2nd WORST product — $97 below the $1,547 Speed median. Rivals price Speed $200+ above Mountain; BB LLC runs Mountain $1,365 (same as ours) and Speed $1,580. We copied their Mountain price and missed their Speed price.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="199" t="inlineStr">
+        <is>
+          <t>WHY NOT GO ABOVE $1,580?</t>
+        </is>
+      </c>
+      <c r="B19" s="259" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="200" t="inlineStr">
+        <is>
+          <t>$1,581-$1,748 is untested</t>
+        </is>
+      </c>
+      <c r="B20" s="260" t="inlineStr">
+        <is>
+          <t>Nobody in the industry prices in that band, so we cannot see where Speed judgment breaks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="200" t="inlineStr">
+        <is>
+          <t>Capacity binds this quarter</t>
+        </is>
+      </c>
+      <c r="B21" s="260" t="inlineStr">
+        <is>
+          <t>Forecast 1,171 vs capacity 1,154 leaves only 17 units of slack. A price rise that dents Speed demand could leave printers under-filled, and Q2 already cost us $148,652 for scheduled capacity we did not use.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="200" t="inlineStr">
+        <is>
+          <t>$1,580 is free money; beyond is a bet</t>
+        </is>
+      </c>
+      <c r="B22" s="260" t="inlineStr">
+        <is>
+          <t>It is verified by four separate brands and captures $130 of the $384 available headroom at zero risk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="200" t="inlineStr">
+        <is>
+          <t>Q5 is not the time either</t>
+        </is>
+      </c>
+      <c r="B23" s="260" t="inlineStr">
+        <is>
+          <t>Two new printers take capacity to ~40/day, so Q5 needs MORE demand, not less. Probe higher only when demand comfortably exceeds capacity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="199" t="inlineStr">
+        <is>
+          <t>REBATE — keep both at $0</t>
+        </is>
+      </c>
+      <c r="B26" s="259" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="200" t="inlineStr">
+        <is>
+          <t>Only 2 brands in the game rebate</t>
+        </is>
+      </c>
+      <c r="B27" s="260" t="inlineStr">
+        <is>
+          <t>Mars Rover $1,100-$50 and Whole MILC $1,050-$100. Both Recreation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="200" t="inlineStr">
+        <is>
+          <t>Zero Mountain, zero Speed rebates</t>
+        </is>
+      </c>
+      <c r="B28" s="260" t="inlineStr">
+        <is>
+          <t>Not one rival in either of our segments discounts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="200" t="inlineStr">
+        <is>
+          <t>A rebate is a tier walk-back</t>
+        </is>
+      </c>
+      <c r="B29" s="260" t="inlineStr">
+        <is>
+          <t>It is a price cut that prints as its own line — it moves us back DOWN the ladder we are climbing and signals discount in the two segments where we chase margin leadership.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="200" t="inlineStr">
+        <is>
+          <t>Recreation is the price battleground</t>
+        </is>
+      </c>
+      <c r="B30" s="260" t="inlineStr">
+        <is>
+          <t>Its three winners are simply the cheapest bikes in the game. Recreation stays parked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="199" t="inlineStr">
+        <is>
+          <t>SALES PRIORITY — the trade-off</t>
+        </is>
+      </c>
+      <c r="B33" s="259" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="200" t="inlineStr">
+        <is>
+          <t>SHARE says promote Hike Bike</t>
+        </is>
+      </c>
+      <c r="B34" s="260" t="inlineStr">
+        <is>
+          <t>Market Performance = avg share x pct served, and share is units / SEGMENT demand. Mountain demand is 1,621 vs Speed 2,878, so one Mountain unit = 0.0617 share points against 0.0347 for a Speed unit — a Mountain unit is worth 1.78x. This is division, not estimation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="200" t="inlineStr">
+        <is>
+          <t>MARGIN says promote Swift Bike</t>
+        </is>
+      </c>
+      <c r="B35" s="260" t="inlineStr">
+        <is>
+          <t>Hike Bike contributes $747/unit; Swift at $1,580 contributes $886 — $139 more, and the 14-speed swap should widen it since the feature text says fewer parts than the 24-speed it replaces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="200" t="inlineStr">
+        <is>
+          <t>But Q3 says the field did nothing</t>
+        </is>
+      </c>
+      <c r="B36" s="262" t="inlineStr">
+        <is>
+          <t>We set Hike Bike to priority 1 in Q3 and it stocked out 32.5% while Swift stocked out 32.6%. If priority rationed production, Hike Bike should have filled FIRST. It did not — the shortfall went roughly PRO-RATA. The mechanism is UNVERIFIED; do not treat priority as insurance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="200" t="inlineStr">
+        <is>
+          <t>And the stake is tiny at plan</t>
+        </is>
+      </c>
+      <c r="B37" s="260" t="inlineStr">
+        <is>
+          <t>At the planned 17-unit shortfall the whole question is worth about $2,363. It only matters if demand overshoots — which it plausibly will once the ad rebuilds, web rebuild, Rio staffing and Biking concentration all land together.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="206" t="inlineStr">
+        <is>
+          <t>DECISION: leave it (Hike 1, Swift 2)</t>
+        </is>
+      </c>
+      <c r="B38" s="261" t="inlineStr">
+        <is>
+          <t>Mountain is the one position we can hold — 22.1% share, a product TIED for best at 73, and a Rio monopoly delivering 58% of Rio Mountain, versus 6th place and the 2nd-worst product in Speed. The margin case looks strong only through Financial Performance, whose numerator is ~$132,975, so any marginal dollar swings it wildly — an artefact of being barely profitable that breaks entirely if Q4 posts a loss. Prefer the stable arithmetic. And the $130 price rise is captured on every Swift bike we DO sell either way; priority only decides the last few units.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="199" t="inlineStr">
+        <is>
+          <t>CHECK ON THE SCREEN</t>
+        </is>
+      </c>
+      <c r="B41" s="259" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="200" t="inlineStr">
+        <is>
+          <t>'Available for Sale' is BLANK for both</t>
+        </is>
+      </c>
+      <c r="B42" s="262" t="inlineStr">
+        <is>
+          <t>Confirm both brands are actually enabled for World Market. We are spending ~$33,000 on web tactics and taking web staff from 3 to 7 this quarter — if a brand is not flagged available in the web channel, none of that can convert. A blank field is exactly how a brand silently fails to list.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="200" t="inlineStr">
+        <is>
+          <t>Is this screen global or per-market?</t>
+        </is>
+      </c>
+      <c r="B43" s="260" t="inlineStr">
+        <is>
+          <t>It is headed 'World Market', our web centre. Check whether Amsterdam and Rio have their own price screens. Q3 reported ONE price per brand industry-wide, suggesting pricing is global — but if it is per-market, both prices must be entered in all three places.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="200" t="inlineStr">
+        <is>
+          <t>Sequencing</t>
+        </is>
+      </c>
+      <c r="B44" s="260" t="inlineStr">
+        <is>
+          <t>Do the price rise in the SAME quarter as the design fix (24sp -&gt; 14sp, add decals =&gt; 77). A price rise on the 2nd-worst Speed product invites resistance; the same rise on a joint-best product does not.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:F2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/quarters/Q3/Q3Data.xlsx
+++ b/quarters/Q3/Q3Data.xlsx
@@ -57,6 +57,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q4_Financing" sheetId="49" state="visible" r:id="rId49"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q4_Ads_SEO_Media" sheetId="50" state="visible" r:id="rId50"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q4_Price_Priority" sheetId="51" state="visible" r:id="rId51"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q4_Paid_SEM" sheetId="52" state="visible" r:id="rId52"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q4_Social_Media" sheetId="53" state="visible" r:id="rId53"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -672,7 +674,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="16"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="16"/>
   </cellStyleXfs>
-  <cellXfs count="274">
+  <cellXfs count="275">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1059,6 +1061,7 @@
     <xf numFmtId="164" fontId="28" fillId="29" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="0" fillId="29" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="0" fillId="32" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="28" fillId="29" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -62301,6 +62304,1218 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" style="146" min="1" max="1"/>
+    <col width="88" customWidth="1" style="146" min="2" max="2"/>
+    <col width="20" customWidth="1" style="146" min="3" max="3"/>
+    <col width="16" customWidth="1" style="146" min="4" max="4"/>
+    <col width="18" customWidth="1" style="146" min="5" max="5"/>
+    <col width="20" customWidth="1" style="146" min="6" max="6"/>
+    <col width="26" customWidth="1" style="146" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="169" t="inlineStr">
+        <is>
+          <t>Q4 paid SEM — match the posted average on the bid, throttle with the budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="72" customHeight="1" s="146">
+      <c r="A2" s="258" t="inlineStr">
+        <is>
+          <t>Paid search is demand generation that sits ABOVE organic. Q4 output is capped at 1,154 against a 1,171 forecast (demand already 17 over), so extra clicks are strictly negative for Market Performance — the same reason media volume was restrained. Do not sit out: BB LLC will buy the slot above HikeBike 1's organic #2. Enter $2.40 / $150 on HikeBike 1 and $1.95 / $80 on Swift Bike. Keywords = the agency set already attached to each page (Mountain / Speed). OPEN — majority vote required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="199" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="B4" s="199" t="inlineStr">
+        <is>
+          <t>Segment / keywords</t>
+        </is>
+      </c>
+      <c r="C4" s="199" t="inlineStr">
+        <is>
+          <t>Industry avg bid</t>
+        </is>
+      </c>
+      <c r="D4" s="199" t="inlineStr">
+        <is>
+          <t>OUR max bid</t>
+        </is>
+      </c>
+      <c r="E4" s="199" t="inlineStr">
+        <is>
+          <t>OUR max budget</t>
+        </is>
+      </c>
+      <c r="F4" s="199" t="inlineStr">
+        <is>
+          <t>Clicks at max bid</t>
+        </is>
+      </c>
+      <c r="G4" s="199" t="inlineStr">
+        <is>
+          <t>Clicks if CPC = 75% of bid</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="206" t="inlineStr">
+        <is>
+          <t>HikeBike 1</t>
+        </is>
+      </c>
+      <c r="B5" s="206" t="inlineStr">
+        <is>
+          <t>Mountain (agency set)</t>
+        </is>
+      </c>
+      <c r="C5" s="206" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D5" s="206" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E5" s="206" t="n">
+        <v>150</v>
+      </c>
+      <c r="F5" s="206" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="G5" s="206" t="n">
+        <v>83.3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="206" t="inlineStr">
+        <is>
+          <t>Swift Bike</t>
+        </is>
+      </c>
+      <c r="B6" s="206" t="inlineStr">
+        <is>
+          <t>Speed (agency set)</t>
+        </is>
+      </c>
+      <c r="C6" s="206" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="D6" s="206" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="E6" s="206" t="n">
+        <v>80</v>
+      </c>
+      <c r="F6" s="206" t="n">
+        <v>41</v>
+      </c>
+      <c r="G6" s="206" t="n">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="200" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B7" s="200" t="inlineStr"/>
+      <c r="C7" s="200" t="inlineStr"/>
+      <c r="D7" s="200" t="inlineStr"/>
+      <c r="E7" s="200" t="n">
+        <v>230</v>
+      </c>
+      <c r="F7" s="200" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="G7" s="200" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="259" t="inlineStr">
+        <is>
+          <t>Why this split</t>
+        </is>
+      </c>
+      <c r="B10" s="259" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="260" t="inlineStr">
+        <is>
+          <t>Bid matches the posted average</t>
+        </is>
+      </c>
+      <c r="B11" s="260" t="inlineStr">
+        <is>
+          <t>Classmates unlocking paid SEM will be the ones who bid $3–$4. Matching $2.40 / $1.95 IS the lecture's moderate bid: we stay in the auction all quarter as they exhaust.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="260" t="inlineStr">
+        <is>
+          <t>Budget is the volume throttle</t>
+        </is>
+      </c>
+      <c r="B12" s="260" t="inlineStr">
+        <is>
+          <t>$150 / $80 caps us at ~104 clicks if we pay the full bid. A $1,000 Hike budget would cap at 417 clicks we cannot build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="260" t="inlineStr">
+        <is>
+          <t>Hike Bike gets the larger budget</t>
+        </is>
+      </c>
+      <c r="B13" s="260" t="inlineStr">
+        <is>
+          <t>Primary segment. Organic #2 (115 clicks) must not lose the slot above it to BB LLC. One Mountain unit = 1.78x a Speed unit for Market Performance. Ad 80 (heading to 81–82) is a quality-score advantage, so actual CPC should land below $2.40.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="260" t="inlineStr">
+        <is>
+          <t>Swift Bike gets the probe budget</t>
+        </is>
+      </c>
+      <c r="B14" s="260" t="inlineStr">
+        <is>
+          <t>Secondary segment, smallest search pool (894), Speed rank is not predicted by ad judgment, and the 72→77 brand + 70→77 ad + $1,450→$1,580 price are already adding Speed demand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="260" t="inlineStr">
+        <is>
+          <t>Do not bid $0</t>
+        </is>
+      </c>
+      <c r="B15" s="260" t="inlineStr">
+        <is>
+          <t>Paid listings render above organic. Sitting out hands BB LLC the intercept on Mountain searches. We still have organic after the budget caps; we just do not surrender the sponsored slot for the whole quarter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="260" t="inlineStr">
+        <is>
+          <t>Do not bid above the average</t>
+        </is>
+      </c>
+      <c r="B16" s="260" t="inlineStr">
+        <is>
+          <t>Starts the Q5 bid-inflation the lecture warns about, spends the small budget in days (high bid + small budget = the trap), and buys demand the 24 printers cannot fill.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="260" t="inlineStr">
+        <is>
+          <t>Keywords are already set</t>
+        </is>
+      </c>
+      <c r="B17" s="260" t="inlineStr">
+        <is>
+          <t>Choosing the segment when the page was created attached the agency keyword set. HikeBike 1 = Mountain. Swift Bike = Speed. Do not retarget either page at Recreation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="260" t="inlineStr">
+        <is>
+          <t>Cash is not the issue</t>
+        </is>
+      </c>
+      <c r="B18" s="260" t="inlineStr">
+        <is>
+          <t>$230 is noise against the ~$146k operating plan and the $950k loan. The cost of over-bidding is unmet demand, not the click invoice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="260" t="inlineStr">
+        <is>
+          <t>Q5 is when this scales</t>
+        </is>
+      </c>
+      <c r="B19" s="260" t="inlineStr">
+        <is>
+          <t>Two printers land next quarter (~40/day). Raise budgets toward $400–$600/page and re-read the new posted averages. Extra clicks can be filled then.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="199" t="inlineStr">
+        <is>
+          <t>Rejected alternatives</t>
+        </is>
+      </c>
+      <c r="B22" s="199" t="inlineStr">
+        <is>
+          <t>Bid Hike / Swift</t>
+        </is>
+      </c>
+      <c r="C22" s="199" t="inlineStr">
+        <is>
+          <t>Budget Hike / Swift</t>
+        </is>
+      </c>
+      <c r="D22" s="259" t="inlineStr">
+        <is>
+          <t>Why not</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="200" t="inlineStr">
+        <is>
+          <t>Sit out paid SEM</t>
+        </is>
+      </c>
+      <c r="B23" s="200" t="inlineStr">
+        <is>
+          <t>$0 / $0</t>
+        </is>
+      </c>
+      <c r="C23" s="200" t="inlineStr">
+        <is>
+          <t>$0 / $0</t>
+        </is>
+      </c>
+      <c r="D23" s="260" t="inlineStr">
+        <is>
+          <t>Hands BB LLC the sponsored slot above our Mountain organic #2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="200" t="inlineStr">
+        <is>
+          <t>Shade 15c below average</t>
+        </is>
+      </c>
+      <c r="B24" s="200" t="inlineStr">
+        <is>
+          <t>$2.25 / $1.80</t>
+        </is>
+      </c>
+      <c r="C24" s="200" t="inlineStr">
+        <is>
+          <t>$150 / $80</t>
+        </is>
+      </c>
+      <c r="D24" s="260" t="inlineStr">
+        <is>
+          <t>Fine if the auction is sleepy; risky if 6 classmates open at $3+. Match is safer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="200" t="inlineStr">
+        <is>
+          <t>Copy a 'win the auction' bid</t>
+        </is>
+      </c>
+      <c r="B25" s="200" t="inlineStr">
+        <is>
+          <t>$3.50 / $3.00</t>
+        </is>
+      </c>
+      <c r="C25" s="200" t="inlineStr">
+        <is>
+          <t>$1,000 / $600</t>
+        </is>
+      </c>
+      <c r="D25" s="260" t="inlineStr">
+        <is>
+          <t>Burns cash in days, inflates Q5 averages, and dumps 400+ clicks on a 17-unit hole.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="200" t="inlineStr">
+        <is>
+          <t>Equal budgets</t>
+        </is>
+      </c>
+      <c r="B26" s="200" t="inlineStr">
+        <is>
+          <t>$2.40 / $1.95</t>
+        </is>
+      </c>
+      <c r="C26" s="200" t="inlineStr">
+        <is>
+          <t>$115 / $115</t>
+        </is>
+      </c>
+      <c r="D26" s="260" t="inlineStr">
+        <is>
+          <t>Ignores Mountain-primary and the organic-#2 defense. Speed is the smaller search pool.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:G2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E71"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="50" customWidth="1" style="146" min="1" max="1"/>
+    <col width="16" customWidth="1" style="146" min="2" max="2"/>
+    <col width="100" customWidth="1" style="146" min="3" max="3"/>
+    <col width="44" customWidth="1" style="146" min="4" max="4"/>
+    <col width="14" customWidth="1" style="146" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="169" t="inlineStr">
+        <is>
+          <t>Q4 social media — START Social Networking at $10,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="58" customHeight="1" s="146">
+      <c r="A2" s="258" t="inlineStr">
+        <is>
+          <t>THE CASE IS ENTIRELY ABOUT TIMING. Media inserts deliver demand THIS quarter, which is why we cut them — Q4 output is capped at 1,154 units against a 1,171 forecast. Social media delivers almost NO demand this quarter (the brief says so explicitly) and matures in Q5-Q6, exactly when two new printers take capacity to 1,924 units and a New York store opens. Its ramp curve matches our capacity curve. And the clock only runs once we start: waiting does not skip the learning curve, it shifts it right.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="199" t="inlineStr">
+        <is>
+          <t>TIMING — ramp curve vs capacity curve</t>
+        </is>
+      </c>
+      <c r="B4" s="199" t="inlineStr">
+        <is>
+          <t>Capacity (units)</t>
+        </is>
+      </c>
+      <c r="C4" s="199" t="inlineStr">
+        <is>
+          <t>Social media state</t>
+        </is>
+      </c>
+      <c r="D4" s="199" t="inlineStr">
+        <is>
+          <t>Can we use new demand?</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="200" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="B5" s="220" t="n">
+        <v>1154</v>
+      </c>
+      <c r="C5" s="200" t="inlineStr">
+        <is>
+          <t>contributes ~nothing</t>
+        </is>
+      </c>
+      <c r="D5" s="204" t="inlineStr">
+        <is>
+          <t>NO — capped, forecast already 1,171</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="200" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
+      <c r="B6" s="220" t="n">
+        <v>1924</v>
+      </c>
+      <c r="C6" s="200" t="inlineStr">
+        <is>
+          <t>starting to work</t>
+        </is>
+      </c>
+      <c r="D6" s="206" t="inlineStr">
+        <is>
+          <t>YES — 2 printers land, New York opens</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="200" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="B7" s="220" t="n">
+        <v>1924</v>
+      </c>
+      <c r="C7" s="200" t="inlineStr">
+        <is>
+          <t>near peak</t>
+        </is>
+      </c>
+      <c r="D7" s="206" t="inlineStr">
+        <is>
+          <t>YES — needs several hundred new units</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="199" t="inlineStr">
+        <is>
+          <t>WHY NOT WAIT</t>
+        </is>
+      </c>
+      <c r="B10" s="259" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="200" t="inlineStr">
+        <is>
+          <t>The clock is start-date driven, not calendar driven</t>
+        </is>
+      </c>
+      <c r="B11" s="260" t="inlineStr">
+        <is>
+          <t>The tip is explicit: 'if you decide to wait, you just push back the time it takes for search engines to do their work and your social media team to learn.' Delaying does not let us skip the ramp later — it moves the whole curve right. Every quarter of delay is a quarter of maturity we can never recover.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="200" t="inlineStr">
+        <is>
+          <t>Two independent sources of delay</t>
+        </is>
+      </c>
+      <c r="B12" s="260" t="inlineStr">
+        <is>
+          <t>Search engines must find and cross-list us, AND our own team must learn by trial and error. Neither can be bought later.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="200" t="inlineStr">
+        <is>
+          <t>Same logic as the rapid R&amp;D schedule</t>
+        </is>
+      </c>
+      <c r="B13" s="260" t="inlineStr">
+        <is>
+          <t>When the scarce resource is TIME rather than money, buy time. The team already accepted that reasoning when scheduling both R&amp;D projects as 1-quarter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="199" t="inlineStr">
+        <is>
+          <t>NO COMPETITOR BENCHMARK EXISTS (verified across all 52 sheets)</t>
+        </is>
+      </c>
+      <c r="B16" s="259" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="200" t="inlineStr">
+        <is>
+          <t>Zero social media data anywhere</t>
+        </is>
+      </c>
+      <c r="B17" s="260" t="inlineStr">
+        <is>
+          <t>Checked Competitor Profiles, Media, Organic SEM, Ad Judgment and Web Ops. Nothing. The Q2 internet-marketing background listed social as a tool that 'unlocks over later quarters' — this is that unlock.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="200" t="inlineStr">
+        <is>
+          <t>So EVERY firm starts from zero</t>
+        </is>
+      </c>
+      <c r="B18" s="260" t="inlineStr">
+        <is>
+          <t>For once we are not behind. Every rival faces the same unknown effectiveness and the same ramp delay, starting now.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="200" t="inlineStr">
+        <is>
+          <t>Spend anchors we DO have</t>
+        </is>
+      </c>
+      <c r="B19" s="260" t="inlineStr">
+        <is>
+          <t>Organic SEM page $1,000 (industry-wide) · ad design $6,000 · Biking insert $4,500 · BB LLC web tactics: toll-free $9,000, page upgrades $9,000, order tracking $8,000, cart $7,000. The sim's unit for one meaningful activity is roughly $5,000-$10,000 a quarter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="199" t="inlineStr">
+        <is>
+          <t>WHICH MEDIUM — needs evidence</t>
+        </is>
+      </c>
+      <c r="B22" s="199" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="C22" s="199" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="D22" s="259" t="inlineStr">
+        <is>
+          <t>Fit</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="206" t="inlineStr">
+        <is>
+          <t>Status symbol/exclusivity</t>
+        </is>
+      </c>
+      <c r="B23" s="206" t="n">
+        <v>121</v>
+      </c>
+      <c r="C23" s="206" t="n">
+        <v>116</v>
+      </c>
+      <c r="D23" s="261" t="inlineStr">
+        <is>
+          <t>Social Networking (identity/image cluster)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="206" t="inlineStr">
+        <is>
+          <t>Colorful</t>
+        </is>
+      </c>
+      <c r="B24" s="206" t="n">
+        <v>120</v>
+      </c>
+      <c r="C24" s="206" t="n">
+        <v>109</v>
+      </c>
+      <c r="D24" s="261" t="inlineStr">
+        <is>
+          <t>Social Networking (identity/image cluster)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="206" t="inlineStr">
+        <is>
+          <t>Stylish</t>
+        </is>
+      </c>
+      <c r="B25" s="206" t="n">
+        <v>118</v>
+      </c>
+      <c r="C25" s="206" t="n">
+        <v>116</v>
+      </c>
+      <c r="D25" s="261" t="inlineStr">
+        <is>
+          <t>Social Networking (identity/image cluster)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="206" t="inlineStr">
+        <is>
+          <t>Feel young at heart</t>
+        </is>
+      </c>
+      <c r="B26" s="206" t="n">
+        <v>115</v>
+      </c>
+      <c r="C26" s="206" t="n">
+        <v>117</v>
+      </c>
+      <c r="D26" s="261" t="inlineStr">
+        <is>
+          <t>Social Networking (identity/image cluster)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="206" t="inlineStr">
+        <is>
+          <t>Fits rider's personality</t>
+        </is>
+      </c>
+      <c r="B27" s="206" t="n">
+        <v>113</v>
+      </c>
+      <c r="C27" s="206" t="n">
+        <v>116</v>
+      </c>
+      <c r="D27" s="261" t="inlineStr">
+        <is>
+          <t>Social Networking (identity/image cluster)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="200" t="inlineStr">
+        <is>
+          <t>Rider expertise required</t>
+        </is>
+      </c>
+      <c r="B28" s="200" t="n">
+        <v>123</v>
+      </c>
+      <c r="C28" s="200" t="n">
+        <v>126</v>
+      </c>
+      <c r="D28" s="260" t="inlineStr">
+        <is>
+          <t>Blog / Newsletter — Q6 candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="200" t="inlineStr">
+        <is>
+          <t>Provides competitive advantage</t>
+        </is>
+      </c>
+      <c r="B29" s="200" t="n">
+        <v>117</v>
+      </c>
+      <c r="C29" s="200" t="n">
+        <v>124</v>
+      </c>
+      <c r="D29" s="260" t="inlineStr">
+        <is>
+          <t>Blog / Newsletter — Q6 candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="170" t="inlineStr">
+        <is>
+          <t>Social Networking maps onto five needs that ALL score 109-121 in BOTH our segments — the same cluster the bright-colourful-decals R&amp;D project targets, so the two reinforce each other. No reason to override the agency. PRE-REGISTERING Q5: VIDEO SHARING. Bicycles are a visual action product and the most-used benefit in the whole industry is a PICTURE ('rider on a steep trail' on 4 of 4 Mountain ads, 'road race' on 8 of 8 Speed ads). Video extends the one creative device every firm already agrees on. Q6: Blog, for 'Rider expertise required' (Mtn 123, Speed 126) — a top-scoring need we currently do nothing about.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="199" t="inlineStr">
+        <is>
+          <t>BUDGET OPTIONS</t>
+        </is>
+      </c>
+      <c r="B32" s="199" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="C32" s="259" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="200" t="inlineStr">
+        <is>
+          <t>Skip it</t>
+        </is>
+      </c>
+      <c r="B33" s="232" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="260" t="inlineStr">
+        <is>
+          <t>Only defensible if the simulation ends at Q5. A channel needing 'a few quarters' to mature would never pay back.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="200" t="inlineStr">
+        <is>
+          <t>Pure clock-start</t>
+        </is>
+      </c>
+      <c r="B34" s="232" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C34" s="260" t="inlineStr">
+        <is>
+          <t>Cheapest way to avoid losing a quarter of ramp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="222" t="inlineStr">
+        <is>
+          <t>RECOMMENDED</t>
+        </is>
+      </c>
+      <c r="B35" s="274" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C35" s="263" t="inlineStr">
+        <is>
+          <t>Top of the sim's observed per-activity unit, so credible rather than token. Starts the clock, buys the MEASUREMENT cheaply, and is 1% of the loan. Same principle the team already accepted on R&amp;D: calibrate first, then size the bet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="200" t="inlineStr">
+        <is>
+          <t>Aggressive</t>
+        </is>
+      </c>
+      <c r="B36" s="232" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C36" s="260" t="inlineStr">
+        <is>
+          <t>Only if the team believes trial-and-error learning scales with headcount. The brief pulls both ways — budget drives headcount, but the delay is attributed to INEXPERIENCE, and a bigger team during the ramp is a bigger team that does not yet know what it is doing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="199" t="inlineStr">
+        <is>
+          <t>REVISED Q4 CASH</t>
+        </is>
+      </c>
+      <c r="B39" s="199" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="C39" s="259" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="200" t="inlineStr">
+        <is>
+          <t>R&amp;D — decals + 11-speed, listed</t>
+        </is>
+      </c>
+      <c r="B40" s="220" t="n">
+        <v>677669</v>
+      </c>
+      <c r="C40" s="260" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="200" t="inlineStr">
+        <is>
+          <t>R&amp;D rapid premium (~30% ESTIMATE)</t>
+        </is>
+      </c>
+      <c r="B41" s="220" t="n">
+        <v>203301</v>
+      </c>
+      <c r="C41" s="260" t="inlineStr">
+        <is>
+          <t>biggest unknown in the plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="200" t="inlineStr">
+        <is>
+          <t>Operating plan, recurring</t>
+        </is>
+      </c>
+      <c r="B42" s="220" t="n">
+        <v>75000</v>
+      </c>
+      <c r="C42" s="260" t="inlineStr">
+        <is>
+          <t>was $146,000 — media swings from +$27,000 to -$44,000 under Option C</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="200" t="inlineStr">
+        <is>
+          <t>Operating plan, one-time</t>
+        </is>
+      </c>
+      <c r="B43" s="220" t="n">
+        <v>67000</v>
+      </c>
+      <c r="C43" s="260" t="inlineStr">
+        <is>
+          <t>hiring and setup</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="200" t="inlineStr">
+        <is>
+          <t>Swift Bike brand redesign</t>
+        </is>
+      </c>
+      <c r="B44" s="220" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C44" s="260" t="inlineStr">
+        <is>
+          <t>14-speed + decals =&gt; 77</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="200" t="inlineStr">
+        <is>
+          <t>Swift Bike ad redesign</t>
+        </is>
+      </c>
+      <c r="B45" s="220" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C45" s="260" t="inlineStr">
+        <is>
+          <t>AndStill's stack</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="200" t="inlineStr">
+        <is>
+          <t>HikeBike 1 ad redesign</t>
+        </is>
+      </c>
+      <c r="B46" s="220" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C46" s="260" t="inlineStr">
+        <is>
+          <t>BB LLC's stack — this was missing from my earlier table</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="200" t="inlineStr">
+        <is>
+          <t>Printers #4 and #5</t>
+        </is>
+      </c>
+      <c r="B47" s="220" t="n">
+        <v>480000</v>
+      </c>
+      <c r="C47" s="260" t="inlineStr">
+        <is>
+          <t>arrive Q5, when New York opens</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="222" t="inlineStr">
+        <is>
+          <t>SOCIAL NETWORKING</t>
+        </is>
+      </c>
+      <c r="B48" s="265" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C48" s="263" t="inlineStr">
+        <is>
+          <t>NEW — starts the ramp clock</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="200" t="inlineStr">
+        <is>
+          <t>TOTAL USES</t>
+        </is>
+      </c>
+      <c r="B49" s="220" t="n">
+        <v>1562970</v>
+      </c>
+      <c r="C49" s="260" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="200" t="inlineStr">
+        <is>
+          <t>Cash on hand</t>
+        </is>
+      </c>
+      <c r="B50" s="220" t="n">
+        <v>1010838</v>
+      </c>
+      <c r="C50" s="260" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="200" t="inlineStr">
+        <is>
+          <t>Bank loan</t>
+        </is>
+      </c>
+      <c r="B51" s="220" t="n">
+        <v>950000</v>
+      </c>
+      <c r="C51" s="260" t="inlineStr">
+        <is>
+          <t>7% annual</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="200" t="inlineStr">
+        <is>
+          <t>Total available</t>
+        </is>
+      </c>
+      <c r="B52" s="220" t="n">
+        <v>1960838</v>
+      </c>
+      <c r="C52" s="260" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="200" t="inlineStr">
+        <is>
+          <t>ENDING CASH</t>
+        </is>
+      </c>
+      <c r="B53" s="220" t="n">
+        <v>397868</v>
+      </c>
+      <c r="C53" s="260" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="200" t="inlineStr">
+        <is>
+          <t>Hard floor</t>
+        </is>
+      </c>
+      <c r="B54" s="220" t="n">
+        <v>300000</v>
+      </c>
+      <c r="C54" s="260" t="inlineStr">
+        <is>
+          <t>ending Cash + CD must stay at or above</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="223" t="inlineStr">
+        <is>
+          <t>HEADROOM ABOVE FLOOR</t>
+        </is>
+      </c>
+      <c r="B55" s="267" t="n">
+        <v>97868</v>
+      </c>
+      <c r="C55" s="268" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="170" t="inlineStr">
+        <is>
+          <t>THE MEDIA DECISION FUNDED THIS OUTRIGHT. Option C takes inserts from $116,000 to $72,000; against the superseded Option B (+$27,000) that is a $71,000 swing, seven times the social media budget. We are not adding spend — we are REALLOCATING it out of a channel that would have generated demand we cannot build, into one that generates demand exactly when we can. Note the HikeBike 1 ad redesign fee was missing from my earlier sources-and-uses table and is now included.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="199" t="inlineStr">
+        <is>
+          <t>THE CASE AGAINST</t>
+        </is>
+      </c>
+      <c r="B58" s="259" t="inlineStr">
+        <is>
+          <t>Rebuttal</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="200" t="inlineStr">
+        <is>
+          <t>Attribution will be impossible — Q4 already changes 11 other things</t>
+        </is>
+      </c>
+      <c r="B59" s="260" t="inlineStr">
+        <is>
+          <t>Real. But it argues for a SMALL STEADY budget we do not fiddle with, not for delay. Delay does not improve attribution; it just costs a quarter of ramp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="200" t="inlineStr">
+        <is>
+          <t>We are last and should fix basics first</t>
+        </is>
+      </c>
+      <c r="B60" s="260" t="inlineStr">
+        <is>
+          <t>Also true, and precisely why the number is $10,000 not $50,000. At 1% of the loan it does not compete with the capacity and web fixes for resources.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="200" t="inlineStr">
+        <is>
+          <t>Effectiveness may be zero for carbon bikes</t>
+        </is>
+      </c>
+      <c r="B61" s="260" t="inlineStr">
+        <is>
+          <t>Which is why we buy the small version. And 'You can stop these activities at any time' — this is a cheap OPTION, not a commitment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="200" t="inlineStr">
+        <is>
+          <t>HOW MANY QUARTERS REMAIN? — the real caveat</t>
+        </is>
+      </c>
+      <c r="B62" s="262" t="inlineStr">
+        <is>
+          <t>Same unanswered question hanging over the R&amp;D schedule. If the sim ends at Q5, the honest answer is $0. If it runs to Q6+, starting now is clearly right. The ASYMMETRY is why I still recommend starting: downside $10,000, upside a matured demand channel, and we can stop any time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="199" t="inlineStr">
+        <is>
+          <t>DECISION</t>
+        </is>
+      </c>
+      <c r="B65" s="259" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="200" t="inlineStr">
+        <is>
+          <t>Start Social Networking</t>
+        </is>
+      </c>
+      <c r="B66" s="260" t="inlineStr">
+        <is>
+          <t>$10,000 for Q4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="200" t="inlineStr">
+        <is>
+          <t>Follow the agency's cadence</t>
+        </is>
+      </c>
+      <c r="B67" s="260" t="inlineStr">
+        <is>
+          <t>One medium now, add one per quarter. Q5 Video sharing, Q6 Blog/Newsletter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="200" t="inlineStr">
+        <is>
+          <t>Expect nothing this quarter</t>
+        </is>
+      </c>
+      <c r="B68" s="260" t="inlineStr">
+        <is>
+          <t>Judge it on the Q5 and Q6 trend, not on Q4 results.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="200" t="inlineStr">
+        <is>
+          <t>Do not cut it later</t>
+        </is>
+      </c>
+      <c r="B69" s="260" t="inlineStr">
+        <is>
+          <t>Cutting restarts the very clock we are paying to start. Hold the budget unless we see a signal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="200" t="inlineStr">
+        <is>
+          <t>Record the baseline</t>
+        </is>
+      </c>
+      <c r="B70" s="260" t="inlineStr">
+        <is>
+          <t>Log the $10,000 now so Q5 has something clean to measure against.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="200" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B71" s="260" t="inlineStr">
+        <is>
+          <t>ANALYSIS ONLY — majority vote required.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:E2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/quarters/Q3/Q3Data.xlsx
+++ b/quarters/Q3/Q3Data.xlsx
@@ -59,6 +59,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q4_Price_Priority" sheetId="51" state="visible" r:id="rId51"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q4_Paid_SEM" sheetId="52" state="visible" r:id="rId52"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q4_Social_Media" sheetId="53" state="visible" r:id="rId53"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q4_Staffing_Stores" sheetId="54" state="visible" r:id="rId54"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -67,7 +68,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="11">
+  <numFmts count="12">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
@@ -79,6 +80,7 @@
     <numFmt numFmtId="172" formatCode="#,##0;+#,##0;-#,##0"/>
     <numFmt numFmtId="173" formatCode="+0.0%;-0.0%"/>
     <numFmt numFmtId="174" formatCode="+$#,##0"/>
+    <numFmt numFmtId="175" formatCode="+#,##0"/>
   </numFmts>
   <fonts count="33">
     <font>
@@ -674,7 +676,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="16"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="16"/>
   </cellStyleXfs>
-  <cellXfs count="275">
+  <cellXfs count="277">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1062,6 +1064,10 @@
     <xf numFmtId="168" fontId="0" fillId="29" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="0" fillId="32" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="28" fillId="29" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="175" fontId="0" fillId="29" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -63516,6 +63522,903 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" style="146" min="1" max="1"/>
+    <col width="14" customWidth="1" style="146" min="2" max="2"/>
+    <col width="100" customWidth="1" style="146" min="3" max="3"/>
+    <col width="12" customWidth="1" style="146" min="4" max="4"/>
+    <col width="12" customWidth="1" style="146" min="5" max="5"/>
+    <col width="66" customWidth="1" style="146" min="6" max="6"/>
+    <col width="14" customWidth="1" style="146" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="169" t="inlineStr">
+        <is>
+          <t>Q4 sales force and stores — hire 7, train 2, open NO new store</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="58" customHeight="1" s="146">
+      <c r="A2" s="258" t="inlineStr">
+        <is>
+          <t>ANSWER: YES change the people, NO change the stores. Train both untrained staff ($800), fill Rio's 3 open slots and take the web centre from 3 to 7. That clones BB LLC exactly — 14 store people, 7 web, 21 total, with 6 Mountain and 6 Speed specialists. But NO new store: printers arrive a quarter late, so Q4 capacity is 1,154 against a forecast that already assumes these hires. New York opens in Q5, into capacity that exists, entering via SPEED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="199" t="inlineStr">
+        <is>
+          <t>ROSTER — city by city</t>
+        </is>
+      </c>
+      <c r="B4" s="199" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="C4" s="199" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="D4" s="199" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="E4" s="199" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="F4" s="259" t="inlineStr">
+        <is>
+          <t>How</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="200" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="B5" s="200" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C5" s="200" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="200" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="200" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="260" t="inlineStr">
+        <is>
+          <t>no change</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="200" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="B6" s="200" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="C6" s="200" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="200" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="200" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="260" t="inlineStr">
+        <is>
+          <t>no change</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="200" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="B7" s="200" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="C7" s="200" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="200" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" s="200" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="260" t="inlineStr">
+        <is>
+          <t>no change</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="200" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="B8" s="200" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="C8" s="200" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="200" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="206" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="260" t="inlineStr">
+        <is>
+          <t>TRAIN the 1 untrained -&gt; Speed ($400). NO HIRE — city is at the 7-person cap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="248" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="B9" s="248" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C9" s="248" t="n">
+        <v>7</v>
+      </c>
+      <c r="D9" s="248" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" s="248" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="275" t="inlineStr">
+        <is>
+          <t>AT CAP already — 0 hires</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="200" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="B10" s="200" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C10" s="200" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="200" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="200" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="260" t="inlineStr">
+        <is>
+          <t>no change</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="200" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="B11" s="200" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="C11" s="200" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="200" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="200" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="260" t="inlineStr">
+        <is>
+          <t>no change</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="200" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="B12" s="200" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="C12" s="200" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="200" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" s="206" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" s="260" t="inlineStr">
+        <is>
+          <t>TRAIN the 1 untrained -&gt; Mountain ($400), then HIRE +1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="200" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="B13" s="200" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="C13" s="200" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="200" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" s="206" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" s="260" t="inlineStr">
+        <is>
+          <t>HIRE +2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="248" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="B14" s="248" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C14" s="248" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" s="248" t="n">
+        <v>7</v>
+      </c>
+      <c r="E14" s="222" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" s="275" t="inlineStr">
+        <is>
+          <t>fills all 3 open slots</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="200" t="inlineStr">
+        <is>
+          <t>Web centre</t>
+        </is>
+      </c>
+      <c r="B15" s="200" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="C15" s="200" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="200" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" s="206" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" s="260" t="inlineStr">
+        <is>
+          <t>BB LLC runs 5 sales + 2 service = 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="200" t="inlineStr">
+        <is>
+          <t>Web centre</t>
+        </is>
+      </c>
+      <c r="B16" s="200" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C16" s="200" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="200" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" s="206" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="260" t="inlineStr">
+        <is>
+          <t>BB LLC runs 5 sales + 2 service = 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="248" t="inlineStr">
+        <is>
+          <t>Web centre</t>
+        </is>
+      </c>
+      <c r="B17" s="248" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C17" s="248" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" s="248" t="n">
+        <v>7</v>
+      </c>
+      <c r="E17" s="222" t="n">
+        <v>4</v>
+      </c>
+      <c r="F17" s="275" t="inlineStr">
+        <is>
+          <t>4 open slots — same 7-person ceiling as a store</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="199" t="inlineStr">
+        <is>
+          <t>SPECIALIST COUNT</t>
+        </is>
+      </c>
+      <c r="B20" s="199" t="inlineStr">
+        <is>
+          <t>WeBike now</t>
+        </is>
+      </c>
+      <c r="C20" s="199" t="inlineStr">
+        <is>
+          <t>WeBike Q4</t>
+        </is>
+      </c>
+      <c r="D20" s="199" t="inlineStr">
+        <is>
+          <t>BB LLC</t>
+        </is>
+      </c>
+      <c r="E20" s="259" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="200" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="B21" s="200" t="n">
+        <v>2</v>
+      </c>
+      <c r="C21" s="200" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" s="200" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" s="260" t="inlineStr">
+        <is>
+          <t>Already at BB LLC's level.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="200" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="B22" s="200" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="200" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="200" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="260" t="inlineStr">
+        <is>
+          <t>Stay at 0 — BB LLC also runs 0. Recreation is parked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="200" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="B23" s="200" t="n">
+        <v>4</v>
+      </c>
+      <c r="C23" s="200" t="n">
+        <v>6</v>
+      </c>
+      <c r="D23" s="200" t="n">
+        <v>6</v>
+      </c>
+      <c r="E23" s="260" t="inlineStr">
+        <is>
+          <t>Matches BB LLC, who took 46.3% Mountain share with exactly these 6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="200" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="B24" s="200" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" s="200" t="n">
+        <v>6</v>
+      </c>
+      <c r="D24" s="200" t="n">
+        <v>6</v>
+      </c>
+      <c r="E24" s="261" t="inlineStr">
+        <is>
+          <t>DOUBLED — the largest segment (2,878 units) where we hold only 7.5%, and where we are ALSO fixing the product 72-&gt;77 and the ad 70-&gt;77 this quarter. Coverage is what lets those fixes convert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="248" t="inlineStr">
+        <is>
+          <t>Store people</t>
+        </is>
+      </c>
+      <c r="B25" s="248" t="n">
+        <v>11</v>
+      </c>
+      <c r="C25" s="248" t="n">
+        <v>14</v>
+      </c>
+      <c r="D25" s="248" t="n">
+        <v>14</v>
+      </c>
+      <c r="E25" s="275" t="inlineStr">
+        <is>
+          <t>exact match</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="248" t="inlineStr">
+        <is>
+          <t>Web people</t>
+        </is>
+      </c>
+      <c r="B26" s="248" t="n">
+        <v>3</v>
+      </c>
+      <c r="C26" s="248" t="n">
+        <v>7</v>
+      </c>
+      <c r="D26" s="248" t="n">
+        <v>7</v>
+      </c>
+      <c r="E26" s="275" t="inlineStr">
+        <is>
+          <t>exact match</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="248" t="inlineStr">
+        <is>
+          <t>TOTAL PEOPLE</t>
+        </is>
+      </c>
+      <c r="B27" s="248" t="n">
+        <v>14</v>
+      </c>
+      <c r="C27" s="248" t="n">
+        <v>21</v>
+      </c>
+      <c r="D27" s="248" t="n">
+        <v>21</v>
+      </c>
+      <c r="E27" s="275" t="inlineStr">
+        <is>
+          <t>exact match</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="199" t="inlineStr">
+        <is>
+          <t>COST AND RETURN</t>
+        </is>
+      </c>
+      <c r="B30" s="199" t="inlineStr">
+        <is>
+          <t>Cost/qtr</t>
+        </is>
+      </c>
+      <c r="C30" s="259" t="inlineStr">
+        <is>
+          <t>Return</t>
+        </is>
+      </c>
+      <c r="D30" s="199" t="inlineStr">
+        <is>
+          <t>Net/qtr</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="200" t="inlineStr">
+        <is>
+          <t>Train 2 untrained (1 Rio Mountain, 1 AMS Speed)</t>
+        </is>
+      </c>
+      <c r="B31" s="220" t="n">
+        <v>800</v>
+      </c>
+      <c r="C31" s="260" t="inlineStr">
+        <is>
+          <t>free productivity — we pay 2 full salaries for untrained sellers</t>
+        </is>
+      </c>
+      <c r="D31" s="200" t="inlineStr">
+        <is>
+          <t>cheapest item on the Q4 board</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="200" t="inlineStr">
+        <is>
+          <t>Rio: hire +3 (1 Mountain, 2 Speed)</t>
+        </is>
+      </c>
+      <c r="B32" s="220" t="n">
+        <v>20553</v>
+      </c>
+      <c r="C32" s="260" t="inlineStr">
+        <is>
+          <t>~+190 units at Rio's measured 60-67/head</t>
+        </is>
+      </c>
+      <c r="D32" s="276" t="n">
+        <v>131447</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="200" t="inlineStr">
+        <is>
+          <t>Web: hire +4 (3 sales, 1 service)</t>
+        </is>
+      </c>
+      <c r="B33" s="220" t="n">
+        <v>27404</v>
+      </c>
+      <c r="C33" s="260" t="inlineStr">
+        <is>
+          <t>~+315 units (120 -&gt; 435, the full-tactic cohort floor)</t>
+        </is>
+      </c>
+      <c r="D33" s="276" t="n">
+        <v>186846</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="200" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B34" s="220" t="n">
+        <v>48757</v>
+      </c>
+      <c r="C34" s="260" t="inlineStr"/>
+      <c r="D34" s="200" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="170" t="inlineStr">
+        <is>
+          <t>The web hires ONLY deliver alongside funding all four web productivity tactics ($22,000 more). Every firm funding all four lands at 435-569 web units; both firms funding fewer land at 120-138. Staff and tactics move together, so do not split them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="199" t="inlineStr">
+        <is>
+          <t>STORES — no change in Q4</t>
+        </is>
+      </c>
+      <c r="B37" s="259" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="200" t="inlineStr">
+        <is>
+          <t>New York IS the right third city</t>
+        </is>
+      </c>
+      <c r="B38" s="260" t="inlineStr">
+        <is>
+          <t>2,039 units and 31.1% of the market against Bangalore's 761. Only 3 of 7 firms have a store there, and NOBODY in the industry has three stores — city #3 is unclaimed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="200" t="inlineStr">
+        <is>
+          <t>The store effect is roughly 10x</t>
+        </is>
+      </c>
+      <c r="B39" s="260" t="inlineStr">
+        <is>
+          <t>No store = 1.9-3.2% share. A store against 6 rivals = 9.9%. SOLE store in a city = 34.9% (us in Rio) to 48.6% (LiteCycle in Bangalore). Highest-leverage decision we have.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="200" t="inlineStr">
+        <is>
+          <t>BUT IT CANNOT OPEN IN Q4</t>
+        </is>
+      </c>
+      <c r="B40" s="264" t="inlineStr">
+        <is>
+          <t>Printers arrive a quarter late, so Q4 capacity is 1,154 units against a forecast of 1,171 that ALREADY assumes these hires — -17 units of spare. An NYC store adds 340-570 on top. That is a direct repeat of Q3: 33% stocked out, 16.3% ill will carried forward.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="200" t="inlineStr">
+        <is>
+          <t>Worst possible city to stock out in</t>
+        </is>
+      </c>
+      <c r="B41" s="260" t="inlineStr">
+        <is>
+          <t>BB LLC already holds 82.8% of NYC Mountain. Arriving and immediately failing to supply hands them the city.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="200" t="inlineStr">
+        <is>
+          <t>THE SEQUENCE</t>
+        </is>
+      </c>
+      <c r="B42" s="261" t="inlineStr">
+        <is>
+          <t>Q4 buy printers #4 and #5 ($480,000, loan-funded), capacity stays 1,154. Q5 printers come online at 1,924 units, THEN open New York — entering via SPEED (NYC Speed is 880 units with no dominant firm, best is Armstrong at 272) on the back of the Swift Bike fix to 77.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="200" t="inlineStr">
+        <is>
+          <t>Amsterdam cannot be deepened</t>
+        </is>
+      </c>
+      <c r="B43" s="260" t="inlineStr">
+        <is>
+          <t>It is at the 7-person hard cap. Not one firm in any of the 12 city rows exceeds 7. 'Invest more in our best city' is not a legal move.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="199" t="inlineStr">
+        <is>
+          <t>WHY THIS DOES NOT CONTRADICT CUTTING MEDIA INSERTS</t>
+        </is>
+      </c>
+      <c r="B46" s="259" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="200" t="inlineStr">
+        <is>
+          <t>The staffing is already INSIDE the forecast</t>
+        </is>
+      </c>
+      <c r="B47" s="260" t="inlineStr">
+        <is>
+          <t>The 1,171-unit number is not a do-nothing baseline — it is scenario D, which explicitly assumes Rio filled to the cap AND the full web rebuild. These hires ARE the plan that produces 1,171 against 1,154 of capacity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="200" t="inlineStr">
+        <is>
+          <t>Removing them causes the OPPOSITE failure</t>
+        </is>
+      </c>
+      <c r="B48" s="260" t="inlineStr">
+        <is>
+          <t>Without the hires demand falls to roughly 656 units, or 13.6/day against 24/day of owned capacity. That is under-scheduling — the Q3 mistake that followed the Q2 mistake of $148,652 in excess-capacity charges.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="200" t="inlineStr">
+        <is>
+          <t>Ads and media were the OVERSHOOT</t>
+        </is>
+      </c>
+      <c r="B49" s="260" t="inlineStr">
+        <is>
+          <t>The ad rebuilds and Biking concentration stack on top of the staffed plan. That is why the media insert cut is the right offset: inserts are discretionary and purely demand-generating, while people are the capability that produces the base plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="200" t="inlineStr">
+        <is>
+          <t>And people are DURABLE</t>
+        </is>
+      </c>
+      <c r="B50" s="261" t="inlineStr">
+        <is>
+          <t>Q5 capacity roughly doubles to 1,924 units and New York unlocks 7 MORE slots. These 7 hires need to be trained and productive BEFORE that, not during it. Same timing argument as rapid R&amp;D and the social media start.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="199" t="inlineStr">
+        <is>
+          <t>WHAT NOT TO DO</t>
+        </is>
+      </c>
+      <c r="B53" s="259" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="200" t="inlineStr">
+        <is>
+          <t>Do not cut anyone</t>
+        </is>
+      </c>
+      <c r="B54" s="260" t="inlineStr">
+        <is>
+          <t>We cut web staff 5 -&gt; 3 in Q3 and web demand per head is now 40, worst of any firm with a web centre. Bike Bros is the cautionary tale: 1 store, 0 web, 7 people, LAST place.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="200" t="inlineStr">
+        <is>
+          <t>Do not hire Recreation specialists</t>
+        </is>
+      </c>
+      <c r="B55" s="260" t="inlineStr">
+        <is>
+          <t>We run 0 and so does BB LLC. Hike Bike scores 56 with Rec buyers against dedicated Rec brands at 73-76, so spillover cannot win. Rec stays parked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="200" t="inlineStr">
+        <is>
+          <t>Do not try to add in Amsterdam</t>
+        </is>
+      </c>
+      <c r="B56" s="260" t="inlineStr">
+        <is>
+          <t>At the 7-person cap. Illegal move.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="200" t="inlineStr">
+        <is>
+          <t>Do not open Bangalore</t>
+        </is>
+      </c>
+      <c r="B57" s="260" t="inlineStr">
+        <is>
+          <t>761 units against New York's 2,039, and LiteCycle already holds 48.6% of it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="200" t="inlineStr">
+        <is>
+          <t>Do not put new hires on the old package</t>
+        </is>
+      </c>
+      <c r="B58" s="260" t="inlineStr">
+        <is>
+          <t>Move sales to BB LLC's exact terms ($22,000 / Expanded / 2 weeks / 4% = $27,402), which produced the industry-best 78% sales productivity. And budget 73-75% productivity, NEVER the 85% we assumed in Q3.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:G2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/quarters/Q3/Q3Data.xlsx
+++ b/quarters/Q3/Q3Data.xlsx
@@ -60,6 +60,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q4_Paid_SEM" sheetId="52" state="visible" r:id="rId52"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q4_Social_Media" sheetId="53" state="visible" r:id="rId53"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q4_Staffing_Stores" sheetId="54" state="visible" r:id="rId54"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q4_Screen_Audit" sheetId="55" state="visible" r:id="rId55"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -82,7 +83,7 @@
     <numFmt numFmtId="174" formatCode="+$#,##0"/>
     <numFmt numFmtId="175" formatCode="+#,##0"/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="35">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -285,8 +286,16 @@
       <b val="1"/>
       <sz val="14"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="34">
+  <fills count="38">
     <fill>
       <patternFill/>
     </fill>
@@ -457,6 +466,26 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF7B7B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
       </patternFill>
     </fill>
   </fills>
@@ -676,7 +705,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="16"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="16"/>
   </cellStyleXfs>
-  <cellXfs count="277">
+  <cellXfs count="286">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1068,6 +1097,31 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="175" fontId="0" fillId="29" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="34" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="36" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="37" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -64419,6 +64473,1390 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" style="146" min="1" max="1"/>
+    <col width="52" customWidth="1" style="146" min="2" max="2"/>
+    <col width="42" customWidth="1" style="146" min="3" max="3"/>
+    <col width="11" customWidth="1" style="146" min="4" max="4"/>
+    <col width="72" customWidth="1" style="146" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="257" t="inlineStr">
+        <is>
+          <t>Q4 decision screen audit - dump vs plan of record</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>5 blockers, 3 misses, 14 items correct. The brand, ads, staffing, R&amp;D and printer decisions are all in correctly; the gaps are capacity, financing and the web tactic Start checkboxes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="277" t="inlineStr">
+        <is>
+          <t>Line-by-line</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="278" t="inlineStr">
+        <is>
+          <t>Screen area</t>
+        </is>
+      </c>
+      <c r="B5" s="278" t="inlineStr">
+        <is>
+          <t>What the screen shows</t>
+        </is>
+      </c>
+      <c r="C5" s="278" t="inlineStr">
+        <is>
+          <t>What the plan says</t>
+        </is>
+      </c>
+      <c r="D5" s="278" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+      <c r="E5" s="278" t="inlineStr">
+        <is>
+          <t>Consequence</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="258" t="inlineStr">
+        <is>
+          <t>Manufacturing / Operating capacity</t>
+        </is>
+      </c>
+      <c r="B6" s="258" t="inlineStr">
+        <is>
+          <t>Operating capacity = 8/day (520/qtr); effective 5.84/day = 380 units</t>
+        </is>
+      </c>
+      <c r="C6" s="258" t="inlineStr">
+        <is>
+          <t>Schedule the full 24/day owned, overtime 0.00</t>
+        </is>
+      </c>
+      <c r="D6" s="279" t="inlineStr">
+        <is>
+          <t>BLOCKER</t>
+        </is>
+      </c>
+      <c r="E6" s="258" t="inlineStr">
+        <is>
+          <t>380 units vs ~1,142 projected demand. This is the Q3 error verbatim: 67% stock-out, Q5 ill will ~33%. 24/day at 73% = 1139 units.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="258" t="inlineStr">
+        <is>
+          <t>Improve Web Productivity</t>
+        </is>
+      </c>
+      <c r="B7" s="258" t="inlineStr">
+        <is>
+          <t>Total expenses = 6,000. Only toll-free shows status 'operational'. Secure site / cart / page upgrades / order tracking all status '-' with budgets typed but Start not checked</t>
+        </is>
+      </c>
+      <c r="C7" s="258" t="inlineStr">
+        <is>
+          <t>Fund ALL tactics: setup 48,000 + quarterly 25,000 on the four new ones</t>
+        </is>
+      </c>
+      <c r="D7" s="279" t="inlineStr">
+        <is>
+          <t>BLOCKER</t>
+        </is>
+      </c>
+      <c r="E7" s="258" t="inlineStr">
+        <is>
+          <t>Q3 evidence is a step function: firms funding all tactics land 435-569 web units; firms funding 1-2 land 120-138. Typing a budget without checking Start leaves us in the losing band while paying 45,501 for 7 web staff.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="258" t="inlineStr">
+        <is>
+          <t>Finance / Stock</t>
+        </is>
+      </c>
+      <c r="B8" s="258" t="inlineStr">
+        <is>
+          <t>Common Stock, Venture Capitalists, 25,000 shares @ 100 = 2,500,000, Quarter 4</t>
+        </is>
+      </c>
+      <c r="C8" s="258" t="inlineStr">
+        <is>
+          <t>Do NOT take the 2.5M equity round; remove or zero this row</t>
+        </is>
+      </c>
+      <c r="D8" s="279" t="inlineStr">
+        <is>
+          <t>BLOCKER</t>
+        </is>
+      </c>
+      <c r="E8" s="258" t="inlineStr">
+        <is>
+          <t>2.5M against 677,669 of R&amp;D recreates the idle-cash problem that made Asset Management 0.353 = LAST, and 25,000 new shares halve Financial Performance (divided by total shares issued).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="258" t="inlineStr">
+        <is>
+          <t>Finance / Short Term Loan</t>
+        </is>
+      </c>
+      <c r="B9" s="258" t="inlineStr">
+        <is>
+          <t>'No outstanding conventional loans this quarter'</t>
+        </is>
+      </c>
+      <c r="C9" s="258" t="inlineStr">
+        <is>
+          <t>Draw the ~950,000 conventional loan at 7% annual</t>
+        </is>
+      </c>
+      <c r="D9" s="279" t="inlineStr">
+        <is>
+          <t>BLOCKER</t>
+        </is>
+      </c>
+      <c r="E9" s="258" t="inlineStr">
+        <is>
+          <t>Cash 1,010,838 cannot cover R&amp;D 677,669 + ~380,000 visible operating + 2 printers and still clear the 300,000 floor. Nothing is funded without this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="258" t="inlineStr">
+        <is>
+          <t>Demand Projection</t>
+        </is>
+      </c>
+      <c r="B10" s="258" t="inlineStr">
+        <is>
+          <t>Store demand/SP = 0, Web demand/SP = 0, all totals 0, operating capacity required = 0</t>
+        </is>
+      </c>
+      <c r="C10" s="258" t="inlineStr">
+        <is>
+          <t>Store 50.5/head x 14 = 707; Web 62.1/head x 7 = 435; total 1,142</t>
+        </is>
+      </c>
+      <c r="D10" s="279" t="inlineStr">
+        <is>
+          <t>BLOCKER</t>
+        </is>
+      </c>
+      <c r="E10" s="258" t="inlineStr">
+        <is>
+          <t>This is the input the capacity decision is read against. Left at 0 it argues for OC 0 and hides the 8/day error.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="258" t="inlineStr">
+        <is>
+          <t>Price and Priority / Swifter Bike</t>
+        </is>
+      </c>
+      <c r="B11" s="258" t="inlineStr">
+        <is>
+          <t>Retail Price 1,450</t>
+        </is>
+      </c>
+      <c r="C11" s="258" t="inlineStr">
+        <is>
+          <t>Raise to 1,580</t>
+        </is>
+      </c>
+      <c r="D11" s="280" t="inlineStr">
+        <is>
+          <t>MISS</t>
+        </is>
+      </c>
+      <c r="E11" s="258" t="inlineStr">
+        <is>
+          <t>1,580 draws ZERO Speed price resistance (proven by Blu Aero, Blu Tube, Armstrong at that exact price). +130/unit of pure margin on ~457 units = +59,410, and it relieves the capacity squeeze.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="258" t="inlineStr">
+        <is>
+          <t>HR / Sales Force Compensation</t>
+        </is>
+      </c>
+      <c r="B12" s="258" t="inlineStr">
+        <is>
+          <t>19,000 salary + Full coverage + 2 weeks + 1% = 24,425/yr; projected prod 70</t>
+        </is>
+      </c>
+      <c r="C12" s="258" t="inlineStr">
+        <is>
+          <t>22,000 + Expanded + 2 weeks + 4% = 27,402/yr (BB LLC exact); project 75</t>
+        </is>
+      </c>
+      <c r="D12" s="280" t="inlineStr">
+        <is>
+          <t>MISS</t>
+        </is>
+      </c>
+      <c r="E12" s="258" t="inlineStr">
+        <is>
+          <t>Still the Q2 lock. Mix is the error, not the total: BB LLC hit 78.4% on Expanded/2wk/4%; MILC paid MORE (27,630) on Full/1wk and scored 8.4 pts worse. Cost +2,977/head/yr = +15,634/qtr across 21 heads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="258" t="inlineStr">
+        <is>
+          <t>HR / Production Worker Compensation</t>
+        </is>
+      </c>
+      <c r="B13" s="258" t="inlineStr">
+        <is>
+          <t>16,800 + Expanded + 2 weeks + 3% = 20,757/yr; projected prod 73</t>
+        </is>
+      </c>
+      <c r="C13" s="258" t="inlineStr">
+        <is>
+          <t>18,500 + Expanded + 2 weeks + 4% = 23,042/yr (BB LLC exact); project 75</t>
+        </is>
+      </c>
+      <c r="D13" s="280" t="inlineStr">
+        <is>
+          <t>MISS</t>
+        </is>
+      </c>
+      <c r="E13" s="258" t="inlineStr">
+        <is>
+          <t>Buys capacity directly: 73% -&gt; 75% takes 24/day from 1139 to 1170 units (+31) and cuts labour cost/unit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="258" t="inlineStr">
+        <is>
+          <t>Regional Media / off-Biking inserts</t>
+        </is>
+      </c>
+      <c r="B14" s="258" t="inlineStr">
+        <is>
+          <t>Swifter Bike 1: Sport 1 (10,000), Business 1 (9,500), New Venture 2 (11,000)</t>
+        </is>
+      </c>
+      <c r="C14" s="258" t="inlineStr">
+        <is>
+          <t>Concentrate in Biking; New Venture and Sport are the Q3 diversification error</t>
+        </is>
+      </c>
+      <c r="D14" s="281" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="E14" s="258" t="inlineStr">
+        <is>
+          <t>Biking is 51 industry pages and BB LLC owns 24 of them at 4,500 each - the cheapest insert on the board. Business is Speed's #2 medium so Business 1 is defensible; Sport 1 + New Venture 2 = 21,000 for 3 poorly-targeted pages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="258" t="inlineStr">
+        <is>
+          <t>Regional Media / totals do not reconcile</t>
+        </is>
+      </c>
+      <c r="B15" s="258" t="inlineStr">
+        <is>
+          <t>Per-brand totals 42,119 + 45,433 = 87,552</t>
+        </is>
+      </c>
+      <c r="C15" s="258" t="inlineStr">
+        <is>
+          <t>20 inserts at list = 12x4,500 + 4x4,500 + 10,000 + 9,500 + 2x5,500 = 102,500</t>
+        </is>
+      </c>
+      <c r="D15" s="281" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="E15" s="258" t="inlineStr">
+        <is>
+          <t>45,433 is exactly Swift Bike's Q3 brand advertising expense, so the Total row looks like prior-period or amortised figures, not this quarter's bill. Confirm what will actually be charged before locking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="258" t="inlineStr">
+        <is>
+          <t>Modify Ad / HikeBike 2 is a new ad number</t>
+        </is>
+      </c>
+      <c r="B16" s="258" t="inlineStr">
+        <is>
+          <t>Ad is named 'HikeBike 2'; Q3's Mountain ad was 'HikeBike 1'</t>
+        </is>
+      </c>
+      <c r="C16" s="258" t="inlineStr">
+        <is>
+          <t>Modify HikeBike 1 in place if the sim allows it</t>
+        </is>
+      </c>
+      <c r="D16" s="281" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="E16" s="258" t="inlineStr">
+        <is>
+          <t>HikeBike 1 was organic Mountain #2 (115 clicks). If a new ad number spawns a new web page, we may reset page tenure and pay a second design fee. Speed SERP rank is already suspected to reflect tenure (AndStill, ad 78, sits 7th).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="258" t="inlineStr">
+        <is>
+          <t>Price and Priority / Available for Sale</t>
+        </is>
+      </c>
+      <c r="B17" s="258" t="inlineStr">
+        <is>
+          <t>'Available for Sale' column appears blank for both brands</t>
+        </is>
+      </c>
+      <c r="C17" s="258" t="inlineStr">
+        <is>
+          <t>Both brands must be flagged available in World Market</t>
+        </is>
+      </c>
+      <c r="D17" s="282" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="E17" s="258" t="inlineStr">
+        <is>
+          <t>Brand Production shows both as 'produced', so this is probably a rendering artefact - but a brand built and not offered for sale sells zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="258" t="inlineStr">
+        <is>
+          <t>Social Media</t>
+        </is>
+      </c>
+      <c r="B18" s="258" t="inlineStr">
+        <is>
+          <t>Social Networking: setup 8,000 + quarterly 3,500 = 11,500</t>
+        </is>
+      </c>
+      <c r="C18" s="258" t="inlineStr">
+        <is>
+          <t>~10,000 quarterly was the earlier recommendation</t>
+        </is>
+      </c>
+      <c r="D18" s="282" t="inlineStr">
+        <is>
+          <t>OPTIONAL</t>
+        </is>
+      </c>
+      <c r="E18" s="258" t="inlineStr">
+        <is>
+          <t>3,500 is defensible during the ramp - the sim warns demand response is slow and spend mostly buys team learning. The 8,000 setup was not in the earlier estimate. Consider 6,000-8,000 quarterly now that R&amp;D came in cheaper than modelled.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="258" t="inlineStr">
+        <is>
+          <t>Modify Brand / Swifter Bike</t>
+        </is>
+      </c>
+      <c r="B19" s="258" t="inlineStr">
+        <is>
+          <t>Aero frame, standard carbon, racing tires, precision brakes, basic drop-down, 14 speed (2x7), polymer gel racing seat, reflectors, colourful thin brushstroke decals, standard lights</t>
+        </is>
+      </c>
+      <c r="C19" s="258" t="inlineStr">
+        <is>
+          <t>The 77 recipe exactly</t>
+        </is>
+      </c>
+      <c r="D19" s="283" t="inlineStr">
+        <is>
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="E19" s="258" t="inlineStr">
+        <is>
+          <t>24sp -&gt; 14sp is +3 and decals are +2. This is 72 -&gt; 77, tying the industry ceiling (MACH I.I, LiteSpeed Pro+). Do not touch it again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="258" t="inlineStr">
+        <is>
+          <t>Modify Brand / Hike Bike</t>
+        </is>
+      </c>
+      <c r="B20" s="258" t="inlineStr">
+        <is>
+          <t>Not listed as modified</t>
+        </is>
+      </c>
+      <c r="C20" s="258" t="inlineStr">
+        <is>
+          <t>Leave Hike Bike alone - 73 of 73, verified optimal</t>
+        </is>
+      </c>
+      <c r="D20" s="283" t="inlineStr">
+        <is>
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="E20" s="258" t="inlineStr">
+        <is>
+          <t>Tied for best Mountain brand in the industry. Any change is downside.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="258" t="inlineStr">
+        <is>
+          <t>Modify Ad / benefit stacks</t>
+        </is>
+      </c>
+      <c r="B21" s="258" t="inlineStr">
+        <is>
+          <t>HikeBike 2: gears, high tread, highest rated Mountain, local sales, brand, steep-trail picture. Swifter: road-race picture, brand, wind-cheater, elite look, 3D printing, racing tires, local sales</t>
+        </is>
+      </c>
+      <c r="C21" s="258" t="inlineStr">
+        <is>
+          <t>BB LLC's Mountain stack and AndStill's Speed stack</t>
+        </is>
+      </c>
+      <c r="D21" s="283" t="inlineStr">
+        <is>
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="E21" s="258" t="inlineStr">
+        <is>
+          <t>Lights, reflectors and 'great price' are gone from the Speed ad - those were the Recreation cues that held it to 70, 8th of 9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="258" t="inlineStr">
+        <is>
+          <t>Hire Sales People</t>
+        </is>
+      </c>
+      <c r="B22" s="258" t="inlineStr">
+        <is>
+          <t>Rio 1/0/3/3 = 7, Amsterdam 1/0/3/3 = 7, 11 -&gt; 14 heads, 92,897</t>
+        </is>
+      </c>
+      <c r="C22" s="258" t="inlineStr">
+        <is>
+          <t>Clone BB LLC's identical-in-both-cities store template</t>
+        </is>
+      </c>
+      <c r="D22" s="283" t="inlineStr">
+        <is>
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="E22" s="258" t="inlineStr">
+        <is>
+          <t>Reconciles exactly: 14 x 24,425/4 = 85,487 salaries + 5,400 training = 90,888. Speed specialists go 3 -&gt; 6, matching BB LLC and LiteCycle. No untrained staff left.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="258" t="inlineStr">
+        <is>
+          <t>Hire Web Sales People</t>
+        </is>
+      </c>
+      <c r="B23" s="258" t="inlineStr">
+        <is>
+          <t>5 web sales + 2 web support = 7; 3 -&gt; 7 heads, 45,501</t>
+        </is>
+      </c>
+      <c r="C23" s="258" t="inlineStr">
+        <is>
+          <t>BB LLC's exact 5+2 web split at the 7-head cap</t>
+        </is>
+      </c>
+      <c r="D23" s="283" t="inlineStr">
+        <is>
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="E23" s="258" t="inlineStr">
+        <is>
+          <t>Only pays off if the web productivity tactics are actually started.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="258" t="inlineStr">
+        <is>
+          <t>Manufacturing / Fixed Capacity</t>
+        </is>
+      </c>
+      <c r="B24" s="258" t="inlineStr">
+        <is>
+          <t>Planned increase 16/day; 24 -&gt; 40 available next quarter</t>
+        </is>
+      </c>
+      <c r="C24" s="258" t="inlineStr">
+        <is>
+          <t>Two printers for Q5 NYC entry</t>
+        </is>
+      </c>
+      <c r="D24" s="283" t="inlineStr">
+        <is>
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="E24" s="258" t="inlineStr">
+        <is>
+          <t>Ordered in Q4, live in Q5 - the right sequencing for a Q5 NYC store. Does not raise Q4 capacity, which is why OC must be 24 now.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="258" t="inlineStr">
+        <is>
+          <t>Feature R&amp;D</t>
+        </is>
+      </c>
+      <c r="B25" s="258" t="inlineStr">
+        <is>
+          <t>11 speed 568,514 + decals 109,155 = 677,669; both available Q5</t>
+        </is>
+      </c>
+      <c r="C25" s="258" t="inlineStr">
+        <is>
+          <t>Two rapid projects, third slot deliberately empty</t>
+        </is>
+      </c>
+      <c r="D25" s="283" t="inlineStr">
+        <is>
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="E25" s="258" t="inlineStr">
+        <is>
+          <t>Rapid premium is now KNOWN: 2-quarter prices are 478,062 and 91,788, so rapid costs 107,819 (18.9%) more and lands Q5 instead of Q6. Earlier planning assumed a ~203,301 premium on top of 677,669 - that was wrong, so cash is ~203k better than modelled.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="258" t="inlineStr">
+        <is>
+          <t>Search Engine Marketing (paid)</t>
+        </is>
+      </c>
+      <c r="B26" s="258" t="inlineStr">
+        <is>
+          <t>Mountain bid 2.40 / budget 150; Speed bid 1.95 / budget 80; total 230</t>
+        </is>
+      </c>
+      <c r="C26" s="258" t="inlineStr">
+        <is>
+          <t>Match the posted industry average bid, throttle volume with the budget</t>
+        </is>
+      </c>
+      <c r="D26" s="283" t="inlineStr">
+        <is>
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="E26" s="258" t="inlineStr">
+        <is>
+          <t>Matches Q4_Paid_SEM exactly. Bid stays in the auction all quarter; the small budget caps us near 104-138 clicks, which is all the printers can absorb.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="258" t="inlineStr">
+        <is>
+          <t>Manage Web Pages</t>
+        </is>
+      </c>
+      <c r="B27" s="258" t="inlineStr">
+        <is>
+          <t>HikeBike 2 -&gt; Mountain, Swifter Bike 1 -&gt; Speed, 1,000 each = 2,000</t>
+        </is>
+      </c>
+      <c r="C27" s="258" t="inlineStr">
+        <is>
+          <t>Two pages, one per targeted segment, no Recreation page</t>
+        </is>
+      </c>
+      <c r="D27" s="283" t="inlineStr">
+        <is>
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="E27" s="258" t="inlineStr">
+        <is>
+          <t>Two pages in one segment cannibalise - Bike Bros ran 2 Mountain ads for 79 clicks against our single page's 115.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="258" t="inlineStr">
+        <is>
+          <t>Open Store / Open Webcenter</t>
+        </is>
+      </c>
+      <c r="B28" s="258" t="inlineStr">
+        <is>
+          <t>Rio + Amsterdam operational (61,000); World Market webcenter (60,000)</t>
+        </is>
+      </c>
+      <c r="C28" s="258" t="inlineStr">
+        <is>
+          <t>No third store in Q4 - depth before breadth</t>
+        </is>
+      </c>
+      <c r="D28" s="283" t="inlineStr">
+        <is>
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="E28" s="258" t="inlineStr">
+        <is>
+          <t>NYC needs the printers that only arrive in Q5, plus 7 new hires. Adding it now would generate demand against a 1,139-unit ceiling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="258" t="inlineStr">
+        <is>
+          <t>Price and Priority / the rest</t>
+        </is>
+      </c>
+      <c r="B29" s="258" t="inlineStr">
+        <is>
+          <t>Hike Bike 1,365, both rebates 0, priority Hike 1 / Swift 2</t>
+        </is>
+      </c>
+      <c r="C29" s="258" t="inlineStr">
+        <is>
+          <t>Hold Hike at 1,365, no rebates, priority unchanged</t>
+        </is>
+      </c>
+      <c r="D29" s="283" t="inlineStr">
+        <is>
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="E29" s="258" t="inlineStr">
+        <is>
+          <t>1,365 is the highest tier that still scores 100 on Mountain price judgment. Only the two cheapest Recreation brands use rebates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="258" t="inlineStr">
+        <is>
+          <t>Overtime</t>
+        </is>
+      </c>
+      <c r="B30" s="258" t="inlineStr">
+        <is>
+          <t>Overtime table present; no hours selected</t>
+        </is>
+      </c>
+      <c r="C30" s="258" t="inlineStr">
+        <is>
+          <t>Overtime 0.00</t>
+        </is>
+      </c>
+      <c r="D30" s="283" t="inlineStr">
+        <is>
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="E30" s="258" t="inlineStr">
+        <is>
+          <t>Manufacturing Productivity = utilisation - (OT/OC / 2). 24 scheduled with 0 OT = 1.000; BB LLC's 6.90 OT drags them to 0.856. This is the one place we beat them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="258" t="inlineStr">
+        <is>
+          <t>Buy Market Research</t>
+        </is>
+      </c>
+      <c r="B31" s="258" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="C31" s="258" t="inlineStr">
+        <is>
+          <t>Not previously sized</t>
+        </is>
+      </c>
+      <c r="D31" s="283" t="inlineStr">
+        <is>
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="E31" s="258" t="inlineStr">
+        <is>
+          <t>On-strategy in a closed system where competitor intelligence is the only route to the numbers this whole plan is built from.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="258" t="inlineStr">
+        <is>
+          <t>Corporate / Goals and Strategy</t>
+        </is>
+      </c>
+      <c r="B32" s="258" t="inlineStr">
+        <is>
+          <t>Mountain &gt; Speed &gt; Recreation; six strategic directions</t>
+        </is>
+      </c>
+      <c r="C32" s="258" t="inlineStr">
+        <is>
+          <t>Unchanged from the locked directions</t>
+        </is>
+      </c>
+      <c r="D32" s="283" t="inlineStr">
+        <is>
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="E32" s="258" t="inlineStr">
+        <is>
+          <t>Matches the ratified team goals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="277" t="inlineStr">
+        <is>
+          <t>Capacity ladder (units = OC x 65 days x worker productivity)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="278" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B35" s="278" t="inlineStr">
+        <is>
+          <t>OC/day</t>
+        </is>
+      </c>
+      <c r="C35" s="278" t="inlineStr">
+        <is>
+          <t>Productivity</t>
+        </is>
+      </c>
+      <c r="D35" s="278" t="inlineStr">
+        <is>
+          <t>Units/qtr</t>
+        </is>
+      </c>
+      <c r="E35" s="278" t="inlineStr">
+        <is>
+          <t>vs 1,142 demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="258" t="inlineStr">
+        <is>
+          <t>Screen as entered</t>
+        </is>
+      </c>
+      <c r="B36" s="258" t="n">
+        <v>8</v>
+      </c>
+      <c r="C36" s="258" t="inlineStr">
+        <is>
+          <t>73%</t>
+        </is>
+      </c>
+      <c r="D36" s="258" t="n">
+        <v>380</v>
+      </c>
+      <c r="E36" s="258" t="n">
+        <v>-762</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="258" t="inlineStr">
+        <is>
+          <t>Plan of record</t>
+        </is>
+      </c>
+      <c r="B37" s="258" t="n">
+        <v>24</v>
+      </c>
+      <c r="C37" s="258" t="inlineStr">
+        <is>
+          <t>73%</t>
+        </is>
+      </c>
+      <c r="D37" s="258" t="n">
+        <v>1139</v>
+      </c>
+      <c r="E37" s="258" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="258" t="inlineStr">
+        <is>
+          <t>Plan + production comp fix</t>
+        </is>
+      </c>
+      <c r="B38" s="258" t="n">
+        <v>24</v>
+      </c>
+      <c r="C38" s="258" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="D38" s="258" t="n">
+        <v>1170</v>
+      </c>
+      <c r="E38" s="258" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="277" t="inlineStr">
+        <is>
+          <t>Demand Projection - what to type into the zeros</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="278" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="B41" s="278" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+      <c r="C41" s="278" t="inlineStr">
+        <is>
+          <t>Demand/person</t>
+        </is>
+      </c>
+      <c r="D41" s="278" t="inlineStr">
+        <is>
+          <t>Total demand</t>
+        </is>
+      </c>
+      <c r="E41" s="278" t="inlineStr">
+        <is>
+          <t>Basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="258" t="inlineStr">
+        <is>
+          <t>Stores</t>
+        </is>
+      </c>
+      <c r="B42" s="258" t="n">
+        <v>14</v>
+      </c>
+      <c r="C42" s="258" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="D42" s="258" t="n">
+        <v>707</v>
+      </c>
+      <c r="E42" s="258" t="inlineStr">
+        <is>
+          <t>Q3 was 46.09/head on 11 untrained heads. Anchors: Rio store-only measured 60/head, industry average excluding us 61.1, BB LLC 67. 50.5 is deliberately below all three to absorb the 16.3% Q4 ill will.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="258" t="inlineStr">
+        <is>
+          <t>Web Sales Center</t>
+        </is>
+      </c>
+      <c r="B43" s="258" t="n">
+        <v>7</v>
+      </c>
+      <c r="C43" s="258" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="D43" s="258" t="n">
+        <v>435</v>
+      </c>
+      <c r="E43" s="258" t="inlineStr">
+        <is>
+          <t>Q3 was 40.00/head with one tactic funded. 62.1 is the FLOOR of the all-tactics cohort (LiteCycle and MILC both 435 units), not BB LLC's 81.3. Conditional on starting the tactics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="165" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B44" s="165" t="n">
+        <v>21</v>
+      </c>
+      <c r="D44" s="165" t="n">
+        <v>1142</v>
+      </c>
+      <c r="E44" s="258" t="inlineStr">
+        <is>
+          <t>Required OC = 1142 / (0.73 x 65) = 24.07/day -&gt; schedule 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="277" t="inlineStr">
+        <is>
+          <t>Brand split of projected demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="278" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="B47" s="278" t="inlineStr">
+        <is>
+          <t>Share</t>
+        </is>
+      </c>
+      <c r="C47" s="278" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="D47" s="278" t="inlineStr">
+        <is>
+          <t>Basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="258" t="inlineStr">
+        <is>
+          <t>Hike Bike</t>
+        </is>
+      </c>
+      <c r="B48" s="258" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="C48" s="258" t="n">
+        <v>685</v>
+      </c>
+      <c r="D48" s="258" t="inlineStr">
+        <is>
+          <t>Q3 was 65.7%. Ad 80 -&gt; ~82 and Biking inserts 6 -&gt; 12 help, but Mountain is the smallest segment (1,621) and we already hold 22.1%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="258" t="inlineStr">
+        <is>
+          <t>Swifter Bike</t>
+        </is>
+      </c>
+      <c r="B49" s="258" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="C49" s="258" t="n">
+        <v>457</v>
+      </c>
+      <c r="D49" s="258" t="inlineStr">
+        <is>
+          <t>Q3 was 34.3%. Brand 72 -&gt; 77, ad 70 -&gt; 77, Speed specialists 3 -&gt; 6, price +130. Speed is the largest segment (2,878) and we hold only 7.5%, so the headroom is here. Judgment call, not a measured figure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="277" t="inlineStr">
+        <is>
+          <t>Cash uses visible on the screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="278" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="B52" s="278" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="C52" s="278" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="258" t="inlineStr">
+        <is>
+          <t>Feature R&amp;D (2 rapid projects)</t>
+        </is>
+      </c>
+      <c r="B53" s="284" t="n">
+        <v>677669</v>
+      </c>
+      <c r="C53" s="258" t="inlineStr">
+        <is>
+          <t>entered</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="258" t="inlineStr">
+        <is>
+          <t>Sales and service people</t>
+        </is>
+      </c>
+      <c r="B54" s="284" t="n">
+        <v>92897</v>
+      </c>
+      <c r="C54" s="258" t="inlineStr">
+        <is>
+          <t>entered</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="258" t="inlineStr">
+        <is>
+          <t>Media inserts (list price, 20 inserts)</t>
+        </is>
+      </c>
+      <c r="B55" s="284" t="n">
+        <v>102500</v>
+      </c>
+      <c r="C55" s="258" t="inlineStr">
+        <is>
+          <t>entered, total row unclear</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="258" t="inlineStr">
+        <is>
+          <t>Web personnel</t>
+        </is>
+      </c>
+      <c r="B56" s="284" t="n">
+        <v>45501</v>
+      </c>
+      <c r="C56" s="258" t="inlineStr">
+        <is>
+          <t>entered</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="258" t="inlineStr">
+        <is>
+          <t>Store operations (Rio + Amsterdam)</t>
+        </is>
+      </c>
+      <c r="B57" s="284" t="n">
+        <v>61000</v>
+      </c>
+      <c r="C57" s="258" t="inlineStr">
+        <is>
+          <t>entered</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="258" t="inlineStr">
+        <is>
+          <t>Web sales center</t>
+        </is>
+      </c>
+      <c r="B58" s="284" t="n">
+        <v>60000</v>
+      </c>
+      <c r="C58" s="258" t="inlineStr">
+        <is>
+          <t>entered</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="258" t="inlineStr">
+        <is>
+          <t>Market research</t>
+        </is>
+      </c>
+      <c r="B59" s="284" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C59" s="258" t="inlineStr">
+        <is>
+          <t>entered</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="258" t="inlineStr">
+        <is>
+          <t>Social media (8,000 setup + 3,500)</t>
+        </is>
+      </c>
+      <c r="B60" s="284" t="n">
+        <v>11500</v>
+      </c>
+      <c r="C60" s="258" t="inlineStr">
+        <is>
+          <t>entered</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="258" t="inlineStr">
+        <is>
+          <t>Web productivity: toll-free</t>
+        </is>
+      </c>
+      <c r="B61" s="284" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C61" s="258" t="inlineStr">
+        <is>
+          <t>entered</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="258" t="inlineStr">
+        <is>
+          <t>Web pages</t>
+        </is>
+      </c>
+      <c r="B62" s="284" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C62" s="258" t="inlineStr">
+        <is>
+          <t>entered</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="258" t="inlineStr">
+        <is>
+          <t>Paid SEM</t>
+        </is>
+      </c>
+      <c r="B63" s="284" t="n">
+        <v>230</v>
+      </c>
+      <c r="C63" s="258" t="inlineStr">
+        <is>
+          <t>entered</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="258" t="inlineStr">
+        <is>
+          <t>Web tactics setup (4 new)</t>
+        </is>
+      </c>
+      <c r="B64" s="284" t="n">
+        <v>48000</v>
+      </c>
+      <c r="C64" s="285" t="inlineStr">
+        <is>
+          <t>MISSING - Start not checked</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="258" t="inlineStr">
+        <is>
+          <t>Web tactics quarterly (4 new)</t>
+        </is>
+      </c>
+      <c r="B65" s="284" t="n">
+        <v>25000</v>
+      </c>
+      <c r="C65" s="285" t="inlineStr">
+        <is>
+          <t>MISSING - Start not checked</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="258" t="inlineStr">
+        <is>
+          <t>Sales comp uplift to BB LLC package</t>
+        </is>
+      </c>
+      <c r="B66" s="284" t="n">
+        <v>15634</v>
+      </c>
+      <c r="C66" s="285" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="258" t="inlineStr">
+        <is>
+          <t>Production comp uplift to BB LLC package</t>
+        </is>
+      </c>
+      <c r="B67" s="284" t="n">
+        <v>12000</v>
+      </c>
+      <c r="C67" s="285" t="inlineStr">
+        <is>
+          <t>MISSING (estimate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="258" t="inlineStr">
+        <is>
+          <t>Operating capacity change expense 8 -&gt; 24</t>
+        </is>
+      </c>
+      <c r="B68" s="284" t="n">
+        <v>0</v>
+      </c>
+      <c r="C68" s="258" t="inlineStr">
+        <is>
+          <t>UNKNOWN - screen shows 0 at OC 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="258" t="inlineStr">
+        <is>
+          <t>Two printers (fixed capacity +16)</t>
+        </is>
+      </c>
+      <c r="B69" s="284" t="n">
+        <v>480000</v>
+      </c>
+      <c r="C69" s="258" t="inlineStr">
+        <is>
+          <t>committed, not priced on screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="165" t="inlineStr">
+        <is>
+          <t>Entered subtotal</t>
+        </is>
+      </c>
+      <c r="B70" s="71" t="n">
+        <v>976797</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="165" t="inlineStr">
+        <is>
+          <t>Still to add</t>
+        </is>
+      </c>
+      <c r="B71" s="71" t="n">
+        <v>100634</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="165" t="inlineStr">
+        <is>
+          <t>Cash on hand entering Q4</t>
+        </is>
+      </c>
+      <c r="B72" s="71" t="n">
+        <v>1010838</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Shortfall before the loan (incl. printers, excl. 300k floor)</t>
+        </is>
+      </c>
+      <c r="B73" s="71" t="n">
+        <v>-546593</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="258" t="inlineStr">
+        <is>
+          <t>Note: rapid R&amp;D premium is 107,819 (18.9%), not the ~203,301 used in earlier cash planning. 677,669 IS the rapid price. Cash is roughly 203k better than modelled, which comfortably funds the 73,000 of web tactics and the two comp uplifts.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
